--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2678,9 +2678,43 @@
         <v>64.31</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>604</v>
+      </c>
+      <c r="C67" t="n">
+        <v>145</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E67" t="n">
+        <v>60</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="H67" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="I67" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="J67" t="n">
+        <v>64.31</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B66">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="B2:B67">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2689,8 +2723,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C66">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="C2:C67">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2699,8 +2733,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D66">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="D2:D67">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -2711,8 +2745,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E66">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="E2:E67">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2721,8 +2755,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F66">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="F2:F67">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2731,8 +2765,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J66">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="G2:J67">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,8 +2712,42 @@
         <v>64.31</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>604</v>
+      </c>
+      <c r="C68" t="n">
+        <v>145</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E68" t="n">
+        <v>60</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="H68" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="I68" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="J68" t="n">
+        <v>64.31</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B67">
+  <conditionalFormatting sqref="B2:B68">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2723,7 +2757,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C67">
+  <conditionalFormatting sqref="C2:C68">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2733,7 +2767,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D67">
+  <conditionalFormatting sqref="D2:D68">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2745,7 +2779,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E67">
+  <conditionalFormatting sqref="E2:E68">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2755,7 +2789,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F67">
+  <conditionalFormatting sqref="F2:F68">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2765,7 +2799,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J67">
+  <conditionalFormatting sqref="G2:J68">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2746,8 +2746,42 @@
         <v>64.31</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>604</v>
+      </c>
+      <c r="C69" t="n">
+        <v>145</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E69" t="n">
+        <v>60</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="H69" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="I69" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="J69" t="n">
+        <v>64.31</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B68">
+  <conditionalFormatting sqref="B2:B69">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2757,7 +2791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C68">
+  <conditionalFormatting sqref="C2:C69">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2767,7 +2801,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D68">
+  <conditionalFormatting sqref="D2:D69">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2779,7 +2813,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E68">
+  <conditionalFormatting sqref="E2:E69">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2789,7 +2823,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F68">
+  <conditionalFormatting sqref="F2:F69">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2799,7 +2833,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J68">
+  <conditionalFormatting sqref="G2:J69">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2780,8 +2780,42 @@
         <v>64.31</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>604</v>
+      </c>
+      <c r="C70" t="n">
+        <v>145</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="E70" t="n">
+        <v>60</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="H70" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="I70" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="J70" t="n">
+        <v>64.31</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B69">
+  <conditionalFormatting sqref="B2:B70">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2791,7 +2825,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C69">
+  <conditionalFormatting sqref="C2:C70">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2801,7 +2835,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D69">
+  <conditionalFormatting sqref="D2:D70">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2813,7 +2847,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E69">
+  <conditionalFormatting sqref="E2:E70">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2823,7 +2857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F69">
+  <conditionalFormatting sqref="F2:F70">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2833,7 +2867,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J69">
+  <conditionalFormatting sqref="G2:J70">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2814,8 +2814,42 @@
         <v>64.31</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>362</v>
+      </c>
+      <c r="C71" t="n">
+        <v>387</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E71" t="n">
+        <v>33</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4</v>
+      </c>
+      <c r="G71" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="H71" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I71" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="J71" t="n">
+        <v>63.38</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B70">
+  <conditionalFormatting sqref="B2:B71">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2825,7 +2859,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C70">
+  <conditionalFormatting sqref="C2:C71">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2835,7 +2869,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D70">
+  <conditionalFormatting sqref="D2:D71">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2847,7 +2881,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E70">
+  <conditionalFormatting sqref="E2:E71">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2857,7 +2891,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F70">
+  <conditionalFormatting sqref="F2:F71">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2867,7 +2901,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J70">
+  <conditionalFormatting sqref="G2:J71">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2848,8 +2848,42 @@
         <v>63.38</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>353</v>
+      </c>
+      <c r="C72" t="n">
+        <v>398</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E72" t="n">
+        <v>33</v>
+      </c>
+      <c r="F72" t="n">
+        <v>7</v>
+      </c>
+      <c r="G72" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="H72" t="n">
+        <v>64</v>
+      </c>
+      <c r="I72" t="n">
+        <v>63.65</v>
+      </c>
+      <c r="J72" t="n">
+        <v>62.05</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B71">
+  <conditionalFormatting sqref="B2:B72">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2859,7 +2893,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C71">
+  <conditionalFormatting sqref="C2:C72">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2869,7 +2903,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D71">
+  <conditionalFormatting sqref="D2:D72">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2881,7 +2915,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E71">
+  <conditionalFormatting sqref="E2:E72">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2891,7 +2925,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F71">
+  <conditionalFormatting sqref="F2:F72">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2901,7 +2935,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J71">
+  <conditionalFormatting sqref="G2:J72">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -488,34 +488,34 @@
         <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="E2" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="F2" t="n">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="G2" t="n">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="H2" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="I2" t="n">
-        <v>57.9</v>
+        <v>57.04</v>
       </c>
       <c r="J2" t="n">
-        <v>65.2</v>
+        <v>65.33</v>
       </c>
       <c r="K2" t="n">
-        <v>64.98</v>
+        <v>65.11</v>
       </c>
       <c r="L2" t="n">
-        <v>65.11</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2506,7 +2506,7 @@
         <v>2.44</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>46.96</v>
       </c>
       <c r="J52" t="n">
         <v>80.63</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>43.65</v>
       </c>
       <c r="J53" t="n">
         <v>77.48</v>
@@ -2586,7 +2586,7 @@
         <v>0.36</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>41.93</v>
       </c>
       <c r="J54" t="n">
         <v>77.47</v>
@@ -2626,7 +2626,7 @@
         <v>0.98</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>43.74</v>
       </c>
       <c r="J55" t="n">
         <v>79.2</v>
@@ -2666,7 +2666,7 @@
         <v>0.62</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>44.06</v>
       </c>
       <c r="J56" t="n">
         <v>77.87</v>
@@ -2706,7 +2706,7 @@
         <v>6.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>44.22</v>
       </c>
       <c r="J57" t="n">
         <v>80.13</v>
@@ -2744,7 +2744,7 @@
         <v>0.26</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>40.1</v>
       </c>
       <c r="J58" t="n">
         <v>71.87</v>
@@ -2782,7 +2782,7 @@
         <v>0.46</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>42.63</v>
       </c>
       <c r="J59" t="n">
         <v>78.8</v>
@@ -2820,7 +2820,7 @@
         <v>1.98</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>43.4</v>
       </c>
       <c r="J60" t="n">
         <v>82</v>
@@ -2858,7 +2858,7 @@
         <v>2.14</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>41.08</v>
       </c>
       <c r="J61" t="n">
         <v>81.59999999999999</v>
@@ -2896,7 +2896,7 @@
         <v>0.58</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>38.69</v>
       </c>
       <c r="J62" t="n">
         <v>76.8</v>
@@ -2932,7 +2932,7 @@
         <v>3.48</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>39.33</v>
       </c>
       <c r="J63" t="n">
         <v>79.06999999999999</v>
@@ -2968,7 +2968,7 @@
         <v>2.07</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>37.26</v>
       </c>
       <c r="J64" t="n">
         <v>74.93000000000001</v>
@@ -3004,7 +3004,7 @@
         <v>10.18</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>34.71</v>
       </c>
       <c r="J65" t="n">
         <v>68.40000000000001</v>
@@ -3040,7 +3040,7 @@
         <v>0.49</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>31.26</v>
       </c>
       <c r="J66" t="n">
         <v>52.93</v>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -415,6 +415,20 @@
   </sheetPr>
   <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -485,37 +499,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="E2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="F2" t="n">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="G2" t="n">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="H2" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>57.04</v>
       </c>
       <c r="J2" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="K2" t="n">
         <v>65.33</v>
       </c>
-      <c r="K2" t="n">
-        <v>65.11</v>
-      </c>
       <c r="L2" t="n">
-        <v>64.18000000000001</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="3">
@@ -531,31 +545,31 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="E3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="F3" t="n">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G3" t="n">
         <v>145</v>
       </c>
       <c r="H3" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="I3" t="n">
         <v>55.67</v>
       </c>
       <c r="J3" t="n">
-        <v>64.93000000000001</v>
+        <v>64.89</v>
       </c>
       <c r="K3" t="n">
-        <v>64.45</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>64.31</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="4">
@@ -571,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="F4" t="n">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G4" t="n">
         <v>127</v>
@@ -589,13 +603,13 @@
         <v>52.75</v>
       </c>
       <c r="J4" t="n">
-        <v>56.16</v>
+        <v>56.09</v>
       </c>
       <c r="K4" t="n">
-        <v>51.53</v>
+        <v>51.47</v>
       </c>
       <c r="L4" t="n">
-        <v>45.54</v>
+        <v>45.47</v>
       </c>
     </row>
     <row r="5">
@@ -608,19 +622,19 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="F5" t="n">
         <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H5" t="n">
         <v>0.13</v>
@@ -629,13 +643,13 @@
         <v>49.83</v>
       </c>
       <c r="J5" t="n">
-        <v>50</v>
+        <v>49.92</v>
       </c>
       <c r="K5" t="n">
-        <v>37.95</v>
+        <v>37.87</v>
       </c>
       <c r="L5" t="n">
-        <v>26.23</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="6">
@@ -654,10 +668,10 @@
         <v>2.27</v>
       </c>
       <c r="E6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="F6" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G6" t="n">
         <v>505</v>
@@ -669,13 +683,13 @@
         <v>56.36</v>
       </c>
       <c r="J6" t="n">
-        <v>60.81</v>
+        <v>60.75</v>
       </c>
       <c r="K6" t="n">
-        <v>58.19</v>
+        <v>58.13</v>
       </c>
       <c r="L6" t="n">
-        <v>51.8</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="7">
@@ -694,10 +708,10 @@
         <v>3.5</v>
       </c>
       <c r="E7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="F7" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G7" t="n">
         <v>386</v>
@@ -709,13 +723,13 @@
         <v>57.14</v>
       </c>
       <c r="J7" t="n">
-        <v>63.66</v>
+        <v>63.61</v>
       </c>
       <c r="K7" t="n">
-        <v>65.65000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>63.65</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="8">
@@ -731,31 +745,31 @@
         <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="E8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="F8" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G8" t="n">
         <v>395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I8" t="n">
         <v>56.97</v>
       </c>
       <c r="J8" t="n">
-        <v>65.02</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>66.84</v>
+        <v>66.8</v>
       </c>
       <c r="L8" t="n">
-        <v>66.18000000000001</v>
+        <v>66.13</v>
       </c>
     </row>
     <row r="9">
@@ -771,13 +785,13 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="E9" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="F9" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G9" t="n">
         <v>212</v>
@@ -789,13 +803,13 @@
         <v>56.63</v>
       </c>
       <c r="J9" t="n">
-        <v>64.56</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>69.73</v>
+        <v>69.69</v>
       </c>
       <c r="L9" t="n">
-        <v>68.67</v>
+        <v>68.62</v>
       </c>
     </row>
     <row r="10">
@@ -811,13 +825,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="E10" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="F10" t="n">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G10" t="n">
         <v>333</v>
@@ -829,13 +843,13 @@
         <v>53.01</v>
       </c>
       <c r="J10" t="n">
-        <v>60.21</v>
+        <v>60.15</v>
       </c>
       <c r="K10" t="n">
-        <v>61.47</v>
+        <v>61.42</v>
       </c>
       <c r="L10" t="n">
-        <v>57.07</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="11">
@@ -851,31 +865,31 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="E11" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="F11" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G11" t="n">
         <v>305</v>
       </c>
       <c r="H11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I11" t="n">
         <v>51.98</v>
       </c>
       <c r="J11" t="n">
-        <v>58.11</v>
+        <v>58.2</v>
       </c>
       <c r="K11" t="n">
-        <v>57.87</v>
+        <v>57.81</v>
       </c>
       <c r="L11" t="n">
-        <v>50.13</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="12">
@@ -888,19 +902,19 @@
         <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="F12" t="n">
         <v>278</v>
       </c>
       <c r="G12" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H12" t="n">
         <v>0.59</v>
@@ -909,13 +923,13 @@
         <v>50.43</v>
       </c>
       <c r="J12" t="n">
-        <v>55.86</v>
+        <v>55.94</v>
       </c>
       <c r="K12" t="n">
-        <v>50.13</v>
+        <v>50.2</v>
       </c>
       <c r="L12" t="n">
-        <v>41.33</v>
+        <v>41.39</v>
       </c>
     </row>
     <row r="13">
@@ -949,13 +963,13 @@
         <v>52.67</v>
       </c>
       <c r="J13" t="n">
-        <v>59.91</v>
+        <v>59.85</v>
       </c>
       <c r="K13" t="n">
-        <v>60.27</v>
+        <v>60.21</v>
       </c>
       <c r="L13" t="n">
-        <v>50.8</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="14">
@@ -980,7 +994,7 @@
         <v>249</v>
       </c>
       <c r="G14" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H14" t="n">
         <v>0.5</v>
@@ -989,13 +1003,13 @@
         <v>52.5</v>
       </c>
       <c r="J14" t="n">
-        <v>60.06</v>
+        <v>60</v>
       </c>
       <c r="K14" t="n">
-        <v>60.27</v>
+        <v>60.21</v>
       </c>
       <c r="L14" t="n">
-        <v>50.8</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="15">
@@ -1020,7 +1034,7 @@
         <v>388</v>
       </c>
       <c r="G15" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H15" t="n">
         <v>1.07</v>
@@ -1029,13 +1043,13 @@
         <v>53.01</v>
       </c>
       <c r="J15" t="n">
-        <v>62.46</v>
+        <v>62.41</v>
       </c>
       <c r="K15" t="n">
-        <v>68.40000000000001</v>
+        <v>68.36</v>
       </c>
       <c r="L15" t="n">
-        <v>63.73</v>
+        <v>63.68</v>
       </c>
     </row>
     <row r="16">
@@ -1060,7 +1074,7 @@
         <v>181</v>
       </c>
       <c r="G16" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H16" t="n">
         <v>0.32</v>
@@ -1069,13 +1083,13 @@
         <v>53.36</v>
       </c>
       <c r="J16" t="n">
-        <v>61.86</v>
+        <v>61.8</v>
       </c>
       <c r="K16" t="n">
-        <v>69.33</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>64.13</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="17">
@@ -1097,7 +1111,7 @@
         <v>6.03</v>
       </c>
       <c r="F17" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G17" t="n">
         <v>253</v>
@@ -1109,13 +1123,13 @@
         <v>55.59</v>
       </c>
       <c r="J17" t="n">
-        <v>68.47</v>
+        <v>68.42</v>
       </c>
       <c r="K17" t="n">
-        <v>79.2</v>
+        <v>79.17</v>
       </c>
       <c r="L17" t="n">
-        <v>81.06999999999999</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1140,22 +1154,22 @@
         <v>394</v>
       </c>
       <c r="G18" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I18" t="n">
         <v>54.04</v>
       </c>
       <c r="J18" t="n">
-        <v>65.47</v>
+        <v>65.56</v>
       </c>
       <c r="K18" t="n">
-        <v>74</v>
+        <v>73.97</v>
       </c>
       <c r="L18" t="n">
-        <v>75.06999999999999</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="19">
@@ -1177,7 +1191,7 @@
         <v>3.01</v>
       </c>
       <c r="F19" t="n">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G19" t="n">
         <v>302</v>
@@ -1189,13 +1203,13 @@
         <v>53.36</v>
       </c>
       <c r="J19" t="n">
-        <v>65.92</v>
+        <v>65.86</v>
       </c>
       <c r="K19" t="n">
-        <v>76.8</v>
+        <v>76.77</v>
       </c>
       <c r="L19" t="n">
-        <v>79.47</v>
+        <v>79.44</v>
       </c>
     </row>
     <row r="20">
@@ -1217,7 +1231,7 @@
         <v>3.09</v>
       </c>
       <c r="F20" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G20" t="n">
         <v>295</v>
@@ -1229,13 +1243,13 @@
         <v>51.98</v>
       </c>
       <c r="J20" t="n">
-        <v>63.66</v>
+        <v>63.76</v>
       </c>
       <c r="K20" t="n">
-        <v>74.67</v>
+        <v>74.63</v>
       </c>
       <c r="L20" t="n">
-        <v>78.27</v>
+        <v>78.23999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1260,7 +1274,7 @@
         <v>435</v>
       </c>
       <c r="G21" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H21" t="n">
         <v>1.39</v>
@@ -1269,13 +1283,13 @@
         <v>50.43</v>
       </c>
       <c r="J21" t="n">
-        <v>61.86</v>
+        <v>61.95</v>
       </c>
       <c r="K21" t="n">
-        <v>73.47</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>79.2</v>
+        <v>79.17</v>
       </c>
     </row>
     <row r="22">
@@ -1297,25 +1311,25 @@
         <v>2.83</v>
       </c>
       <c r="F22" t="n">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G22" t="n">
         <v>175</v>
       </c>
       <c r="H22" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="I22" t="n">
         <v>49.83</v>
       </c>
       <c r="J22" t="n">
-        <v>59.91</v>
+        <v>60</v>
       </c>
       <c r="K22" t="n">
-        <v>70.27</v>
+        <v>70.23</v>
       </c>
       <c r="L22" t="n">
-        <v>79.06999999999999</v>
+        <v>79.04000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1337,25 +1351,25 @@
         <v>1.9</v>
       </c>
       <c r="F23" t="n">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G23" t="n">
         <v>58</v>
       </c>
       <c r="H23" t="n">
-        <v>11.91</v>
+        <v>11.9</v>
       </c>
       <c r="I23" t="n">
         <v>46.72</v>
       </c>
       <c r="J23" t="n">
-        <v>50</v>
+        <v>50.08</v>
       </c>
       <c r="K23" t="n">
-        <v>53.07</v>
+        <v>53</v>
       </c>
       <c r="L23" t="n">
-        <v>61.2</v>
+        <v>61.15</v>
       </c>
     </row>
     <row r="24">
@@ -1377,7 +1391,7 @@
         <v>1.09</v>
       </c>
       <c r="F24" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G24" t="n">
         <v>575</v>
@@ -1389,13 +1403,13 @@
         <v>39.14</v>
       </c>
       <c r="J24" t="n">
-        <v>38.44</v>
+        <v>38.5</v>
       </c>
       <c r="K24" t="n">
-        <v>27.73</v>
+        <v>27.77</v>
       </c>
       <c r="L24" t="n">
-        <v>22</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="25">
@@ -1420,7 +1434,7 @@
         <v>160</v>
       </c>
       <c r="G25" t="n">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H25" t="n">
         <v>0.27</v>
@@ -1429,13 +1443,13 @@
         <v>43.28</v>
       </c>
       <c r="J25" t="n">
-        <v>44.29</v>
+        <v>44.36</v>
       </c>
       <c r="K25" t="n">
-        <v>36.27</v>
+        <v>36.32</v>
       </c>
       <c r="L25" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="26">
@@ -1460,22 +1474,22 @@
         <v>597</v>
       </c>
       <c r="G26" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H26" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="I26" t="n">
         <v>45</v>
       </c>
       <c r="J26" t="n">
-        <v>51.05</v>
+        <v>51.13</v>
       </c>
       <c r="K26" t="n">
-        <v>43.87</v>
+        <v>43.93</v>
       </c>
       <c r="L26" t="n">
-        <v>43.2</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="27">
@@ -1500,7 +1514,7 @@
         <v>103</v>
       </c>
       <c r="G27" t="n">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H27" t="n">
         <v>0.16</v>
@@ -1509,13 +1523,13 @@
         <v>41.55</v>
       </c>
       <c r="J27" t="n">
-        <v>44.89</v>
+        <v>44.96</v>
       </c>
       <c r="K27" t="n">
-        <v>30.4</v>
+        <v>30.44</v>
       </c>
       <c r="L27" t="n">
-        <v>24.27</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="28">
@@ -1540,22 +1554,22 @@
         <v>360</v>
       </c>
       <c r="G28" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H28" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I28" t="n">
         <v>45</v>
       </c>
       <c r="J28" t="n">
-        <v>55.11</v>
+        <v>55.19</v>
       </c>
       <c r="K28" t="n">
-        <v>44.93</v>
+        <v>44.99</v>
       </c>
       <c r="L28" t="n">
-        <v>45.33</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="29">
@@ -1580,7 +1594,7 @@
         <v>399</v>
       </c>
       <c r="G29" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H29" t="n">
         <v>1.14</v>
@@ -1589,13 +1603,13 @@
         <v>44.91</v>
       </c>
       <c r="J29" t="n">
-        <v>57.06</v>
+        <v>57.14</v>
       </c>
       <c r="K29" t="n">
-        <v>45.47</v>
+        <v>45.53</v>
       </c>
       <c r="L29" t="n">
-        <v>43.2</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="30">
@@ -1617,7 +1631,7 @@
         <v>1.86</v>
       </c>
       <c r="F30" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G30" t="n">
         <v>441</v>
@@ -1629,13 +1643,13 @@
         <v>43.87</v>
       </c>
       <c r="J30" t="n">
-        <v>57.36</v>
+        <v>57.44</v>
       </c>
       <c r="K30" t="n">
-        <v>43.2</v>
+        <v>43.26</v>
       </c>
       <c r="L30" t="n">
-        <v>37.73</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="31">
@@ -1657,7 +1671,7 @@
         <v>1.96</v>
       </c>
       <c r="F31" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G31" t="n">
         <v>280</v>
@@ -1669,13 +1683,13 @@
         <v>43.7</v>
       </c>
       <c r="J31" t="n">
-        <v>60.06</v>
+        <v>60.15</v>
       </c>
       <c r="K31" t="n">
-        <v>43.73</v>
+        <v>43.79</v>
       </c>
       <c r="L31" t="n">
-        <v>40</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="32">
@@ -1697,25 +1711,25 @@
         <v>1.93</v>
       </c>
       <c r="F32" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G32" t="n">
         <v>530</v>
       </c>
       <c r="H32" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I32" t="n">
         <v>42.83</v>
       </c>
       <c r="J32" t="n">
-        <v>59.01</v>
+        <v>59.1</v>
       </c>
       <c r="K32" t="n">
-        <v>38</v>
+        <v>38.05</v>
       </c>
       <c r="L32" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
     </row>
     <row r="33">
@@ -1740,7 +1754,7 @@
         <v>210</v>
       </c>
       <c r="G33" t="n">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H33" t="n">
         <v>0.39</v>
@@ -1749,13 +1763,13 @@
         <v>44.04</v>
       </c>
       <c r="J33" t="n">
-        <v>66.37</v>
+        <v>66.47</v>
       </c>
       <c r="K33" t="n">
-        <v>47.6</v>
+        <v>47.66</v>
       </c>
       <c r="L33" t="n">
-        <v>42.13</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="34">
@@ -1789,13 +1803,13 @@
         <v>47.67</v>
       </c>
       <c r="J34" t="n">
-        <v>72.52</v>
+        <v>72.63</v>
       </c>
       <c r="K34" t="n">
-        <v>61.33</v>
+        <v>61.42</v>
       </c>
       <c r="L34" t="n">
-        <v>60.67</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="35">
@@ -1820,7 +1834,7 @@
         <v>390</v>
       </c>
       <c r="G35" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H35" t="n">
         <v>1.09</v>
@@ -1829,13 +1843,13 @@
         <v>47.75</v>
       </c>
       <c r="J35" t="n">
-        <v>73.27</v>
+        <v>73.38</v>
       </c>
       <c r="K35" t="n">
-        <v>61.33</v>
+        <v>61.42</v>
       </c>
       <c r="L35" t="n">
-        <v>60.67</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="36">
@@ -1860,7 +1874,7 @@
         <v>362</v>
       </c>
       <c r="G36" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H36" t="n">
         <v>0.9399999999999999</v>
@@ -1869,13 +1883,13 @@
         <v>46.97</v>
       </c>
       <c r="J36" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="K36" t="n">
-        <v>62.13</v>
+        <v>62.22</v>
       </c>
       <c r="L36" t="n">
-        <v>63.47</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="37">
@@ -1897,25 +1911,25 @@
         <v>0.9</v>
       </c>
       <c r="F37" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G37" t="n">
         <v>182</v>
       </c>
       <c r="H37" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="I37" t="n">
         <v>46.27</v>
       </c>
       <c r="J37" t="n">
-        <v>74.77</v>
+        <v>74.89</v>
       </c>
       <c r="K37" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="L37" t="n">
-        <v>63.6</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="38">
@@ -1937,7 +1951,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G38" t="n">
         <v>373</v>
@@ -1949,13 +1963,13 @@
         <v>44.19</v>
       </c>
       <c r="J38" t="n">
-        <v>68.17</v>
+        <v>68.27</v>
       </c>
       <c r="K38" t="n">
-        <v>48.8</v>
+        <v>48.87</v>
       </c>
       <c r="L38" t="n">
-        <v>46.93</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39">
@@ -1980,22 +1994,22 @@
         <v>445</v>
       </c>
       <c r="G39" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H39" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I39" t="n">
         <v>42.11</v>
       </c>
       <c r="J39" t="n">
-        <v>68.62</v>
+        <v>68.72</v>
       </c>
       <c r="K39" t="n">
-        <v>48.13</v>
+        <v>48.2</v>
       </c>
       <c r="L39" t="n">
-        <v>45.73</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="40">
@@ -2017,7 +2031,7 @@
         <v>0.76</v>
       </c>
       <c r="F40" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G40" t="n">
         <v>382</v>
@@ -2029,13 +2043,13 @@
         <v>41.25</v>
       </c>
       <c r="J40" t="n">
-        <v>66.81999999999999</v>
+        <v>66.92</v>
       </c>
       <c r="K40" t="n">
-        <v>42</v>
+        <v>42.06</v>
       </c>
       <c r="L40" t="n">
-        <v>38.13</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="41">
@@ -2060,7 +2074,7 @@
         <v>493</v>
       </c>
       <c r="G41" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H41" t="n">
         <v>1.93</v>
@@ -2069,13 +2083,13 @@
         <v>41.42</v>
       </c>
       <c r="J41" t="n">
-        <v>67.12</v>
+        <v>67.22</v>
       </c>
       <c r="K41" t="n">
-        <v>40.93</v>
+        <v>40.99</v>
       </c>
       <c r="L41" t="n">
-        <v>34.4</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="42">
@@ -2097,7 +2111,7 @@
         <v>0.86</v>
       </c>
       <c r="F42" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G42" t="n">
         <v>585</v>
@@ -2109,13 +2123,13 @@
         <v>39.86</v>
       </c>
       <c r="J42" t="n">
-        <v>65.02</v>
+        <v>65.11</v>
       </c>
       <c r="K42" t="n">
-        <v>32.53</v>
+        <v>32.58</v>
       </c>
       <c r="L42" t="n">
-        <v>23.33</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="43">
@@ -2137,7 +2151,7 @@
         <v>1.11</v>
       </c>
       <c r="F43" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G43" t="n">
         <v>494</v>
@@ -2149,13 +2163,13 @@
         <v>44.37</v>
       </c>
       <c r="J43" t="n">
-        <v>71.17</v>
+        <v>71.28</v>
       </c>
       <c r="K43" t="n">
-        <v>42.27</v>
+        <v>42.32</v>
       </c>
       <c r="L43" t="n">
-        <v>31.87</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="44">
@@ -2180,7 +2194,7 @@
         <v>424</v>
       </c>
       <c r="G44" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H44" t="n">
         <v>1.3</v>
@@ -2189,13 +2203,13 @@
         <v>44.89</v>
       </c>
       <c r="J44" t="n">
-        <v>72.37</v>
+        <v>72.48</v>
       </c>
       <c r="K44" t="n">
-        <v>46.4</v>
+        <v>46.46</v>
       </c>
       <c r="L44" t="n">
-        <v>35.47</v>
+        <v>35.51</v>
       </c>
     </row>
     <row r="45">
@@ -2220,7 +2234,7 @@
         <v>449</v>
       </c>
       <c r="G45" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H45" t="n">
         <v>1.51</v>
@@ -2229,13 +2243,13 @@
         <v>43.33</v>
       </c>
       <c r="J45" t="n">
-        <v>71.31999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>43.73</v>
+        <v>43.79</v>
       </c>
       <c r="L45" t="n">
-        <v>29.73</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="46">
@@ -2260,7 +2274,7 @@
         <v>54</v>
       </c>
       <c r="G46" t="n">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H46" t="n">
         <v>0.08</v>
@@ -2269,13 +2283,13 @@
         <v>42.29</v>
       </c>
       <c r="J46" t="n">
-        <v>70.27</v>
+        <v>70.38</v>
       </c>
       <c r="K46" t="n">
-        <v>37.73</v>
+        <v>37.78</v>
       </c>
       <c r="L46" t="n">
-        <v>22.93</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="47">
@@ -2300,7 +2314,7 @@
         <v>188</v>
       </c>
       <c r="G47" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H47" t="n">
         <v>0.34</v>
@@ -2309,13 +2323,13 @@
         <v>50</v>
       </c>
       <c r="J47" t="n">
-        <v>82.43000000000001</v>
+        <v>82.56</v>
       </c>
       <c r="K47" t="n">
-        <v>67.59999999999999</v>
+        <v>67.69</v>
       </c>
       <c r="L47" t="n">
-        <v>50.53</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="48">
@@ -2337,7 +2351,7 @@
         <v>4.32</v>
       </c>
       <c r="F48" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G48" t="n">
         <v>425</v>
@@ -2349,13 +2363,13 @@
         <v>54.86</v>
       </c>
       <c r="J48" t="n">
-        <v>87.23999999999999</v>
+        <v>87.37</v>
       </c>
       <c r="K48" t="n">
-        <v>82.27</v>
+        <v>82.38</v>
       </c>
       <c r="L48" t="n">
-        <v>73.47</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="49">
@@ -2380,7 +2394,7 @@
         <v>499</v>
       </c>
       <c r="G49" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
@@ -2389,13 +2403,13 @@
         <v>56.6</v>
       </c>
       <c r="J49" t="n">
-        <v>87.98999999999999</v>
+        <v>88.12</v>
       </c>
       <c r="K49" t="n">
-        <v>87.87</v>
+        <v>87.98</v>
       </c>
       <c r="L49" t="n">
-        <v>82.67</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="50">
@@ -2417,7 +2431,7 @@
         <v>2.92</v>
       </c>
       <c r="F50" t="n">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G50" t="n">
         <v>145</v>
@@ -2429,13 +2443,13 @@
         <v>52.6</v>
       </c>
       <c r="J50" t="n">
-        <v>86.94</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>86.8</v>
+        <v>86.92</v>
       </c>
       <c r="L50" t="n">
-        <v>80.93000000000001</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2460,7 +2474,7 @@
         <v>344</v>
       </c>
       <c r="G51" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H51" t="n">
         <v>0.85</v>
@@ -2469,13 +2483,13 @@
         <v>47.74</v>
       </c>
       <c r="J51" t="n">
-        <v>79.73</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>73.87</v>
+        <v>73.97</v>
       </c>
       <c r="L51" t="n">
-        <v>62.67</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="52">
@@ -2500,22 +2514,22 @@
         <v>531</v>
       </c>
       <c r="G52" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H52" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="I52" t="n">
         <v>46.96</v>
       </c>
       <c r="J52" t="n">
-        <v>80.63</v>
+        <v>80.75</v>
       </c>
       <c r="K52" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="L52" t="n">
-        <v>66.93000000000001</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="53">
@@ -2549,13 +2563,13 @@
         <v>43.65</v>
       </c>
       <c r="J53" t="n">
-        <v>77.48</v>
+        <v>77.59</v>
       </c>
       <c r="K53" t="n">
-        <v>64.93000000000001</v>
+        <v>65.02</v>
       </c>
       <c r="L53" t="n">
-        <v>49.87</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="54">
@@ -2580,7 +2594,7 @@
         <v>196</v>
       </c>
       <c r="G54" t="n">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H54" t="n">
         <v>0.36</v>
@@ -2589,13 +2603,13 @@
         <v>41.93</v>
       </c>
       <c r="J54" t="n">
-        <v>77.47</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>73.06999999999999</v>
+        <v>73.16</v>
       </c>
       <c r="L54" t="n">
-        <v>55.2</v>
+        <v>55.27</v>
       </c>
     </row>
     <row r="55">
@@ -2617,7 +2631,7 @@
         <v>4.03</v>
       </c>
       <c r="F55" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G55" t="n">
         <v>377</v>
@@ -2629,13 +2643,13 @@
         <v>43.74</v>
       </c>
       <c r="J55" t="n">
-        <v>79.2</v>
+        <v>79.31</v>
       </c>
       <c r="K55" t="n">
-        <v>80.67</v>
+        <v>80.77</v>
       </c>
       <c r="L55" t="n">
-        <v>70.27</v>
+        <v>70.36</v>
       </c>
     </row>
     <row r="56">
@@ -2660,7 +2674,7 @@
         <v>285</v>
       </c>
       <c r="G56" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H56" t="n">
         <v>0.62</v>
@@ -2669,13 +2683,13 @@
         <v>44.06</v>
       </c>
       <c r="J56" t="n">
-        <v>77.87</v>
+        <v>77.97</v>
       </c>
       <c r="K56" t="n">
-        <v>81.2</v>
+        <v>81.31</v>
       </c>
       <c r="L56" t="n">
-        <v>70.8</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="57">
@@ -2697,25 +2711,25 @@
         <v>5.42</v>
       </c>
       <c r="F57" t="n">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G57" t="n">
         <v>102</v>
       </c>
       <c r="H57" t="n">
-        <v>6.35</v>
+        <v>6.34</v>
       </c>
       <c r="I57" t="n">
         <v>44.22</v>
       </c>
       <c r="J57" t="n">
-        <v>80.13</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>86.93000000000001</v>
+        <v>87.05</v>
       </c>
       <c r="L57" t="n">
-        <v>81.59999999999999</v>
+        <v>81.70999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2738,7 +2752,7 @@
         <v>156</v>
       </c>
       <c r="G58" t="n">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H58" t="n">
         <v>0.26</v>
@@ -2747,13 +2761,13 @@
         <v>40.1</v>
       </c>
       <c r="J58" t="n">
-        <v>71.87</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>62.13</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="59">
@@ -2776,22 +2790,22 @@
         <v>237</v>
       </c>
       <c r="G59" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H59" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="I59" t="n">
         <v>42.63</v>
       </c>
       <c r="J59" t="n">
-        <v>78.8</v>
+        <v>78.91</v>
       </c>
       <c r="K59" t="n">
-        <v>87.33</v>
+        <v>87.45</v>
       </c>
       <c r="L59" t="n">
-        <v>82.13</v>
+        <v>82.23999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2814,22 +2828,22 @@
         <v>496</v>
       </c>
       <c r="G60" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H60" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I60" t="n">
         <v>43.4</v>
       </c>
       <c r="J60" t="n">
-        <v>82</v>
+        <v>82.11</v>
       </c>
       <c r="K60" t="n">
-        <v>91.73</v>
+        <v>91.72</v>
       </c>
       <c r="L60" t="n">
-        <v>89.87</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2849,7 +2863,7 @@
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G61" t="n">
         <v>238</v>
@@ -2861,13 +2875,13 @@
         <v>41.08</v>
       </c>
       <c r="J61" t="n">
-        <v>81.59999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="K61" t="n">
-        <v>93.47</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>92.53</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="62">
@@ -2890,7 +2904,7 @@
         <v>275</v>
       </c>
       <c r="G62" t="n">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H62" t="n">
         <v>0.58</v>
@@ -2899,13 +2913,13 @@
         <v>38.69</v>
       </c>
       <c r="J62" t="n">
-        <v>76.8</v>
+        <v>76.77</v>
       </c>
       <c r="K62" t="n">
-        <v>93.2</v>
+        <v>93.19</v>
       </c>
       <c r="L62" t="n">
-        <v>92</v>
+        <v>91.98999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2923,22 +2937,22 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G63" t="n">
         <v>167</v>
       </c>
       <c r="H63" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="I63" t="n">
         <v>39.33</v>
       </c>
       <c r="J63" t="n">
-        <v>79.06999999999999</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>95.2</v>
+        <v>95.19</v>
       </c>
       <c r="L63" t="n">
         <v>96.53</v>
@@ -2959,7 +2973,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G64" t="n">
         <v>243</v>
@@ -2971,13 +2985,13 @@
         <v>37.26</v>
       </c>
       <c r="J64" t="n">
-        <v>74.93000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>92.67</v>
+        <v>92.66</v>
       </c>
       <c r="L64" t="n">
-        <v>94.8</v>
+        <v>94.79000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2995,22 +3009,22 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G65" t="n">
         <v>67</v>
       </c>
       <c r="H65" t="n">
-        <v>10.18</v>
+        <v>10.16</v>
       </c>
       <c r="I65" t="n">
         <v>34.71</v>
       </c>
       <c r="J65" t="n">
-        <v>68.40000000000001</v>
+        <v>68.36</v>
       </c>
       <c r="K65" t="n">
-        <v>93.87</v>
+        <v>93.86</v>
       </c>
       <c r="L65" t="n">
         <v>96.13</v>
@@ -3034,7 +3048,7 @@
         <v>244</v>
       </c>
       <c r="G66" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H66" t="n">
         <v>0.49</v>
@@ -3043,13 +3057,13 @@
         <v>31.26</v>
       </c>
       <c r="J66" t="n">
-        <v>52.93</v>
+        <v>53</v>
       </c>
       <c r="K66" t="n">
-        <v>84.27</v>
+        <v>84.25</v>
       </c>
       <c r="L66" t="n">
-        <v>90.40000000000001</v>
+        <v>90.39</v>
       </c>
     </row>
     <row r="67">
@@ -3092,8 +3106,8 @@
   <conditionalFormatting sqref="B2:B67">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="200"/>
         <color rgb="00FFFFFF"/>
         <color rgb="0063BE7B"/>
       </colorScale>
@@ -3102,8 +3116,8 @@
   <conditionalFormatting sqref="C2:C67">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="200"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00F8696B"/>
       </colorScale>
@@ -3112,9 +3126,9 @@
   <conditionalFormatting sqref="D2:E67">
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="2"/>
         <color rgb="00F8696B"/>
         <color rgb="00FFFFFF"/>
         <color rgb="0063BE7B"/>
@@ -3122,20 +3136,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F67">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="750"/>
         <color rgb="00FFFFFF"/>
         <color rgb="0063BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G67">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="750"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00F8696B"/>
       </colorScale>
@@ -3144,9 +3158,9 @@
   <conditionalFormatting sqref="H2:H67">
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="2"/>
         <color rgb="00F8696B"/>
         <color rgb="00FFFFFF"/>
         <color rgb="0063BE7B"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -424,10 +424,13 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,20 +476,35 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>52W Highs</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>52W Lows</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Volume Breadth</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>&gt; 200 SMA (%)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>&gt; 50 SMA (%)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>&gt; 20 EMA (%)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>&gt; 10 EMA (%)</t>
         </is>
@@ -505,31 +523,40 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="E2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="F2" t="n">
         <v>382</v>
       </c>
       <c r="G2" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L2" t="n">
         <v>57.04</v>
       </c>
-      <c r="J2" t="n">
-        <v>65.15000000000001</v>
-      </c>
-      <c r="K2" t="n">
-        <v>65.33</v>
-      </c>
-      <c r="L2" t="n">
-        <v>64.67</v>
+      <c r="M2" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="O2" t="n">
+        <v>64.58</v>
       </c>
     </row>
     <row r="3">
@@ -545,31 +572,40 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="E3" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="F3" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G3" t="n">
         <v>145</v>
       </c>
       <c r="H3" t="n">
-        <v>4.16</v>
+        <v>4.17</v>
       </c>
       <c r="I3" t="n">
+        <v>27</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="L3" t="n">
         <v>55.67</v>
       </c>
-      <c r="J3" t="n">
-        <v>64.89</v>
-      </c>
-      <c r="K3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="L3" t="n">
-        <v>64.27</v>
+      <c r="M3" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="N3" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="O3" t="n">
+        <v>64.31</v>
       </c>
     </row>
     <row r="4">
@@ -585,13 +621,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="F4" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G4" t="n">
         <v>127</v>
@@ -600,16 +636,25 @@
         <v>4.91</v>
       </c>
       <c r="I4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="L4" t="n">
         <v>52.75</v>
       </c>
-      <c r="J4" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="K4" t="n">
-        <v>51.47</v>
-      </c>
-      <c r="L4" t="n">
-        <v>45.47</v>
+      <c r="M4" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="O4" t="n">
+        <v>45.54</v>
       </c>
     </row>
     <row r="5">
@@ -622,34 +667,43 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="F5" t="n">
         <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H5" t="n">
         <v>0.13</v>
       </c>
       <c r="I5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L5" t="n">
         <v>49.83</v>
       </c>
-      <c r="J5" t="n">
-        <v>49.92</v>
-      </c>
-      <c r="K5" t="n">
-        <v>37.87</v>
-      </c>
-      <c r="L5" t="n">
-        <v>26.13</v>
+      <c r="M5" t="n">
+        <v>50</v>
+      </c>
+      <c r="N5" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="O5" t="n">
+        <v>26.23</v>
       </c>
     </row>
     <row r="6">
@@ -668,10 +722,10 @@
         <v>2.27</v>
       </c>
       <c r="E6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="F6" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G6" t="n">
         <v>505</v>
@@ -680,16 +734,25 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
+        <v>26</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L6" t="n">
         <v>56.36</v>
       </c>
-      <c r="J6" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="K6" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="L6" t="n">
-        <v>51.73</v>
+      <c r="M6" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="N6" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="O6" t="n">
+        <v>51.8</v>
       </c>
     </row>
     <row r="7">
@@ -708,10 +771,10 @@
         <v>3.5</v>
       </c>
       <c r="E7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="F7" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G7" t="n">
         <v>386</v>
@@ -720,16 +783,25 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L7" t="n">
         <v>57.14</v>
       </c>
-      <c r="J7" t="n">
-        <v>63.61</v>
-      </c>
-      <c r="K7" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="L7" t="n">
-        <v>63.6</v>
+      <c r="M7" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="N7" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="O7" t="n">
+        <v>63.65</v>
       </c>
     </row>
     <row r="8">
@@ -745,31 +817,40 @@
         <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="E8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="F8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G8" t="n">
         <v>395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L8" t="n">
         <v>56.97</v>
       </c>
-      <c r="J8" t="n">
-        <v>64.95999999999999</v>
-      </c>
-      <c r="K8" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>66.13</v>
+      <c r="M8" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>66.84</v>
+      </c>
+      <c r="O8" t="n">
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -785,13 +866,13 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="E9" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="F9" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G9" t="n">
         <v>212</v>
@@ -800,16 +881,25 @@
         <v>2.53</v>
       </c>
       <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L9" t="n">
         <v>56.63</v>
       </c>
-      <c r="J9" t="n">
-        <v>64.51000000000001</v>
-      </c>
-      <c r="K9" t="n">
-        <v>69.69</v>
-      </c>
-      <c r="L9" t="n">
-        <v>68.62</v>
+      <c r="M9" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="N9" t="n">
+        <v>69.73</v>
+      </c>
+      <c r="O9" t="n">
+        <v>68.67</v>
       </c>
     </row>
     <row r="10">
@@ -825,13 +915,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="E10" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="F10" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G10" t="n">
         <v>333</v>
@@ -840,16 +930,25 @@
         <v>1.25</v>
       </c>
       <c r="I10" t="n">
+        <v>29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="L10" t="n">
         <v>53.01</v>
       </c>
-      <c r="J10" t="n">
-        <v>60.15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>61.42</v>
-      </c>
-      <c r="L10" t="n">
-        <v>57.01</v>
+      <c r="M10" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="N10" t="n">
+        <v>61.47</v>
+      </c>
+      <c r="O10" t="n">
+        <v>57.07</v>
       </c>
     </row>
     <row r="11">
@@ -865,31 +964,40 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="E11" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="F11" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G11" t="n">
         <v>305</v>
       </c>
       <c r="H11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I11" t="n">
+        <v>27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L11" t="n">
         <v>51.98</v>
       </c>
-      <c r="J11" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="L11" t="n">
-        <v>50.2</v>
+      <c r="M11" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O11" t="n">
+        <v>50.13</v>
       </c>
     </row>
     <row r="12">
@@ -902,34 +1010,43 @@
         <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="E12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="F12" t="n">
         <v>278</v>
       </c>
       <c r="G12" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H12" t="n">
         <v>0.59</v>
       </c>
       <c r="I12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="L12" t="n">
         <v>50.43</v>
       </c>
-      <c r="J12" t="n">
-        <v>55.94</v>
-      </c>
-      <c r="K12" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>41.39</v>
+      <c r="M12" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="N12" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="O12" t="n">
+        <v>41.33</v>
       </c>
     </row>
     <row r="13">
@@ -960,16 +1077,25 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>52.67</v>
       </c>
-      <c r="J13" t="n">
-        <v>59.85</v>
-      </c>
-      <c r="K13" t="n">
-        <v>60.21</v>
-      </c>
-      <c r="L13" t="n">
-        <v>50.73</v>
+      <c r="M13" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="N13" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="O13" t="n">
+        <v>50.8</v>
       </c>
     </row>
     <row r="14">
@@ -994,22 +1120,31 @@
         <v>249</v>
       </c>
       <c r="G14" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H14" t="n">
         <v>0.5</v>
       </c>
       <c r="I14" t="n">
+        <v>19</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L14" t="n">
         <v>52.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>60</v>
-      </c>
-      <c r="K14" t="n">
-        <v>60.21</v>
-      </c>
-      <c r="L14" t="n">
-        <v>50.73</v>
+      <c r="M14" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="O14" t="n">
+        <v>50.8</v>
       </c>
     </row>
     <row r="15">
@@ -1034,22 +1169,31 @@
         <v>388</v>
       </c>
       <c r="G15" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H15" t="n">
         <v>1.07</v>
       </c>
       <c r="I15" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L15" t="n">
         <v>53.01</v>
       </c>
-      <c r="J15" t="n">
-        <v>62.41</v>
-      </c>
-      <c r="K15" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="L15" t="n">
-        <v>63.68</v>
+      <c r="M15" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="N15" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>63.73</v>
       </c>
     </row>
     <row r="16">
@@ -1074,22 +1218,31 @@
         <v>181</v>
       </c>
       <c r="G16" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H16" t="n">
         <v>0.32</v>
       </c>
       <c r="I16" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L16" t="n">
         <v>53.36</v>
       </c>
-      <c r="J16" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="L16" t="n">
-        <v>64.09</v>
+      <c r="M16" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="N16" t="n">
+        <v>69.33</v>
+      </c>
+      <c r="O16" t="n">
+        <v>64.13</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1264,7 @@
         <v>6.03</v>
       </c>
       <c r="F17" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G17" t="n">
         <v>253</v>
@@ -1120,16 +1273,25 @@
         <v>1.96</v>
       </c>
       <c r="I17" t="n">
+        <v>28</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L17" t="n">
         <v>55.59</v>
       </c>
-      <c r="J17" t="n">
-        <v>68.42</v>
-      </c>
-      <c r="K17" t="n">
-        <v>79.17</v>
-      </c>
-      <c r="L17" t="n">
-        <v>81.04000000000001</v>
+      <c r="M17" t="n">
+        <v>68.47</v>
+      </c>
+      <c r="N17" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>81.06999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1154,22 +1316,31 @@
         <v>394</v>
       </c>
       <c r="G18" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I18" t="n">
+        <v>29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L18" t="n">
         <v>54.04</v>
       </c>
-      <c r="J18" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="K18" t="n">
-        <v>73.97</v>
-      </c>
-      <c r="L18" t="n">
-        <v>75.03</v>
+      <c r="M18" t="n">
+        <v>65.47</v>
+      </c>
+      <c r="N18" t="n">
+        <v>74</v>
+      </c>
+      <c r="O18" t="n">
+        <v>75.06999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1191,7 +1362,7 @@
         <v>3.01</v>
       </c>
       <c r="F19" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G19" t="n">
         <v>302</v>
@@ -1200,16 +1371,25 @@
         <v>1.48</v>
       </c>
       <c r="I19" t="n">
+        <v>38</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L19" t="n">
         <v>53.36</v>
       </c>
-      <c r="J19" t="n">
-        <v>65.86</v>
-      </c>
-      <c r="K19" t="n">
-        <v>76.77</v>
-      </c>
-      <c r="L19" t="n">
-        <v>79.44</v>
+      <c r="M19" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="N19" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>79.47</v>
       </c>
     </row>
     <row r="20">
@@ -1231,7 +1411,7 @@
         <v>3.09</v>
       </c>
       <c r="F20" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G20" t="n">
         <v>295</v>
@@ -1240,16 +1420,25 @@
         <v>1.53</v>
       </c>
       <c r="I20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="L20" t="n">
         <v>51.98</v>
       </c>
-      <c r="J20" t="n">
-        <v>63.76</v>
-      </c>
-      <c r="K20" t="n">
-        <v>74.63</v>
-      </c>
-      <c r="L20" t="n">
-        <v>78.23999999999999</v>
+      <c r="M20" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="N20" t="n">
+        <v>74.67</v>
+      </c>
+      <c r="O20" t="n">
+        <v>78.27</v>
       </c>
     </row>
     <row r="21">
@@ -1274,22 +1463,31 @@
         <v>435</v>
       </c>
       <c r="G21" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H21" t="n">
         <v>1.39</v>
       </c>
       <c r="I21" t="n">
+        <v>23</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L21" t="n">
         <v>50.43</v>
       </c>
-      <c r="J21" t="n">
-        <v>61.95</v>
-      </c>
-      <c r="K21" t="n">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="L21" t="n">
-        <v>79.17</v>
+      <c r="M21" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="N21" t="n">
+        <v>73.47</v>
+      </c>
+      <c r="O21" t="n">
+        <v>79.2</v>
       </c>
     </row>
     <row r="22">
@@ -1311,25 +1509,34 @@
         <v>2.83</v>
       </c>
       <c r="F22" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G22" t="n">
         <v>175</v>
       </c>
       <c r="H22" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="I22" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="L22" t="n">
         <v>49.83</v>
       </c>
-      <c r="J22" t="n">
-        <v>60</v>
-      </c>
-      <c r="K22" t="n">
-        <v>70.23</v>
-      </c>
-      <c r="L22" t="n">
-        <v>79.04000000000001</v>
+      <c r="M22" t="n">
+        <v>59.91</v>
+      </c>
+      <c r="N22" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="O22" t="n">
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1351,25 +1558,34 @@
         <v>1.9</v>
       </c>
       <c r="F23" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G23" t="n">
         <v>58</v>
       </c>
       <c r="H23" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="I23" t="n">
+        <v>14</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="L23" t="n">
         <v>46.72</v>
       </c>
-      <c r="J23" t="n">
-        <v>50.08</v>
-      </c>
-      <c r="K23" t="n">
-        <v>53</v>
-      </c>
-      <c r="L23" t="n">
-        <v>61.15</v>
+      <c r="M23" t="n">
+        <v>50</v>
+      </c>
+      <c r="N23" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="O23" t="n">
+        <v>61.2</v>
       </c>
     </row>
     <row r="24">
@@ -1391,7 +1607,7 @@
         <v>1.09</v>
       </c>
       <c r="F24" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G24" t="n">
         <v>575</v>
@@ -1400,16 +1616,25 @@
         <v>0.3</v>
       </c>
       <c r="I24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>21</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L24" t="n">
         <v>39.14</v>
       </c>
-      <c r="J24" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>27.77</v>
-      </c>
-      <c r="L24" t="n">
-        <v>22.03</v>
+      <c r="M24" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="N24" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="O24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1434,22 +1659,31 @@
         <v>160</v>
       </c>
       <c r="G25" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H25" t="n">
         <v>0.27</v>
       </c>
       <c r="I25" t="n">
+        <v>23</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L25" t="n">
         <v>43.28</v>
       </c>
-      <c r="J25" t="n">
-        <v>44.36</v>
-      </c>
-      <c r="K25" t="n">
-        <v>36.32</v>
-      </c>
-      <c r="L25" t="n">
-        <v>30.71</v>
+      <c r="M25" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="N25" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="O25" t="n">
+        <v>30.67</v>
       </c>
     </row>
     <row r="26">
@@ -1474,22 +1708,31 @@
         <v>597</v>
       </c>
       <c r="G26" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H26" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="I26" t="n">
+        <v>21</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L26" t="n">
         <v>45</v>
       </c>
-      <c r="J26" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="K26" t="n">
-        <v>43.93</v>
-      </c>
-      <c r="L26" t="n">
-        <v>43.26</v>
+      <c r="M26" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="N26" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="O26" t="n">
+        <v>43.2</v>
       </c>
     </row>
     <row r="27">
@@ -1514,22 +1757,31 @@
         <v>103</v>
       </c>
       <c r="G27" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H27" t="n">
         <v>0.16</v>
       </c>
       <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="n">
+        <v>16</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L27" t="n">
         <v>41.55</v>
       </c>
-      <c r="J27" t="n">
-        <v>44.96</v>
-      </c>
-      <c r="K27" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="L27" t="n">
-        <v>24.3</v>
+      <c r="M27" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="N27" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>24.27</v>
       </c>
     </row>
     <row r="28">
@@ -1554,22 +1806,31 @@
         <v>360</v>
       </c>
       <c r="G28" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H28" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I28" t="n">
+        <v>26</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L28" t="n">
         <v>45</v>
       </c>
-      <c r="J28" t="n">
-        <v>55.19</v>
-      </c>
-      <c r="K28" t="n">
-        <v>44.99</v>
-      </c>
-      <c r="L28" t="n">
-        <v>45.39</v>
+      <c r="M28" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="O28" t="n">
+        <v>45.33</v>
       </c>
     </row>
     <row r="29">
@@ -1594,22 +1855,31 @@
         <v>399</v>
       </c>
       <c r="G29" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H29" t="n">
         <v>1.14</v>
       </c>
       <c r="I29" t="n">
+        <v>28</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L29" t="n">
         <v>44.91</v>
       </c>
-      <c r="J29" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="K29" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="L29" t="n">
-        <v>43.26</v>
+      <c r="M29" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="N29" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="O29" t="n">
+        <v>43.2</v>
       </c>
     </row>
     <row r="30">
@@ -1631,7 +1901,7 @@
         <v>1.86</v>
       </c>
       <c r="F30" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G30" t="n">
         <v>441</v>
@@ -1640,16 +1910,25 @@
         <v>0.7</v>
       </c>
       <c r="I30" t="n">
+        <v>21</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="L30" t="n">
         <v>43.87</v>
       </c>
-      <c r="J30" t="n">
-        <v>57.44</v>
-      </c>
-      <c r="K30" t="n">
-        <v>43.26</v>
-      </c>
-      <c r="L30" t="n">
-        <v>37.78</v>
+      <c r="M30" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="N30" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>37.73</v>
       </c>
     </row>
     <row r="31">
@@ -1671,7 +1950,7 @@
         <v>1.96</v>
       </c>
       <c r="F31" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G31" t="n">
         <v>280</v>
@@ -1680,16 +1959,25 @@
         <v>1.67</v>
       </c>
       <c r="I31" t="n">
+        <v>13</v>
+      </c>
+      <c r="J31" t="n">
+        <v>16</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L31" t="n">
         <v>43.7</v>
       </c>
-      <c r="J31" t="n">
-        <v>60.15</v>
-      </c>
-      <c r="K31" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="L31" t="n">
-        <v>40.05</v>
+      <c r="M31" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="N31" t="n">
+        <v>43.73</v>
+      </c>
+      <c r="O31" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="32">
@@ -1711,25 +1999,34 @@
         <v>1.93</v>
       </c>
       <c r="F32" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G32" t="n">
         <v>530</v>
       </c>
       <c r="H32" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="I32" t="n">
+        <v>17</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L32" t="n">
         <v>42.83</v>
       </c>
-      <c r="J32" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>38.05</v>
-      </c>
-      <c r="L32" t="n">
-        <v>31.91</v>
+      <c r="M32" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>38</v>
+      </c>
+      <c r="O32" t="n">
+        <v>31.87</v>
       </c>
     </row>
     <row r="33">
@@ -1754,22 +2051,31 @@
         <v>210</v>
       </c>
       <c r="G33" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H33" t="n">
         <v>0.39</v>
       </c>
       <c r="I33" t="n">
+        <v>38</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L33" t="n">
         <v>44.04</v>
       </c>
-      <c r="J33" t="n">
-        <v>66.47</v>
-      </c>
-      <c r="K33" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="L33" t="n">
-        <v>42.19</v>
+      <c r="M33" t="n">
+        <v>66.37</v>
+      </c>
+      <c r="N33" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="O33" t="n">
+        <v>42.13</v>
       </c>
     </row>
     <row r="34">
@@ -1800,16 +2106,25 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>47.67</v>
       </c>
-      <c r="J34" t="n">
-        <v>72.63</v>
-      </c>
-      <c r="K34" t="n">
-        <v>61.42</v>
-      </c>
-      <c r="L34" t="n">
-        <v>60.75</v>
+      <c r="M34" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="N34" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="O34" t="n">
+        <v>60.67</v>
       </c>
     </row>
     <row r="35">
@@ -1834,22 +2149,31 @@
         <v>390</v>
       </c>
       <c r="G35" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H35" t="n">
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
+        <v>41</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="L35" t="n">
         <v>47.75</v>
       </c>
-      <c r="J35" t="n">
-        <v>73.38</v>
-      </c>
-      <c r="K35" t="n">
-        <v>61.42</v>
-      </c>
-      <c r="L35" t="n">
-        <v>60.75</v>
+      <c r="M35" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="N35" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="O35" t="n">
+        <v>60.67</v>
       </c>
     </row>
     <row r="36">
@@ -1874,22 +2198,31 @@
         <v>362</v>
       </c>
       <c r="G36" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H36" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="I36" t="n">
+        <v>27</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L36" t="n">
         <v>46.97</v>
       </c>
-      <c r="J36" t="n">
-        <v>73.98</v>
-      </c>
-      <c r="K36" t="n">
-        <v>62.22</v>
-      </c>
-      <c r="L36" t="n">
-        <v>63.55</v>
+      <c r="M36" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="N36" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="O36" t="n">
+        <v>63.47</v>
       </c>
     </row>
     <row r="37">
@@ -1911,25 +2244,34 @@
         <v>0.9</v>
       </c>
       <c r="F37" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G37" t="n">
         <v>182</v>
       </c>
       <c r="H37" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="I37" t="n">
+        <v>28</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="L37" t="n">
         <v>46.27</v>
       </c>
-      <c r="J37" t="n">
-        <v>74.89</v>
-      </c>
-      <c r="K37" t="n">
-        <v>61.28</v>
-      </c>
-      <c r="L37" t="n">
-        <v>63.55</v>
+      <c r="M37" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="N37" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>63.6</v>
       </c>
     </row>
     <row r="38">
@@ -1951,7 +2293,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G38" t="n">
         <v>373</v>
@@ -1960,16 +2302,25 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
+        <v>20</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L38" t="n">
         <v>44.19</v>
       </c>
-      <c r="J38" t="n">
-        <v>68.27</v>
-      </c>
-      <c r="K38" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="L38" t="n">
-        <v>47</v>
+      <c r="M38" t="n">
+        <v>68.17</v>
+      </c>
+      <c r="N38" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>46.93</v>
       </c>
     </row>
     <row r="39">
@@ -1994,22 +2345,31 @@
         <v>445</v>
       </c>
       <c r="G39" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H39" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I39" t="n">
+        <v>22</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L39" t="n">
         <v>42.11</v>
       </c>
-      <c r="J39" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="K39" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>45.79</v>
+      <c r="M39" t="n">
+        <v>68.62</v>
+      </c>
+      <c r="N39" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="O39" t="n">
+        <v>45.73</v>
       </c>
     </row>
     <row r="40">
@@ -2031,7 +2391,7 @@
         <v>0.76</v>
       </c>
       <c r="F40" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G40" t="n">
         <v>382</v>
@@ -2040,16 +2400,25 @@
         <v>0.96</v>
       </c>
       <c r="I40" t="n">
+        <v>16</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L40" t="n">
         <v>41.25</v>
       </c>
-      <c r="J40" t="n">
-        <v>66.92</v>
-      </c>
-      <c r="K40" t="n">
-        <v>42.06</v>
-      </c>
-      <c r="L40" t="n">
-        <v>38.18</v>
+      <c r="M40" t="n">
+        <v>66.81999999999999</v>
+      </c>
+      <c r="N40" t="n">
+        <v>42</v>
+      </c>
+      <c r="O40" t="n">
+        <v>38.13</v>
       </c>
     </row>
     <row r="41">
@@ -2074,22 +2443,31 @@
         <v>493</v>
       </c>
       <c r="G41" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H41" t="n">
         <v>1.93</v>
       </c>
       <c r="I41" t="n">
+        <v>14</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L41" t="n">
         <v>41.42</v>
       </c>
-      <c r="J41" t="n">
-        <v>67.22</v>
-      </c>
-      <c r="K41" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="L41" t="n">
-        <v>34.45</v>
+      <c r="M41" t="n">
+        <v>67.12</v>
+      </c>
+      <c r="N41" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="O41" t="n">
+        <v>34.4</v>
       </c>
     </row>
     <row r="42">
@@ -2111,7 +2489,7 @@
         <v>0.86</v>
       </c>
       <c r="F42" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G42" t="n">
         <v>585</v>
@@ -2120,16 +2498,25 @@
         <v>0.28</v>
       </c>
       <c r="I42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>15</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L42" t="n">
         <v>39.86</v>
       </c>
-      <c r="J42" t="n">
-        <v>65.11</v>
-      </c>
-      <c r="K42" t="n">
-        <v>32.58</v>
-      </c>
-      <c r="L42" t="n">
-        <v>23.23</v>
+      <c r="M42" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="N42" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O42" t="n">
+        <v>23.33</v>
       </c>
     </row>
     <row r="43">
@@ -2151,7 +2538,7 @@
         <v>1.11</v>
       </c>
       <c r="F43" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G43" t="n">
         <v>494</v>
@@ -2160,16 +2547,25 @@
         <v>0.52</v>
       </c>
       <c r="I43" t="n">
+        <v>21</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L43" t="n">
         <v>44.37</v>
       </c>
-      <c r="J43" t="n">
-        <v>71.28</v>
-      </c>
-      <c r="K43" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="L43" t="n">
-        <v>31.78</v>
+      <c r="M43" t="n">
+        <v>71.17</v>
+      </c>
+      <c r="N43" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="O43" t="n">
+        <v>31.87</v>
       </c>
     </row>
     <row r="44">
@@ -2194,22 +2590,31 @@
         <v>424</v>
       </c>
       <c r="G44" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H44" t="n">
         <v>1.3</v>
       </c>
       <c r="I44" t="n">
+        <v>24</v>
+      </c>
+      <c r="J44" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L44" t="n">
         <v>44.89</v>
       </c>
-      <c r="J44" t="n">
-        <v>72.48</v>
-      </c>
-      <c r="K44" t="n">
-        <v>46.46</v>
-      </c>
-      <c r="L44" t="n">
-        <v>35.51</v>
+      <c r="M44" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="N44" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O44" t="n">
+        <v>35.47</v>
       </c>
     </row>
     <row r="45">
@@ -2234,22 +2639,31 @@
         <v>449</v>
       </c>
       <c r="G45" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H45" t="n">
         <v>1.51</v>
       </c>
       <c r="I45" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" t="n">
+        <v>13</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L45" t="n">
         <v>43.33</v>
       </c>
-      <c r="J45" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="K45" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="L45" t="n">
-        <v>29.77</v>
+      <c r="M45" t="n">
+        <v>71.31999999999999</v>
+      </c>
+      <c r="N45" t="n">
+        <v>43.73</v>
+      </c>
+      <c r="O45" t="n">
+        <v>29.73</v>
       </c>
     </row>
     <row r="46">
@@ -2274,22 +2688,31 @@
         <v>54</v>
       </c>
       <c r="G46" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H46" t="n">
         <v>0.08</v>
       </c>
       <c r="I46" t="n">
+        <v>14</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L46" t="n">
         <v>42.29</v>
       </c>
-      <c r="J46" t="n">
-        <v>70.38</v>
-      </c>
-      <c r="K46" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="L46" t="n">
-        <v>22.96</v>
+      <c r="M46" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="N46" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="O46" t="n">
+        <v>22.93</v>
       </c>
     </row>
     <row r="47">
@@ -2314,22 +2737,31 @@
         <v>188</v>
       </c>
       <c r="G47" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H47" t="n">
         <v>0.34</v>
       </c>
       <c r="I47" t="n">
+        <v>29</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L47" t="n">
         <v>50</v>
       </c>
-      <c r="J47" t="n">
-        <v>82.56</v>
-      </c>
-      <c r="K47" t="n">
-        <v>67.69</v>
-      </c>
-      <c r="L47" t="n">
-        <v>50.6</v>
+      <c r="M47" t="n">
+        <v>82.43000000000001</v>
+      </c>
+      <c r="N47" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="O47" t="n">
+        <v>50.53</v>
       </c>
     </row>
     <row r="48">
@@ -2351,7 +2783,7 @@
         <v>4.32</v>
       </c>
       <c r="F48" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G48" t="n">
         <v>425</v>
@@ -2360,16 +2792,25 @@
         <v>0.76</v>
       </c>
       <c r="I48" t="n">
+        <v>44</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L48" t="n">
         <v>54.86</v>
       </c>
-      <c r="J48" t="n">
-        <v>87.37</v>
-      </c>
-      <c r="K48" t="n">
-        <v>82.38</v>
-      </c>
-      <c r="L48" t="n">
-        <v>73.56</v>
+      <c r="M48" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="N48" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="O48" t="n">
+        <v>73.47</v>
       </c>
     </row>
     <row r="49">
@@ -2394,22 +2835,31 @@
         <v>499</v>
       </c>
       <c r="G49" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
       <c r="I49" t="n">
+        <v>45</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L49" t="n">
         <v>56.6</v>
       </c>
-      <c r="J49" t="n">
-        <v>88.12</v>
-      </c>
-      <c r="K49" t="n">
-        <v>87.98</v>
-      </c>
-      <c r="L49" t="n">
-        <v>82.78</v>
+      <c r="M49" t="n">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="N49" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="O49" t="n">
+        <v>82.67</v>
       </c>
     </row>
     <row r="50">
@@ -2431,7 +2881,7 @@
         <v>2.92</v>
       </c>
       <c r="F50" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G50" t="n">
         <v>145</v>
@@ -2440,16 +2890,25 @@
         <v>4.17</v>
       </c>
       <c r="I50" t="n">
+        <v>38</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="L50" t="n">
         <v>52.6</v>
       </c>
-      <c r="J50" t="n">
-        <v>87.06999999999999</v>
-      </c>
-      <c r="K50" t="n">
-        <v>86.92</v>
-      </c>
-      <c r="L50" t="n">
-        <v>81.04000000000001</v>
+      <c r="M50" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="N50" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="O50" t="n">
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2474,22 +2933,31 @@
         <v>344</v>
       </c>
       <c r="G51" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H51" t="n">
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
+        <v>28</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L51" t="n">
         <v>47.74</v>
       </c>
-      <c r="J51" t="n">
-        <v>79.84999999999999</v>
-      </c>
-      <c r="K51" t="n">
-        <v>73.97</v>
-      </c>
-      <c r="L51" t="n">
-        <v>62.75</v>
+      <c r="M51" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="N51" t="n">
+        <v>73.87</v>
+      </c>
+      <c r="O51" t="n">
+        <v>62.67</v>
       </c>
     </row>
     <row r="52">
@@ -2514,22 +2982,31 @@
         <v>531</v>
       </c>
       <c r="G52" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H52" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="I52" t="n">
+        <v>43</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L52" t="n">
         <v>46.96</v>
       </c>
-      <c r="J52" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="K52" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="L52" t="n">
-        <v>67.02</v>
+      <c r="M52" t="n">
+        <v>80.63</v>
+      </c>
+      <c r="N52" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="O52" t="n">
+        <v>66.93000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2560,16 +3037,25 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
         <v>43.65</v>
       </c>
-      <c r="J53" t="n">
-        <v>77.59</v>
-      </c>
-      <c r="K53" t="n">
-        <v>65.02</v>
-      </c>
-      <c r="L53" t="n">
-        <v>49.93</v>
+      <c r="M53" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="N53" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="O53" t="n">
+        <v>49.87</v>
       </c>
     </row>
     <row r="54">
@@ -2594,22 +3080,31 @@
         <v>196</v>
       </c>
       <c r="G54" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H54" t="n">
         <v>0.36</v>
       </c>
       <c r="I54" t="n">
+        <v>20</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L54" t="n">
         <v>41.93</v>
       </c>
-      <c r="J54" t="n">
-        <v>77.56999999999999</v>
-      </c>
-      <c r="K54" t="n">
-        <v>73.16</v>
-      </c>
-      <c r="L54" t="n">
-        <v>55.27</v>
+      <c r="M54" t="n">
+        <v>77.47</v>
+      </c>
+      <c r="N54" t="n">
+        <v>73.06999999999999</v>
+      </c>
+      <c r="O54" t="n">
+        <v>55.2</v>
       </c>
     </row>
     <row r="55">
@@ -2631,7 +3126,7 @@
         <v>4.03</v>
       </c>
       <c r="F55" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G55" t="n">
         <v>377</v>
@@ -2640,16 +3135,25 @@
         <v>0.98</v>
       </c>
       <c r="I55" t="n">
+        <v>46</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L55" t="n">
         <v>43.74</v>
       </c>
-      <c r="J55" t="n">
-        <v>79.31</v>
-      </c>
-      <c r="K55" t="n">
-        <v>80.77</v>
-      </c>
-      <c r="L55" t="n">
-        <v>70.36</v>
+      <c r="M55" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="O55" t="n">
+        <v>70.27</v>
       </c>
     </row>
     <row r="56">
@@ -2674,22 +3178,31 @@
         <v>285</v>
       </c>
       <c r="G56" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H56" t="n">
         <v>0.62</v>
       </c>
       <c r="I56" t="n">
+        <v>45</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L56" t="n">
         <v>44.06</v>
       </c>
-      <c r="J56" t="n">
-        <v>77.97</v>
-      </c>
-      <c r="K56" t="n">
-        <v>81.31</v>
-      </c>
-      <c r="L56" t="n">
-        <v>70.89</v>
+      <c r="M56" t="n">
+        <v>77.87</v>
+      </c>
+      <c r="N56" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>70.8</v>
       </c>
     </row>
     <row r="57">
@@ -2711,25 +3224,34 @@
         <v>5.42</v>
       </c>
       <c r="F57" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G57" t="n">
         <v>102</v>
       </c>
       <c r="H57" t="n">
-        <v>6.34</v>
+        <v>6.35</v>
       </c>
       <c r="I57" t="n">
+        <v>37</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="L57" t="n">
         <v>44.22</v>
       </c>
-      <c r="J57" t="n">
-        <v>80.23999999999999</v>
-      </c>
-      <c r="K57" t="n">
-        <v>87.05</v>
-      </c>
-      <c r="L57" t="n">
-        <v>81.70999999999999</v>
+      <c r="M57" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="N57" t="n">
+        <v>86.93000000000001</v>
+      </c>
+      <c r="O57" t="n">
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2752,22 +3274,31 @@
         <v>156</v>
       </c>
       <c r="G58" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H58" t="n">
         <v>0.26</v>
       </c>
       <c r="I58" t="n">
+        <v>24</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L58" t="n">
         <v>40.1</v>
       </c>
-      <c r="J58" t="n">
-        <v>71.95999999999999</v>
-      </c>
-      <c r="K58" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="L58" t="n">
-        <v>62.22</v>
+      <c r="M58" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="N58" t="n">
+        <v>78</v>
+      </c>
+      <c r="O58" t="n">
+        <v>62.13</v>
       </c>
     </row>
     <row r="59">
@@ -2790,22 +3321,31 @@
         <v>237</v>
       </c>
       <c r="G59" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H59" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="I59" t="n">
+        <v>32</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L59" t="n">
         <v>42.63</v>
       </c>
-      <c r="J59" t="n">
-        <v>78.91</v>
-      </c>
-      <c r="K59" t="n">
-        <v>87.45</v>
-      </c>
-      <c r="L59" t="n">
-        <v>82.23999999999999</v>
+      <c r="M59" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="N59" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="O59" t="n">
+        <v>82.13</v>
       </c>
     </row>
     <row r="60">
@@ -2828,22 +3368,31 @@
         <v>496</v>
       </c>
       <c r="G60" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H60" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I60" t="n">
+        <v>34</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L60" t="n">
         <v>43.4</v>
       </c>
-      <c r="J60" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="K60" t="n">
-        <v>91.72</v>
-      </c>
-      <c r="L60" t="n">
-        <v>89.84999999999999</v>
+      <c r="M60" t="n">
+        <v>82</v>
+      </c>
+      <c r="N60" t="n">
+        <v>91.73</v>
+      </c>
+      <c r="O60" t="n">
+        <v>89.87</v>
       </c>
     </row>
     <row r="61">
@@ -2863,7 +3412,7 @@
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G61" t="n">
         <v>238</v>
@@ -2872,16 +3421,25 @@
         <v>2.14</v>
       </c>
       <c r="I61" t="n">
+        <v>32</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L61" t="n">
         <v>41.08</v>
       </c>
-      <c r="J61" t="n">
-        <v>81.58</v>
-      </c>
-      <c r="K61" t="n">
-        <v>93.45999999999999</v>
-      </c>
-      <c r="L61" t="n">
-        <v>92.52</v>
+      <c r="M61" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="N61" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="O61" t="n">
+        <v>92.53</v>
       </c>
     </row>
     <row r="62">
@@ -2904,22 +3462,31 @@
         <v>275</v>
       </c>
       <c r="G62" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H62" t="n">
         <v>0.58</v>
       </c>
       <c r="I62" t="n">
+        <v>42</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L62" t="n">
         <v>38.69</v>
       </c>
-      <c r="J62" t="n">
-        <v>76.77</v>
-      </c>
-      <c r="K62" t="n">
-        <v>93.19</v>
-      </c>
-      <c r="L62" t="n">
-        <v>91.98999999999999</v>
+      <c r="M62" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="N62" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="O62" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="63">
@@ -2937,24 +3504,33 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G63" t="n">
         <v>167</v>
       </c>
       <c r="H63" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="I63" t="n">
+        <v>43</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="L63" t="n">
         <v>39.33</v>
       </c>
-      <c r="J63" t="n">
-        <v>79.04000000000001</v>
-      </c>
-      <c r="K63" t="n">
-        <v>95.19</v>
-      </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="N63" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="O63" t="n">
         <v>96.53</v>
       </c>
     </row>
@@ -2973,7 +3549,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G64" t="n">
         <v>243</v>
@@ -2982,16 +3558,25 @@
         <v>2.07</v>
       </c>
       <c r="I64" t="n">
+        <v>37</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="L64" t="n">
         <v>37.26</v>
       </c>
-      <c r="J64" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="K64" t="n">
-        <v>92.66</v>
-      </c>
-      <c r="L64" t="n">
-        <v>94.79000000000001</v>
+      <c r="M64" t="n">
+        <v>74.93000000000001</v>
+      </c>
+      <c r="N64" t="n">
+        <v>92.67</v>
+      </c>
+      <c r="O64" t="n">
+        <v>94.8</v>
       </c>
     </row>
     <row r="65">
@@ -3009,24 +3594,33 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G65" t="n">
         <v>67</v>
       </c>
       <c r="H65" t="n">
-        <v>10.16</v>
+        <v>10.18</v>
       </c>
       <c r="I65" t="n">
+        <v>32</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="L65" t="n">
         <v>34.71</v>
       </c>
-      <c r="J65" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="K65" t="n">
-        <v>93.86</v>
-      </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="N65" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="O65" t="n">
         <v>96.13</v>
       </c>
     </row>
@@ -3048,22 +3642,31 @@
         <v>244</v>
       </c>
       <c r="G66" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H66" t="n">
         <v>0.49</v>
       </c>
       <c r="I66" t="n">
+        <v>18</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L66" t="n">
         <v>31.26</v>
       </c>
-      <c r="J66" t="n">
-        <v>53</v>
-      </c>
-      <c r="K66" t="n">
-        <v>84.25</v>
-      </c>
-      <c r="L66" t="n">
-        <v>90.39</v>
+      <c r="M66" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N66" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O66" t="n">
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -3089,16 +3692,19 @@
       <c r="H67" t="n">
         <v>7.02</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
         <v>31.42</v>
       </c>
-      <c r="J67" t="n">
+      <c r="M67" t="n">
         <v>56.67</v>
       </c>
-      <c r="K67" t="n">
+      <c r="N67" t="n">
         <v>89.33</v>
       </c>
-      <c r="L67" t="n">
+      <c r="O67" t="n">
         <v>95.59999999999999</v>
       </c>
     </row>
@@ -3167,8 +3773,40 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L67">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="I2:I67">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="200"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J67">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="200"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K67">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:O67">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,24 +420,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,70 +450,80 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Nifty 500 Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Nifty 500 Chg %</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Up 4% Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Down 4% Today</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5 Day Ratio</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>10 Day Ratio</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Advances</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Declines</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A/D Ratio</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>52W Highs</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>52W Lows</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Volume Breadth</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>&gt; 200 SMA (%)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>&gt; 50 SMA (%)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>&gt; 20 EMA (%)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>&gt; 10 EMA (%)</t>
         </is>
@@ -516,46 +535,48 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
         <v>37</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>1.64</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>2.24</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>382</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>367</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>1.04</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>28</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.79</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>57.04</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>65.2</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>65.25</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>64.58</v>
       </c>
     </row>
@@ -565,46 +586,48 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
         <v>60</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>1.54</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>1.91</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>604</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>145</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>4.17</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>27</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>11.13</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>55.67</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>64.93000000000001</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>64.45</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>64.31</v>
       </c>
     </row>
@@ -614,46 +637,48 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
         <v>69</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>1.05</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>1.63</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>624</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>127</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>4.91</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>21</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>7.66</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>52.75</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>56.16</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>51.53</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>45.54</v>
       </c>
     </row>
@@ -663,46 +688,48 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
         <v>7</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>70</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>1.24</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>87</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>664</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.13</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>21</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>6</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.6</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>49.83</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>50</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>37.95</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>26.23</v>
       </c>
     </row>
@@ -712,46 +739,48 @@
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
         <v>12</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>27</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>2.27</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>1.86</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>242</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>505</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.48</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>26</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.62</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>56.36</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>60.81</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>58.19</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>51.8</v>
       </c>
     </row>
@@ -761,46 +790,48 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
         <v>29</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>3.5</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>2.06</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>364</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>386</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>40</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.52</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>57.14</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>63.66</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>65.65000000000001</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>63.65</v>
       </c>
     </row>
@@ -810,46 +841,48 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
         <v>17</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>17</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>2.45</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>2.34</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>354</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>395</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.9</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>40</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>1.44</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>56.97</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>65.02</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>66.84</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>66.18000000000001</v>
       </c>
     </row>
@@ -859,46 +892,48 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
         <v>55</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>2.87</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>2.77</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>537</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>212</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>2.53</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>24</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>2.03</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>56.63</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>64.56</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>69.73</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>68.67</v>
       </c>
     </row>
@@ -908,46 +943,48 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
         <v>48</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>13</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>1.76</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>2.49</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>417</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>333</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>1.25</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>29</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>11</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>3.41</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>53.01</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>60.21</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>61.47</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>57.07</v>
       </c>
     </row>
@@ -957,46 +994,48 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
         <v>40</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>1.47</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>2.73</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>444</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>305</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>1.46</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>27</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>15</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>1.73</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>51.98</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>58.11</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>57.87</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>50.13</v>
       </c>
     </row>
@@ -1006,46 +1045,48 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
         <v>29</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>33</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>1.04</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>2.7</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>278</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>471</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.59</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>25</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>12</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>1.84</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>50.43</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>55.86</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>50.13</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>41.33</v>
       </c>
     </row>
@@ -1055,23 +1096,19 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>2.16</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>4.71</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1086,15 +1123,21 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>52.67</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>59.91</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>60.27</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>50.8</v>
       </c>
     </row>
@@ -1104,46 +1147,48 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>18</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>2.66</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>6.86</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>249</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>500</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.5</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>19</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.55</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>52.5</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>60.06</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>60.27</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>50.8</v>
       </c>
     </row>
@@ -1153,46 +1198,48 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
         <v>27</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>13</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>3.69</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>6.54</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>388</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>362</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>1.07</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>19</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>1.08</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>53.01</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>62.46</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>63.73</v>
       </c>
     </row>
@@ -1202,46 +1249,48 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>12</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>5.4</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>4.93</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>181</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>569</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.32</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>30</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.27</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>53.36</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>61.86</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>69.33</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>64.13</v>
       </c>
     </row>
@@ -1251,46 +1300,48 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
         <v>47</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>6.9</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>6.03</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>497</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>253</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>1.96</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>28</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>2.09</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>55.59</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>68.47</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>79.2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>81.06999999999999</v>
       </c>
     </row>
@@ -1300,46 +1351,48 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
         <v>44</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>8</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>3.2</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>394</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>354</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>1.11</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>29</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>1.05</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>54.04</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>65.47</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>74</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>75.06999999999999</v>
       </c>
     </row>
@@ -1349,46 +1402,48 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
         <v>38</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>10</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>16.52</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>3.01</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>448</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>302</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>1.48</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>38</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>1.85</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>53.36</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>65.92</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>76.8</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>79.47</v>
       </c>
     </row>
@@ -1398,46 +1453,48 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
         <v>50</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>3</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>10.32</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>3.09</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>452</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>295</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>1.53</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>24</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>4.15</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>51.98</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>63.66</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>74.67</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>78.27</v>
       </c>
     </row>
@@ -1447,46 +1504,48 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
         <v>28</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>7</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>4.69</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>2.75</v>
       </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
         <v>435</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>314</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>1.39</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>23</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>1.26</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>50.43</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>61.86</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>73.47</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>79.2</v>
       </c>
     </row>
@@ -1496,46 +1555,48 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
         <v>96</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>5.62</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>2.83</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>574</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>175</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>3.28</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>30</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>5.84</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>49.83</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>59.91</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>70.27</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>79.06999999999999</v>
       </c>
     </row>
@@ -1545,46 +1606,48 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
         <v>168</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>1.9</v>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>691</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>58</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>11.91</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>33.39</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>46.72</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>50</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>53.07</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>61.2</v>
       </c>
     </row>
@@ -1594,46 +1657,48 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
         <v>9</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>21</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>0.85</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>1.09</v>
       </c>
-      <c r="F24" t="n">
+      <c r="H24" t="n">
         <v>174</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>575</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.3</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>8</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>21</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.74</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>39.14</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>38.44</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>27.73</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1643,46 +1708,48 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
         <v>13</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>36</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>1.23</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>1.14</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
         <v>160</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
         <v>590</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.27</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>23</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.18</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>43.28</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>44.29</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>36.27</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>30.67</v>
       </c>
     </row>
@@ -1692,46 +1759,48 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
         <v>68</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>1.6</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>1.38</v>
       </c>
-      <c r="F26" t="n">
+      <c r="H26" t="n">
         <v>597</v>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>152</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>3.93</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>21</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>6</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>1.9</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>45</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>51.05</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>43.87</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>43.2</v>
       </c>
     </row>
@@ -1741,46 +1810,48 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
         <v>8</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>72</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>1.37</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>1.22</v>
       </c>
-      <c r="F27" t="n">
+      <c r="H27" t="n">
         <v>103</v>
       </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>647</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.16</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>20</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>16</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.14</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>41.55</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>44.89</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>30.4</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>24.27</v>
       </c>
     </row>
@@ -1790,46 +1861,48 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
         <v>24</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>12</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>1.78</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>1.9</v>
       </c>
-      <c r="F28" t="n">
+      <c r="H28" t="n">
         <v>360</v>
       </c>
-      <c r="G28" t="n">
+      <c r="I28" t="n">
         <v>390</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.92</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>26</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>3</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>2.32</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>45</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>55.11</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>44.93</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>45.33</v>
       </c>
     </row>
@@ -1839,46 +1912,48 @@
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
         <v>49</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>9</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>1.32</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>1.9</v>
       </c>
-      <c r="F29" t="n">
+      <c r="H29" t="n">
         <v>399</v>
       </c>
-      <c r="G29" t="n">
+      <c r="I29" t="n">
         <v>351</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>1.14</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>28</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>2.31</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>44.91</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>57.06</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>45.47</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>43.2</v>
       </c>
     </row>
@@ -1888,46 +1963,48 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
         <v>32</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>17</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>1.06</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>1.86</v>
       </c>
-      <c r="F30" t="n">
+      <c r="H30" t="n">
         <v>308</v>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>441</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.7</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>21</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>10</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>2.04</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>43.87</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>57.36</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>43.2</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>37.73</v>
       </c>
     </row>
@@ -1937,46 +2014,48 @@
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
         <v>53</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>11</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>1.2</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>1.96</v>
       </c>
-      <c r="F31" t="n">
+      <c r="H31" t="n">
         <v>468</v>
       </c>
-      <c r="G31" t="n">
+      <c r="I31" t="n">
         <v>280</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>1.67</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>13</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>16</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>2.72</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>43.7</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>60.06</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>43.73</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1986,46 +2065,48 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
         <v>27</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>55</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>1.08</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>1.93</v>
       </c>
-      <c r="F32" t="n">
+      <c r="H32" t="n">
         <v>220</v>
       </c>
-      <c r="G32" t="n">
+      <c r="I32" t="n">
         <v>530</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.42</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>17</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>10</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.31</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>42.83</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>59.01</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>38</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>31.87</v>
       </c>
     </row>
@@ -2035,46 +2116,48 @@
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
         <v>41</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>61</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>2.02</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>1.85</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>210</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>540</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.39</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>38</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>10</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.51</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>44.04</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>66.37</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>47.6</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>42.13</v>
       </c>
     </row>
@@ -2084,46 +2167,48 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>3.73</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>2.11</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>47.67</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>72.52</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>61.33</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>60.67</v>
       </c>
     </row>
@@ -2133,46 +2218,48 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="1" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
         <v>51</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>16</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>3.98</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>2.15</v>
       </c>
-      <c r="F35" t="n">
+      <c r="H35" t="n">
         <v>390</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
         <v>358</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>1.09</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>41</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>3</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>4.35</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>47.75</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>73.27</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>61.33</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>60.67</v>
       </c>
     </row>
@@ -2182,46 +2269,48 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
         <v>37</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>12</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>4.3</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>2.12</v>
       </c>
-      <c r="F36" t="n">
+      <c r="H36" t="n">
         <v>362</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
         <v>386</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>27</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>1.98</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>46.97</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>73.87</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>62.13</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>63.47</v>
       </c>
     </row>
@@ -2231,46 +2320,48 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="1" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
         <v>65</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>7</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>4.64</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>0.9</v>
       </c>
-      <c r="F37" t="n">
+      <c r="H37" t="n">
         <v>567</v>
       </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>182</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>3.12</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>28</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>8.33</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>46.27</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>74.77</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>61.2</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>63.6</v>
       </c>
     </row>
@@ -2280,46 +2371,48 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="1" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
         <v>26</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>13</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>1.67</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="F38" t="n">
+      <c r="H38" t="n">
         <v>373</v>
       </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
         <v>373</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>20</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>2</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>2.48</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>44.19</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>68.17</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>48.8</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>46.93</v>
       </c>
     </row>
@@ -2329,46 +2422,48 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="1" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
         <v>36</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>6</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>1.41</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>0.71</v>
       </c>
-      <c r="F39" t="n">
+      <c r="H39" t="n">
         <v>445</v>
       </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
         <v>302</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>1.47</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>22</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>2</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>2.81</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>42.11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>68.62</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>48.13</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>45.73</v>
       </c>
     </row>
@@ -2378,46 +2473,48 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="1" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
         <v>34</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>8</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>1.34</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>0.76</v>
       </c>
-      <c r="F40" t="n">
+      <c r="H40" t="n">
         <v>366</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>382</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.96</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>16</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>5</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>2.65</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>41.25</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>66.81999999999999</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>42</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>38.13</v>
       </c>
     </row>
@@ -2427,46 +2524,48 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="1" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
         <v>48</v>
       </c>
-      <c r="C41" t="n">
+      <c r="E41" t="n">
         <v>11</v>
       </c>
-      <c r="D41" t="n">
+      <c r="F41" t="n">
         <v>1.33</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>0.91</v>
       </c>
-      <c r="F41" t="n">
+      <c r="H41" t="n">
         <v>493</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>256</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>1.93</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>14</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>4</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>2.38</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>41.42</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>67.12</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>40.93</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>34.4</v>
       </c>
     </row>
@@ -2476,46 +2575,48 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="1" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
         <v>15</v>
       </c>
-      <c r="C42" t="n">
+      <c r="E42" t="n">
         <v>57</v>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
         <v>0.39</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
         <v>0.86</v>
       </c>
-      <c r="F42" t="n">
+      <c r="H42" t="n">
         <v>164</v>
       </c>
-      <c r="G42" t="n">
+      <c r="I42" t="n">
         <v>585</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>0.28</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>7</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>15</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.29</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>39.86</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>65.02</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>32.53</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>23.33</v>
       </c>
     </row>
@@ -2525,46 +2626,48 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="1" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
         <v>24</v>
       </c>
-      <c r="C43" t="n">
+      <c r="E43" t="n">
         <v>29</v>
       </c>
-      <c r="D43" t="n">
+      <c r="F43" t="n">
         <v>0.41</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
         <v>1.11</v>
       </c>
-      <c r="F43" t="n">
+      <c r="H43" t="n">
         <v>256</v>
       </c>
-      <c r="G43" t="n">
+      <c r="I43" t="n">
         <v>494</v>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>0.52</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>21</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>4</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>0.92</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>44.37</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>71.17</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>42.27</v>
       </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
         <v>31.87</v>
       </c>
     </row>
@@ -2574,46 +2677,48 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="1" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
         <v>41</v>
       </c>
-      <c r="C44" t="n">
+      <c r="E44" t="n">
         <v>16</v>
       </c>
-      <c r="D44" t="n">
+      <c r="F44" t="n">
         <v>0.46</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
         <v>1.13</v>
       </c>
-      <c r="F44" t="n">
+      <c r="H44" t="n">
         <v>424</v>
       </c>
-      <c r="G44" t="n">
+      <c r="I44" t="n">
         <v>326</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>1.3</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>24</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>3.4</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>44.89</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>72.37</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>46.4</v>
       </c>
-      <c r="O44" t="n">
+      <c r="Q44" t="n">
         <v>35.47</v>
       </c>
     </row>
@@ -2623,46 +2728,48 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="1" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
         <v>41</v>
       </c>
-      <c r="C45" t="n">
+      <c r="E45" t="n">
         <v>14</v>
       </c>
-      <c r="D45" t="n">
+      <c r="F45" t="n">
         <v>0.54</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
         <v>1.05</v>
       </c>
-      <c r="F45" t="n">
+      <c r="H45" t="n">
         <v>449</v>
       </c>
-      <c r="G45" t="n">
+      <c r="I45" t="n">
         <v>298</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>1.51</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>13</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>3.9</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>43.33</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>71.31999999999999</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>43.73</v>
       </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
         <v>29.73</v>
       </c>
     </row>
@@ -2672,46 +2779,48 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="1" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
         <v>6</v>
       </c>
-      <c r="C46" t="n">
+      <c r="E46" t="n">
         <v>212</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>0.74</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
         <v>1.01</v>
       </c>
-      <c r="F46" t="n">
+      <c r="H46" t="n">
         <v>54</v>
       </c>
-      <c r="G46" t="n">
+      <c r="I46" t="n">
         <v>696</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>0.08</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>14</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>8</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>0.12</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>42.29</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>70.27</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>37.73</v>
       </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
         <v>22.93</v>
       </c>
     </row>
@@ -2721,46 +2830,48 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="1" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
         <v>26</v>
       </c>
-      <c r="C47" t="n">
+      <c r="E47" t="n">
         <v>65</v>
       </c>
-      <c r="D47" t="n">
+      <c r="F47" t="n">
         <v>2.25</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
         <v>2.28</v>
       </c>
-      <c r="F47" t="n">
+      <c r="H47" t="n">
         <v>188</v>
       </c>
-      <c r="G47" t="n">
+      <c r="I47" t="n">
         <v>561</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>0.34</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>29</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>0</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>0.88</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>50</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>82.43000000000001</v>
       </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="O47" t="n">
+      <c r="Q47" t="n">
         <v>50.53</v>
       </c>
     </row>
@@ -2770,46 +2881,48 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="1" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
         <v>36</v>
       </c>
-      <c r="C48" t="n">
+      <c r="E48" t="n">
         <v>17</v>
       </c>
-      <c r="D48" t="n">
+      <c r="F48" t="n">
         <v>4.87</v>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
         <v>4.32</v>
       </c>
-      <c r="F48" t="n">
+      <c r="H48" t="n">
         <v>324</v>
       </c>
-      <c r="G48" t="n">
+      <c r="I48" t="n">
         <v>425</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>0.76</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>44</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>1.53</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>54.86</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>87.23999999999999</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>82.27</v>
       </c>
-      <c r="O48" t="n">
+      <c r="Q48" t="n">
         <v>73.47</v>
       </c>
     </row>
@@ -2819,46 +2932,48 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="1" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
         <v>63</v>
       </c>
-      <c r="C49" t="n">
+      <c r="E49" t="n">
         <v>8</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>5.91</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
         <v>3.35</v>
       </c>
-      <c r="F49" t="n">
+      <c r="H49" t="n">
         <v>499</v>
       </c>
-      <c r="G49" t="n">
+      <c r="I49" t="n">
         <v>250</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>2</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>45</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>1.69</v>
       </c>
-      <c r="L49" t="n">
+      <c r="N49" t="n">
         <v>56.6</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>87.98999999999999</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>87.87</v>
       </c>
-      <c r="O49" t="n">
+      <c r="Q49" t="n">
         <v>82.67</v>
       </c>
     </row>
@@ -2868,46 +2983,48 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
         <v>96</v>
       </c>
-      <c r="C50" t="n">
+      <c r="E50" t="n">
         <v>6</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
         <v>3.68</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
         <v>2.92</v>
       </c>
-      <c r="F50" t="n">
+      <c r="H50" t="n">
         <v>605</v>
       </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
         <v>145</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>4.17</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>38</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>6.12</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>52.6</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>86.94</v>
       </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
         <v>86.8</v>
       </c>
-      <c r="O50" t="n">
+      <c r="Q50" t="n">
         <v>80.93000000000001</v>
       </c>
     </row>
@@ -2917,46 +3034,48 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
         <v>29</v>
       </c>
-      <c r="C51" t="n">
+      <c r="E51" t="n">
         <v>15</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
         <v>2.22</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
         <v>2.66</v>
       </c>
-      <c r="F51" t="n">
+      <c r="H51" t="n">
         <v>344</v>
       </c>
-      <c r="G51" t="n">
+      <c r="I51" t="n">
         <v>404</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>0.85</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>28</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>1.86</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>47.74</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>79.73</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>73.87</v>
       </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
         <v>62.67</v>
       </c>
     </row>
@@ -2966,46 +3085,48 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
         <v>78</v>
       </c>
-      <c r="C52" t="n">
+      <c r="E52" t="n">
         <v>16</v>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
         <v>2.33</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>3.02</v>
       </c>
-      <c r="F52" t="n">
+      <c r="H52" t="n">
         <v>531</v>
       </c>
-      <c r="G52" t="n">
+      <c r="I52" t="n">
         <v>218</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>2.44</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>43</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>2</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>2.58</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>46.96</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>80.63</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>77.2</v>
       </c>
-      <c r="O52" t="n">
+      <c r="Q52" t="n">
         <v>66.93000000000001</v>
       </c>
     </row>
@@ -3015,23 +3136,19 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
         <v>0</v>
       </c>
-      <c r="C53" t="n">
+      <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
         <v>3.64</v>
       </c>
-      <c r="E53" t="n">
+      <c r="G53" t="n">
         <v>2.68</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3046,15 +3163,21 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
         <v>43.65</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>77.48</v>
       </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
         <v>64.93000000000001</v>
       </c>
-      <c r="O53" t="n">
+      <c r="Q53" t="n">
         <v>49.87</v>
       </c>
     </row>
@@ -3064,46 +3187,48 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
         <v>18</v>
       </c>
-      <c r="C54" t="n">
+      <c r="E54" t="n">
         <v>23</v>
       </c>
-      <c r="D54" t="n">
+      <c r="F54" t="n">
         <v>2.08</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>3.14</v>
       </c>
-      <c r="F54" t="n">
+      <c r="H54" t="n">
         <v>196</v>
       </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
         <v>552</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>0.36</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>20</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>3</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>0.54</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>41.93</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>77.47</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>73.06999999999999</v>
       </c>
-      <c r="O54" t="n">
+      <c r="Q54" t="n">
         <v>55.2</v>
       </c>
     </row>
@@ -3113,46 +3238,48 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="1" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
         <v>26</v>
       </c>
-      <c r="C55" t="n">
+      <c r="E55" t="n">
         <v>14</v>
       </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
         <v>2.38</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
         <v>4.03</v>
       </c>
-      <c r="F55" t="n">
+      <c r="H55" t="n">
         <v>371</v>
       </c>
-      <c r="G55" t="n">
+      <c r="I55" t="n">
         <v>377</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>0.98</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>46</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>1</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>2.06</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>43.74</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>79.2</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>80.67</v>
       </c>
-      <c r="O55" t="n">
+      <c r="Q55" t="n">
         <v>70.27</v>
       </c>
     </row>
@@ -3162,46 +3289,48 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="1" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
         <v>27</v>
       </c>
-      <c r="C56" t="n">
+      <c r="E56" t="n">
         <v>11</v>
       </c>
-      <c r="D56" t="n">
+      <c r="F56" t="n">
         <v>3.02</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
         <v>5.64</v>
       </c>
-      <c r="F56" t="n">
+      <c r="H56" t="n">
         <v>285</v>
       </c>
-      <c r="G56" t="n">
+      <c r="I56" t="n">
         <v>463</v>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>0.62</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>45</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>1.94</v>
       </c>
-      <c r="L56" t="n">
+      <c r="N56" t="n">
         <v>44.06</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>77.87</v>
       </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
         <v>81.2</v>
       </c>
-      <c r="O56" t="n">
+      <c r="Q56" t="n">
         <v>70.8</v>
       </c>
     </row>
@@ -3211,46 +3340,48 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="1" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="n">
         <v>111</v>
       </c>
-      <c r="C57" t="n">
+      <c r="E57" t="n">
         <v>2</v>
       </c>
-      <c r="D57" t="n">
+      <c r="F57" t="n">
         <v>3.62</v>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
         <v>5.42</v>
       </c>
-      <c r="F57" t="n">
+      <c r="H57" t="n">
         <v>648</v>
       </c>
-      <c r="G57" t="n">
+      <c r="I57" t="n">
         <v>102</v>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>6.35</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>37</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>0</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>8.17</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>44.22</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>80.13</v>
       </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
         <v>86.93000000000001</v>
       </c>
-      <c r="O57" t="n">
+      <c r="Q57" t="n">
         <v>81.59999999999999</v>
       </c>
     </row>
@@ -3260,44 +3391,46 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="1" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
         <v>7</v>
       </c>
-      <c r="C58" t="n">
+      <c r="E58" t="n">
         <v>41</v>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
         <v>2.12</v>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="n">
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
         <v>156</v>
       </c>
-      <c r="G58" t="n">
+      <c r="I58" t="n">
         <v>590</v>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>0.26</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>24</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>3</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>0.37</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>40.1</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>71.87</v>
       </c>
-      <c r="N58" t="n">
+      <c r="P58" t="n">
         <v>78</v>
       </c>
-      <c r="O58" t="n">
+      <c r="Q58" t="n">
         <v>62.13</v>
       </c>
     </row>
@@ -3307,44 +3440,46 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="1" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="n">
         <v>31</v>
       </c>
-      <c r="C59" t="n">
+      <c r="E59" t="n">
         <v>17</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>5.24</v>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="n">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
         <v>237</v>
       </c>
-      <c r="G59" t="n">
+      <c r="I59" t="n">
         <v>510</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>0.46</v>
       </c>
-      <c r="I59" t="n">
+      <c r="K59" t="n">
         <v>32</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
         <v>0.66</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>42.63</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>78.8</v>
       </c>
-      <c r="N59" t="n">
+      <c r="P59" t="n">
         <v>87.33</v>
       </c>
-      <c r="O59" t="n">
+      <c r="Q59" t="n">
         <v>82.13</v>
       </c>
     </row>
@@ -3354,44 +3489,46 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="1" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
         <v>66</v>
       </c>
-      <c r="C60" t="n">
+      <c r="E60" t="n">
         <v>9</v>
       </c>
-      <c r="D60" t="n">
+      <c r="F60" t="n">
         <v>8.58</v>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="n">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
         <v>496</v>
       </c>
-      <c r="G60" t="n">
+      <c r="I60" t="n">
         <v>250</v>
       </c>
-      <c r="H60" t="n">
+      <c r="J60" t="n">
         <v>1.98</v>
       </c>
-      <c r="I60" t="n">
+      <c r="K60" t="n">
         <v>34</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
         <v>2.88</v>
       </c>
-      <c r="L60" t="n">
+      <c r="N60" t="n">
         <v>43.4</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>82</v>
       </c>
-      <c r="N60" t="n">
+      <c r="P60" t="n">
         <v>91.73</v>
       </c>
-      <c r="O60" t="n">
+      <c r="Q60" t="n">
         <v>89.87</v>
       </c>
     </row>
@@ -3401,44 +3538,46 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="1" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="n">
         <v>53</v>
       </c>
-      <c r="C61" t="n">
+      <c r="E61" t="n">
         <v>5</v>
       </c>
-      <c r="D61" t="n">
+      <c r="F61" t="n">
         <v>13.69</v>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="n">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
         <v>510</v>
       </c>
-      <c r="G61" t="n">
+      <c r="I61" t="n">
         <v>238</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>2.14</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>32</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>0</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
         <v>2.82</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>41.08</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="N61" t="n">
+      <c r="P61" t="n">
         <v>93.47</v>
       </c>
-      <c r="O61" t="n">
+      <c r="Q61" t="n">
         <v>92.53</v>
       </c>
     </row>
@@ -3448,44 +3587,46 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="1" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="n">
         <v>23</v>
       </c>
-      <c r="C62" t="n">
+      <c r="E62" t="n">
         <v>13</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="n">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="n">
         <v>275</v>
       </c>
-      <c r="G62" t="n">
+      <c r="I62" t="n">
         <v>475</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>0.58</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>42</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>0</v>
       </c>
-      <c r="K62" t="n">
+      <c r="M62" t="n">
         <v>0.53</v>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>38.69</v>
       </c>
-      <c r="M62" t="n">
+      <c r="O62" t="n">
         <v>76.8</v>
       </c>
-      <c r="N62" t="n">
+      <c r="P62" t="n">
         <v>93.2</v>
       </c>
-      <c r="O62" t="n">
+      <c r="Q62" t="n">
         <v>92</v>
       </c>
     </row>
@@ -3495,42 +3636,44 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="1" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="n">
         <v>68</v>
       </c>
-      <c r="C63" t="n">
+      <c r="E63" t="n">
         <v>2</v>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="n">
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="n">
         <v>581</v>
       </c>
-      <c r="G63" t="n">
+      <c r="I63" t="n">
         <v>167</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>3.48</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>43</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>0</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
         <v>4.48</v>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>39.33</v>
       </c>
-      <c r="M63" t="n">
+      <c r="O63" t="n">
         <v>79.06999999999999</v>
       </c>
-      <c r="N63" t="n">
+      <c r="P63" t="n">
         <v>95.2</v>
       </c>
-      <c r="O63" t="n">
+      <c r="Q63" t="n">
         <v>96.53</v>
       </c>
     </row>
@@ -3540,42 +3683,44 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="1" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="n">
         <v>56</v>
       </c>
-      <c r="C64" t="n">
+      <c r="E64" t="n">
         <v>2</v>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="n">
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="n">
         <v>504</v>
       </c>
-      <c r="G64" t="n">
+      <c r="I64" t="n">
         <v>243</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>2.07</v>
       </c>
-      <c r="I64" t="n">
+      <c r="K64" t="n">
         <v>37</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>0</v>
       </c>
-      <c r="K64" t="n">
+      <c r="M64" t="n">
         <v>3.43</v>
       </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
         <v>37.26</v>
       </c>
-      <c r="M64" t="n">
+      <c r="O64" t="n">
         <v>74.93000000000001</v>
       </c>
-      <c r="N64" t="n">
+      <c r="P64" t="n">
         <v>92.67</v>
       </c>
-      <c r="O64" t="n">
+      <c r="Q64" t="n">
         <v>94.8</v>
       </c>
     </row>
@@ -3585,42 +3730,44 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="1" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="n">
         <v>156</v>
       </c>
-      <c r="C65" t="n">
+      <c r="E65" t="n">
         <v>4</v>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="n">
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="n">
         <v>682</v>
       </c>
-      <c r="G65" t="n">
+      <c r="I65" t="n">
         <v>67</v>
       </c>
-      <c r="H65" t="n">
+      <c r="J65" t="n">
         <v>10.18</v>
       </c>
-      <c r="I65" t="n">
+      <c r="K65" t="n">
         <v>32</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>0</v>
       </c>
-      <c r="K65" t="n">
+      <c r="M65" t="n">
         <v>17.31</v>
       </c>
-      <c r="L65" t="n">
+      <c r="N65" t="n">
         <v>34.71</v>
       </c>
-      <c r="M65" t="n">
+      <c r="O65" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="N65" t="n">
+      <c r="P65" t="n">
         <v>93.87</v>
       </c>
-      <c r="O65" t="n">
+      <c r="Q65" t="n">
         <v>96.13</v>
       </c>
     </row>
@@ -3630,42 +3777,44 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="1" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="n">
         <v>25</v>
       </c>
-      <c r="C66" t="n">
+      <c r="E66" t="n">
         <v>15</v>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="n">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
         <v>244</v>
       </c>
-      <c r="G66" t="n">
+      <c r="I66" t="n">
         <v>501</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>0.49</v>
       </c>
-      <c r="I66" t="n">
+      <c r="K66" t="n">
         <v>18</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>2</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
         <v>0.75</v>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>31.26</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O66" t="n">
         <v>52.93</v>
       </c>
-      <c r="N66" t="n">
+      <c r="P66" t="n">
         <v>84.27</v>
       </c>
-      <c r="O66" t="n">
+      <c r="Q66" t="n">
         <v>90.40000000000001</v>
       </c>
     </row>
@@ -3675,42 +3824,56 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="1" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="n">
         <v>82</v>
       </c>
-      <c r="C67" t="n">
+      <c r="E67" t="n">
         <v>2</v>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="n">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
         <v>653</v>
       </c>
-      <c r="G67" t="n">
+      <c r="I67" t="n">
         <v>93</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>7.02</v>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
         <v>31.42</v>
       </c>
-      <c r="M67" t="n">
+      <c r="O67" t="n">
         <v>56.67</v>
       </c>
-      <c r="N67" t="n">
+      <c r="P67" t="n">
         <v>89.33</v>
       </c>
-      <c r="O67" t="n">
+      <c r="Q67" t="n">
         <v>95.59999999999999</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B67">
+  <conditionalFormatting sqref="C2:C67">
     <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="-2"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D67">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="200"/>
@@ -3719,8 +3882,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C67">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="E2:E67">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="200"/>
@@ -3729,8 +3892,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E67">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="F2:G67">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
@@ -3741,8 +3904,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F67">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="H2:H67">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="750"/>
@@ -3751,8 +3914,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G67">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="I2:I67">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="750"/>
@@ -3761,8 +3924,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H67">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="J2:J67">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
@@ -3773,8 +3936,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I67">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="K2:K67">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="200"/>
@@ -3783,8 +3946,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J67">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="L2:L67">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="200"/>
@@ -3793,8 +3956,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K67">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="M2:M67">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
@@ -3805,8 +3968,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O67">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="N2:Q67">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="50"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,17 +26,305 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="51">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D2"/>
+        <bgColor rgb="00C9E8D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF7EF"/>
+        <bgColor rgb="00ECF7EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFDFD"/>
+        <bgColor rgb="00FEFDFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C7E7CF"/>
+        <bgColor rgb="00C7E7CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BEE4C8"/>
+        <bgColor rgb="00BEE4C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFEBD7"/>
+        <bgColor rgb="00CFEBD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDB"/>
+        <bgColor rgb="00D4EDDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5EB"/>
+        <bgColor rgb="00E8F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FBF8"/>
+        <bgColor rgb="00F7FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6FBF8"/>
+        <bgColor rgb="00F6FBF8"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5FAF6"/>
+        <bgColor rgb="00F5FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F3E8"/>
+        <bgColor rgb="00E4F3E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E1"/>
+        <bgColor rgb="00DCF0E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFCFC"/>
+        <bgColor rgb="00FEFCFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEAEA"/>
+        <bgColor rgb="00FEEAEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCCBCC"/>
+        <bgColor rgb="00FCCBCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCD3D3"/>
+        <bgColor rgb="00FCD3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDBDC"/>
+        <bgColor rgb="00FDDBDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCCFD0"/>
+        <bgColor rgb="00FCCFD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE1E2"/>
+        <bgColor rgb="00FDE1E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE3E4"/>
+        <bgColor rgb="00FDE3E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE0E1"/>
+        <bgColor rgb="00FDE0E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE5E5"/>
+        <bgColor rgb="00FDE5E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDFE0"/>
+        <bgColor rgb="00FDDFE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEDED"/>
+        <bgColor rgb="00FEEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFDFB"/>
+        <bgColor rgb="00FAFDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFEFE"/>
+        <bgColor rgb="00FEFEFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE1E1"/>
+        <bgColor rgb="00FDE1E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE5E6"/>
+        <bgColor rgb="00FDE5E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEAEB"/>
+        <bgColor rgb="00FEEAEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDCDC"/>
+        <bgColor rgb="00FDDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDD7D7"/>
+        <bgColor rgb="00FDD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF6F6"/>
+        <bgColor rgb="00FEF6F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7F5EB"/>
+        <bgColor rgb="00E7F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBF0E0"/>
+        <bgColor rgb="00DBF0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5F4E9"/>
+        <bgColor rgb="00E5F4E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF7F7"/>
+        <bgColor rgb="00FEF7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF8F8"/>
+        <bgColor rgb="00FEF8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEFEF"/>
+        <bgColor rgb="00FEEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFAFB"/>
+        <bgColor rgb="00FEFAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF4F4"/>
+        <bgColor rgb="00FEF4F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FCF8"/>
+        <bgColor rgb="00F7FCF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F9F3"/>
+        <bgColor rgb="00F1F9F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFAFA"/>
+        <bgColor rgb="00FEFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE9EA"/>
+        <bgColor rgb="00FEE9EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDADA"/>
+        <bgColor rgb="00FDDADA"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +340,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -535,8 +871,12 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" s="1" t="n">
+        <v>23347.05</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.01</v>
+      </c>
       <c r="D2" t="n">
         <v>37</v>
       </c>
@@ -586,8 +926,12 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" s="1" t="n">
+        <v>23348.4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.16</v>
+      </c>
       <c r="D3" t="n">
         <v>60</v>
       </c>
@@ -637,8 +981,12 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" s="2" t="n">
+        <v>23081.15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.76</v>
+      </c>
       <c r="D4" t="n">
         <v>69</v>
       </c>
@@ -688,8 +1036,12 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" s="3" t="n">
+        <v>22908.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.97</v>
+      </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
@@ -739,8 +1091,12 @@
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" s="4" t="n">
+        <v>23368.85</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.28</v>
+      </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
@@ -790,8 +1146,12 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" s="5" t="n">
+        <v>23433.95</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.57</v>
+      </c>
       <c r="D7" t="n">
         <v>29</v>
       </c>
@@ -841,8 +1201,12 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="B8" s="6" t="n">
+        <v>23301.15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.16</v>
+      </c>
       <c r="D8" t="n">
         <v>17</v>
       </c>
@@ -892,8 +1256,12 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" s="7" t="n">
+        <v>23264.8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.66</v>
+      </c>
       <c r="D9" t="n">
         <v>55</v>
       </c>
@@ -943,8 +1311,12 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" s="8" t="n">
+        <v>23111.65</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D10" t="n">
         <v>48</v>
       </c>
@@ -994,8 +1366,12 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" s="9" t="n">
+        <v>22995.65</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="D11" t="n">
         <v>40</v>
       </c>
@@ -1045,8 +1421,12 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" s="10" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.49</v>
+      </c>
       <c r="D12" t="n">
         <v>29</v>
       </c>
@@ -1096,7 +1476,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
+      <c r="B13" s="11" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>0</v>
@@ -1147,8 +1527,12 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" s="8" t="n">
+        <v>23113.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="D14" t="n">
         <v>13</v>
       </c>
@@ -1198,8 +1582,12 @@
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" s="12" t="n">
+        <v>23126.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D15" t="n">
         <v>27</v>
       </c>
@@ -1249,8 +1637,12 @@
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" s="13" t="n">
+        <v>23010.95</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.08</v>
+      </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
@@ -1300,8 +1692,12 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" s="7" t="n">
+        <v>23261.85</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.51</v>
+      </c>
       <c r="D17" t="n">
         <v>47</v>
       </c>
@@ -1351,8 +1747,12 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" s="14" t="n">
+        <v>23144.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.27</v>
+      </c>
       <c r="D18" t="n">
         <v>44</v>
       </c>
@@ -1402,8 +1802,12 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" s="15" t="n">
+        <v>23206.45</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.42</v>
+      </c>
       <c r="D19" t="n">
         <v>38</v>
       </c>
@@ -1453,8 +1857,12 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" s="8" t="n">
+        <v>23109.7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.49</v>
+      </c>
       <c r="D20" t="n">
         <v>50</v>
       </c>
@@ -1504,8 +1912,12 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="B21" s="9" t="n">
+        <v>22997.25</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.46</v>
+      </c>
       <c r="D21" t="n">
         <v>28</v>
       </c>
@@ -1555,8 +1967,12 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="B22" s="16" t="n">
+        <v>22891.3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.29</v>
+      </c>
       <c r="D22" t="n">
         <v>96</v>
       </c>
@@ -1606,8 +2022,12 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" s="17" t="n">
+        <v>22599.8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.19</v>
+      </c>
       <c r="D23" t="n">
         <v>168</v>
       </c>
@@ -1657,8 +2077,12 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="B24" s="18" t="n">
+        <v>22114.45</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.54</v>
+      </c>
       <c r="D24" t="n">
         <v>9</v>
       </c>
@@ -1708,8 +2132,12 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="B25" s="19" t="n">
+        <v>22233.85</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.61</v>
+      </c>
       <c r="D25" t="n">
         <v>13</v>
       </c>
@@ -1759,8 +2187,12 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="B26" s="20" t="n">
+        <v>22370.15</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.89</v>
+      </c>
       <c r="D26" t="n">
         <v>68</v>
       </c>
@@ -1810,8 +2242,12 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="B27" s="21" t="n">
+        <v>22173.7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.3</v>
+      </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
@@ -1861,8 +2297,12 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="B28" s="22" t="n">
+        <v>22465.35</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="D28" t="n">
         <v>24</v>
       </c>
@@ -1912,8 +2352,12 @@
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="B29" s="23" t="n">
+        <v>22497.7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.2</v>
+      </c>
       <c r="D29" t="n">
         <v>49</v>
       </c>
@@ -1963,8 +2407,12 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="B30" s="24" t="n">
+        <v>22451.85</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.31</v>
+      </c>
       <c r="D30" t="n">
         <v>32</v>
       </c>
@@ -2014,8 +2462,12 @@
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="B31" s="25" t="n">
+        <v>22521.1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.37</v>
+      </c>
       <c r="D31" t="n">
         <v>53</v>
       </c>
@@ -2065,8 +2517,12 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="B32" s="26" t="n">
+        <v>22437.95</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.97</v>
+      </c>
       <c r="D32" t="n">
         <v>27</v>
       </c>
@@ -2116,8 +2572,12 @@
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="B33" s="27" t="n">
+        <v>22657</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.35</v>
+      </c>
       <c r="D33" t="n">
         <v>41</v>
       </c>
@@ -2167,7 +2627,7 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr"/>
+      <c r="B34" s="11" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
         <v>0</v>
@@ -2218,8 +2678,12 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="B35" s="28" t="n">
+        <v>22967.4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.31</v>
+      </c>
       <c r="D35" t="n">
         <v>51</v>
       </c>
@@ -2269,8 +2733,12 @@
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+      <c r="B36" s="16" t="n">
+        <v>22897.2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="D36" t="n">
         <v>37</v>
       </c>
@@ -2320,8 +2788,12 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="B37" s="29" t="n">
+        <v>22929.45</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.23</v>
+      </c>
       <c r="D37" t="n">
         <v>65</v>
       </c>
@@ -2371,8 +2843,12 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="B38" s="27" t="n">
+        <v>22651.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.21</v>
+      </c>
       <c r="D38" t="n">
         <v>26</v>
       </c>
@@ -2422,8 +2898,12 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="B39" s="17" t="n">
+        <v>22602.85</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.11</v>
+      </c>
       <c r="D39" t="n">
         <v>36</v>
       </c>
@@ -2473,8 +2953,12 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="B40" s="30" t="n">
+        <v>22578.15</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.25</v>
+      </c>
       <c r="D40" t="n">
         <v>34</v>
       </c>
@@ -2524,8 +3008,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="B41" s="25" t="n">
+        <v>22521.75</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.27</v>
+      </c>
       <c r="D41" t="n">
         <v>48</v>
       </c>
@@ -2575,8 +3063,12 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="B42" s="31" t="n">
+        <v>22461.05</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.31</v>
+      </c>
       <c r="D42" t="n">
         <v>15</v>
       </c>
@@ -2626,8 +3118,12 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+      <c r="B43" s="32" t="n">
+        <v>22531.15</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.36</v>
+      </c>
       <c r="D43" t="n">
         <v>24</v>
       </c>
@@ -2677,8 +3173,12 @@
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="B44" s="33" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.05</v>
+      </c>
       <c r="D44" t="n">
         <v>41</v>
       </c>
@@ -2728,8 +3228,12 @@
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+      <c r="B45" s="34" t="n">
+        <v>22377.35</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.35</v>
+      </c>
       <c r="D45" t="n">
         <v>41</v>
       </c>
@@ -2779,8 +3283,12 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="B46" s="35" t="n">
+        <v>22299.9</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-2.18</v>
+      </c>
       <c r="D46" t="n">
         <v>6</v>
       </c>
@@ -2830,8 +3338,12 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+      <c r="B47" s="36" t="n">
+        <v>22795.75</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.38</v>
+      </c>
       <c r="D47" t="n">
         <v>26</v>
       </c>
@@ -2881,8 +3393,12 @@
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+      <c r="B48" s="37" t="n">
+        <v>23115.65</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.42</v>
+      </c>
       <c r="D48" t="n">
         <v>36</v>
       </c>
@@ -2932,8 +3448,12 @@
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+      <c r="B49" s="38" t="n">
+        <v>23214</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.35</v>
+      </c>
       <c r="D49" t="n">
         <v>63</v>
       </c>
@@ -2983,8 +3503,12 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+      <c r="B50" s="39" t="n">
+        <v>23133.4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.43</v>
+      </c>
       <c r="D50" t="n">
         <v>96</v>
       </c>
@@ -3034,8 +3558,12 @@
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+      <c r="B51" s="40" t="n">
+        <v>22808.25</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="D51" t="n">
         <v>29</v>
       </c>
@@ -3085,8 +3613,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+      <c r="B52" s="41" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.65</v>
+      </c>
       <c r="D52" t="n">
         <v>78</v>
       </c>
@@ -3136,7 +3668,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr"/>
+      <c r="B53" s="11" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
         <v>0</v>
@@ -3187,8 +3719,12 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+      <c r="B54" s="42" t="n">
+        <v>22683.55</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.82</v>
+      </c>
       <c r="D54" t="n">
         <v>18</v>
       </c>
@@ -3238,8 +3774,12 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+      <c r="B55" s="43" t="n">
+        <v>22871</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.46</v>
+      </c>
       <c r="D55" t="n">
         <v>26</v>
       </c>
@@ -3289,8 +3829,12 @@
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+      <c r="B56" s="44" t="n">
+        <v>22765.6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.24</v>
+      </c>
       <c r="D56" t="n">
         <v>27</v>
       </c>
@@ -3340,8 +3884,12 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+      <c r="B57" s="40" t="n">
+        <v>22821.4</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1.11</v>
+      </c>
       <c r="D57" t="n">
         <v>111</v>
       </c>
@@ -3391,8 +3939,12 @@
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" s="30" t="n">
+        <v>22570.05</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.06</v>
+      </c>
       <c r="D58" t="n">
         <v>7</v>
       </c>
@@ -3440,8 +3992,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+      <c r="B59" s="40" t="n">
+        <v>22810.85</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.79</v>
+      </c>
       <c r="D59" t="n">
         <v>31</v>
       </c>
@@ -3489,8 +4045,12 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
+      <c r="B60" s="45" t="n">
+        <v>22991.5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.22</v>
+      </c>
       <c r="D60" t="n">
         <v>66</v>
       </c>
@@ -3538,8 +4098,12 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+      <c r="B61" s="46" t="n">
+        <v>23042.35</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.77</v>
+      </c>
       <c r="D61" t="n">
         <v>53</v>
       </c>
@@ -3587,8 +4151,12 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+      <c r="B62" s="47" t="n">
+        <v>22865.8</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="D62" t="n">
         <v>23</v>
       </c>
@@ -3636,8 +4204,12 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
+      <c r="B63" s="47" t="n">
+        <v>22869.4</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="D63" t="n">
         <v>68</v>
       </c>
@@ -3683,8 +4255,12 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+      <c r="B64" s="27" t="n">
+        <v>22656.3</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.27</v>
+      </c>
       <c r="D64" t="n">
         <v>56</v>
       </c>
@@ -3730,8 +4306,12 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
+      <c r="B65" s="48" t="n">
+        <v>22595.55</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1.88</v>
+      </c>
       <c r="D65" t="n">
         <v>156</v>
       </c>
@@ -3777,8 +4357,12 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
+      <c r="B66" s="21" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="D66" t="n">
         <v>25</v>
       </c>
@@ -3824,8 +4408,12 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
+      <c r="B67" s="49" t="n">
+        <v>22346.75</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1.4</v>
+      </c>
       <c r="D67" t="n">
         <v>82</v>
       </c>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="51">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E2"/>
+        <bgColor rgb="00DCF0E2"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -340,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -490,6 +496,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -857,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -969,700 +978,704 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>382</v>
+        <v>171</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>367</v>
+        <v>579</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>57.04</v>
+        <v>56.7</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>65.2</v>
+        <v>61.33</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>65.25</v>
+        <v>53.93</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>64.58</v>
+        <v>47.4</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>604</v>
+        <v>382</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>145</v>
+        <v>367</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>4.17</v>
+        <v>1.04</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>11.13</v>
+        <v>0.79</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>55.67</v>
+        <v>57.04</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>64.45</v>
+        <v>65.25</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>23348.4</v>
+        <v>64.58</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>4.91</v>
+        <v>4.17</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>7.66</v>
+        <v>11.13</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>52.75</v>
+        <v>55.67</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>56.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>51.53</v>
+        <v>64.45</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>45.54</v>
+        <v>64.31</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>87</v>
+        <v>624</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>664</v>
+        <v>127</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.13</v>
+        <v>4.91</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>49.83</v>
+        <v>52.75</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>50</v>
+        <v>56.16</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>37.95</v>
+        <v>51.53</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>26.23</v>
+        <v>45.54</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>2.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>242</v>
+        <v>87</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>505</v>
+        <v>664</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>56.36</v>
+        <v>49.83</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>60.81</v>
+        <v>50</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>58.19</v>
+        <v>37.95</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>51.8</v>
+        <v>26.23</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>23368.85</v>
+        <v>22908.05</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>364</v>
+        <v>242</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>386</v>
+        <v>505</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>57.14</v>
+        <v>56.36</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>63.66</v>
+        <v>60.81</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>65.65000000000001</v>
+        <v>58.19</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>63.65</v>
+        <v>51.8</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>23433.95</v>
+        <v>23368.85</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>40</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>56.97</v>
+        <v>57.14</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>65.02</v>
+        <v>63.66</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>66.18000000000001</v>
+        <v>63.65</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>23301.15</v>
+        <v>23433.95</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>537</v>
+        <v>354</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>212</v>
+        <v>395</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>2.53</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>56.63</v>
+        <v>56.97</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>64.56</v>
+        <v>65.02</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>69.73</v>
+        <v>66.84</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>68.67</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>23264.8</v>
+        <v>23301.15</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1.76</v>
+        <v>2.87</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.49</v>
+        <v>2.77</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>417</v>
+        <v>537</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>333</v>
+        <v>212</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>53.01</v>
+        <v>56.63</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>60.21</v>
+        <v>64.56</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>61.47</v>
+        <v>69.73</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>57.07</v>
+        <v>68.67</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>23111.65</v>
+        <v>23264.8</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>51.98</v>
+        <v>53.01</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>58.11</v>
+        <v>60.21</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>57.87</v>
+        <v>61.47</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>50.13</v>
+        <v>57.07</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>22995.65</v>
+        <v>23111.65</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>278</v>
+        <v>444</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>471</v>
+        <v>305</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>50.43</v>
+        <v>51.98</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>55.86</v>
+        <v>58.11</v>
       </c>
       <c r="N12" s="1" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>50.13</v>
       </c>
-      <c r="O12" s="1" t="n">
-        <v>41.33</v>
-      </c>
       <c r="P12" s="11" t="n">
-        <v>23000</v>
+        <v>22995.65</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>4.71</v>
+        <v>2.7</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>52.67</v>
+        <v>50.43</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>59.91</v>
+        <v>55.86</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>60.27</v>
+        <v>50.13</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P13" s="12" t="inlineStr"/>
-      <c r="Q13" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P13" s="12" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>6.86</v>
+        <v>4.71</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>52.5</v>
+        <v>52.67</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>60.06</v>
+        <v>59.91</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>60.27</v>
@@ -1670,1150 +1683,1150 @@
       <c r="O14" s="1" t="n">
         <v>50.8</v>
       </c>
-      <c r="P14" s="9" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q14" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="P14" s="13" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>3.69</v>
+        <v>2.66</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>6.54</v>
+        <v>6.86</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>388</v>
+        <v>249</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>362</v>
+        <v>500</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>53.01</v>
+        <v>52.5</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>62.46</v>
+        <v>60.06</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.27</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>4.93</v>
+        <v>6.54</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>181</v>
+        <v>388</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>569</v>
+        <v>362</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.32</v>
+        <v>1.07</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>53.36</v>
+        <v>53.01</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>61.86</v>
+        <v>62.46</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>69.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>64.13</v>
+        <v>63.73</v>
       </c>
       <c r="P16" s="14" t="n">
-        <v>23010.95</v>
+        <v>23126.3</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>6.03</v>
+        <v>4.93</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>497</v>
+        <v>181</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>253</v>
+        <v>569</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>1.96</v>
+        <v>0.32</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>55.59</v>
+        <v>53.36</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>68.47</v>
+        <v>61.86</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>79.2</v>
+        <v>69.33</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P17" s="15" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>8.529999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>3.2</v>
+        <v>6.03</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>354</v>
+        <v>253</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>54.04</v>
+        <v>55.59</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>65.47</v>
+        <v>68.47</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>74</v>
+        <v>79.2</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="P18" s="15" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>16.52</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>302</v>
+        <v>354</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>53.36</v>
+        <v>54.04</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>65.92</v>
+        <v>65.47</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>76.8</v>
+        <v>74</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>79.47</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>23206.45</v>
+        <v>23144.2</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>10.32</v>
+        <v>16.52</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>51.98</v>
+        <v>53.36</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>63.66</v>
+        <v>65.92</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>74.67</v>
+        <v>76.8</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>78.27</v>
-      </c>
-      <c r="P20" s="9" t="n">
-        <v>23109.7</v>
+        <v>79.47</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>4.69</v>
+        <v>10.32</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>50.43</v>
+        <v>51.98</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>61.86</v>
+        <v>63.66</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>73.47</v>
+        <v>74.67</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>79.2</v>
+        <v>78.27</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>22997.25</v>
+        <v>23109.7</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>5.62</v>
+        <v>4.69</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>574</v>
+        <v>435</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>3.28</v>
+        <v>1.39</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>49.83</v>
+        <v>50.43</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>59.91</v>
+        <v>61.86</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>70.27</v>
+        <v>73.47</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P22" s="17" t="n">
-        <v>22891.3</v>
+        <v>79.2</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>2</v>
+        <v>5.62</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>691</v>
+        <v>574</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>11.91</v>
+        <v>3.28</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>33.39</v>
+        <v>5.84</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46.72</v>
+        <v>49.83</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>50</v>
+        <v>59.91</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>53.07</v>
+        <v>70.27</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>61.2</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P23" s="18" t="n">
-        <v>22599.8</v>
+        <v>22891.3</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>174</v>
+        <v>691</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>575</v>
+        <v>58</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>39.14</v>
+        <v>46.72</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>38.44</v>
+        <v>50</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>27.73</v>
+        <v>53.07</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>22</v>
+        <v>61.2</v>
       </c>
       <c r="P24" s="19" t="n">
-        <v>22114.45</v>
+        <v>22599.8</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>43.28</v>
+        <v>39.14</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>44.29</v>
+        <v>38.44</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>36.27</v>
+        <v>27.73</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>30.67</v>
+        <v>22</v>
       </c>
       <c r="P25" s="20" t="n">
-        <v>22233.85</v>
+        <v>22114.45</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>597</v>
+        <v>160</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>152</v>
+        <v>590</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>3.93</v>
+        <v>0.27</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>45</v>
+        <v>43.28</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>51.05</v>
+        <v>44.29</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>43.87</v>
+        <v>36.27</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>43.2</v>
+        <v>30.67</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>22370.15</v>
+        <v>22233.85</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>103</v>
+        <v>597</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>647</v>
+        <v>152</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.16</v>
+        <v>3.93</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>41.55</v>
+        <v>45</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>44.89</v>
+        <v>51.05</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>30.4</v>
+        <v>43.87</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>24.27</v>
+        <v>43.2</v>
       </c>
       <c r="P27" s="22" t="n">
-        <v>22173.7</v>
+        <v>22370.15</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>360</v>
+        <v>103</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>390</v>
+        <v>647</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>45</v>
+        <v>41.55</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>55.11</v>
+        <v>44.89</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>44.93</v>
+        <v>30.4</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>45.33</v>
+        <v>24.27</v>
       </c>
       <c r="P28" s="23" t="n">
-        <v>22465.35</v>
+        <v>22173.7</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>1.9</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>44.91</v>
+        <v>45</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>57.06</v>
+        <v>55.11</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>45.47</v>
+        <v>44.93</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>43.2</v>
+        <v>45.33</v>
       </c>
       <c r="P29" s="24" t="n">
-        <v>22497.7</v>
+        <v>22465.35</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>441</v>
+        <v>351</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>43.87</v>
+        <v>44.91</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>57.36</v>
+        <v>57.06</v>
       </c>
       <c r="N30" s="1" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="O30" s="1" t="n">
         <v>43.2</v>
       </c>
-      <c r="O30" s="1" t="n">
-        <v>37.73</v>
-      </c>
       <c r="P30" s="25" t="n">
-        <v>22451.85</v>
+        <v>22497.7</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>468</v>
+        <v>308</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>280</v>
+        <v>441</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>1.67</v>
+        <v>0.7</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>43.7</v>
+        <v>43.87</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>60.06</v>
+        <v>57.36</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>43.73</v>
+        <v>43.2</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>40</v>
+        <v>37.73</v>
       </c>
       <c r="P31" s="26" t="n">
-        <v>22521.1</v>
+        <v>22451.85</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>220</v>
+        <v>468</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>530</v>
+        <v>280</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.42</v>
+        <v>1.67</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>42.83</v>
+        <v>43.7</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>59.01</v>
+        <v>60.06</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>38</v>
+        <v>43.73</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>31.87</v>
+        <v>40</v>
       </c>
       <c r="P32" s="27" t="n">
-        <v>22437.95</v>
+        <v>22521.1</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>44.04</v>
+        <v>42.83</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>66.37</v>
+        <v>59.01</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>47.6</v>
+        <v>38</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>42.13</v>
+        <v>31.87</v>
       </c>
       <c r="P33" s="28" t="n">
-        <v>22657</v>
+        <v>22437.95</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>47.67</v>
+        <v>44.04</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>72.52</v>
+        <v>66.37</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>61.33</v>
+        <v>47.6</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P34" s="12" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P34" s="29" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q34" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>47.75</v>
+        <v>47.67</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>73.27</v>
+        <v>72.52</v>
       </c>
       <c r="N35" s="1" t="n">
         <v>61.33</v>
@@ -2821,1543 +2834,1539 @@
       <c r="O35" s="1" t="n">
         <v>60.67</v>
       </c>
-      <c r="P35" s="29" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q35" s="1" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="P35" s="13" t="inlineStr"/>
+      <c r="Q35" s="1" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>46.97</v>
+        <v>47.75</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>73.87</v>
+        <v>73.27</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>62.13</v>
+        <v>61.33</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P36" s="17" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P36" s="30" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>567</v>
+        <v>362</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>3.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>8.33</v>
+        <v>1.98</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>46.27</v>
+        <v>46.97</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>74.77</v>
+        <v>73.87</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>61.2</v>
+        <v>62.13</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P37" s="30" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P37" s="18" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>373</v>
+        <v>567</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>373</v>
+        <v>182</v>
       </c>
       <c r="H38" s="1" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="J38" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="J38" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="K38" s="1" t="n">
-        <v>2.48</v>
+        <v>8.33</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>44.19</v>
+        <v>46.27</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>68.17</v>
+        <v>74.77</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>48.8</v>
+        <v>61.2</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P38" s="28" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P38" s="31" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>445</v>
+        <v>373</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>302</v>
+        <v>373</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1.47</v>
+        <v>1</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>42.11</v>
+        <v>44.19</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>68.62</v>
+        <v>68.17</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>48.13</v>
+        <v>48.8</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P39" s="18" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P39" s="29" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>366</v>
+        <v>445</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>382</v>
+        <v>302</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>41.25</v>
+        <v>42.11</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>66.81999999999999</v>
+        <v>68.62</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>42</v>
+        <v>48.13</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P40" s="31" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P40" s="19" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>256</v>
+        <v>382</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>41.42</v>
+        <v>41.25</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>67.12</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>40.93</v>
+        <v>42</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P41" s="26" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P41" s="32" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>39.86</v>
+        <v>41.42</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>65.02</v>
+        <v>67.12</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>32.53</v>
+        <v>40.93</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P42" s="32" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P42" s="27" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>44.37</v>
+        <v>39.86</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>71.17</v>
+        <v>65.02</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>42.27</v>
+        <v>32.53</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>31.87</v>
+        <v>23.33</v>
       </c>
       <c r="P43" s="33" t="n">
-        <v>22531.15</v>
+        <v>22461.05</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>44.89</v>
+        <v>44.37</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>72.37</v>
+        <v>71.17</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>46.4</v>
+        <v>42.27</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>35.47</v>
+        <v>31.87</v>
       </c>
       <c r="P44" s="34" t="n">
-        <v>22613.1</v>
+        <v>22531.15</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="E45" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L45" s="1" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="M45" s="1" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="N45" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O45" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P45" s="35" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q45" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F45" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H45" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I45" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K45" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L45" s="1" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="M45" s="1" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="N45" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O45" s="1" t="n">
-        <v>29.73</v>
-      </c>
-      <c r="P45" s="35" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q45" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>696</v>
+        <v>298</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>42.29</v>
+        <v>43.33</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>70.27</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>37.73</v>
+        <v>43.73</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>22.93</v>
+        <v>29.73</v>
       </c>
       <c r="P46" s="36" t="n">
-        <v>22299.9</v>
+        <v>22377.35</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>2.25</v>
+        <v>0.74</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>50</v>
+        <v>42.29</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>82.43000000000001</v>
+        <v>70.27</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.73</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>50.53</v>
+        <v>22.93</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>22795.75</v>
+        <v>22299.9</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>4.87</v>
+        <v>2.25</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>4.32</v>
+        <v>2.28</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>54.86</v>
+        <v>50</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>87.23999999999999</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>82.27</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>73.47</v>
+        <v>50.53</v>
       </c>
       <c r="P48" s="38" t="n">
-        <v>23115.65</v>
+        <v>22795.75</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>5.91</v>
+        <v>4.87</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J49" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>56.6</v>
+        <v>54.86</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>87.98999999999999</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>87.87</v>
+        <v>82.27</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>82.67</v>
+        <v>73.47</v>
       </c>
       <c r="P49" s="39" t="n">
-        <v>23214</v>
+        <v>23115.65</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>3.68</v>
+        <v>5.91</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>52.6</v>
+        <v>56.6</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>86.94</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>86.8</v>
+        <v>87.87</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>80.93000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="P50" s="40" t="n">
-        <v>23133.4</v>
+        <v>23214</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>2.22</v>
+        <v>3.68</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>344</v>
+        <v>605</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>404</v>
+        <v>145</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>47.74</v>
+        <v>52.6</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>79.73</v>
+        <v>86.94</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>73.87</v>
+        <v>86.8</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>62.67</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="P51" s="41" t="n">
-        <v>22808.25</v>
+        <v>23133.4</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>531</v>
+        <v>344</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>218</v>
+        <v>404</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>46.96</v>
+        <v>47.74</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>80.63</v>
+        <v>79.73</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>77.2</v>
+        <v>73.87</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>66.93000000000001</v>
+        <v>62.67</v>
       </c>
       <c r="P52" s="42" t="n">
-        <v>22830.75</v>
+        <v>22808.25</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>3.64</v>
+        <v>2.33</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>2.68</v>
+        <v>3.02</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>43.65</v>
+        <v>46.96</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>77.48</v>
+        <v>80.63</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>49.87</v>
-      </c>
-      <c r="P53" s="12" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr"/>
+        <v>66.93000000000001</v>
+      </c>
+      <c r="P53" s="43" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q53" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>3.14</v>
+        <v>2.68</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>41.93</v>
+        <v>43.65</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>77.47</v>
+        <v>77.48</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="P54" s="43" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q54" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.87</v>
+      </c>
+      <c r="P54" s="13" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>4.03</v>
+        <v>3.14</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>371</v>
+        <v>196</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>377</v>
+        <v>552</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>43.74</v>
+        <v>41.93</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>79.2</v>
+        <v>77.47</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>80.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>70.27</v>
+        <v>55.2</v>
       </c>
       <c r="P55" s="44" t="n">
-        <v>22871</v>
+        <v>22683.55</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>3.02</v>
+        <v>2.38</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>5.64</v>
+        <v>4.03</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>285</v>
+        <v>371</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>463</v>
+        <v>377</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>44.06</v>
+        <v>43.74</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>77.87</v>
+        <v>79.2</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>81.2</v>
+        <v>80.67</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>70.8</v>
+        <v>70.27</v>
       </c>
       <c r="P56" s="45" t="n">
-        <v>22765.6</v>
+        <v>22871</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>285</v>
+      </c>
+      <c r="G57" s="1" t="n">
+        <v>463</v>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="J57" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="1" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="F57" s="1" t="n">
-        <v>648</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="H57" s="1" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="I57" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="J57" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K57" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>44.22</v>
+        <v>44.06</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>80.13</v>
+        <v>77.87</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P57" s="41" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P57" s="46" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.12</v>
+        <v>3.62</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>40.1</v>
+        <v>44.22</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>71.87</v>
+        <v>80.13</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>78</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P58" s="31" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P58" s="42" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>5.24</v>
+        <v>2.12</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>510</v>
+        <v>590</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>42.63</v>
+        <v>40.1</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>78.8</v>
+        <v>71.87</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>87.33</v>
+        <v>78</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P59" s="41" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P59" s="32" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>8.58</v>
+        <v>5.24</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>496</v>
+        <v>237</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>250</v>
+        <v>510</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>1.98</v>
+        <v>0.46</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>43.4</v>
+        <v>42.63</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>82</v>
+        <v>78.8</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>91.73</v>
+        <v>87.33</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>89.87</v>
-      </c>
-      <c r="P60" s="46" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P60" s="42" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>13.69</v>
+        <v>8.58</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>41.08</v>
+        <v>43.4</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>81.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>93.47</v>
+        <v>91.73</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>92.53</v>
+        <v>89.87</v>
       </c>
       <c r="P61" s="47" t="n">
-        <v>23042.35</v>
+        <v>22991.5</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>9.109999999999999</v>
+        <v>13.69</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>275</v>
+        <v>510</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>475</v>
+        <v>238</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.58</v>
+        <v>2.14</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J62" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>76.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>93.2</v>
+        <v>93.47</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>92</v>
+        <v>92.53</v>
       </c>
       <c r="P62" s="48" t="n">
-        <v>22865.8</v>
+        <v>23042.35</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>581</v>
+        <v>275</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>167</v>
+        <v>475</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>3.48</v>
+        <v>0.58</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>4.48</v>
+        <v>0.53</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>39.33</v>
+        <v>38.69</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>79.06999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>95.2</v>
+        <v>93.2</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>96.53</v>
-      </c>
-      <c r="P63" s="48" t="n">
-        <v>22869.4</v>
+        <v>92</v>
+      </c>
+      <c r="P63" s="49" t="n">
+        <v>22865.8</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C64" s="1" t="n">
         <v>2</v>
@@ -4365,191 +4374,242 @@
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>504</v>
+        <v>581</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>243</v>
+        <v>167</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>2.07</v>
+        <v>3.48</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>3.43</v>
+        <v>4.48</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>37.26</v>
+        <v>39.33</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>74.93000000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>92.67</v>
+        <v>95.2</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="P64" s="28" t="n">
-        <v>22656.3</v>
+        <v>96.53</v>
+      </c>
+      <c r="P64" s="49" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>682</v>
+        <v>504</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>10.18</v>
+        <v>2.07</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>17.31</v>
+        <v>3.43</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>34.71</v>
+        <v>37.26</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>93.87</v>
+        <v>92.67</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>96.13</v>
-      </c>
-      <c r="P65" s="49" t="n">
-        <v>22595.55</v>
+        <v>94.8</v>
+      </c>
+      <c r="P65" s="29" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>244</v>
+        <v>682</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>501</v>
+        <v>67</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>0.49</v>
+        <v>10.18</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>0.75</v>
+        <v>17.31</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>31.26</v>
+        <v>34.71</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>52.93</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>84.27</v>
+        <v>93.87</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P66" s="22" t="n">
-        <v>22179.05</v>
+        <v>96.13</v>
+      </c>
+      <c r="P66" s="50" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L67" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M67" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N67" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O67" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P67" s="23" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q67" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="1" t="inlineStr"/>
+      <c r="E68" s="1" t="inlineStr"/>
+      <c r="F68" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G67" s="1" t="n">
+      <c r="G68" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H67" s="1" t="n">
+      <c r="H68" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr"/>
-      <c r="L67" s="1" t="n">
+      <c r="I68" s="1" t="inlineStr"/>
+      <c r="J68" s="1" t="inlineStr"/>
+      <c r="K68" s="1" t="inlineStr"/>
+      <c r="L68" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M67" s="1" t="n">
+      <c r="M68" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N67" s="1" t="n">
+      <c r="N68" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O67" s="1" t="n">
+      <c r="O68" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P67" s="50" t="n">
+      <c r="P68" s="51" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q67" s="1" t="n">
+      <c r="Q68" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B67">
+  <conditionalFormatting sqref="B2:B68">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4559,7 +4619,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C67">
+  <conditionalFormatting sqref="C2:C68">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4569,7 +4629,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E67">
+  <conditionalFormatting sqref="D2:E68">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4581,7 +4641,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F67">
+  <conditionalFormatting sqref="F2:F68">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4591,7 +4651,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G67">
+  <conditionalFormatting sqref="G2:G68">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4601,7 +4661,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H67">
+  <conditionalFormatting sqref="H2:H68">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4613,7 +4673,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I67">
+  <conditionalFormatting sqref="I2:I68">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4623,7 +4683,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J67">
+  <conditionalFormatting sqref="J2:J68">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4633,7 +4693,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K67">
+  <conditionalFormatting sqref="K2:K68">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4645,7 +4705,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O67">
+  <conditionalFormatting sqref="L2:O68">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4657,7 +4717,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q67">
+  <conditionalFormatting sqref="Q2:Q68">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -988,16 +988,16 @@
         <v>18</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>171</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>0.3</v>
@@ -1012,16 +1012,16 @@
         <v>0.38</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>61.33</v>
+        <v>61.28</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>53.93</v>
+        <v>53.79</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>47.4</v>
+        <v>47.27</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>23199.45</v>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>367</v>
@@ -1064,19 +1064,19 @@
         <v>2</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>57.04</v>
+        <v>57.14</v>
       </c>
       <c r="M3" s="1" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <v>65.2</v>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>65.25</v>
-      </c>
       <c r="O3" s="1" t="n">
-        <v>64.58</v>
+        <v>64.53</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>23347.05</v>
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>145</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>27</v>
@@ -1119,19 +1119,19 @@
         <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>11.13</v>
+        <v>11.11</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>55.67</v>
+        <v>55.77</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>64.89</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>64.45</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>64.31</v>
+        <v>64.27</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>23348.4</v>
@@ -1147,19 +1147,19 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>127</v>
@@ -1174,19 +1174,19 @@
         <v>3</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>7.66</v>
+        <v>7.65</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>52.75</v>
+        <v>52.84</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>56.16</v>
+        <v>56.09</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>51.53</v>
+        <v>51.47</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>45.54</v>
+        <v>45.47</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>23081.15</v>
@@ -1208,16 +1208,16 @@
         <v>70</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>87</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>0.13</v>
@@ -1232,16 +1232,16 @@
         <v>0.6</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>49.83</v>
+        <v>49.91</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>50</v>
+        <v>50.08</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>37.95</v>
+        <v>38</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>26.23</v>
+        <v>26.27</v>
       </c>
       <c r="P6" s="5" t="n">
         <v>22908.05</v>
@@ -1263,13 +1263,13 @@
         <v>27</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>1.86</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>505</v>
@@ -1287,16 +1287,16 @@
         <v>0.62</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>56.36</v>
+        <v>56.45</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>60.81</v>
+        <v>60.9</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>58.19</v>
+        <v>58.13</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>51.8</v>
+        <v>51.73</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>23368.85</v>
@@ -1318,19 +1318,19 @@
         <v>10</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>364</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>40</v>
@@ -1342,16 +1342,16 @@
         <v>0.52</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>57.14</v>
+        <v>57.24</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>63.66</v>
+        <v>63.76</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>65.65000000000001</v>
+        <v>65.73</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>63.65</v>
+        <v>63.6</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>23433.95</v>
@@ -1373,7 +1373,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>2.34</v>
@@ -1382,7 +1382,7 @@
         <v>354</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>0.9</v>
@@ -1394,19 +1394,19 @@
         <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>56.97</v>
+        <v>57.07</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>65.02</v>
+        <v>65.11</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>66.84</v>
+        <v>66.8</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>66.18000000000001</v>
+        <v>66.13</v>
       </c>
       <c r="P9" s="8" t="n">
         <v>23301.15</v>
@@ -1422,19 +1422,19 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>212</v>
@@ -1449,19 +1449,19 @@
         <v>2</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>56.63</v>
+        <v>56.72</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>64.56</v>
+        <v>64.66</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>69.73</v>
+        <v>69.69</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>68.67</v>
+        <v>68.62</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>23264.8</v>
@@ -1492,10 +1492,10 @@
         <v>417</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>29</v>
@@ -1507,16 +1507,16 @@
         <v>3.41</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>53.01</v>
+        <v>53.1</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>60.21</v>
+        <v>60.3</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>61.47</v>
+        <v>61.55</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>57.07</v>
+        <v>57.14</v>
       </c>
       <c r="P11" s="10" t="n">
         <v>23111.65</v>
@@ -1544,13 +1544,13 @@
         <v>2.73</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>305</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>27</v>
@@ -1562,16 +1562,16 @@
         <v>1.73</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>51.98</v>
+        <v>52.07</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>58.11</v>
+        <v>58.2</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>57.87</v>
+        <v>57.94</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>50.13</v>
+        <v>50.2</v>
       </c>
       <c r="P12" s="11" t="n">
         <v>22995.65</v>
@@ -1602,7 +1602,7 @@
         <v>278</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>0.59</v>
@@ -1617,16 +1617,16 @@
         <v>1.84</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>50.43</v>
+        <v>50.52</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>55.86</v>
+        <v>55.94</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>50.13</v>
+        <v>50.2</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>41.33</v>
+        <v>41.39</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>23000</v>
@@ -1672,16 +1672,16 @@
         <v>0</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>52.67</v>
+        <v>52.76</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>59.91</v>
+        <v>60</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>60.27</v>
+        <v>60.35</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>50.8</v>
+        <v>50.87</v>
       </c>
       <c r="P14" s="13" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
         <v>249</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>0.5</v>
@@ -1723,16 +1723,16 @@
         <v>0.55</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>52.5</v>
+        <v>52.59</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>60.06</v>
+        <v>60.15</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>60.27</v>
+        <v>60.35</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>50.8</v>
+        <v>50.87</v>
       </c>
       <c r="P15" s="10" t="n">
         <v>23113.7</v>
@@ -1760,7 +1760,7 @@
         <v>6.54</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>362</v>
@@ -1778,16 +1778,16 @@
         <v>1.08</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>53.01</v>
+        <v>53.1</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>62.46</v>
+        <v>62.56</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>63.73</v>
+        <v>63.82</v>
       </c>
       <c r="P16" s="14" t="n">
         <v>23126.3</v>
@@ -1818,7 +1818,7 @@
         <v>181</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>0.32</v>
@@ -1833,16 +1833,16 @@
         <v>0.27</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>53.36</v>
+        <v>53.45</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>61.86</v>
+        <v>61.95</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>69.33</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>64.13</v>
+        <v>64.22</v>
       </c>
       <c r="P17" s="15" t="n">
         <v>23010.95</v>
@@ -1870,7 +1870,7 @@
         <v>6.03</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>253</v>
@@ -1888,16 +1888,16 @@
         <v>2.09</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>55.59</v>
+        <v>55.69</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>68.47</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>79.2</v>
+        <v>79.31</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>81.06999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="P18" s="9" t="n">
         <v>23261.85</v>
@@ -1928,10 +1928,10 @@
         <v>394</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>29</v>
@@ -1943,16 +1943,16 @@
         <v>1.05</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>54.04</v>
+        <v>54.14</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>65.47</v>
+        <v>65.56</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>75.06999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="P19" s="16" t="n">
         <v>23144.2</v>
@@ -1983,10 +1983,10 @@
         <v>448</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>38</v>
@@ -1998,16 +1998,16 @@
         <v>1.85</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>53.36</v>
+        <v>53.45</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>79.47</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="P20" s="17" t="n">
         <v>23206.45</v>
@@ -2035,7 +2035,7 @@
         <v>3.09</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>295</v>
@@ -2053,16 +2053,16 @@
         <v>4.15</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>51.98</v>
+        <v>52.07</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>63.66</v>
+        <v>63.76</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>74.67</v>
+        <v>74.77</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>78.27</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="P21" s="10" t="n">
         <v>23109.7</v>
@@ -2090,13 +2090,13 @@
         <v>2.75</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>314</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>23</v>
@@ -2108,16 +2108,16 @@
         <v>1.26</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>50.43</v>
+        <v>50.52</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>61.86</v>
+        <v>61.95</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>73.47</v>
+        <v>73.56</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>79.2</v>
+        <v>79.31</v>
       </c>
       <c r="P22" s="11" t="n">
         <v>22997.25</v>
@@ -2145,13 +2145,13 @@
         <v>2.83</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>175</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>30</v>
@@ -2163,16 +2163,16 @@
         <v>5.84</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>49.83</v>
+        <v>49.91</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>59.91</v>
+        <v>60</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>70.27</v>
+        <v>70.36</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>79.06999999999999</v>
+        <v>79.17</v>
       </c>
       <c r="P23" s="18" t="n">
         <v>22891.3</v>
@@ -2200,13 +2200,13 @@
         <v>1.9</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>58</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>11.91</v>
+        <v>11.9</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>14</v>
@@ -2215,19 +2215,19 @@
         <v>4</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>33.39</v>
+        <v>33.37</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46.72</v>
+        <v>46.8</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>50</v>
+        <v>50.08</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>53.07</v>
+        <v>53.14</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="P24" s="19" t="n">
         <v>22599.8</v>
@@ -2258,7 +2258,7 @@
         <v>174</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>0.3</v>
@@ -2273,16 +2273,16 @@
         <v>0.74</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>39.14</v>
+        <v>39.21</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>38.44</v>
+        <v>38.5</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>27.73</v>
+        <v>27.77</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>22</v>
+        <v>22.03</v>
       </c>
       <c r="P25" s="20" t="n">
         <v>22114.45</v>
@@ -2313,7 +2313,7 @@
         <v>160</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>0.27</v>
@@ -2328,16 +2328,16 @@
         <v>0.18</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>43.28</v>
+        <v>43.35</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>44.29</v>
+        <v>44.36</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>36.27</v>
+        <v>36.32</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>30.67</v>
+        <v>30.71</v>
       </c>
       <c r="P26" s="21" t="n">
         <v>22233.85</v>
@@ -2368,10 +2368,10 @@
         <v>597</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>21</v>
@@ -2383,16 +2383,16 @@
         <v>1.9</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>45</v>
+        <v>45.08</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>51.05</v>
+        <v>51.13</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>43.87</v>
+        <v>43.93</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>43.2</v>
+        <v>43.26</v>
       </c>
       <c r="P27" s="22" t="n">
         <v>22370.15</v>
@@ -2423,7 +2423,7 @@
         <v>103</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>0.16</v>
@@ -2438,16 +2438,16 @@
         <v>0.14</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>41.55</v>
+        <v>41.62</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>44.89</v>
+        <v>44.96</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>30.4</v>
+        <v>30.44</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>24.27</v>
+        <v>24.3</v>
       </c>
       <c r="P28" s="23" t="n">
         <v>22173.7</v>
@@ -2478,10 +2478,10 @@
         <v>360</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I29" s="1" t="n">
         <v>26</v>
@@ -2493,16 +2493,16 @@
         <v>2.32</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>45</v>
+        <v>45.08</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>55.11</v>
+        <v>55.19</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>44.93</v>
+        <v>44.99</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>45.33</v>
+        <v>45.39</v>
       </c>
       <c r="P29" s="24" t="n">
         <v>22465.35</v>
@@ -2533,7 +2533,7 @@
         <v>399</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>1.14</v>
@@ -2548,16 +2548,16 @@
         <v>2.31</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>44.91</v>
+        <v>44.98</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>57.06</v>
+        <v>57.14</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>45.47</v>
+        <v>45.53</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>43.2</v>
+        <v>43.26</v>
       </c>
       <c r="P30" s="25" t="n">
         <v>22497.7</v>
@@ -2588,7 +2588,7 @@
         <v>308</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>0.7</v>
@@ -2603,16 +2603,16 @@
         <v>2.04</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>43.87</v>
+        <v>43.94</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>57.36</v>
+        <v>57.44</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>43.2</v>
+        <v>43.26</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>37.73</v>
+        <v>37.78</v>
       </c>
       <c r="P31" s="26" t="n">
         <v>22451.85</v>
@@ -2643,10 +2643,10 @@
         <v>468</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I32" s="1" t="n">
         <v>13</v>
@@ -2655,19 +2655,19 @@
         <v>16</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>43.7</v>
+        <v>43.77</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>60.06</v>
+        <v>60</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>43.73</v>
+        <v>43.66</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>40</v>
+        <v>39.92</v>
       </c>
       <c r="P32" s="27" t="n">
         <v>22521.1</v>
@@ -2695,13 +2695,13 @@
         <v>1.93</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>530</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>17</v>
@@ -2713,16 +2713,16 @@
         <v>0.31</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>42.83</v>
+        <v>42.91</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>59.01</v>
+        <v>58.95</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>38</v>
+        <v>37.92</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>31.87</v>
+        <v>31.78</v>
       </c>
       <c r="P33" s="28" t="n">
         <v>22437.95</v>
@@ -2753,7 +2753,7 @@
         <v>210</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>0.39</v>
@@ -2768,16 +2768,16 @@
         <v>0.51</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>44.04</v>
+        <v>44.12</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>66.37</v>
+        <v>66.47</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>47.6</v>
+        <v>47.66</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>42.13</v>
+        <v>42.19</v>
       </c>
       <c r="P34" s="29" t="n">
         <v>22657</v>
@@ -2823,16 +2823,16 @@
         <v>0</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>47.67</v>
+        <v>47.75</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>72.52</v>
+        <v>72.48</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>61.33</v>
+        <v>61.28</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>60.67</v>
+        <v>60.61</v>
       </c>
       <c r="P35" s="13" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
         <v>2.15</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>358</v>
@@ -2874,16 +2874,16 @@
         <v>4.35</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>47.75</v>
+        <v>47.83</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>73.27</v>
+        <v>73.23</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>61.33</v>
+        <v>61.28</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>60.67</v>
+        <v>60.61</v>
       </c>
       <c r="P36" s="30" t="n">
         <v>22967.4</v>
@@ -2911,7 +2911,7 @@
         <v>2.12</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>386</v>
@@ -2929,16 +2929,16 @@
         <v>1.98</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>46.97</v>
+        <v>47.05</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>73.87</v>
+        <v>73.98</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>62.13</v>
+        <v>62.08</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>63.47</v>
+        <v>63.42</v>
       </c>
       <c r="P37" s="18" t="n">
         <v>22897.2</v>
@@ -2966,13 +2966,13 @@
         <v>0.9</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>182</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>28</v>
@@ -2984,16 +2984,16 @@
         <v>8.33</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46.27</v>
+        <v>46.35</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>74.77</v>
+        <v>74.89</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>61.2</v>
+        <v>61.15</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>63.6</v>
+        <v>63.55</v>
       </c>
       <c r="P38" s="31" t="n">
         <v>22929.45</v>
@@ -3024,7 +3024,7 @@
         <v>373</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>1</v>
@@ -3039,16 +3039,16 @@
         <v>2.48</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>44.19</v>
+        <v>44.27</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>68.17</v>
+        <v>68.27</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>48.8</v>
+        <v>48.87</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>46.93</v>
+        <v>46.86</v>
       </c>
       <c r="P39" s="29" t="n">
         <v>22651.3</v>
@@ -3079,10 +3079,10 @@
         <v>445</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I40" s="1" t="n">
         <v>22</v>
@@ -3091,19 +3091,19 @@
         <v>2</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>42.11</v>
+        <v>42.19</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>68.62</v>
+        <v>68.72</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>48.13</v>
+        <v>48.06</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>45.73</v>
+        <v>45.66</v>
       </c>
       <c r="P40" s="19" t="n">
         <v>22602.85</v>
@@ -3128,10 +3128,10 @@
         <v>1.34</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>382</v>
@@ -3149,16 +3149,16 @@
         <v>2.65</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>41.25</v>
+        <v>41.32</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>66.81999999999999</v>
+        <v>66.92</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>42</v>
+        <v>41.92</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>38.13</v>
+        <v>38.05</v>
       </c>
       <c r="P41" s="32" t="n">
         <v>22578.15</v>
@@ -3186,13 +3186,13 @@
         <v>0.91</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>256</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>14</v>
@@ -3204,16 +3204,16 @@
         <v>2.38</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>41.42</v>
+        <v>41.49</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>67.12</v>
+        <v>67.22</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>40.93</v>
+        <v>40.99</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>34.4</v>
+        <v>34.45</v>
       </c>
       <c r="P42" s="27" t="n">
         <v>22521.75</v>
@@ -3244,7 +3244,7 @@
         <v>164</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>0.28</v>
@@ -3259,16 +3259,16 @@
         <v>0.29</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>39.86</v>
+        <v>39.93</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>65.02</v>
+        <v>65.11</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>32.53</v>
+        <v>32.58</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>23.33</v>
+        <v>23.36</v>
       </c>
       <c r="P43" s="33" t="n">
         <v>22461.05</v>
@@ -3296,7 +3296,7 @@
         <v>1.11</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>494</v>
@@ -3314,16 +3314,16 @@
         <v>0.92</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>44.37</v>
+        <v>44.44</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>71.17</v>
+        <v>71.28</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>42.27</v>
+        <v>42.32</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="P44" s="34" t="n">
         <v>22531.15</v>
@@ -3351,7 +3351,7 @@
         <v>1.13</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>326</v>
@@ -3369,16 +3369,16 @@
         <v>3.4</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>44.89</v>
+        <v>44.97</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>72.37</v>
+        <v>72.48</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>46.4</v>
+        <v>46.46</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>35.47</v>
+        <v>35.51</v>
       </c>
       <c r="P45" s="35" t="n">
         <v>22613.1</v>
@@ -3400,7 +3400,7 @@
         <v>14</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>1.05</v>
@@ -3409,7 +3409,7 @@
         <v>449</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>1.51</v>
@@ -3424,16 +3424,16 @@
         <v>3.9</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>43.33</v>
+        <v>43.4</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>71.31999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>43.73</v>
+        <v>43.79</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>29.73</v>
+        <v>29.77</v>
       </c>
       <c r="P46" s="36" t="n">
         <v>22377.35</v>
@@ -3452,7 +3452,7 @@
         <v>6</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>0.74</v>
@@ -3464,7 +3464,7 @@
         <v>54</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>0.08</v>
@@ -3479,16 +3479,16 @@
         <v>0.12</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>42.29</v>
+        <v>42.36</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>70.27</v>
+        <v>70.38</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>37.73</v>
+        <v>37.78</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>22.93</v>
+        <v>22.96</v>
       </c>
       <c r="P47" s="37" t="n">
         <v>22299.9</v>
@@ -3519,7 +3519,7 @@
         <v>188</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>0.34</v>
@@ -3534,16 +3534,16 @@
         <v>0.88</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>50</v>
+        <v>50.09</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>82.43000000000001</v>
+        <v>82.41</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>67.56</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>50.53</v>
+        <v>50.6</v>
       </c>
       <c r="P48" s="38" t="n">
         <v>22795.75</v>
@@ -3568,10 +3568,10 @@
         <v>4.87</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>425</v>
@@ -3589,16 +3589,16 @@
         <v>1.53</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>54.86</v>
+        <v>54.96</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>87.23999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>82.27</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>73.47</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="P49" s="39" t="n">
         <v>23115.65</v>
@@ -3623,16 +3623,16 @@
         <v>5.91</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>250</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I50" s="1" t="n">
         <v>45</v>
@@ -3644,16 +3644,16 @@
         <v>1.69</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>87.98999999999999</v>
+        <v>87.97</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>87.87</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>82.67</v>
+        <v>82.64</v>
       </c>
       <c r="P50" s="40" t="n">
         <v>23214</v>
@@ -3678,10 +3678,10 @@
         <v>3.68</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>145</v>
@@ -3696,19 +3696,19 @@
         <v>1</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>86.94</v>
+        <v>86.92</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>86.8</v>
+        <v>86.78</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>80.93000000000001</v>
+        <v>80.91</v>
       </c>
       <c r="P51" s="41" t="n">
         <v>23133.4</v>
@@ -3733,10 +3733,10 @@
         <v>2.22</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>404</v>
@@ -3754,16 +3754,16 @@
         <v>1.86</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>47.74</v>
+        <v>47.83</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>79.73</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>73.87</v>
+        <v>73.83</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>62.67</v>
+        <v>62.62</v>
       </c>
       <c r="P52" s="42" t="n">
         <v>22808.25</v>
@@ -3788,16 +3788,16 @@
         <v>2.33</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>218</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>43</v>
@@ -3809,16 +3809,16 @@
         <v>2.58</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>46.96</v>
+        <v>47.04</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>80.63</v>
+        <v>80.75</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>66.93000000000001</v>
+        <v>66.89</v>
       </c>
       <c r="P53" s="43" t="n">
         <v>22830.75</v>
@@ -3840,10 +3840,10 @@
         <v>0</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>0</v>
@@ -3864,16 +3864,16 @@
         <v>0</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>43.65</v>
+        <v>43.73</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>77.48</v>
+        <v>77.59</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.02</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>49.87</v>
+        <v>49.93</v>
       </c>
       <c r="P54" s="13" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr"/>
@@ -3891,19 +3891,19 @@
         <v>23</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>552</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>20</v>
@@ -3915,16 +3915,16 @@
         <v>0.54</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>41.93</v>
+        <v>42</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>77.47</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>73.16</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>55.2</v>
+        <v>55.27</v>
       </c>
       <c r="P55" s="44" t="n">
         <v>22683.55</v>
@@ -3946,13 +3946,13 @@
         <v>14</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>4.03</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>377</v>
@@ -3970,16 +3970,16 @@
         <v>2.06</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>43.74</v>
+        <v>43.81</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>79.2</v>
+        <v>79.31</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>80.67</v>
+        <v>80.77</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>70.27</v>
+        <v>70.36</v>
       </c>
       <c r="P56" s="45" t="n">
         <v>22871</v>
@@ -4001,16 +4001,16 @@
         <v>11</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>5.64</v>
+        <v>5.63</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>285</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>0.62</v>
@@ -4025,16 +4025,16 @@
         <v>1.94</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>44.06</v>
+        <v>44.13</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>77.87</v>
+        <v>77.97</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>81.2</v>
+        <v>81.31</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>70.8</v>
+        <v>70.89</v>
       </c>
       <c r="P57" s="46" t="n">
         <v>22765.6</v>
@@ -4050,23 +4050,23 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C58" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>102</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>6.35</v>
+        <v>6.34</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>37</v>
@@ -4075,19 +4075,19 @@
         <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>8.17</v>
+        <v>8.16</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>44.22</v>
+        <v>44.29</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>80.13</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>87.05</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>81.59999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="P58" s="42" t="n">
         <v>22821.4</v>
@@ -4116,7 +4116,7 @@
         <v>156</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>0.26</v>
@@ -4131,16 +4131,16 @@
         <v>0.37</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>40.1</v>
+        <v>40.16</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>71.87</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>62.13</v>
+        <v>62.22</v>
       </c>
       <c r="P59" s="32" t="n">
         <v>22570.05</v>
@@ -4169,10 +4169,10 @@
         <v>237</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="I60" s="1" t="n">
         <v>32</v>
@@ -4184,16 +4184,16 @@
         <v>0.66</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>42.63</v>
+        <v>42.7</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>78.8</v>
+        <v>78.91</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>87.33</v>
+        <v>87.45</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>82.13</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="P60" s="42" t="n">
         <v>22810.85</v>
@@ -4222,10 +4222,10 @@
         <v>496</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I61" s="1" t="n">
         <v>34</v>
@@ -4237,16 +4237,16 @@
         <v>2.88</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>43.4</v>
+        <v>43.47</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>82</v>
+        <v>82.11</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>91.73</v>
+        <v>91.86</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>89.87</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="P61" s="47" t="n">
         <v>22991.5</v>
@@ -4275,10 +4275,10 @@
         <v>510</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="I62" s="1" t="n">
         <v>32</v>
@@ -4290,16 +4290,16 @@
         <v>2.82</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>41.08</v>
+        <v>41.15</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>81.59999999999999</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>93.47</v>
+        <v>93.59</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>92.53</v>
+        <v>92.66</v>
       </c>
       <c r="P62" s="48" t="n">
         <v>23042.35</v>
@@ -4326,7 +4326,7 @@
         <v>275</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H63" s="1" t="n">
         <v>0.58</v>
@@ -4341,16 +4341,16 @@
         <v>0.53</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>38.69</v>
+        <v>38.76</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>93.2</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>92</v>
+        <v>92.12</v>
       </c>
       <c r="P63" s="49" t="n">
         <v>22865.8</v>
@@ -4374,13 +4374,13 @@
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>167</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="I64" s="1" t="n">
         <v>43</v>
@@ -4392,13 +4392,13 @@
         <v>4.48</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>39.33</v>
+        <v>39.39</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>79.06999999999999</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>95.2</v>
+        <v>95.33</v>
       </c>
       <c r="O64" s="1" t="n">
         <v>96.53</v>
@@ -4425,7 +4425,7 @@
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>243</v>
@@ -4443,16 +4443,16 @@
         <v>3.43</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>37.26</v>
+        <v>37.32</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>74.93000000000001</v>
+        <v>75.03</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>92.67</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>94.8</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="P65" s="29" t="n">
         <v>22656.3</v>
@@ -4476,13 +4476,13 @@
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>67</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>10.18</v>
+        <v>10.16</v>
       </c>
       <c r="I66" s="1" t="n">
         <v>32</v>
@@ -4494,16 +4494,16 @@
         <v>17.31</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>34.71</v>
+        <v>34.77</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>93.87</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>96.13</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="P66" s="50" t="n">
         <v>22595.55</v>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -35,6 +35,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDB"/>
+        <bgColor rgb="00D4EDDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DCF0E2"/>
         <bgColor rgb="00DCF0E2"/>
       </patternFill>
@@ -73,12 +79,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CFEBD7"/>
         <bgColor rgb="00CFEBD7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDB"/>
-        <bgColor rgb="00D4EDDB"/>
       </patternFill>
     </fill>
     <fill>
@@ -866,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -978,3446 +978,3446 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="D2" s="1" t="n">
-        <v>1.71</v>
+        <v>4.9</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>171</v>
+        <v>452</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>578</v>
+        <v>299</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.3</v>
+        <v>1.51</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.38</v>
+        <v>2.25</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>56.8</v>
+        <v>57.9</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>61.28</v>
+        <v>64.13</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>53.79</v>
+        <v>59.12</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>47.27</v>
+        <v>54.19</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>381</v>
+        <v>171</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>367</v>
+        <v>579</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.78</v>
+        <v>0.38</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>57.14</v>
+        <v>56.7</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>65.15000000000001</v>
+        <v>61.33</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>65.2</v>
+        <v>53.93</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>64.53</v>
+        <v>47.4</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>603</v>
+        <v>382</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>145</v>
+        <v>367</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>4.16</v>
+        <v>1.04</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>11.11</v>
+        <v>0.79</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>55.77</v>
+        <v>57.04</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>64.89</v>
+        <v>65.2</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>65.25</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>23348.4</v>
+        <v>64.58</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>623</v>
+        <v>604</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>4.91</v>
+        <v>4.17</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>7.65</v>
+        <v>11.13</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>52.84</v>
+        <v>55.67</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>56.09</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>51.47</v>
+        <v>64.45</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>45.47</v>
+        <v>64.31</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>87</v>
+        <v>624</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>663</v>
+        <v>127</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.13</v>
+        <v>4.91</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>49.91</v>
+        <v>52.75</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>50.08</v>
+        <v>56.16</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>38</v>
+        <v>51.53</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>26.27</v>
+        <v>45.54</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>2.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>241</v>
+        <v>87</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>505</v>
+        <v>664</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>56.45</v>
+        <v>49.83</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>60.9</v>
+        <v>50</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>58.13</v>
+        <v>37.95</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>51.73</v>
+        <v>26.23</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>23368.85</v>
+        <v>22908.05</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.48</v>
+        <v>2.27</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>364</v>
+        <v>242</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>385</v>
+        <v>505</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.95</v>
+        <v>0.48</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>57.24</v>
+        <v>56.36</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>63.76</v>
+        <v>60.81</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>65.73</v>
+        <v>58.19</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>63.6</v>
+        <v>51.8</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>23433.95</v>
+        <v>23368.85</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>40</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>1.45</v>
+        <v>0.52</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>57.07</v>
+        <v>57.14</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>65.11</v>
+        <v>63.66</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>66.8</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>66.13</v>
+        <v>63.65</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>23301.15</v>
+        <v>23433.95</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.76</v>
+        <v>2.34</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>536</v>
+        <v>354</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>212</v>
+        <v>395</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>2.53</v>
+        <v>0.9</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>56.72</v>
+        <v>56.97</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>64.66</v>
+        <v>65.02</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>69.69</v>
+        <v>66.84</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>68.62</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>23264.8</v>
+        <v>23301.15</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1.76</v>
+        <v>2.87</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.49</v>
+        <v>2.77</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>417</v>
+        <v>537</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>332</v>
+        <v>212</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1.26</v>
+        <v>2.53</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>53.1</v>
+        <v>56.63</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>60.3</v>
+        <v>64.56</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>61.55</v>
+        <v>69.73</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="P11" s="10" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>52.07</v>
+        <v>53.01</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>58.2</v>
+        <v>60.21</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>57.94</v>
+        <v>61.47</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="P12" s="11" t="n">
-        <v>22995.65</v>
+        <v>57.07</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>23111.65</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>278</v>
+        <v>444</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>470</v>
+        <v>305</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>50.52</v>
+        <v>51.98</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>55.94</v>
+        <v>58.11</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>50.2</v>
+        <v>57.87</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="P13" s="12" t="n">
-        <v>23000</v>
+        <v>50.13</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>22995.65</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>4.71</v>
+        <v>2.7</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>52.76</v>
+        <v>50.43</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>60</v>
+        <v>55.86</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>60.35</v>
+        <v>50.13</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>50.87</v>
-      </c>
-      <c r="P14" s="13" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P14" s="12" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>6.86</v>
+        <v>4.71</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>52.59</v>
+        <v>52.67</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>60.15</v>
+        <v>59.91</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>60.35</v>
+        <v>60.27</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>50.87</v>
-      </c>
-      <c r="P15" s="10" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q15" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+        <v>50.8</v>
+      </c>
+      <c r="P15" s="13" t="inlineStr"/>
+      <c r="Q15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>3.69</v>
+        <v>2.66</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>6.54</v>
+        <v>6.86</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>387</v>
+        <v>249</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>362</v>
+        <v>500</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>53.1</v>
+        <v>52.5</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>62.56</v>
+        <v>60.06</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>68.48999999999999</v>
+        <v>60.27</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>63.82</v>
-      </c>
-      <c r="P16" s="14" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>4.93</v>
+        <v>6.54</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>181</v>
+        <v>388</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>568</v>
+        <v>362</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.32</v>
+        <v>1.07</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>53.45</v>
+        <v>53.01</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>61.95</v>
+        <v>62.46</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>69.43000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>64.22</v>
-      </c>
-      <c r="P17" s="15" t="n">
-        <v>23010.95</v>
+        <v>63.73</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>23126.3</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>6.03</v>
+        <v>4.93</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>253</v>
+        <v>569</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>1.96</v>
+        <v>0.32</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>55.69</v>
+        <v>53.36</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>68.56999999999999</v>
+        <v>61.86</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>79.31</v>
+        <v>69.33</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>81.17</v>
-      </c>
-      <c r="P18" s="9" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P18" s="15" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>8.529999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>3.2</v>
+        <v>6.03</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>54.14</v>
+        <v>55.59</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>65.56</v>
+        <v>68.47</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>74.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>75.17</v>
-      </c>
-      <c r="P19" s="16" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>16.52</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>53.45</v>
+        <v>54.04</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>66.02</v>
+        <v>65.47</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>76.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>79.56999999999999</v>
-      </c>
-      <c r="P20" s="17" t="n">
-        <v>23206.45</v>
+        <v>75.06999999999999</v>
+      </c>
+      <c r="P20" s="16" t="n">
+        <v>23144.2</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>10.32</v>
+        <v>16.52</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>52.07</v>
+        <v>53.36</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>63.76</v>
+        <v>65.92</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>74.77</v>
+        <v>76.8</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>78.23999999999999</v>
-      </c>
-      <c r="P21" s="10" t="n">
-        <v>23109.7</v>
+        <v>79.47</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>4.69</v>
+        <v>10.32</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>50.52</v>
+        <v>51.98</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>61.95</v>
+        <v>63.66</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>73.56</v>
+        <v>74.67</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>79.31</v>
-      </c>
-      <c r="P22" s="11" t="n">
-        <v>22997.25</v>
+        <v>78.27</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>23109.7</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>5.62</v>
+        <v>4.69</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>573</v>
+        <v>435</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>3.27</v>
+        <v>1.39</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>49.91</v>
+        <v>50.43</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>60</v>
+        <v>61.86</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>70.36</v>
+        <v>73.47</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>79.17</v>
-      </c>
-      <c r="P23" s="18" t="n">
-        <v>22891.3</v>
+        <v>79.2</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>2</v>
+        <v>5.62</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>690</v>
+        <v>574</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>11.9</v>
+        <v>3.28</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>33.37</v>
+        <v>5.84</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>46.8</v>
+        <v>49.83</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>50.08</v>
+        <v>59.91</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>53.14</v>
+        <v>70.27</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>61.28</v>
-      </c>
-      <c r="P24" s="19" t="n">
-        <v>22599.8</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="P24" s="18" t="n">
+        <v>22891.3</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>174</v>
+        <v>691</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>574</v>
+        <v>58</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>39.21</v>
+        <v>46.72</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>27.77</v>
+        <v>53.07</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>22.03</v>
-      </c>
-      <c r="P25" s="20" t="n">
-        <v>22114.45</v>
+        <v>61.2</v>
+      </c>
+      <c r="P25" s="19" t="n">
+        <v>22599.8</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>43.35</v>
+        <v>39.14</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>44.36</v>
+        <v>38.44</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>36.32</v>
+        <v>27.73</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>30.71</v>
-      </c>
-      <c r="P26" s="21" t="n">
-        <v>22233.85</v>
+        <v>22</v>
+      </c>
+      <c r="P26" s="20" t="n">
+        <v>22114.45</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>597</v>
+        <v>160</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>151</v>
+        <v>590</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>3.95</v>
+        <v>0.27</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>45.08</v>
+        <v>43.28</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>51.13</v>
+        <v>44.29</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>43.93</v>
+        <v>36.27</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>43.26</v>
-      </c>
-      <c r="P27" s="22" t="n">
-        <v>22370.15</v>
+        <v>30.67</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>22233.85</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>103</v>
+        <v>597</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>646</v>
+        <v>152</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.16</v>
+        <v>3.93</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>41.62</v>
+        <v>45</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>44.96</v>
+        <v>51.05</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>30.44</v>
+        <v>43.87</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="P28" s="23" t="n">
-        <v>22173.7</v>
+        <v>43.2</v>
+      </c>
+      <c r="P28" s="22" t="n">
+        <v>22370.15</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>360</v>
+        <v>103</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>389</v>
+        <v>647</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.93</v>
+        <v>0.16</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>45.08</v>
+        <v>41.55</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>55.19</v>
+        <v>44.89</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>44.99</v>
+        <v>30.4</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>45.39</v>
-      </c>
-      <c r="P29" s="24" t="n">
-        <v>22465.35</v>
+        <v>24.27</v>
+      </c>
+      <c r="P29" s="23" t="n">
+        <v>22173.7</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>1.9</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>44.98</v>
+        <v>45</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>57.14</v>
+        <v>55.11</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>45.53</v>
+        <v>44.93</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>43.26</v>
-      </c>
-      <c r="P30" s="25" t="n">
-        <v>22497.7</v>
+        <v>45.33</v>
+      </c>
+      <c r="P30" s="24" t="n">
+        <v>22465.35</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>440</v>
+        <v>351</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>43.94</v>
+        <v>44.91</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>57.44</v>
+        <v>57.06</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>43.26</v>
+        <v>45.47</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="P31" s="26" t="n">
-        <v>22451.85</v>
+        <v>43.2</v>
+      </c>
+      <c r="P31" s="25" t="n">
+        <v>22497.7</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>468</v>
+        <v>308</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>2.73</v>
+        <v>2.04</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>43.77</v>
+        <v>43.87</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>60</v>
+        <v>57.36</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>43.66</v>
+        <v>43.2</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="P32" s="27" t="n">
-        <v>22521.1</v>
+        <v>37.73</v>
+      </c>
+      <c r="P32" s="26" t="n">
+        <v>22451.85</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>219</v>
+        <v>468</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>530</v>
+        <v>280</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.41</v>
+        <v>1.67</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>42.91</v>
+        <v>43.7</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>58.95</v>
+        <v>60.06</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>37.92</v>
+        <v>43.73</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="P33" s="28" t="n">
-        <v>22437.95</v>
+        <v>40</v>
+      </c>
+      <c r="P33" s="27" t="n">
+        <v>22521.1</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>44.12</v>
+        <v>42.83</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>66.47</v>
+        <v>59.01</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>47.66</v>
+        <v>38</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>42.19</v>
-      </c>
-      <c r="P34" s="29" t="n">
-        <v>22657</v>
+        <v>31.87</v>
+      </c>
+      <c r="P34" s="28" t="n">
+        <v>22437.95</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>47.75</v>
+        <v>44.04</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>72.48</v>
+        <v>66.37</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>61.28</v>
+        <v>47.6</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>60.61</v>
-      </c>
-      <c r="P35" s="13" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P35" s="29" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>47.83</v>
+        <v>47.67</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>73.23</v>
+        <v>72.52</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>61.28</v>
+        <v>61.33</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>60.61</v>
-      </c>
-      <c r="P36" s="30" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q36" s="1" t="n">
-        <v>0.31</v>
-      </c>
+        <v>60.67</v>
+      </c>
+      <c r="P36" s="13" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>47.05</v>
+        <v>47.75</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>73.98</v>
+        <v>73.27</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>62.08</v>
+        <v>61.33</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>63.42</v>
-      </c>
-      <c r="P37" s="18" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P37" s="30" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>3.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>8.33</v>
+        <v>1.98</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46.35</v>
+        <v>46.97</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>74.89</v>
+        <v>73.87</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>61.15</v>
+        <v>62.13</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>63.55</v>
-      </c>
-      <c r="P38" s="31" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P38" s="18" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>373</v>
+        <v>567</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>372</v>
+        <v>182</v>
       </c>
       <c r="H39" s="1" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="J39" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="J39" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="K39" s="1" t="n">
-        <v>2.48</v>
+        <v>8.33</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>44.27</v>
+        <v>46.27</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>68.27</v>
+        <v>74.77</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>48.87</v>
+        <v>61.2</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="P39" s="29" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P39" s="31" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>445</v>
+        <v>373</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>301</v>
+        <v>373</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1.48</v>
+        <v>1</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>42.19</v>
+        <v>44.19</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>68.72</v>
+        <v>68.17</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>48.06</v>
+        <v>48.8</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>45.66</v>
-      </c>
-      <c r="P40" s="19" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P40" s="29" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>365</v>
+        <v>445</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>382</v>
+        <v>302</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>41.32</v>
+        <v>42.11</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>66.92</v>
+        <v>68.62</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>41.92</v>
+        <v>48.13</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>38.05</v>
-      </c>
-      <c r="P41" s="32" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P41" s="19" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>492</v>
+        <v>366</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>256</v>
+        <v>382</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1.92</v>
+        <v>0.96</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>41.49</v>
+        <v>41.25</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>67.22</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>40.99</v>
+        <v>42</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="P42" s="27" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P42" s="32" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>584</v>
+        <v>256</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>39.93</v>
+        <v>41.42</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>65.11</v>
+        <v>67.12</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>32.58</v>
+        <v>40.93</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="P43" s="33" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P43" s="27" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>44.44</v>
+        <v>39.86</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>71.28</v>
+        <v>65.02</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>42.32</v>
+        <v>32.53</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="P44" s="34" t="n">
-        <v>22531.15</v>
+        <v>23.33</v>
+      </c>
+      <c r="P44" s="33" t="n">
+        <v>22461.05</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>423</v>
+        <v>256</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>44.97</v>
+        <v>44.37</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>72.48</v>
+        <v>71.17</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>46.46</v>
+        <v>42.27</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>35.51</v>
-      </c>
-      <c r="P45" s="35" t="n">
-        <v>22613.1</v>
+        <v>31.87</v>
+      </c>
+      <c r="P45" s="34" t="n">
+        <v>22531.15</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="E46" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L46" s="1" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="M46" s="1" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="N46" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O46" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P46" s="35" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q46" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F46" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>297</v>
-      </c>
-      <c r="H46" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I46" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J46" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K46" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L46" s="1" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="M46" s="1" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="N46" s="1" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="O46" s="1" t="n">
-        <v>29.77</v>
-      </c>
-      <c r="P46" s="36" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q46" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>695</v>
+        <v>298</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>42.36</v>
+        <v>43.33</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>70.38</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>37.78</v>
+        <v>43.73</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>22.96</v>
-      </c>
-      <c r="P47" s="37" t="n">
-        <v>22299.9</v>
+        <v>29.73</v>
+      </c>
+      <c r="P47" s="36" t="n">
+        <v>22377.35</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>2.25</v>
+        <v>0.74</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>560</v>
+        <v>696</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>50.09</v>
+        <v>42.29</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>82.41</v>
+        <v>70.27</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>67.56</v>
+        <v>37.73</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="P48" s="38" t="n">
-        <v>22795.75</v>
+        <v>22.93</v>
+      </c>
+      <c r="P48" s="37" t="n">
+        <v>22299.9</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>4.87</v>
+        <v>2.25</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>4.31</v>
+        <v>2.28</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>323</v>
+        <v>188</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>54.96</v>
+        <v>50</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>87.22</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>82.23999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="P49" s="39" t="n">
-        <v>23115.65</v>
+        <v>50.53</v>
+      </c>
+      <c r="P49" s="38" t="n">
+        <v>22795.75</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>5.91</v>
+        <v>4.87</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>3.34</v>
+        <v>4.32</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>498</v>
+        <v>324</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>1.99</v>
+        <v>0.76</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J50" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>56.7</v>
+        <v>54.86</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>87.97</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>87.84999999999999</v>
+        <v>82.27</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>82.64</v>
-      </c>
-      <c r="P50" s="40" t="n">
-        <v>23214</v>
+        <v>73.47</v>
+      </c>
+      <c r="P50" s="39" t="n">
+        <v>23115.65</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>3.68</v>
+        <v>5.91</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>604</v>
+        <v>499</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>6.11</v>
+        <v>1.69</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>52.7</v>
+        <v>56.6</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>86.92</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>86.78</v>
+        <v>87.87</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>80.91</v>
-      </c>
-      <c r="P51" s="41" t="n">
-        <v>23133.4</v>
+        <v>82.67</v>
+      </c>
+      <c r="P51" s="40" t="n">
+        <v>23214</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>2.22</v>
+        <v>3.68</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>343</v>
+        <v>605</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>404</v>
+        <v>145</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>47.83</v>
+        <v>52.6</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>79.84999999999999</v>
+        <v>86.94</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>73.83</v>
+        <v>86.8</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>62.62</v>
-      </c>
-      <c r="P52" s="42" t="n">
-        <v>22808.25</v>
+        <v>80.93000000000001</v>
+      </c>
+      <c r="P52" s="41" t="n">
+        <v>23133.4</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>3.01</v>
+        <v>2.66</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>530</v>
+        <v>344</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>218</v>
+        <v>404</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>2.43</v>
+        <v>0.85</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>47.04</v>
+        <v>47.74</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>80.75</v>
+        <v>79.73</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>77.3</v>
+        <v>73.87</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>66.89</v>
-      </c>
-      <c r="P53" s="43" t="n">
-        <v>22830.75</v>
+        <v>62.67</v>
+      </c>
+      <c r="P53" s="42" t="n">
+        <v>22808.25</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>3.62</v>
+        <v>2.33</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>2.67</v>
+        <v>3.02</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>43.73</v>
+        <v>46.96</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>77.59</v>
+        <v>80.63</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>65.02</v>
+        <v>77.2</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>49.93</v>
-      </c>
-      <c r="P54" s="13" t="inlineStr"/>
-      <c r="Q54" s="1" t="inlineStr"/>
+        <v>66.93000000000001</v>
+      </c>
+      <c r="P54" s="43" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q54" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>2.07</v>
+        <v>3.64</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>3.13</v>
+        <v>2.68</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>42</v>
+        <v>43.65</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>77.56999999999999</v>
+        <v>77.48</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>73.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>55.27</v>
-      </c>
-      <c r="P55" s="44" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q55" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.87</v>
+      </c>
+      <c r="P55" s="13" t="inlineStr"/>
+      <c r="Q55" s="1" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>4.03</v>
+        <v>3.14</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>377</v>
+        <v>552</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>43.81</v>
+        <v>41.93</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>79.31</v>
+        <v>77.47</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>80.77</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="P56" s="45" t="n">
-        <v>22871</v>
+        <v>55.2</v>
+      </c>
+      <c r="P56" s="44" t="n">
+        <v>22683.55</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>3.01</v>
+        <v>2.38</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>5.63</v>
+        <v>4.03</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>285</v>
+        <v>371</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>462</v>
+        <v>377</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>44.13</v>
+        <v>43.74</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>77.97</v>
+        <v>79.2</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>81.31</v>
+        <v>80.67</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>70.89</v>
-      </c>
-      <c r="P57" s="46" t="n">
-        <v>22765.6</v>
+        <v>70.27</v>
+      </c>
+      <c r="P57" s="45" t="n">
+        <v>22871</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>3.61</v>
+        <v>3.02</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>647</v>
+        <v>285</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>6.34</v>
+        <v>0.62</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>8.16</v>
+        <v>1.94</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>44.29</v>
+        <v>44.06</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>80.23999999999999</v>
+        <v>77.87</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>87.05</v>
+        <v>81.2</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>81.58</v>
-      </c>
-      <c r="P58" s="42" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P58" s="46" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>2.12</v>
+        <v>3.62</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>589</v>
+        <v>102</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>40.16</v>
+        <v>44.22</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>71.95999999999999</v>
+        <v>80.13</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>78.09999999999999</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>62.22</v>
-      </c>
-      <c r="P59" s="32" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P59" s="42" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>5.24</v>
+        <v>2.12</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>509</v>
+        <v>590</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>42.7</v>
+        <v>40.1</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>78.91</v>
+        <v>71.87</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>87.45</v>
+        <v>78</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>82.23999999999999</v>
-      </c>
-      <c r="P60" s="42" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P60" s="32" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>8.58</v>
+        <v>5.24</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>496</v>
+        <v>237</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>249</v>
+        <v>510</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>43.47</v>
+        <v>42.63</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>82.11</v>
+        <v>78.8</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>91.86</v>
+        <v>87.33</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="P61" s="47" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P61" s="42" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>13.69</v>
+        <v>8.58</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>41.15</v>
+        <v>43.4</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>81.70999999999999</v>
+        <v>82</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>93.59</v>
+        <v>91.73</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>92.66</v>
-      </c>
-      <c r="P62" s="48" t="n">
-        <v>23042.35</v>
+        <v>89.87</v>
+      </c>
+      <c r="P62" s="47" t="n">
+        <v>22991.5</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>275</v>
+        <v>510</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>474</v>
+        <v>238</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0.58</v>
+        <v>2.14</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>38.76</v>
+        <v>41.08</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>76.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>93.31999999999999</v>
+        <v>93.47</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>92.12</v>
-      </c>
-      <c r="P63" s="49" t="n">
-        <v>22865.8</v>
+        <v>92.53</v>
+      </c>
+      <c r="P63" s="48" t="n">
+        <v>23042.35</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>580</v>
+        <v>275</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>167</v>
+        <v>475</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>3.47</v>
+        <v>0.58</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>4.48</v>
+        <v>0.53</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>39.39</v>
+        <v>38.69</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>79.04000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>95.33</v>
+        <v>93.2</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>96.53</v>
+        <v>92</v>
       </c>
       <c r="P64" s="49" t="n">
-        <v>22869.4</v>
+        <v>22865.8</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C65" s="1" t="n">
         <v>2</v>
@@ -4425,191 +4425,242 @@
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>503</v>
+        <v>581</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>243</v>
+        <v>167</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>2.07</v>
+        <v>3.48</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>3.43</v>
+        <v>4.48</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>37.32</v>
+        <v>39.33</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>75.03</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>92.79000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>94.79000000000001</v>
-      </c>
-      <c r="P65" s="29" t="n">
-        <v>22656.3</v>
+        <v>96.53</v>
+      </c>
+      <c r="P65" s="49" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>681</v>
+        <v>504</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>10.16</v>
+        <v>2.07</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>17.31</v>
+        <v>3.43</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>34.77</v>
+        <v>37.26</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>68.48999999999999</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>93.98999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>96.26000000000001</v>
-      </c>
-      <c r="P66" s="50" t="n">
-        <v>22595.55</v>
+        <v>94.8</v>
+      </c>
+      <c r="P66" s="29" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>244</v>
+        <v>681</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>501</v>
+        <v>67</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>0.49</v>
+        <v>10.16</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>0.75</v>
+        <v>17.31</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>31.26</v>
+        <v>34.77</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>52.93</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>84.27</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P67" s="23" t="n">
-        <v>22179.05</v>
+        <v>96.26000000000001</v>
+      </c>
+      <c r="P67" s="50" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J68" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L68" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M68" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N68" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O68" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P68" s="23" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q68" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="1" t="inlineStr"/>
+      <c r="E69" s="1" t="inlineStr"/>
+      <c r="F69" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G68" s="1" t="n">
+      <c r="G69" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H68" s="1" t="n">
+      <c r="H69" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr"/>
-      <c r="L68" s="1" t="n">
+      <c r="I69" s="1" t="inlineStr"/>
+      <c r="J69" s="1" t="inlineStr"/>
+      <c r="K69" s="1" t="inlineStr"/>
+      <c r="L69" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="M69" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N68" s="1" t="n">
+      <c r="N69" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O68" s="1" t="n">
+      <c r="O69" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P68" s="51" t="n">
+      <c r="P69" s="51" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q68" s="1" t="n">
+      <c r="Q69" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B68">
+  <conditionalFormatting sqref="B2:B69">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4619,7 +4670,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C68">
+  <conditionalFormatting sqref="C2:C69">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4629,7 +4680,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E68">
+  <conditionalFormatting sqref="D2:E69">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4641,7 +4692,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F68">
+  <conditionalFormatting sqref="F2:F69">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4651,7 +4702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G68">
+  <conditionalFormatting sqref="G2:G69">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4661,7 +4712,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H68">
+  <conditionalFormatting sqref="H2:H69">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4673,7 +4724,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I68">
+  <conditionalFormatting sqref="I2:I69">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4683,7 +4734,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J68">
+  <conditionalFormatting sqref="J2:J69">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4693,7 +4744,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K68">
+  <conditionalFormatting sqref="K2:K69">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4705,7 +4756,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O68">
+  <conditionalFormatting sqref="L2:O69">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4717,7 +4768,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q68">
+  <conditionalFormatting sqref="Q2:Q69">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="52">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EFDE"/>
+        <bgColor rgb="00D8EFDE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -346,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -499,6 +505,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -866,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -978,3497 +987,3497 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>4.9</v>
+        <v>3.16</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>452</v>
+        <v>298</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>299</v>
+        <v>448</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.51</v>
+        <v>0.67</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>2.25</v>
+        <v>0.95</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>57.9</v>
+        <v>56.19</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>64.13</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>59.12</v>
+        <v>56.06</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>54.19</v>
+        <v>49.93</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="D3" s="1" t="n">
-        <v>1.74</v>
+        <v>4.9</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>171</v>
+        <v>451</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>579</v>
+        <v>299</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.3</v>
+        <v>1.51</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.38</v>
+        <v>2.24</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>56.7</v>
+        <v>58</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>61.33</v>
+        <v>64.22</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>53.93</v>
+        <v>59.2</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>47.4</v>
+        <v>54.27</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>382</v>
+        <v>171</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>367</v>
+        <v>578</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>57.04</v>
+        <v>56.8</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>65.2</v>
+        <v>61.42</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>65.25</v>
+        <v>54</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>64.58</v>
+        <v>47.47</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>604</v>
+        <v>382</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>145</v>
+        <v>366</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>4.17</v>
+        <v>1.04</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>11.13</v>
+        <v>0.79</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>55.67</v>
+        <v>57.14</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>64.45</v>
+        <v>65.33</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>23348.4</v>
+        <v>64.67</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>4.91</v>
+        <v>4.16</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7.66</v>
+        <v>11.12</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>52.75</v>
+        <v>55.77</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>56.16</v>
+        <v>65.02</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>51.53</v>
+        <v>64.53</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>45.54</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>87</v>
+        <v>624</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>664</v>
+        <v>126</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.13</v>
+        <v>4.95</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.6</v>
+        <v>7.68</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>49.83</v>
+        <v>52.84</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>50</v>
+        <v>56.24</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>37.95</v>
+        <v>51.6</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>26.23</v>
+        <v>45.6</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>2.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>242</v>
+        <v>87</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>505</v>
+        <v>663</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>56.36</v>
+        <v>49.91</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>60.81</v>
+        <v>50.08</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>58.19</v>
+        <v>38</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>51.8</v>
+        <v>26.27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>23368.85</v>
+        <v>22908.05</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>364</v>
+        <v>242</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>386</v>
+        <v>504</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>57.14</v>
+        <v>56.45</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>63.66</v>
+        <v>60.9</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>65.65000000000001</v>
+        <v>58.27</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>63.65</v>
+        <v>51.87</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>23433.95</v>
+        <v>23368.85</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>40</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>56.97</v>
+        <v>57.07</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>65.02</v>
+        <v>63.76</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>66.84</v>
+        <v>65.73</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>66.18000000000001</v>
+        <v>63.73</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>23301.15</v>
+        <v>23433.95</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.77</v>
+        <v>2.34</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>537</v>
+        <v>354</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>212</v>
+        <v>394</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>2.53</v>
+        <v>0.9</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>56.63</v>
+        <v>56.9</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>64.56</v>
+        <v>65.11</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>69.73</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>23264.8</v>
+        <v>66.13</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1.76</v>
+        <v>2.87</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.49</v>
+        <v>2.77</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>417</v>
+        <v>536</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>333</v>
+        <v>212</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>53.01</v>
+        <v>56.55</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>60.21</v>
+        <v>64.66</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>61.47</v>
+        <v>69.83</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="P12" s="10" t="n">
-        <v>23111.65</v>
+        <v>68.62</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>51.98</v>
+        <v>52.93</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>58.11</v>
+        <v>60.3</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>57.87</v>
+        <v>61.55</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>50.13</v>
+        <v>57.01</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>22995.65</v>
+        <v>23111.65</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>278</v>
+        <v>443</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>471</v>
+        <v>305</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.59</v>
+        <v>1.45</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>50.43</v>
+        <v>51.9</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>55.86</v>
+        <v>58.2</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>50.13</v>
+        <v>57.94</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>41.33</v>
+        <v>50.2</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>23000</v>
+        <v>22995.65</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>4.71</v>
+        <v>2.7</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>52.67</v>
+        <v>50.52</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>59.91</v>
+        <v>55.94</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>60.27</v>
+        <v>50.2</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P15" s="13" t="inlineStr"/>
-      <c r="Q15" s="1" t="inlineStr"/>
+        <v>41.39</v>
+      </c>
+      <c r="P15" s="13" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>6.86</v>
+        <v>4.71</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>52.5</v>
+        <v>52.59</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>60.06</v>
+        <v>60</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>60.27</v>
+        <v>60.35</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P16" s="10" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q16" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+        <v>50.87</v>
+      </c>
+      <c r="P16" s="14" t="inlineStr"/>
+      <c r="Q16" s="1" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>3.69</v>
+        <v>2.66</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>6.54</v>
+        <v>6.84</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>388</v>
+        <v>249</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>362</v>
+        <v>499</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>53.01</v>
+        <v>52.41</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>62.46</v>
+        <v>60.15</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.35</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <v>23126.3</v>
+        <v>50.87</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>4.93</v>
+        <v>6.53</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>181</v>
+        <v>388</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>569</v>
+        <v>361</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.32</v>
+        <v>1.07</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>53.36</v>
+        <v>52.93</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>61.86</v>
+        <v>62.56</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>69.33</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>64.13</v>
+        <v>63.82</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>23010.95</v>
+        <v>23126.3</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>6.03</v>
+        <v>4.92</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>497</v>
+        <v>181</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>253</v>
+        <v>568</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.96</v>
+        <v>0.32</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>55.59</v>
+        <v>53.28</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>68.47</v>
+        <v>61.95</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>79.2</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>23261.85</v>
+        <v>64.22</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>8.529999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>3.2</v>
+        <v>6.02</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>354</v>
+        <v>253</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>54.04</v>
+        <v>55.52</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>65.47</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>74</v>
+        <v>79.17</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="P20" s="16" t="n">
-        <v>23144.2</v>
+        <v>81.04000000000001</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>16.52</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>53.36</v>
+        <v>53.97</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>65.92</v>
+        <v>65.56</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>76.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>79.47</v>
+        <v>75.17</v>
       </c>
       <c r="P21" s="17" t="n">
-        <v>23206.45</v>
+        <v>23144.2</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>3.09</v>
-      </c>
       <c r="F22" s="1" t="n">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>4.15</v>
+        <v>1.84</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>51.98</v>
+        <v>53.28</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>63.66</v>
+        <v>66.02</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>74.67</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>78.27</v>
-      </c>
-      <c r="P22" s="10" t="n">
-        <v>23109.7</v>
+        <v>79.56999999999999</v>
+      </c>
+      <c r="P22" s="18" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>4.69</v>
+        <v>10.29</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>1.26</v>
+        <v>4.16</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>50.43</v>
+        <v>51.9</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>61.86</v>
+        <v>63.76</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>73.47</v>
+        <v>74.77</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>79.2</v>
+        <v>78.37</v>
       </c>
       <c r="P23" s="11" t="n">
-        <v>22997.25</v>
+        <v>23109.7</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>5.62</v>
+        <v>4.67</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>574</v>
+        <v>434</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>3.28</v>
+        <v>1.38</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>49.83</v>
+        <v>50.34</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>59.91</v>
+        <v>61.95</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>70.27</v>
+        <v>73.56</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P24" s="18" t="n">
-        <v>22891.3</v>
+        <v>79.31</v>
+      </c>
+      <c r="P24" s="12" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>691</v>
+        <v>573</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>11.91</v>
+        <v>3.27</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>33.39</v>
+        <v>5.84</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>46.72</v>
+        <v>49.74</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>53.07</v>
+        <v>70.36</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>61.2</v>
+        <v>79.17</v>
       </c>
       <c r="P25" s="19" t="n">
-        <v>22599.8</v>
+        <v>22891.3</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.85</v>
+        <v>1.99</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>174</v>
+        <v>690</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>575</v>
+        <v>58</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.3</v>
+        <v>11.9</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.74</v>
+        <v>33.38</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>39.14</v>
+        <v>46.63</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>38.44</v>
+        <v>50.08</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>27.73</v>
+        <v>53.14</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>22</v>
+        <v>61.28</v>
       </c>
       <c r="P26" s="20" t="n">
-        <v>22114.45</v>
+        <v>22599.8</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>43.28</v>
+        <v>39.03</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>44.29</v>
+        <v>38.5</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>36.27</v>
+        <v>27.77</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>30.67</v>
+        <v>22.03</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>22233.85</v>
+        <v>22114.45</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>597</v>
+        <v>160</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>152</v>
+        <v>589</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>3.93</v>
+        <v>0.27</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>45</v>
+        <v>43.18</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>51.05</v>
+        <v>44.36</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>43.87</v>
+        <v>36.32</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>43.2</v>
+        <v>30.71</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>22370.15</v>
+        <v>22233.85</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>103</v>
+        <v>597</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>647</v>
+        <v>151</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.16</v>
+        <v>3.95</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>41.55</v>
+        <v>44.91</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>44.89</v>
+        <v>51.13</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>30.4</v>
+        <v>43.93</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>24.27</v>
+        <v>43.26</v>
       </c>
       <c r="P29" s="23" t="n">
-        <v>22173.7</v>
+        <v>22370.15</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>360</v>
+        <v>103</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>390</v>
+        <v>646</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>45</v>
+        <v>41.45</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>55.11</v>
+        <v>44.96</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>44.93</v>
+        <v>30.44</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>45.33</v>
+        <v>24.3</v>
       </c>
       <c r="P30" s="24" t="n">
-        <v>22465.35</v>
+        <v>22173.7</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>399</v>
+        <v>359</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L31" s="1" t="n">
         <v>44.91</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>57.06</v>
+        <v>55.04</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>45.47</v>
+        <v>44.99</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>43.2</v>
+        <v>45.39</v>
       </c>
       <c r="P31" s="25" t="n">
-        <v>22497.7</v>
+        <v>22465.35</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>43.87</v>
+        <v>44.81</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>57.36</v>
+        <v>56.99</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>43.2</v>
+        <v>45.53</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>37.73</v>
+        <v>43.26</v>
       </c>
       <c r="P32" s="26" t="n">
-        <v>22451.85</v>
+        <v>22497.7</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>468</v>
+        <v>307</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>280</v>
+        <v>441</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1.67</v>
+        <v>0.7</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>43.7</v>
+        <v>43.77</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>60.06</v>
+        <v>57.29</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>43.73</v>
+        <v>43.26</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>40</v>
+        <v>37.78</v>
       </c>
       <c r="P33" s="27" t="n">
-        <v>22521.1</v>
+        <v>22451.85</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>220</v>
+        <v>467</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>530</v>
+        <v>280</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.42</v>
+        <v>1.67</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>42.83</v>
+        <v>43.6</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>59.01</v>
+        <v>60</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>38</v>
+        <v>43.79</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>31.87</v>
+        <v>40.05</v>
       </c>
       <c r="P34" s="28" t="n">
-        <v>22437.95</v>
+        <v>22521.1</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J35" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>44.04</v>
+        <v>42.73</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>66.37</v>
+        <v>58.95</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>47.6</v>
+        <v>38.05</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>42.13</v>
+        <v>31.91</v>
       </c>
       <c r="P35" s="29" t="n">
-        <v>22657</v>
+        <v>22437.95</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>3.73</v>
+        <v>2.01</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>47.67</v>
+        <v>43.94</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>72.52</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>61.33</v>
+        <v>47.53</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P36" s="13" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr"/>
+        <v>42.19</v>
+      </c>
+      <c r="P36" s="30" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>3.98</v>
+        <v>3.71</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>47.75</v>
+        <v>47.58</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>73.27</v>
+        <v>72.48</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>61.33</v>
+        <v>61.28</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P37" s="30" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q37" s="1" t="n">
-        <v>0.31</v>
-      </c>
+        <v>60.61</v>
+      </c>
+      <c r="P37" s="14" t="inlineStr"/>
+      <c r="Q37" s="1" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>4.3</v>
+        <v>3.96</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>46.97</v>
+        <v>47.66</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>73.87</v>
+        <v>73.23</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>62.13</v>
+        <v>61.28</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P38" s="18" t="n">
-        <v>22897.2</v>
+        <v>60.61</v>
+      </c>
+      <c r="P38" s="31" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>4.64</v>
+        <v>4.28</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>567</v>
+        <v>362</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>182</v>
+        <v>385</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>3.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>8.33</v>
+        <v>1.99</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>46.27</v>
+        <v>46.88</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>74.77</v>
+        <v>73.83</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>61.2</v>
+        <v>62.08</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P39" s="31" t="n">
-        <v>22929.45</v>
+        <v>63.42</v>
+      </c>
+      <c r="P39" s="19" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1.67</v>
+        <v>4.62</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>373</v>
+        <v>566</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>373</v>
+        <v>182</v>
       </c>
       <c r="H40" s="1" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="J40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="J40" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="K40" s="1" t="n">
-        <v>2.48</v>
+        <v>8.31</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>44.19</v>
+        <v>46.18</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>68.17</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>48.8</v>
+        <v>61.15</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P40" s="29" t="n">
-        <v>22651.3</v>
+        <v>63.55</v>
+      </c>
+      <c r="P40" s="32" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>445</v>
+        <v>373</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>302</v>
+        <v>372</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>1.47</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J41" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>42.11</v>
+        <v>44.1</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>68.62</v>
+        <v>68.12</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>48.13</v>
+        <v>48.87</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P41" s="19" t="n">
-        <v>22602.85</v>
+        <v>47</v>
+      </c>
+      <c r="P41" s="30" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>366</v>
+        <v>445</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>382</v>
+        <v>301</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.96</v>
+        <v>1.48</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>41.25</v>
+        <v>42.01</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>66.81999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>42</v>
+        <v>48.2</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P42" s="32" t="n">
-        <v>22578.15</v>
+        <v>45.79</v>
+      </c>
+      <c r="P42" s="20" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>41.42</v>
+        <v>41.15</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>67.12</v>
+        <v>66.77</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>40.93</v>
+        <v>41.92</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P43" s="27" t="n">
-        <v>22521.75</v>
+        <v>38.18</v>
+      </c>
+      <c r="P43" s="33" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>164</v>
+        <v>492</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.28</v>
+        <v>1.92</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>39.86</v>
+        <v>41.32</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>65.02</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>32.53</v>
+        <v>40.85</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P44" s="33" t="n">
-        <v>22461.05</v>
+        <v>34.45</v>
+      </c>
+      <c r="P44" s="28" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>494</v>
+        <v>584</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>44.37</v>
+        <v>39.76</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>71.17</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>42.27</v>
+        <v>32.58</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>31.87</v>
+        <v>23.36</v>
       </c>
       <c r="P45" s="34" t="n">
-        <v>22531.15</v>
+        <v>22461.05</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>326</v>
+        <v>493</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>44.89</v>
+        <v>44.27</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>72.37</v>
+        <v>71.13</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>46.4</v>
+        <v>42.32</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>35.47</v>
+        <v>31.91</v>
       </c>
       <c r="P46" s="35" t="n">
-        <v>22613.1</v>
+        <v>22531.15</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="E47" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>423</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="L47" s="1" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="M47" s="1" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="N47" s="1" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="O47" s="1" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="P47" s="36" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q47" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F47" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H47" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I47" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J47" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K47" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L47" s="1" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="M47" s="1" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="N47" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O47" s="1" t="n">
-        <v>29.73</v>
-      </c>
-      <c r="P47" s="36" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q47" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>696</v>
+        <v>297</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.12</v>
+        <v>3.91</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>42.29</v>
+        <v>43.23</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>70.27</v>
+        <v>71.28</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>37.73</v>
+        <v>43.79</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>22.93</v>
+        <v>29.77</v>
       </c>
       <c r="P48" s="37" t="n">
-        <v>22299.9</v>
+        <v>22377.35</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>2.25</v>
+        <v>0.74</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>561</v>
+        <v>695</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>50</v>
+        <v>42.19</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>82.43000000000001</v>
+        <v>70.23</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.65</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>50.53</v>
+        <v>22.96</v>
       </c>
       <c r="P49" s="38" t="n">
-        <v>22795.75</v>
+        <v>22299.9</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>4.87</v>
+        <v>2.27</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>4.32</v>
+        <v>2.29</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>425</v>
+        <v>560</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>54.86</v>
+        <v>49.91</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>87.23999999999999</v>
+        <v>82.41</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>82.27</v>
+        <v>67.56</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>73.47</v>
+        <v>50.6</v>
       </c>
       <c r="P50" s="39" t="n">
-        <v>23115.65</v>
+        <v>22795.75</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>5.91</v>
+        <v>4.93</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>3.35</v>
+        <v>4.34</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>250</v>
+        <v>424</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>56.6</v>
+        <v>54.78</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>87.98999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>87.87</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>82.67</v>
+        <v>73.56</v>
       </c>
       <c r="P51" s="40" t="n">
-        <v>23214</v>
+        <v>23115.65</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>3.68</v>
+        <v>6.02</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>2.92</v>
+        <v>3.36</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>605</v>
+        <v>498</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>4.17</v>
+        <v>1.99</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>52.6</v>
+        <v>56.52</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>86.94</v>
+        <v>87.97</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>86.8</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>80.93000000000001</v>
+        <v>82.64</v>
       </c>
       <c r="P52" s="41" t="n">
-        <v>23133.4</v>
+        <v>23214</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>2.22</v>
+        <v>3.73</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>344</v>
+        <v>605</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>404</v>
+        <v>144</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0.85</v>
+        <v>4.2</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>1.86</v>
+        <v>6.17</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>47.74</v>
+        <v>52.52</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>79.73</v>
+        <v>86.92</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>73.87</v>
+        <v>86.78</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>62.67</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="P53" s="42" t="n">
-        <v>22808.25</v>
+        <v>23133.4</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>531</v>
+        <v>344</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>218</v>
+        <v>403</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>2.58</v>
+        <v>1.88</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>46.96</v>
+        <v>47.65</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>80.63</v>
+        <v>79.7</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>77.2</v>
+        <v>73.83</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>66.93000000000001</v>
+        <v>62.62</v>
       </c>
       <c r="P54" s="43" t="n">
-        <v>22830.75</v>
+        <v>22808.25</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>3.64</v>
+        <v>2.31</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>2.68</v>
+        <v>3.01</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>43.65</v>
+        <v>46.86</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>77.48</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>77.17</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>49.87</v>
-      </c>
-      <c r="P55" s="13" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr"/>
+        <v>66.89</v>
+      </c>
+      <c r="P55" s="44" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q55" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2.08</v>
+        <v>3.62</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>3.14</v>
+        <v>2.67</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>41.93</v>
+        <v>43.55</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>77.47</v>
+        <v>77.44</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="P56" s="44" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q56" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.8</v>
+      </c>
+      <c r="P56" s="14" t="inlineStr"/>
+      <c r="Q56" s="1" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>4.03</v>
+        <v>3.12</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>371</v>
+        <v>195</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>377</v>
+        <v>552</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0.98</v>
+        <v>0.35</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>43.74</v>
+        <v>41.84</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>79.2</v>
+        <v>77.44</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>80.67</v>
+        <v>73.03</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>70.27</v>
+        <v>55.14</v>
       </c>
       <c r="P57" s="45" t="n">
-        <v>22871</v>
+        <v>22683.55</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>3.02</v>
+        <v>2.36</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>285</v>
+        <v>371</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>463</v>
+        <v>376</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.62</v>
+        <v>0.99</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>45</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>44.06</v>
+        <v>43.65</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>77.87</v>
+        <v>79.17</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>81.2</v>
+        <v>80.64</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>70.8</v>
+        <v>70.23</v>
       </c>
       <c r="P58" s="46" t="n">
-        <v>22765.6</v>
+        <v>22871</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>648</v>
+        <v>284</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>6.35</v>
+        <v>0.61</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>44.22</v>
+        <v>43.97</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>80.13</v>
+        <v>77.84</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.17</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P59" s="42" t="n">
-        <v>22821.4</v>
+        <v>70.76000000000001</v>
+      </c>
+      <c r="P59" s="47" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>2.12</v>
+        <v>3.61</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>156</v>
+        <v>647</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.26</v>
+        <v>6.34</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>0.37</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>40.1</v>
+        <v>44.13</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>71.87</v>
+        <v>80.11</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>78</v>
+        <v>86.92</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P60" s="32" t="n">
-        <v>22570.05</v>
+        <v>81.58</v>
+      </c>
+      <c r="P60" s="43" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>5.24</v>
+        <v>2.11</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>237</v>
+        <v>155</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>510</v>
+        <v>590</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>42.63</v>
+        <v>40</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>78.8</v>
+        <v>71.83</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>87.33</v>
+        <v>77.97</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P61" s="42" t="n">
-        <v>22810.85</v>
+        <v>62.08</v>
+      </c>
+      <c r="P61" s="33" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>8.58</v>
+        <v>5.22</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>496</v>
+        <v>237</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>250</v>
+        <v>509</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>1.98</v>
+        <v>0.47</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>43.4</v>
+        <v>42.54</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>82</v>
+        <v>78.77</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>91.73</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>89.87</v>
-      </c>
-      <c r="P62" s="47" t="n">
-        <v>22991.5</v>
+        <v>82.11</v>
+      </c>
+      <c r="P62" s="43" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>41.08</v>
+        <v>43.31</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>81.59999999999999</v>
+        <v>81.98</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>93.47</v>
+        <v>91.72</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>92.53</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="P63" s="48" t="n">
-        <v>23042.35</v>
+        <v>22991.5</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>275</v>
+        <v>510</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>475</v>
+        <v>237</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>0.58</v>
+        <v>2.15</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>0.53</v>
+        <v>2.83</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>38.69</v>
+        <v>40.99</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>76.8</v>
+        <v>81.58</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>93.2</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>92</v>
+        <v>92.52</v>
       </c>
       <c r="P64" s="49" t="n">
-        <v>22865.8</v>
+        <v>23042.35</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>581</v>
+        <v>274</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>167</v>
+        <v>475</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>3.48</v>
+        <v>0.58</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>4.48</v>
+        <v>0.53</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>39.33</v>
+        <v>38.6</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>79.06999999999999</v>
+        <v>76.77</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>95.2</v>
+        <v>93.19</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>96.53</v>
-      </c>
-      <c r="P65" s="49" t="n">
-        <v>22869.4</v>
+        <v>91.98999999999999</v>
+      </c>
+      <c r="P65" s="50" t="n">
+        <v>22865.8</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C66" s="1" t="n">
         <v>2</v>
@@ -4476,191 +4485,242 @@
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>504</v>
+        <v>580</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>243</v>
+        <v>167</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>2.07</v>
+        <v>3.47</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>3.43</v>
+        <v>4.47</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>37.26</v>
+        <v>39.23</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>74.93000000000001</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>92.67</v>
+        <v>95.19</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="P66" s="29" t="n">
-        <v>22656.3</v>
+        <v>96.53</v>
+      </c>
+      <c r="P66" s="50" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>681</v>
+        <v>504</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>10.16</v>
+        <v>2.07</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>17.31</v>
+        <v>3.43</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>34.77</v>
+        <v>37.26</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>68.48999999999999</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>93.98999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>96.26000000000001</v>
-      </c>
-      <c r="P67" s="50" t="n">
-        <v>22595.55</v>
+        <v>94.8</v>
+      </c>
+      <c r="P67" s="30" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>244</v>
+        <v>681</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>501</v>
+        <v>67</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>0.49</v>
+        <v>10.16</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>0.75</v>
+        <v>17.31</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>31.26</v>
+        <v>34.77</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>52.93</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>84.27</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P68" s="23" t="n">
-        <v>22179.05</v>
+        <v>96.26000000000001</v>
+      </c>
+      <c r="P68" s="51" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G69" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J69" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L69" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M69" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N69" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O69" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P69" s="24" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q69" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" s="1" t="inlineStr"/>
+      <c r="E70" s="1" t="inlineStr"/>
+      <c r="F70" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G69" s="1" t="n">
+      <c r="G70" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H69" s="1" t="n">
+      <c r="H70" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr"/>
-      <c r="L69" s="1" t="n">
+      <c r="I70" s="1" t="inlineStr"/>
+      <c r="J70" s="1" t="inlineStr"/>
+      <c r="K70" s="1" t="inlineStr"/>
+      <c r="L70" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="M70" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N69" s="1" t="n">
+      <c r="N70" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O69" s="1" t="n">
+      <c r="O70" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P69" s="51" t="n">
+      <c r="P70" s="52" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q69" s="1" t="n">
+      <c r="Q70" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B69">
+  <conditionalFormatting sqref="B2:B70">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4670,7 +4730,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C69">
+  <conditionalFormatting sqref="C2:C70">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4680,7 +4740,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E69">
+  <conditionalFormatting sqref="D2:E70">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4692,7 +4752,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F69">
+  <conditionalFormatting sqref="F2:F70">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4702,7 +4762,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G69">
+  <conditionalFormatting sqref="G2:G70">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4712,7 +4772,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H69">
+  <conditionalFormatting sqref="H2:H70">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4724,7 +4784,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I69">
+  <conditionalFormatting sqref="I2:I70">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4734,7 +4794,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J69">
+  <conditionalFormatting sqref="J2:J70">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4744,7 +4804,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K69">
+  <conditionalFormatting sqref="K2:K70">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4756,7 +4816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O69">
+  <conditionalFormatting sqref="L2:O70">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4768,7 +4828,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q69">
+  <conditionalFormatting sqref="Q2:Q70">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="53">
+  <fills count="54">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBE9D3"/>
+        <bgColor rgb="00CBE9D3"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -352,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -508,6 +514,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -875,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -987,3548 +996,3548 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>3.16</v>
+        <v>1.51</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.95</v>
+        <v>0.72</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>56.19</v>
+        <v>55.5</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>64.48999999999999</v>
+        <v>62.53</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>56.06</v>
+        <v>50.87</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>49.93</v>
+        <v>44.07</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23232.65</v>
+        <v>23336.3</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>4.9</v>
+        <v>3.18</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>451</v>
+        <v>300</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>299</v>
+        <v>447</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.51</v>
+        <v>0.67</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>2.24</v>
+        <v>0.95</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>58</v>
+        <v>56.01</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>64.22</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>59.2</v>
+        <v>56.06</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>54.27</v>
+        <v>50.2</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="D4" s="1" t="n">
-        <v>1.74</v>
+        <v>4.9</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>171</v>
+        <v>452</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>578</v>
+        <v>299</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.3</v>
+        <v>1.51</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.38</v>
+        <v>2.25</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>56.8</v>
+        <v>57.83</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>61.42</v>
+        <v>64.13</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>54</v>
+        <v>59.12</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>47.47</v>
+        <v>54.19</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>382</v>
+        <v>170</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>366</v>
+        <v>580</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>57.14</v>
+        <v>56.63</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>65.29000000000001</v>
+        <v>61.33</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>65.33</v>
+        <v>53.79</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>64.67</v>
+        <v>47.27</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>603</v>
+        <v>381</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>145</v>
+        <v>368</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>4.16</v>
+        <v>1.04</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>11.12</v>
+        <v>0.79</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>55.77</v>
+        <v>56.97</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>65.02</v>
+        <v>65.2</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>64.53</v>
+        <v>65.11</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>23348.4</v>
+        <v>64.45</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>7.68</v>
+        <v>11.15</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>52.84</v>
+        <v>55.59</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>56.24</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>51.6</v>
+        <v>64.45</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>45.6</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>87</v>
+        <v>624</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>663</v>
+        <v>127</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.13</v>
+        <v>4.91</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>49.91</v>
+        <v>52.67</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>50.08</v>
+        <v>56.09</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>38</v>
+        <v>51.4</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>26.27</v>
+        <v>45.41</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>504</v>
+        <v>665</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>56.45</v>
+        <v>49.74</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>60.9</v>
+        <v>49.92</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>58.27</v>
+        <v>37.82</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>51.87</v>
+        <v>26.1</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>23368.85</v>
+        <v>22908.05</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>364</v>
+        <v>241</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>385</v>
+        <v>506</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.95</v>
+        <v>0.48</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>57.07</v>
+        <v>56.28</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>63.76</v>
+        <v>60.75</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>65.73</v>
+        <v>58.06</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>63.73</v>
+        <v>51.66</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>23433.95</v>
+        <v>23368.85</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>56.9</v>
+        <v>57.07</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>65.11</v>
+        <v>63.61</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>66.93000000000001</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>66.13</v>
+        <v>63.52</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>23301.15</v>
+        <v>23433.95</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.77</v>
+        <v>2.35</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>56.55</v>
+        <v>56.9</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>64.66</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>69.83</v>
+        <v>66.84</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>68.62</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>23264.8</v>
+        <v>66.05</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.76</v>
+        <v>2.87</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>416</v>
+        <v>537</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>333</v>
+        <v>212</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>52.93</v>
+        <v>56.55</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>60.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>61.55</v>
+        <v>69.73</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>57.01</v>
-      </c>
-      <c r="P13" s="11" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>51.9</v>
+        <v>52.93</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>58.2</v>
+        <v>60.15</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>57.94</v>
+        <v>61.47</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>50.2</v>
+        <v>57.07</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>22995.65</v>
+        <v>23111.65</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>278</v>
+        <v>445</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>470</v>
+        <v>304</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>50.52</v>
+        <v>51.9</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>55.94</v>
+        <v>58.05</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>50.2</v>
+        <v>57.87</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>41.39</v>
+        <v>50.13</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>23000</v>
+        <v>22995.65</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2.16</v>
+        <v>1.05</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>4.71</v>
+        <v>2.71</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>52.59</v>
+        <v>50.34</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>60</v>
+        <v>55.79</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>60.35</v>
+        <v>50.13</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>50.87</v>
-      </c>
-      <c r="P16" s="14" t="inlineStr"/>
-      <c r="Q16" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>6.84</v>
+        <v>4.73</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>52.41</v>
+        <v>52.59</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>60.15</v>
+        <v>59.85</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>60.35</v>
+        <v>60.27</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>50.87</v>
-      </c>
-      <c r="P17" s="11" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q17" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+        <v>50.8</v>
+      </c>
+      <c r="P17" s="15" t="inlineStr"/>
+      <c r="Q17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>6.53</v>
+        <v>6.88</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>388</v>
+        <v>249</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>52.93</v>
+        <v>52.41</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>62.56</v>
+        <v>60</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>68.48999999999999</v>
+        <v>60.27</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>63.82</v>
-      </c>
-      <c r="P18" s="15" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>4.92</v>
+        <v>6.56</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>568</v>
+        <v>361</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>53.28</v>
+        <v>52.93</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>61.95</v>
+        <v>62.41</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>69.43000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>64.22</v>
+        <v>63.73</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>23010.95</v>
+        <v>23126.3</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>6.02</v>
+        <v>4.94</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>253</v>
+        <v>569</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.96</v>
+        <v>0.32</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>55.52</v>
+        <v>53.28</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>68.56999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>79.17</v>
+        <v>69.33</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>81.04000000000001</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>8.529999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>3.2</v>
+        <v>6.04</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>53.97</v>
+        <v>55.52</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>65.56</v>
+        <v>68.42</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>74.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>75.17</v>
-      </c>
-      <c r="P21" s="17" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>16.48</v>
+        <v>8.57</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.84</v>
+        <v>1.05</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>53.28</v>
+        <v>53.97</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>66.02</v>
+        <v>65.41</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>76.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>79.56999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="P22" s="18" t="n">
-        <v>23206.45</v>
+        <v>23144.2</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>10.29</v>
+        <v>16.57</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>4.16</v>
+        <v>1.85</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>51.9</v>
+        <v>53.28</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>63.76</v>
+        <v>65.86</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>74.77</v>
+        <v>76.8</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>78.37</v>
-      </c>
-      <c r="P23" s="11" t="n">
-        <v>23109.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="P23" s="19" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>4.67</v>
+        <v>10.35</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>50.34</v>
+        <v>51.9</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>61.95</v>
+        <v>63.61</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>73.56</v>
+        <v>74.67</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>79.31</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="P24" s="12" t="n">
-        <v>22997.25</v>
+        <v>23109.7</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>573</v>
+        <v>436</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>175</v>
+        <v>313</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>3.27</v>
+        <v>1.39</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>49.74</v>
+        <v>50.34</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>60</v>
+        <v>61.8</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>70.36</v>
+        <v>73.47</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>79.17</v>
-      </c>
-      <c r="P25" s="19" t="n">
-        <v>22891.3</v>
+        <v>79.33</v>
+      </c>
+      <c r="P25" s="13" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>1.99</v>
+        <v>5.63</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>690</v>
+        <v>575</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>11.9</v>
+        <v>3.3</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>33.38</v>
+        <v>5.84</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>46.63</v>
+        <v>49.74</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>50.08</v>
+        <v>59.85</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>53.14</v>
+        <v>70.27</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>61.28</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P26" s="20" t="n">
-        <v>22599.8</v>
+        <v>22891.3</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>174</v>
+        <v>691</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>574</v>
+        <v>58</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>39.03</v>
+        <v>46.63</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>38.5</v>
+        <v>49.92</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>27.77</v>
+        <v>53.07</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>22.03</v>
+        <v>61.2</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>22114.45</v>
+        <v>22599.8</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>43.18</v>
+        <v>39.03</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>44.36</v>
+        <v>38.35</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>36.32</v>
+        <v>27.73</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>30.71</v>
+        <v>21.87</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>22233.85</v>
+        <v>22114.45</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>597</v>
+        <v>160</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>151</v>
+        <v>590</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>3.95</v>
+        <v>0.27</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>44.91</v>
+        <v>43.18</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>51.13</v>
+        <v>44.21</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>43.93</v>
+        <v>36.27</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>43.26</v>
+        <v>30.67</v>
       </c>
       <c r="P29" s="23" t="n">
-        <v>22370.15</v>
+        <v>22233.85</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>103</v>
+        <v>596</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>646</v>
+        <v>153</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.16</v>
+        <v>3.9</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>41.45</v>
+        <v>44.91</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>44.96</v>
+        <v>50.98</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>30.44</v>
+        <v>43.87</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>24.3</v>
+        <v>43.2</v>
       </c>
       <c r="P30" s="24" t="n">
-        <v>22173.7</v>
+        <v>22370.15</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.89</v>
+        <v>1.22</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>359</v>
+        <v>102</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>44.91</v>
+        <v>41.45</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>55.04</v>
+        <v>44.81</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>44.99</v>
+        <v>30.4</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>45.39</v>
+        <v>24.27</v>
       </c>
       <c r="P31" s="25" t="n">
-        <v>22465.35</v>
+        <v>22173.7</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>44.81</v>
+        <v>44.91</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>56.99</v>
+        <v>55.04</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>45.53</v>
+        <v>44.93</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>43.26</v>
+        <v>45.33</v>
       </c>
       <c r="P32" s="26" t="n">
-        <v>22497.7</v>
+        <v>22465.35</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>307</v>
+        <v>400</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>43.77</v>
+        <v>44.81</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>57.29</v>
+        <v>56.99</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>43.26</v>
+        <v>45.6</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>37.78</v>
+        <v>43.33</v>
       </c>
       <c r="P33" s="27" t="n">
-        <v>22451.85</v>
+        <v>22497.7</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>467</v>
+        <v>308</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>280</v>
+        <v>441</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>1.67</v>
+        <v>0.7</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>43.6</v>
+        <v>43.77</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>60</v>
+        <v>57.29</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>43.79</v>
+        <v>43.33</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>40.05</v>
+        <v>37.73</v>
       </c>
       <c r="P34" s="28" t="n">
-        <v>22521.1</v>
+        <v>22451.85</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>220</v>
+        <v>469</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>42.73</v>
+        <v>43.6</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>38.05</v>
+        <v>43.87</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>31.91</v>
+        <v>40</v>
       </c>
       <c r="P35" s="29" t="n">
-        <v>22437.95</v>
+        <v>22521.1</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>2.01</v>
+        <v>1.08</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>43.94</v>
+        <v>42.73</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>66.31999999999999</v>
+        <v>58.95</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>47.53</v>
+        <v>38.13</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>42.19</v>
+        <v>31.87</v>
       </c>
       <c r="P36" s="30" t="n">
-        <v>22657</v>
+        <v>22437.95</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>3.71</v>
+        <v>2.02</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>47.58</v>
+        <v>43.94</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>72.48</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>61.28</v>
+        <v>47.6</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>60.61</v>
-      </c>
-      <c r="P37" s="14" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P37" s="31" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>3.96</v>
+        <v>3.73</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>47.66</v>
+        <v>47.58</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>73.23</v>
+        <v>72.48</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>61.28</v>
+        <v>61.33</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>60.61</v>
-      </c>
-      <c r="P38" s="31" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q38" s="1" t="n">
-        <v>0.31</v>
-      </c>
+        <v>60.67</v>
+      </c>
+      <c r="P38" s="15" t="inlineStr"/>
+      <c r="Q38" s="1" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>4.28</v>
+        <v>3.98</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>1.99</v>
+        <v>4.35</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>46.88</v>
+        <v>47.66</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>73.83</v>
+        <v>73.23</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>62.08</v>
+        <v>61.33</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>63.42</v>
-      </c>
-      <c r="P39" s="19" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P39" s="32" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>4.62</v>
+        <v>4.3</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>3.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>8.31</v>
+        <v>1.98</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>46.18</v>
+        <v>46.88</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>74.73999999999999</v>
+        <v>73.83</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>61.15</v>
+        <v>62.13</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>63.55</v>
-      </c>
-      <c r="P40" s="32" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P40" s="20" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>373</v>
+        <v>566</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>372</v>
+        <v>183</v>
       </c>
       <c r="H41" s="1" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="J41" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="J41" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="K41" s="1" t="n">
-        <v>2.49</v>
+        <v>8.33</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>44.1</v>
+        <v>46.18</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>68.12</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>48.87</v>
+        <v>61.2</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="P41" s="30" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P41" s="33" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1.48</v>
+        <v>0.99</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J42" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>42.01</v>
+        <v>44.1</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>68.56999999999999</v>
+        <v>68.12</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="P42" s="20" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P42" s="31" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>366</v>
+        <v>445</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>381</v>
+        <v>302</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>41.15</v>
+        <v>42.01</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>66.77</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>41.92</v>
+        <v>48.13</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="P43" s="33" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>492</v>
+        <v>367</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>1.92</v>
+        <v>0.96</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>41.32</v>
+        <v>41.15</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>67.06999999999999</v>
+        <v>66.77</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>40.85</v>
+        <v>42</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="P44" s="28" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P44" s="34" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>584</v>
+        <v>256</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>39.76</v>
+        <v>41.32</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>32.58</v>
+        <v>40.93</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="P45" s="34" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P45" s="29" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>493</v>
+        <v>585</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>44.27</v>
+        <v>39.76</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>71.13</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>42.32</v>
+        <v>32.53</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>31.91</v>
+        <v>23.33</v>
       </c>
       <c r="P46" s="35" t="n">
-        <v>22531.15</v>
+        <v>22461.05</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>423</v>
+        <v>256</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>3.39</v>
+        <v>0.92</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>44.79</v>
+        <v>44.27</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>72.33</v>
+        <v>71.13</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>46.33</v>
+        <v>42.27</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>35.38</v>
+        <v>31.87</v>
       </c>
       <c r="P47" s="36" t="n">
-        <v>22613.1</v>
+        <v>22531.15</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="E48" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L48" s="1" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="M48" s="1" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="N48" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O48" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P48" s="37" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q48" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F48" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>297</v>
-      </c>
-      <c r="H48" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I48" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J48" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K48" s="1" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="L48" s="1" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="M48" s="1" t="n">
-        <v>71.28</v>
-      </c>
-      <c r="N48" s="1" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="O48" s="1" t="n">
-        <v>29.77</v>
-      </c>
-      <c r="P48" s="37" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q48" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>695</v>
+        <v>298</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>42.19</v>
+        <v>43.23</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>70.23</v>
+        <v>71.28</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>37.65</v>
+        <v>43.73</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>22.96</v>
+        <v>29.87</v>
       </c>
       <c r="P49" s="38" t="n">
-        <v>22299.9</v>
+        <v>22377.35</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>2.27</v>
+        <v>0.74</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>2.29</v>
+        <v>1.01</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>560</v>
+        <v>696</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>49.91</v>
+        <v>42.19</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>82.41</v>
+        <v>70.23</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>67.56</v>
+        <v>37.73</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>50.6</v>
+        <v>22.93</v>
       </c>
       <c r="P50" s="39" t="n">
-        <v>22795.75</v>
+        <v>22299.9</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>4.93</v>
+        <v>2.27</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>4.34</v>
+        <v>2.29</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>424</v>
+        <v>561</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>1.54</v>
+        <v>0.88</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>54.78</v>
+        <v>49.91</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>87.22</v>
+        <v>82.41</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>82.23999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>73.56</v>
+        <v>50.53</v>
       </c>
       <c r="P51" s="40" t="n">
-        <v>23115.65</v>
+        <v>22795.75</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>6.02</v>
+        <v>4.89</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>498</v>
+        <v>324</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>1.99</v>
+        <v>0.76</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J52" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>56.52</v>
+        <v>54.78</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>87.97</v>
+        <v>87.22</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>87.84999999999999</v>
+        <v>82.27</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>82.64</v>
+        <v>73.47</v>
       </c>
       <c r="P52" s="41" t="n">
-        <v>23214</v>
+        <v>23115.65</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>3.73</v>
+        <v>5.93</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>6.17</v>
+        <v>1.69</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>52.52</v>
+        <v>56.52</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>86.92</v>
+        <v>87.97</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>86.78</v>
+        <v>87.87</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>81.04000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="P53" s="42" t="n">
-        <v>23133.4</v>
+        <v>23214</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>2.24</v>
+        <v>3.7</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>344</v>
+        <v>605</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>403</v>
+        <v>145</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>1.88</v>
+        <v>6.12</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>47.65</v>
+        <v>52.52</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>79.7</v>
+        <v>86.92</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>73.83</v>
+        <v>86.8</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>62.62</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="P54" s="43" t="n">
-        <v>22808.25</v>
+        <v>23133.4</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>3.01</v>
+        <v>2.66</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>530</v>
+        <v>343</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>2.43</v>
+        <v>0.85</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>46.86</v>
+        <v>47.65</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>80.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>77.17</v>
+        <v>73.87</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>66.89</v>
+        <v>62.53</v>
       </c>
       <c r="P55" s="44" t="n">
-        <v>22830.75</v>
+        <v>22808.25</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>3.62</v>
+        <v>2.33</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>2.67</v>
+        <v>3.02</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>43.55</v>
+        <v>46.86</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>77.44</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>64.89</v>
+        <v>77.2</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="P56" s="14" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="P56" s="45" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q56" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>2.07</v>
+        <v>3.64</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>3.12</v>
+        <v>2.68</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>41.84</v>
+        <v>43.55</v>
       </c>
       <c r="M57" s="1" t="n">
         <v>77.44</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>73.03</v>
+        <v>64.8</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>55.14</v>
-      </c>
-      <c r="P57" s="45" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q57" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.73</v>
+      </c>
+      <c r="P57" s="15" t="inlineStr"/>
+      <c r="Q57" s="1" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>371</v>
+        <v>196</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>376</v>
+        <v>552</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.99</v>
+        <v>0.36</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>43.65</v>
+        <v>41.77</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>79.17</v>
+        <v>77.47</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>80.64</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>70.23</v>
+        <v>55.07</v>
       </c>
       <c r="P58" s="46" t="n">
-        <v>22871</v>
+        <v>22683.55</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>3.01</v>
+        <v>2.38</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>284</v>
+        <v>370</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>43.97</v>
+        <v>43.74</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>77.84</v>
+        <v>79.2</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>81.17</v>
+        <v>80.67</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>70.76000000000001</v>
+        <v>70.13</v>
       </c>
       <c r="P59" s="47" t="n">
-        <v>22765.6</v>
+        <v>22871</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>3.61</v>
+        <v>3.02</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>647</v>
+        <v>285</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>6.34</v>
+        <v>0.62</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>8.140000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>44.13</v>
+        <v>44.06</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>80.11</v>
+        <v>77.87</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>86.92</v>
+        <v>81.2</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>81.58</v>
-      </c>
-      <c r="P60" s="43" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P60" s="48" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>2.11</v>
+        <v>3.62</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>155</v>
+        <v>648</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>40</v>
+        <v>44.22</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>71.83</v>
+        <v>80.13</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>77.97</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>62.08</v>
-      </c>
-      <c r="P61" s="33" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P61" s="44" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>5.22</v>
+        <v>2.12</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>509</v>
+        <v>590</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>42.54</v>
+        <v>40.1</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>78.77</v>
+        <v>72</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>87.31999999999999</v>
+        <v>78</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="P62" s="43" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P62" s="34" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>495</v>
+        <v>236</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>250</v>
+        <v>511</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>1.98</v>
+        <v>0.46</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>43.31</v>
+        <v>42.63</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>81.98</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>91.72</v>
+        <v>87.33</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>89.84999999999999</v>
-      </c>
-      <c r="P63" s="48" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P63" s="44" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>40.99</v>
+        <v>43.4</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>81.58</v>
+        <v>82.13</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>93.45999999999999</v>
+        <v>91.87</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>92.52</v>
+        <v>90</v>
       </c>
       <c r="P64" s="49" t="n">
-        <v>23042.35</v>
+        <v>22991.5</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>274</v>
+        <v>509</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>475</v>
+        <v>239</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>38.6</v>
+        <v>41.08</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>76.77</v>
+        <v>81.73</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>93.19</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>91.98999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="P65" s="50" t="n">
-        <v>22865.8</v>
+        <v>23042.35</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>580</v>
+        <v>276</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>167</v>
+        <v>474</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>3.47</v>
+        <v>0.58</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>4.47</v>
+        <v>0.53</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>39.23</v>
+        <v>38.69</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>79.04000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>95.19</v>
+        <v>93.33</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>96.53</v>
-      </c>
-      <c r="P66" s="50" t="n">
-        <v>22869.4</v>
+        <v>92.13</v>
+      </c>
+      <c r="P66" s="51" t="n">
+        <v>22865.8</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C67" s="1" t="n">
         <v>2</v>
@@ -4536,191 +4545,242 @@
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>504</v>
+        <v>580</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>243</v>
+        <v>167</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>2.07</v>
+        <v>3.47</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>3.43</v>
+        <v>4.47</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>37.26</v>
+        <v>39.23</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>74.93000000000001</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>92.67</v>
+        <v>95.19</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="P67" s="30" t="n">
-        <v>22656.3</v>
+        <v>96.53</v>
+      </c>
+      <c r="P67" s="51" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>681</v>
+        <v>504</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>10.16</v>
+        <v>2.07</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J68" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>17.31</v>
+        <v>3.43</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>34.77</v>
+        <v>37.26</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>68.48999999999999</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>93.98999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>96.26000000000001</v>
-      </c>
-      <c r="P68" s="51" t="n">
-        <v>22595.55</v>
+        <v>94.8</v>
+      </c>
+      <c r="P68" s="31" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>244</v>
+        <v>681</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>501</v>
+        <v>67</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>0.49</v>
+        <v>10.16</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>0.75</v>
+        <v>17.31</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>31.26</v>
+        <v>34.77</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>52.93</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>84.27</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P69" s="24" t="n">
-        <v>22179.05</v>
+        <v>96.26000000000001</v>
+      </c>
+      <c r="P69" s="52" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G70" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J70" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L70" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M70" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N70" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O70" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P70" s="25" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q70" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="1" t="inlineStr"/>
+      <c r="E71" s="1" t="inlineStr"/>
+      <c r="F71" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G70" s="1" t="n">
+      <c r="G71" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H70" s="1" t="n">
+      <c r="H71" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr"/>
-      <c r="L70" s="1" t="n">
+      <c r="I71" s="1" t="inlineStr"/>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
+      <c r="L71" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="M71" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N70" s="1" t="n">
+      <c r="N71" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O70" s="1" t="n">
+      <c r="O71" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P70" s="52" t="n">
+      <c r="P71" s="53" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q70" s="1" t="n">
+      <c r="Q71" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B70">
+  <conditionalFormatting sqref="B2:B71">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4730,7 +4790,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C70">
+  <conditionalFormatting sqref="C2:C71">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4740,7 +4800,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E70">
+  <conditionalFormatting sqref="D2:E71">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4752,7 +4812,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F70">
+  <conditionalFormatting sqref="F2:F71">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4762,7 +4822,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G70">
+  <conditionalFormatting sqref="G2:G71">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4772,7 +4832,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H70">
+  <conditionalFormatting sqref="H2:H71">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4784,7 +4844,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I70">
+  <conditionalFormatting sqref="I2:I71">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4794,7 +4854,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J70">
+  <conditionalFormatting sqref="J2:J71">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4804,7 +4864,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K70">
+  <conditionalFormatting sqref="K2:K71">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4816,7 +4876,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O70">
+  <conditionalFormatting sqref="L2:O71">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4828,7 +4888,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q70">
+  <conditionalFormatting sqref="Q2:Q71">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -1143,7 +1143,7 @@
         <v>57.83</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>64.13</v>
+        <v>64</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>59.12</v>
@@ -1250,7 +1250,7 @@
         <v>0.79</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>56.97</v>
+        <v>56.8</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>65.2</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>52.59</v>
+        <v>52.41</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>59.85</v>
@@ -1906,7 +1906,7 @@
         <v>0.55</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>52.41</v>
+        <v>52.24</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>60</v>
@@ -1964,7 +1964,7 @@
         <v>52.93</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>62.41</v>
+        <v>62.26</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>68.40000000000001</v>
@@ -1995,7 +1995,7 @@
         <v>5.4</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>181</v>
@@ -2019,10 +2019,10 @@
         <v>53.28</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>61.8</v>
+        <v>61.65</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>69.33</v>
+        <v>69.2</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>64.13</v>
@@ -2050,7 +2050,7 @@
         <v>6.9</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>496</v>
@@ -2105,7 +2105,7 @@
         <v>8.57</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>395</v>
@@ -2160,7 +2160,7 @@
         <v>16.57</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>448</v>
@@ -2215,7 +2215,7 @@
         <v>10.35</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>452</v>
@@ -2267,10 +2267,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>436</v>
@@ -2294,7 +2294,7 @@
         <v>50.34</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>61.8</v>
+        <v>61.65</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>73.47</v>
@@ -2322,10 +2322,10 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>575</v>
@@ -2377,10 +2377,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>691</v>
@@ -2432,7 +2432,7 @@
         <v>21</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>1.09</v>
@@ -2456,13 +2456,13 @@
         <v>0.74</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>39.03</v>
+        <v>38.86</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>38.35</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>27.73</v>
+        <v>27.6</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>21.87</v>
@@ -2484,10 +2484,10 @@
         <v>13</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>1.14</v>
@@ -2511,16 +2511,16 @@
         <v>0.18</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>43.18</v>
+        <v>43.01</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>44.21</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>36.27</v>
+        <v>36.13</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>30.67</v>
+        <v>30.53</v>
       </c>
       <c r="P29" s="23" t="n">
         <v>22233.85</v>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -1143,7 +1143,7 @@
         <v>57.83</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>64</v>
+        <v>64.13</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>59.12</v>
@@ -1250,7 +1250,7 @@
         <v>0.79</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>56.8</v>
+        <v>56.97</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>65.2</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>52.41</v>
+        <v>52.59</v>
       </c>
       <c r="M17" s="1" t="n">
         <v>59.85</v>
@@ -1906,7 +1906,7 @@
         <v>0.55</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>52.24</v>
+        <v>52.41</v>
       </c>
       <c r="M18" s="1" t="n">
         <v>60</v>
@@ -1964,7 +1964,7 @@
         <v>52.93</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>62.26</v>
+        <v>62.41</v>
       </c>
       <c r="N19" s="1" t="n">
         <v>68.40000000000001</v>
@@ -1995,7 +1995,7 @@
         <v>5.4</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>4.89</v>
+        <v>4.94</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>181</v>
@@ -2019,10 +2019,10 @@
         <v>53.28</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>61.65</v>
+        <v>61.8</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>69.2</v>
+        <v>69.33</v>
       </c>
       <c r="O20" s="1" t="n">
         <v>64.13</v>
@@ -2050,7 +2050,7 @@
         <v>6.9</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>5.98</v>
+        <v>6.04</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>496</v>
@@ -2105,7 +2105,7 @@
         <v>8.57</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>395</v>
@@ -2160,7 +2160,7 @@
         <v>16.57</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>448</v>
@@ -2215,7 +2215,7 @@
         <v>10.35</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>452</v>
@@ -2267,10 +2267,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>436</v>
@@ -2294,7 +2294,7 @@
         <v>50.34</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>61.65</v>
+        <v>61.8</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>73.47</v>
@@ -2322,10 +2322,10 @@
         <v>2</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>5.55</v>
+        <v>5.63</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>575</v>
@@ -2377,10 +2377,10 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>691</v>
@@ -2432,7 +2432,7 @@
         <v>21</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>1.09</v>
@@ -2456,13 +2456,13 @@
         <v>0.74</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>38.86</v>
+        <v>39.03</v>
       </c>
       <c r="M28" s="1" t="n">
         <v>38.35</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>27.6</v>
+        <v>27.73</v>
       </c>
       <c r="O28" s="1" t="n">
         <v>21.87</v>
@@ -2484,10 +2484,10 @@
         <v>13</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>1.14</v>
@@ -2511,16 +2511,16 @@
         <v>0.18</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>43.01</v>
+        <v>43.18</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>44.21</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>36.13</v>
+        <v>36.27</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>30.53</v>
+        <v>30.67</v>
       </c>
       <c r="P29" s="23" t="n">
         <v>22233.85</v>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -1000,46 +1000,46 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.51</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.53</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.57</v>
+        <v>6</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.72</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>55.5</v>
+        <v>33.33</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>62.53</v>
+        <v>83.33</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>50.87</v>
+        <v>100</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>44.07</v>
+        <v>100</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>23336.3</v>
@@ -1055,46 +1055,46 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>3.18</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.65</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>447</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.67</v>
+        <v>5</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.95</v>
+        <v>2.53</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>56.01</v>
+        <v>33.33</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>56.06</v>
+        <v>83.33</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>50.2</v>
+        <v>66.67</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>23232.65</v>
@@ -1110,46 +1110,46 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>452</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>299</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.51</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>2.25</v>
+        <v>7.5</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>57.83</v>
+        <v>33.33</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>64.13</v>
+        <v>66.67</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>59.12</v>
+        <v>83.33</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>54.19</v>
+        <v>83.33</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>23263.9</v>
@@ -1165,46 +1165,46 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.74</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>580</v>
+        <v>5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>56.63</v>
+        <v>33.33</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>61.33</v>
+        <v>66.67</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>53.79</v>
+        <v>66.67</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>47.27</v>
+        <v>50</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>23199.45</v>
@@ -1220,46 +1220,46 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.64</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>381</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>368</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.79</v>
+        <v>1.66</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>56.97</v>
+        <v>33.33</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>65.2</v>
+        <v>50</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>65.11</v>
+        <v>83.33</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>64.45</v>
+        <v>83.33</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>23347.05</v>
@@ -1275,46 +1275,46 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>605</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>11.15</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>55.59</v>
+        <v>33.33</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>50</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>64.45</v>
+        <v>83.33</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>64.18000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>23348.4</v>
@@ -1330,46 +1330,46 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>624</v>
-      </c>
       <c r="G8" s="1" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>4.91</v>
+        <v>2</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>7.66</v>
+        <v>5.95</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>52.67</v>
+        <v>33.33</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>56.09</v>
+        <v>50</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>51.4</v>
+        <v>33.33</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>45.41</v>
+        <v>16.67</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>23081.15</v>
@@ -1385,46 +1385,46 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>2</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>665</v>
+        <v>6</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>49.74</v>
+        <v>33.33</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>49.92</v>
+        <v>50</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>37.82</v>
+        <v>50</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>26.1</v>
+        <v>33.33</v>
       </c>
       <c r="P9" s="8" t="n">
         <v>22908.05</v>
@@ -1440,46 +1440,46 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>241</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>506</v>
+        <v>3</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>56.28</v>
+        <v>33.33</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>60.75</v>
+        <v>50</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>58.06</v>
+        <v>66.67</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>51.66</v>
+        <v>83.33</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>23368.85</v>
@@ -1495,46 +1495,46 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>363</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>387</v>
+        <v>3</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.52</v>
+        <v>4.92</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>57.07</v>
+        <v>33.33</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>63.61</v>
+        <v>50</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>65.65000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>63.52</v>
+        <v>66.67</v>
       </c>
       <c r="P11" s="10" t="n">
         <v>23433.95</v>
@@ -1550,46 +1550,46 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>353</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>396</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.89</v>
+        <v>5</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.44</v>
+        <v>5.97</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>56.9</v>
+        <v>33.33</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>50</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>66.84</v>
+        <v>50</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>66.05</v>
+        <v>83.33</v>
       </c>
       <c r="P12" s="11" t="n">
         <v>23301.15</v>
@@ -1605,46 +1605,46 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>537</v>
-      </c>
       <c r="G13" s="1" t="n">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>2.03</v>
+        <v>1.06</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>56.55</v>
+        <v>33.33</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>64.51000000000001</v>
+        <v>50</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>69.73</v>
+        <v>50</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>68.67</v>
+        <v>50</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>23264.8</v>
@@ -1660,46 +1660,46 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>416</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>334</v>
+        <v>3</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>3.41</v>
+        <v>0.58</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>52.93</v>
+        <v>33.33</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>60.15</v>
+        <v>50</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>61.47</v>
+        <v>50</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>57.07</v>
+        <v>50</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>23111.65</v>
@@ -1715,46 +1715,46 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>304</v>
+        <v>6</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>51.9</v>
+        <v>33.33</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>58.05</v>
+        <v>50</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>57.87</v>
+        <v>50</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>50.13</v>
+        <v>33.33</v>
       </c>
       <c r="P15" s="13" t="n">
         <v>22995.65</v>
@@ -1770,46 +1770,46 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>277</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>472</v>
+        <v>3</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.59</v>
+        <v>1</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.84</v>
+        <v>1.39</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>50.34</v>
+        <v>33.33</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>55.79</v>
+        <v>50</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>50.13</v>
+        <v>50</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>41.33</v>
+        <v>50</v>
       </c>
       <c r="P16" s="14" t="n">
         <v>23000</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>0</v>
@@ -1855,16 +1855,16 @@
         <v>0</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>52.59</v>
+        <v>33.33</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>59.85</v>
+        <v>50</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>60.27</v>
+        <v>66.67</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>50.8</v>
+        <v>66.67</v>
       </c>
       <c r="P17" s="15" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
@@ -1876,46 +1876,46 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>6.88</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>249</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.55</v>
+        <v>4.49</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>52.41</v>
+        <v>33.33</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>60.27</v>
+        <v>66.67</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>50.8</v>
+        <v>66.67</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>23113.7</v>
@@ -1931,46 +1931,46 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>6.56</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>389</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.08</v>
+        <v>6</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>1.08</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>52.93</v>
+        <v>33.33</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>62.41</v>
+        <v>50</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>63.73</v>
+        <v>66.67</v>
       </c>
       <c r="P19" s="16" t="n">
         <v>23126.3</v>
@@ -1986,46 +1986,46 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>569</v>
+        <v>6</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>53.28</v>
+        <v>16.67</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>61.8</v>
+        <v>50</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>69.33</v>
+        <v>50</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>64.13</v>
+        <v>50</v>
       </c>
       <c r="P20" s="17" t="n">
         <v>23010.95</v>
@@ -2041,46 +2041,46 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>496</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>2.09</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>55.52</v>
+        <v>33.33</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>68.42</v>
+        <v>50</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>79.2</v>
+        <v>66.67</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>81.06999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>23261.85</v>
@@ -2096,46 +2096,46 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>395</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>353</v>
+        <v>5</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.12</v>
+        <v>0.2</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>53.97</v>
+        <v>33.33</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>65.41</v>
+        <v>50</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>75.2</v>
+        <v>66.67</v>
       </c>
       <c r="P22" s="18" t="n">
         <v>23144.2</v>
@@ -2151,46 +2151,46 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>16.57</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>448</v>
+        <v>3</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>302</v>
+        <v>3</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.48</v>
+        <v>1</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>53.28</v>
+        <v>16.67</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>65.86</v>
+        <v>50</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>76.8</v>
+        <v>66.67</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>79.59999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="P23" s="19" t="n">
         <v>23206.45</v>
@@ -2206,46 +2206,46 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="M24" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>452</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>295</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="L24" s="1" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="M24" s="1" t="n">
-        <v>63.61</v>
-      </c>
       <c r="N24" s="1" t="n">
-        <v>74.67</v>
+        <v>83.33</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>78.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>23109.7</v>
@@ -2261,46 +2261,46 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>436</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.39</v>
+        <v>5</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1.26</v>
+        <v>7.52</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>50.34</v>
+        <v>16.67</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>61.8</v>
+        <v>50</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>73.47</v>
+        <v>66.67</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>79.33</v>
+        <v>83.33</v>
       </c>
       <c r="P25" s="13" t="n">
         <v>22997.25</v>
@@ -2316,46 +2316,46 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>575</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>5.84</v>
+        <v>5.09</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>49.74</v>
+        <v>16.67</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>59.85</v>
+        <v>50</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>70.27</v>
+        <v>50</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>79.06999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="P26" s="20" t="n">
         <v>22891.3</v>
@@ -2371,46 +2371,46 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>691</v>
+        <v>6</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>11.91</v>
+        <v>6</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>33.39</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46.63</v>
+        <v>16.67</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>49.92</v>
+        <v>33.33</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>53.07</v>
+        <v>50</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>61.2</v>
+        <v>66.67</v>
       </c>
       <c r="P27" s="21" t="n">
         <v>22599.8</v>
@@ -2426,46 +2426,46 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>576</v>
+        <v>4</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>39.03</v>
+        <v>16.67</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>38.35</v>
+        <v>16.67</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>27.73</v>
+        <v>33.33</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>21.87</v>
+        <v>33.33</v>
       </c>
       <c r="P28" s="22" t="n">
         <v>22114.45</v>
@@ -2481,46 +2481,46 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>590</v>
+        <v>2</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.27</v>
+        <v>2</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.18</v>
+        <v>3.09</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>43.18</v>
+        <v>16.67</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>44.21</v>
+        <v>16.67</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>36.27</v>
+        <v>33.33</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>30.67</v>
+        <v>33.33</v>
       </c>
       <c r="P29" s="23" t="n">
         <v>22233.85</v>
@@ -2536,46 +2536,46 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="1" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>596</v>
-      </c>
       <c r="G30" s="1" t="n">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>44.91</v>
+        <v>16.67</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>50.98</v>
+        <v>0</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>43.87</v>
+        <v>33.33</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>43.2</v>
+        <v>33.33</v>
       </c>
       <c r="P30" s="24" t="n">
         <v>22370.15</v>
@@ -2591,46 +2591,46 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>648</v>
+        <v>5</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>41.45</v>
+        <v>16.67</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>44.81</v>
+        <v>0</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>30.4</v>
+        <v>16.67</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>24.27</v>
+        <v>16.67</v>
       </c>
       <c r="P31" s="25" t="n">
         <v>22173.7</v>
@@ -2646,46 +2646,46 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>360</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>390</v>
+        <v>5</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>44.91</v>
+        <v>16.67</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>55.04</v>
+        <v>0</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>44.93</v>
+        <v>50</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>45.33</v>
+        <v>50</v>
       </c>
       <c r="P32" s="26" t="n">
         <v>22465.35</v>
@@ -2701,46 +2701,46 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.32</v>
+        <v>2</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>400</v>
+        <v>3</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>350</v>
+        <v>3</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>44.81</v>
+        <v>16.67</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>56.99</v>
+        <v>0</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>45.6</v>
+        <v>33.33</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>43.33</v>
+        <v>33.33</v>
       </c>
       <c r="P33" s="27" t="n">
         <v>22497.7</v>
@@ -2756,46 +2756,46 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.06</v>
+        <v>2</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>308</v>
+        <v>3</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>441</v>
+        <v>3</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>43.77</v>
+        <v>16.67</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>57.29</v>
+        <v>16.67</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>43.33</v>
+        <v>16.67</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>37.73</v>
+        <v>33.33</v>
       </c>
       <c r="P34" s="28" t="n">
         <v>22451.85</v>
@@ -2811,46 +2811,46 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>469</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>279</v>
+        <v>2</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>43.6</v>
+        <v>0</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>60</v>
+        <v>33.33</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>43.87</v>
+        <v>33.33</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="P35" s="29" t="n">
         <v>22521.1</v>
@@ -2866,46 +2866,46 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.93</v>
+        <v>1</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>221</v>
+        <v>2</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>529</v>
+        <v>4</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>42.73</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>58.95</v>
+        <v>0</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>38.13</v>
+        <v>16.67</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>31.87</v>
+        <v>33.33</v>
       </c>
       <c r="P36" s="30" t="n">
         <v>22437.95</v>
@@ -2921,46 +2921,46 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1.85</v>
+        <v>1</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>540</v>
+        <v>5</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>43.94</v>
+        <v>0</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>66.31999999999999</v>
+        <v>0</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>47.6</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>42.13</v>
+        <v>0</v>
       </c>
       <c r="P37" s="31" t="n">
         <v>22657</v>
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>2.11</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>0</v>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>0</v>
@@ -3006,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>47.58</v>
+        <v>16.67</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>72.48</v>
+        <v>0</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>61.33</v>
+        <v>16.67</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>60.67</v>
+        <v>33.33</v>
       </c>
       <c r="P38" s="15" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
@@ -3027,46 +3027,46 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>2.15</v>
+        <v>1</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>389</v>
+        <v>1</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>359</v>
+        <v>5</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1.08</v>
+        <v>0.2</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>4.35</v>
+        <v>0.02</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>47.66</v>
+        <v>16.67</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>73.23</v>
+        <v>0</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>61.33</v>
+        <v>16.67</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>60.67</v>
+        <v>33.33</v>
       </c>
       <c r="P39" s="32" t="n">
         <v>22967.4</v>
@@ -3082,46 +3082,46 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>2.12</v>
+        <v>1</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>386</v>
+        <v>6</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>46.88</v>
+        <v>16.67</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>73.83</v>
+        <v>16.67</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>62.13</v>
+        <v>33.33</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>63.47</v>
+        <v>66.67</v>
       </c>
       <c r="P40" s="20" t="n">
         <v>22897.2</v>
@@ -3137,46 +3137,46 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>4.64</v>
+        <v>1</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>566</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>3.09</v>
+        <v>5</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>8.33</v>
+        <v>10.4</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>46.18</v>
+        <v>16.67</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>74.73999999999999</v>
+        <v>33.33</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>61.2</v>
+        <v>33.33</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="P41" s="33" t="n">
         <v>22929.45</v>
@@ -3192,46 +3192,46 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>372</v>
+        <v>3</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>374</v>
+        <v>3</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>44.1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>68.12</v>
+        <v>0</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>48.8</v>
+        <v>16.67</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>46.93</v>
+        <v>50</v>
       </c>
       <c r="P42" s="31" t="n">
         <v>22651.3</v>
@@ -3247,46 +3247,46 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>445</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>302</v>
+        <v>4</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>1.47</v>
+        <v>0.25</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>2.81</v>
+        <v>0.22</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>42.01</v>
+        <v>0</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>68.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>48.13</v>
+        <v>16.67</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>45.73</v>
+        <v>16.67</v>
       </c>
       <c r="P43" s="21" t="n">
         <v>22602.85</v>
@@ -3302,46 +3302,46 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>367</v>
+        <v>3</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>381</v>
+        <v>3</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>2.65</v>
+        <v>0.51</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>41.15</v>
+        <v>0</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>66.77</v>
+        <v>0</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>42</v>
+        <v>16.67</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>38.13</v>
+        <v>16.67</v>
       </c>
       <c r="P44" s="34" t="n">
         <v>22578.15</v>
@@ -3357,46 +3357,46 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.91</v>
+        <v>0.5</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>493</v>
+        <v>3</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>256</v>
+        <v>3</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1.93</v>
+        <v>1</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>2.38</v>
+        <v>0.59</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>41.32</v>
+        <v>0</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>67.06999999999999</v>
+        <v>0</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>40.93</v>
+        <v>16.67</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>34.4</v>
+        <v>16.67</v>
       </c>
       <c r="P45" s="29" t="n">
         <v>22521.75</v>
@@ -3412,46 +3412,46 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>585</v>
+        <v>2</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.28</v>
+        <v>2</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>0.29</v>
+        <v>2.02</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>39.76</v>
+        <v>0</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>32.53</v>
+        <v>0</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>23.33</v>
+        <v>0</v>
       </c>
       <c r="P46" s="35" t="n">
         <v>22461.05</v>
@@ -3467,46 +3467,46 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>256</v>
+        <v>3</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>494</v>
+        <v>3</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.52</v>
+        <v>1</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>44.27</v>
+        <v>16.67</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>71.13</v>
+        <v>0</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>42.27</v>
+        <v>0</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>31.87</v>
+        <v>0</v>
       </c>
       <c r="P47" s="36" t="n">
         <v>22531.15</v>
@@ -3522,46 +3522,46 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>424</v>
+        <v>4</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>326</v>
+        <v>2</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>3.4</v>
+        <v>4.49</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>44.79</v>
+        <v>16.67</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>72.33</v>
+        <v>0</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>35.47</v>
+        <v>0</v>
       </c>
       <c r="P48" s="37" t="n">
         <v>22613.1</v>
@@ -3577,46 +3577,46 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>298</v>
+        <v>6</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>43.23</v>
+        <v>0</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>71.28</v>
+        <v>0</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>43.73</v>
+        <v>0</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>29.87</v>
+        <v>0</v>
       </c>
       <c r="P49" s="38" t="n">
         <v>22377.35</v>
@@ -3632,46 +3632,46 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>696</v>
+        <v>5</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>42.19</v>
+        <v>16.67</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>70.23</v>
+        <v>0</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>37.73</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>22.93</v>
+        <v>0</v>
       </c>
       <c r="P50" s="39" t="n">
         <v>22299.9</v>
@@ -3687,46 +3687,46 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>188</v>
+        <v>1</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>561</v>
+        <v>5</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>0.88</v>
+        <v>0.17</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>49.91</v>
+        <v>16.67</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>82.41</v>
+        <v>16.67</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>50.53</v>
+        <v>0</v>
       </c>
       <c r="P51" s="40" t="n">
         <v>22795.75</v>
@@ -3742,46 +3742,46 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>324</v>
+        <v>1</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>425</v>
+        <v>5</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>1.53</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>54.78</v>
+        <v>33.33</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>87.22</v>
+        <v>16.67</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>82.27</v>
+        <v>16.67</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>73.47</v>
+        <v>16.67</v>
       </c>
       <c r="P52" s="41" t="n">
         <v>23115.65</v>
@@ -3797,46 +3797,46 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>56.52</v>
+        <v>33.33</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>87.97</v>
+        <v>16.67</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>87.87</v>
+        <v>50</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>82.67</v>
+        <v>50</v>
       </c>
       <c r="P53" s="42" t="n">
         <v>23214</v>
@@ -3852,46 +3852,46 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>605</v>
+        <v>4</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>6.12</v>
+        <v>3.16</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>52.52</v>
+        <v>33.33</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>86.92</v>
+        <v>33.33</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>86.8</v>
+        <v>50</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>80.93000000000001</v>
+        <v>50</v>
       </c>
       <c r="P54" s="43" t="n">
         <v>23133.4</v>
@@ -3907,46 +3907,46 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>343</v>
+        <v>2</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>405</v>
+        <v>4</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>1.86</v>
+        <v>0.4</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>47.65</v>
+        <v>33.33</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>79.7</v>
+        <v>16.67</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>73.87</v>
+        <v>16.67</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>62.53</v>
+        <v>16.67</v>
       </c>
       <c r="P55" s="44" t="n">
         <v>22808.25</v>
@@ -3962,46 +3962,46 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>531</v>
+        <v>3</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>218</v>
+        <v>3</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>2.44</v>
+        <v>1</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>2.58</v>
+        <v>3.07</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>46.86</v>
+        <v>33.33</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>80.59999999999999</v>
+        <v>16.67</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>77.2</v>
+        <v>16.67</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>66.8</v>
+        <v>16.67</v>
       </c>
       <c r="P56" s="45" t="n">
         <v>22830.75</v>
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>0</v>
@@ -4047,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>43.55</v>
+        <v>16.67</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>77.44</v>
+        <v>16.67</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>64.8</v>
+        <v>16.67</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>49.73</v>
+        <v>16.67</v>
       </c>
       <c r="P57" s="15" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
@@ -4068,44 +4068,44 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>196</v>
+        <v>2</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>552</v>
+        <v>4</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>41.77</v>
+        <v>16.67</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>77.47</v>
+        <v>16.67</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>16.67</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>55.07</v>
+        <v>16.67</v>
       </c>
       <c r="P58" s="46" t="n">
         <v>22683.55</v>
@@ -4121,44 +4121,44 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>370</v>
+        <v>3</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>378</v>
+        <v>3</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>2.06</v>
+        <v>0.87</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>43.74</v>
+        <v>16.67</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>79.2</v>
+        <v>16.67</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>80.67</v>
+        <v>33.33</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>70.13</v>
+        <v>16.67</v>
       </c>
       <c r="P59" s="47" t="n">
         <v>22871</v>
@@ -4174,44 +4174,44 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>285</v>
+        <v>1</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>463</v>
+        <v>5</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.62</v>
+        <v>0.2</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>1.94</v>
+        <v>0.51</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>44.06</v>
+        <v>16.67</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>77.87</v>
+        <v>16.67</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>81.2</v>
+        <v>33.33</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>70.8</v>
+        <v>33.33</v>
       </c>
       <c r="P60" s="48" t="n">
         <v>22765.6</v>
@@ -4227,44 +4227,44 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>648</v>
+        <v>5</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>6.35</v>
+        <v>5</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>8.17</v>
+        <v>5.19</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>44.22</v>
+        <v>16.67</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>80.13</v>
+        <v>16.67</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>33.33</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>81.59999999999999</v>
+        <v>33.33</v>
       </c>
       <c r="P61" s="44" t="n">
         <v>22821.4</v>
@@ -4280,44 +4280,44 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>590</v>
+        <v>4</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>0.37</v>
+        <v>0.57</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>40.1</v>
+        <v>16.67</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>78</v>
+        <v>33.33</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>62.13</v>
+        <v>16.67</v>
       </c>
       <c r="P62" s="34" t="n">
         <v>22570.05</v>
@@ -4333,42 +4333,42 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>511</v>
+        <v>6</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>42.63</v>
+        <v>16.67</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>78.93000000000001</v>
+        <v>16.67</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>87.33</v>
+        <v>33.33</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>82.13</v>
+        <v>33.33</v>
       </c>
       <c r="P63" s="44" t="n">
         <v>22810.85</v>
@@ -4384,42 +4384,42 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>497</v>
+        <v>1</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>2.88</v>
+        <v>0.13</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>43.4</v>
+        <v>16.67</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>82.13</v>
+        <v>16.67</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>91.87</v>
+        <v>66.67</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>90</v>
+        <v>66.67</v>
       </c>
       <c r="P64" s="49" t="n">
         <v>22991.5</v>
@@ -4435,42 +4435,42 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>509</v>
+        <v>5</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>239</v>
+        <v>1</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>2.13</v>
+        <v>5</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>2.82</v>
+        <v>3.74</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>41.08</v>
+        <v>33.33</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>81.73</v>
+        <v>50</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>92.67</v>
+        <v>100</v>
       </c>
       <c r="P65" s="50" t="n">
         <v>23042.35</v>
@@ -4486,42 +4486,42 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>276</v>
+        <v>2</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>474</v>
+        <v>4</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>38.69</v>
+        <v>16.67</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>16.67</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>93.33</v>
+        <v>83.33</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>92.13</v>
+        <v>100</v>
       </c>
       <c r="P66" s="51" t="n">
         <v>22865.8</v>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="54">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -273,78 +273,6 @@
         <bgColor rgb="00E7F5EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBF0E0"/>
-        <bgColor rgb="00DBF0E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5F4E9"/>
-        <bgColor rgb="00E5F4E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF7F7"/>
-        <bgColor rgb="00FEF7F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF8F8"/>
-        <bgColor rgb="00FEF8F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEEFEF"/>
-        <bgColor rgb="00FEEFEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFAFB"/>
-        <bgColor rgb="00FEFAFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF4F4"/>
-        <bgColor rgb="00FEF4F4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7FCF8"/>
-        <bgColor rgb="00F7FCF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F1F9F3"/>
-        <bgColor rgb="00F1F9F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFAFA"/>
-        <bgColor rgb="00FEFAFA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE9EA"/>
-        <bgColor rgb="00FEE9EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDDADA"/>
-        <bgColor rgb="00FDDADA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -358,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -481,42 +409,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,7 +980,7 @@
         <v>33.33</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>83.33</v>
@@ -1122,13 +1014,13 @@
         <v>3</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>0</v>
@@ -1137,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>7.5</v>
+        <v>4.19</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>33.33</v>
       </c>
       <c r="M4" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" s="1" t="n">
         <v>66.67</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>83.33</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>83.33</v>
@@ -1198,7 +1090,7 @@
         <v>33.33</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>66.67</v>
@@ -1311,7 +1203,7 @@
         <v>50</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>83.33</v>
@@ -1421,7 +1313,7 @@
         <v>50</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>33.33</v>
@@ -1476,7 +1368,7 @@
         <v>50</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>83.33</v>
@@ -2025,7 +1917,7 @@
         <v>50</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="P20" s="17" t="n">
         <v>23010.95</v>
@@ -2135,7 +2027,7 @@
         <v>50</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="P22" s="18" t="n">
         <v>23144.2</v>
@@ -2242,7 +2134,7 @@
         <v>50</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>100</v>
@@ -2294,7 +2186,7 @@
         <v>16.67</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>66.67</v>
@@ -2349,7 +2241,7 @@
         <v>16.67</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>50</v>
@@ -2621,7 +2513,7 @@
         <v>0.2</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>0</v>
@@ -2670,19 +2562,19 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>0.14</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>50</v>
@@ -2731,16 +2623,16 @@
         <v>1.97</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="P33" s="27" t="n">
         <v>22497.7</v>
@@ -2786,10 +2678,10 @@
         <v>1.44</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>16.67</v>
@@ -2820,7 +2712,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>4</v>
@@ -2905,7 +2797,7 @@
         <v>16.67</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="P36" s="30" t="n">
         <v>22437.95</v>
@@ -3057,7 +2949,7 @@
         <v>0.02</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="M39" s="1" t="n">
         <v>0</v>
@@ -3066,7 +2958,7 @@
         <v>16.67</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="P39" s="32" t="n">
         <v>22967.4</v>
@@ -3112,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="M40" s="1" t="n">
         <v>16.67</v>
@@ -3121,7 +3013,7 @@
         <v>33.33</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>66.67</v>
+        <v>33.33</v>
       </c>
       <c r="P40" s="20" t="n">
         <v>22897.2</v>
@@ -3149,13 +3041,13 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>0</v>
@@ -3164,10 +3056,10 @@
         <v>0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>10.4</v>
+        <v>6.29</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>33.33</v>
@@ -3176,7 +3068,7 @@
         <v>33.33</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="P41" s="33" t="n">
         <v>22929.45</v>
@@ -3479,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>0</v>
@@ -3494,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>0</v>
@@ -3838,7 +3730,7 @@
       <c r="O53" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P53" s="42" t="n">
+      <c r="P53" s="15" t="n">
         <v>23214</v>
       </c>
       <c r="Q53" s="1" t="n">
@@ -3885,7 +3777,7 @@
         <v>33.33</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="N54" s="1" t="n">
         <v>50</v>
@@ -3893,7 +3785,7 @@
       <c r="O54" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P54" s="43" t="n">
+      <c r="P54" s="15" t="n">
         <v>23133.4</v>
       </c>
       <c r="Q54" s="1" t="n">
@@ -3948,7 +3840,7 @@
       <c r="O55" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P55" s="44" t="n">
+      <c r="P55" s="15" t="n">
         <v>22808.25</v>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4003,7 +3895,7 @@
       <c r="O56" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P56" s="45" t="n">
+      <c r="P56" s="15" t="n">
         <v>22830.75</v>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4076,7 +3968,9 @@
       <c r="D58" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="1" t="inlineStr"/>
+      <c r="E58" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="F58" s="1" t="n">
         <v>2</v>
       </c>
@@ -4107,7 +4001,7 @@
       <c r="O58" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P58" s="46" t="n">
+      <c r="P58" s="15" t="n">
         <v>22683.55</v>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4129,7 +4023,9 @@
       <c r="D59" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="1" t="inlineStr"/>
+      <c r="E59" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="F59" s="1" t="n">
         <v>3</v>
       </c>
@@ -4160,7 +4056,7 @@
       <c r="O59" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P59" s="47" t="n">
+      <c r="P59" s="15" t="n">
         <v>22871</v>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4182,7 +4078,9 @@
       <c r="D60" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="1" t="inlineStr"/>
+      <c r="E60" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="F60" s="1" t="n">
         <v>1</v>
       </c>
@@ -4196,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>0.51</v>
@@ -4213,7 +4111,7 @@
       <c r="O60" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P60" s="48" t="n">
+      <c r="P60" s="15" t="n">
         <v>22765.6</v>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4266,7 +4164,7 @@
       <c r="O61" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P61" s="44" t="n">
+      <c r="P61" s="15" t="n">
         <v>22821.4</v>
       </c>
       <c r="Q61" s="1" t="n">
@@ -4302,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>0.57</v>
@@ -4319,7 +4217,7 @@
       <c r="O62" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P62" s="34" t="n">
+      <c r="P62" s="15" t="n">
         <v>22570.05</v>
       </c>
       <c r="Q62" s="1" t="n">
@@ -4338,7 +4236,9 @@
       <c r="C63" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="1" t="inlineStr"/>
+      <c r="D63" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
         <v>0</v>
@@ -4370,7 +4270,7 @@
       <c r="O63" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P63" s="44" t="n">
+      <c r="P63" s="15" t="n">
         <v>22810.85</v>
       </c>
       <c r="Q63" s="1" t="n">
@@ -4389,7 +4289,9 @@
       <c r="C64" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="1" t="inlineStr"/>
+      <c r="D64" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
         <v>1</v>
@@ -4421,7 +4323,7 @@
       <c r="O64" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P64" s="49" t="n">
+      <c r="P64" s="15" t="n">
         <v>22991.5</v>
       </c>
       <c r="Q64" s="1" t="n">
@@ -4440,7 +4342,9 @@
       <c r="C65" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="1" t="inlineStr"/>
+      <c r="D65" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
         <v>5</v>
@@ -4472,7 +4376,7 @@
       <c r="O65" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P65" s="50" t="n">
+      <c r="P65" s="15" t="n">
         <v>23042.35</v>
       </c>
       <c r="Q65" s="1" t="n">
@@ -4523,7 +4427,7 @@
       <c r="O66" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P66" s="51" t="n">
+      <c r="P66" s="15" t="n">
         <v>22865.8</v>
       </c>
       <c r="Q66" s="1" t="n">
@@ -4537,44 +4441,44 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>580</v>
+        <v>5</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>3.47</v>
+        <v>5</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>4.47</v>
+        <v>7.36</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>39.23</v>
+        <v>16.67</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>79.04000000000001</v>
+        <v>16.67</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>95.19</v>
+        <v>100</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>96.53</v>
-      </c>
-      <c r="P67" s="51" t="n">
+        <v>100</v>
+      </c>
+      <c r="P67" s="15" t="n">
         <v>22869.4</v>
       </c>
       <c r="Q67" s="1" t="n">
@@ -4588,44 +4492,44 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>504</v>
+        <v>2</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>243</v>
+        <v>4</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>2.07</v>
+        <v>0.5</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J68" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>3.43</v>
+        <v>0.16</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>37.26</v>
+        <v>16.67</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>74.93000000000001</v>
+        <v>16.67</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>92.67</v>
+        <v>66.67</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="P68" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="P68" s="15" t="n">
         <v>22656.3</v>
       </c>
       <c r="Q68" s="1" t="n">
@@ -4639,44 +4543,44 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>681</v>
+        <v>5</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>10.16</v>
+        <v>5</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J69" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>17.31</v>
+        <v>3.72</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>34.77</v>
+        <v>16.67</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>68.48999999999999</v>
+        <v>16.67</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>93.98999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>96.26000000000001</v>
-      </c>
-      <c r="P69" s="52" t="n">
+        <v>100</v>
+      </c>
+      <c r="P69" s="15" t="n">
         <v>22595.55</v>
       </c>
       <c r="Q69" s="1" t="n">
@@ -4727,7 +4631,7 @@
       <c r="O70" s="1" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="P70" s="25" t="n">
+      <c r="P70" s="15" t="n">
         <v>22179.05</v>
       </c>
       <c r="Q70" s="1" t="n">
@@ -4772,7 +4676,7 @@
       <c r="O71" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P71" s="53" t="n">
+      <c r="P71" s="15" t="n">
         <v>22346.75</v>
       </c>
       <c r="Q71" s="1" t="n">

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -35,242 +35,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CBE9D3"/>
-        <bgColor rgb="00CBE9D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8EFDE"/>
-        <bgColor rgb="00D8EFDE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDB"/>
-        <bgColor rgb="00D4EDDB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCF0E2"/>
-        <bgColor rgb="00DCF0E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9E8D2"/>
-        <bgColor rgb="00C9E8D2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECF7EF"/>
-        <bgColor rgb="00ECF7EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFDFD"/>
-        <bgColor rgb="00FEFDFD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C7E7CF"/>
-        <bgColor rgb="00C7E7CF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BEE4C8"/>
-        <bgColor rgb="00BEE4C8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CFEBD7"/>
-        <bgColor rgb="00CFEBD7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5EB"/>
-        <bgColor rgb="00E8F5EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7FBF8"/>
-        <bgColor rgb="00F7FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6FBF8"/>
-        <bgColor rgb="00F6FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5FAF6"/>
-        <bgColor rgb="00F5FAF6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4F3E8"/>
-        <bgColor rgb="00E4F3E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCF0E1"/>
-        <bgColor rgb="00DCF0E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFCFC"/>
-        <bgColor rgb="00FEFCFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEEAEA"/>
-        <bgColor rgb="00FEEAEA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCCBCC"/>
-        <bgColor rgb="00FCCBCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCD3D3"/>
-        <bgColor rgb="00FCD3D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDDBDC"/>
-        <bgColor rgb="00FDDBDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCCFD0"/>
-        <bgColor rgb="00FCCFD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE1E2"/>
-        <bgColor rgb="00FDE1E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE3E4"/>
-        <bgColor rgb="00FDE3E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE0E1"/>
-        <bgColor rgb="00FDE0E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE5E5"/>
-        <bgColor rgb="00FDE5E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDDFE0"/>
-        <bgColor rgb="00FDDFE0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEEDED"/>
-        <bgColor rgb="00FEEDED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAFDFB"/>
-        <bgColor rgb="00FAFDFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFEFE"/>
-        <bgColor rgb="00FEFEFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE8E8"/>
-        <bgColor rgb="00FDE8E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE1E1"/>
-        <bgColor rgb="00FDE1E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE5E6"/>
-        <bgColor rgb="00FDE5E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEEAEB"/>
-        <bgColor rgb="00FEEAEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDDCDC"/>
-        <bgColor rgb="00FDDCDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDD7D7"/>
-        <bgColor rgb="00FDD7D7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF6F6"/>
-        <bgColor rgb="00FEF6F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7F5EB"/>
-        <bgColor rgb="00E7F5EB"/>
+        <fgColor rgb="00FDDADA"/>
+        <bgColor rgb="00FDDADA"/>
       </patternFill>
     </fill>
   </fills>
@@ -286,129 +52,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -933,7 +582,7 @@
       <c r="O2" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" s="1" t="n">
         <v>23336.3</v>
       </c>
       <c r="Q2" s="1" t="n">
@@ -980,7 +629,7 @@
         <v>33.33</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>83.33</v>
@@ -988,7 +637,7 @@
       <c r="O3" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="1" t="n">
         <v>23232.65</v>
       </c>
       <c r="Q3" s="1" t="n">
@@ -1014,13 +663,13 @@
         <v>3</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>0</v>
@@ -1029,21 +678,21 @@
         <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>4.19</v>
+        <v>7.5</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>33.33</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="1" t="n">
         <v>23263.9</v>
       </c>
       <c r="Q4" s="1" t="n">
@@ -1090,7 +739,7 @@
         <v>33.33</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>66.67</v>
@@ -1098,7 +747,7 @@
       <c r="O5" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="P5" s="1" t="n">
         <v>23199.45</v>
       </c>
       <c r="Q5" s="1" t="n">
@@ -1153,7 +802,7 @@
       <c r="O6" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="P6" s="1" t="n">
         <v>23347.05</v>
       </c>
       <c r="Q6" s="1" t="n">
@@ -1203,12 +852,12 @@
         <v>50</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="O7" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="P7" s="1" t="n">
         <v>23348.4</v>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1263,7 +912,7 @@
       <c r="O8" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="P8" s="1" t="n">
         <v>23081.15</v>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1313,12 +962,12 @@
         <v>50</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="O9" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="P9" s="1" t="n">
         <v>22908.05</v>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1368,12 +1017,12 @@
         <v>50</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="O10" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" s="1" t="n">
         <v>23368.85</v>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1428,7 +1077,7 @@
       <c r="O11" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P11" s="10" t="n">
+      <c r="P11" s="1" t="n">
         <v>23433.95</v>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1483,7 +1132,7 @@
       <c r="O12" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="1" t="n">
         <v>23301.15</v>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1538,7 +1187,7 @@
       <c r="O13" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="P13" s="1" t="n">
         <v>23264.8</v>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1593,7 +1242,7 @@
       <c r="O14" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P14" s="12" t="n">
+      <c r="P14" s="1" t="n">
         <v>23111.65</v>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1648,7 +1297,7 @@
       <c r="O15" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P15" s="13" t="n">
+      <c r="P15" s="1" t="n">
         <v>22995.65</v>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1703,7 +1352,7 @@
       <c r="O16" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P16" s="14" t="n">
+      <c r="P16" s="1" t="n">
         <v>23000</v>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1758,7 +1407,7 @@
       <c r="O17" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P17" s="15" t="inlineStr"/>
+      <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1809,7 +1458,7 @@
       <c r="O18" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P18" s="12" t="n">
+      <c r="P18" s="1" t="n">
         <v>23113.7</v>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1864,7 +1513,7 @@
       <c r="O19" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P19" s="16" t="n">
+      <c r="P19" s="1" t="n">
         <v>23126.3</v>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1917,9 +1566,9 @@
         <v>50</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="P20" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="P20" s="1" t="n">
         <v>23010.95</v>
       </c>
       <c r="Q20" s="1" t="n">
@@ -1974,7 +1623,7 @@
       <c r="O21" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="P21" s="1" t="n">
         <v>23261.85</v>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2027,9 +1676,9 @@
         <v>50</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="P22" s="18" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="P22" s="1" t="n">
         <v>23144.2</v>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2084,7 +1733,7 @@
       <c r="O23" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P23" s="19" t="n">
+      <c r="P23" s="1" t="n">
         <v>23206.45</v>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2134,12 +1783,12 @@
         <v>50</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="O24" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P24" s="12" t="n">
+      <c r="P24" s="1" t="n">
         <v>23109.7</v>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2186,7 +1835,7 @@
         <v>16.67</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>66.67</v>
@@ -2194,7 +1843,7 @@
       <c r="O25" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P25" s="13" t="n">
+      <c r="P25" s="1" t="n">
         <v>22997.25</v>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2241,7 +1890,7 @@
         <v>16.67</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="N26" s="1" t="n">
         <v>50</v>
@@ -2249,7 +1898,7 @@
       <c r="O26" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P26" s="20" t="n">
+      <c r="P26" s="1" t="n">
         <v>22891.3</v>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2304,7 +1953,7 @@
       <c r="O27" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P27" s="21" t="n">
+      <c r="P27" s="1" t="n">
         <v>22599.8</v>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2359,7 +2008,7 @@
       <c r="O28" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P28" s="22" t="n">
+      <c r="P28" s="1" t="n">
         <v>22114.45</v>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2414,7 +2063,7 @@
       <c r="O29" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P29" s="23" t="n">
+      <c r="P29" s="1" t="n">
         <v>22233.85</v>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2469,7 +2118,7 @@
       <c r="O30" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P30" s="24" t="n">
+      <c r="P30" s="1" t="n">
         <v>22370.15</v>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2513,7 +2162,7 @@
         <v>0.2</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M31" s="1" t="n">
         <v>0</v>
@@ -2524,7 +2173,7 @@
       <c r="O31" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P31" s="25" t="n">
+      <c r="P31" s="1" t="n">
         <v>22173.7</v>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2562,24 +2211,24 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1" t="n">
         <v>0.14</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="O32" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P32" s="26" t="n">
+      <c r="P32" s="1" t="n">
         <v>22465.35</v>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2623,18 +2272,18 @@
         <v>1.97</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="P33" s="27" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="P33" s="1" t="n">
         <v>22497.7</v>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2678,10 +2327,10 @@
         <v>1.44</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>16.67</v>
@@ -2689,7 +2338,7 @@
       <c r="O34" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P34" s="28" t="n">
+      <c r="P34" s="1" t="n">
         <v>22451.85</v>
       </c>
       <c r="Q34" s="1" t="n">
@@ -2712,7 +2361,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>4</v>
@@ -2744,7 +2393,7 @@
       <c r="O35" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P35" s="29" t="n">
+      <c r="P35" s="1" t="n">
         <v>22521.1</v>
       </c>
       <c r="Q35" s="1" t="n">
@@ -2797,9 +2446,9 @@
         <v>16.67</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="P36" s="30" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="P36" s="1" t="n">
         <v>22437.95</v>
       </c>
       <c r="Q36" s="1" t="n">
@@ -2854,7 +2503,7 @@
       <c r="O37" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P37" s="31" t="n">
+      <c r="P37" s="1" t="n">
         <v>22657</v>
       </c>
       <c r="Q37" s="1" t="n">
@@ -2909,7 +2558,7 @@
       <c r="O38" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P38" s="15" t="inlineStr"/>
+      <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2949,7 +2598,7 @@
         <v>0.02</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M39" s="1" t="n">
         <v>0</v>
@@ -2958,9 +2607,9 @@
         <v>16.67</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="P39" s="32" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="P39" s="1" t="n">
         <v>22967.4</v>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3004,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M40" s="1" t="n">
         <v>16.67</v>
@@ -3013,9 +2662,9 @@
         <v>33.33</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="P40" s="20" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="P40" s="1" t="n">
         <v>22897.2</v>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3041,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>0</v>
@@ -3056,10 +2705,10 @@
         <v>0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>6.29</v>
+        <v>10.4</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M41" s="1" t="n">
         <v>33.33</v>
@@ -3068,9 +2717,9 @@
         <v>33.33</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="P41" s="33" t="n">
+        <v>100</v>
+      </c>
+      <c r="P41" s="1" t="n">
         <v>22929.45</v>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3125,7 +2774,7 @@
       <c r="O42" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P42" s="31" t="n">
+      <c r="P42" s="1" t="n">
         <v>22651.3</v>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3180,7 +2829,7 @@
       <c r="O43" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P43" s="21" t="n">
+      <c r="P43" s="1" t="n">
         <v>22602.85</v>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3235,7 +2884,7 @@
       <c r="O44" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P44" s="34" t="n">
+      <c r="P44" s="1" t="n">
         <v>22578.15</v>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3290,7 +2939,7 @@
       <c r="O45" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P45" s="29" t="n">
+      <c r="P45" s="1" t="n">
         <v>22521.75</v>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3345,7 +2994,7 @@
       <c r="O46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P46" s="35" t="n">
+      <c r="P46" s="1" t="n">
         <v>22461.05</v>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3371,13 +3020,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>0</v>
@@ -3386,10 +3035,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.25</v>
+        <v>0.85</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M47" s="1" t="n">
         <v>0</v>
@@ -3400,7 +3049,7 @@
       <c r="O47" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P47" s="36" t="n">
+      <c r="P47" s="1" t="n">
         <v>22531.15</v>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3455,7 +3104,7 @@
       <c r="O48" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P48" s="37" t="n">
+      <c r="P48" s="1" t="n">
         <v>22613.1</v>
       </c>
       <c r="Q48" s="1" t="n">
@@ -3510,7 +3159,7 @@
       <c r="O49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P49" s="38" t="n">
+      <c r="P49" s="1" t="n">
         <v>22377.35</v>
       </c>
       <c r="Q49" s="1" t="n">
@@ -3565,7 +3214,7 @@
       <c r="O50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P50" s="39" t="n">
+      <c r="P50" s="1" t="n">
         <v>22299.9</v>
       </c>
       <c r="Q50" s="1" t="n">
@@ -3620,7 +3269,7 @@
       <c r="O51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P51" s="40" t="n">
+      <c r="P51" s="1" t="n">
         <v>22795.75</v>
       </c>
       <c r="Q51" s="1" t="n">
@@ -3675,7 +3324,7 @@
       <c r="O52" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P52" s="41" t="n">
+      <c r="P52" s="1" t="n">
         <v>23115.65</v>
       </c>
       <c r="Q52" s="1" t="n">
@@ -3730,7 +3379,7 @@
       <c r="O53" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P53" s="15" t="n">
+      <c r="P53" s="1" t="n">
         <v>23214</v>
       </c>
       <c r="Q53" s="1" t="n">
@@ -3777,7 +3426,7 @@
         <v>33.33</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="N54" s="1" t="n">
         <v>50</v>
@@ -3785,7 +3434,7 @@
       <c r="O54" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P54" s="15" t="n">
+      <c r="P54" s="1" t="n">
         <v>23133.4</v>
       </c>
       <c r="Q54" s="1" t="n">
@@ -3840,7 +3489,7 @@
       <c r="O55" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P55" s="15" t="n">
+      <c r="P55" s="1" t="n">
         <v>22808.25</v>
       </c>
       <c r="Q55" s="1" t="n">
@@ -3895,7 +3544,7 @@
       <c r="O56" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P56" s="15" t="n">
+      <c r="P56" s="1" t="n">
         <v>22830.75</v>
       </c>
       <c r="Q56" s="1" t="n">
@@ -3950,7 +3599,7 @@
       <c r="O57" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P57" s="15" t="inlineStr"/>
+      <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
     </row>
     <row r="58">
@@ -3968,9 +3617,7 @@
       <c r="D58" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
         <v>2</v>
       </c>
@@ -4001,7 +3648,7 @@
       <c r="O58" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P58" s="15" t="n">
+      <c r="P58" s="1" t="n">
         <v>22683.55</v>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4023,9 +3670,7 @@
       <c r="D59" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
         <v>3</v>
       </c>
@@ -4056,7 +3701,7 @@
       <c r="O59" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P59" s="15" t="n">
+      <c r="P59" s="1" t="n">
         <v>22871</v>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4078,9 +3723,7 @@
       <c r="D60" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
         <v>1</v>
       </c>
@@ -4094,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" s="1" t="n">
         <v>0.51</v>
@@ -4111,7 +3754,7 @@
       <c r="O60" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P60" s="15" t="n">
+      <c r="P60" s="1" t="n">
         <v>22765.6</v>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4164,7 +3807,7 @@
       <c r="O61" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P61" s="15" t="n">
+      <c r="P61" s="1" t="n">
         <v>22821.4</v>
       </c>
       <c r="Q61" s="1" t="n">
@@ -4200,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1" t="n">
         <v>0.57</v>
@@ -4217,7 +3860,7 @@
       <c r="O62" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P62" s="15" t="n">
+      <c r="P62" s="1" t="n">
         <v>22570.05</v>
       </c>
       <c r="Q62" s="1" t="n">
@@ -4236,9 +3879,7 @@
       <c r="C63" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
         <v>0</v>
@@ -4270,7 +3911,7 @@
       <c r="O63" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P63" s="15" t="n">
+      <c r="P63" s="1" t="n">
         <v>22810.85</v>
       </c>
       <c r="Q63" s="1" t="n">
@@ -4289,9 +3930,7 @@
       <c r="C64" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D64" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
         <v>1</v>
@@ -4323,7 +3962,7 @@
       <c r="O64" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P64" s="15" t="n">
+      <c r="P64" s="1" t="n">
         <v>22991.5</v>
       </c>
       <c r="Q64" s="1" t="n">
@@ -4342,9 +3981,7 @@
       <c r="C65" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
         <v>5</v>
@@ -4376,7 +4013,7 @@
       <c r="O65" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P65" s="15" t="n">
+      <c r="P65" s="1" t="n">
         <v>23042.35</v>
       </c>
       <c r="Q65" s="1" t="n">
@@ -4427,7 +4064,7 @@
       <c r="O66" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P66" s="15" t="n">
+      <c r="P66" s="1" t="n">
         <v>22865.8</v>
       </c>
       <c r="Q66" s="1" t="n">
@@ -4478,7 +4115,7 @@
       <c r="O67" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P67" s="15" t="n">
+      <c r="P67" s="1" t="n">
         <v>22869.4</v>
       </c>
       <c r="Q67" s="1" t="n">
@@ -4529,7 +4166,7 @@
       <c r="O68" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P68" s="15" t="n">
+      <c r="P68" s="1" t="n">
         <v>22656.3</v>
       </c>
       <c r="Q68" s="1" t="n">
@@ -4580,7 +4217,7 @@
       <c r="O69" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P69" s="15" t="n">
+      <c r="P69" s="1" t="n">
         <v>22595.55</v>
       </c>
       <c r="Q69" s="1" t="n">
@@ -4631,7 +4268,7 @@
       <c r="O70" s="1" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="P70" s="15" t="n">
+      <c r="P70" s="1" t="n">
         <v>22179.05</v>
       </c>
       <c r="Q70" s="1" t="n">
@@ -4676,7 +4313,7 @@
       <c r="O71" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P71" s="15" t="n">
+      <c r="P71" s="2" t="n">
         <v>22346.75</v>
       </c>
       <c r="Q71" s="1" t="n">

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,12 +26,318 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="54">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBE9D3"/>
+        <bgColor rgb="00CBE9D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EFDE"/>
+        <bgColor rgb="00D8EFDE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDB"/>
+        <bgColor rgb="00D4EDDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E2"/>
+        <bgColor rgb="00DCF0E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D2"/>
+        <bgColor rgb="00C9E8D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF7EF"/>
+        <bgColor rgb="00ECF7EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFDFD"/>
+        <bgColor rgb="00FEFDFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C7E7CF"/>
+        <bgColor rgb="00C7E7CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BEE4C8"/>
+        <bgColor rgb="00BEE4C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFEBD7"/>
+        <bgColor rgb="00CFEBD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5EB"/>
+        <bgColor rgb="00E8F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FBF8"/>
+        <bgColor rgb="00F7FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6FBF8"/>
+        <bgColor rgb="00F6FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5FAF6"/>
+        <bgColor rgb="00F5FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F3E8"/>
+        <bgColor rgb="00E4F3E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E1"/>
+        <bgColor rgb="00DCF0E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFCFC"/>
+        <bgColor rgb="00FEFCFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEAEA"/>
+        <bgColor rgb="00FEEAEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCCBCC"/>
+        <bgColor rgb="00FCCBCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCD3D3"/>
+        <bgColor rgb="00FCD3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDBDC"/>
+        <bgColor rgb="00FDDBDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCCFD0"/>
+        <bgColor rgb="00FCCFD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE1E2"/>
+        <bgColor rgb="00FDE1E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE3E4"/>
+        <bgColor rgb="00FDE3E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE0E1"/>
+        <bgColor rgb="00FDE0E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE5E5"/>
+        <bgColor rgb="00FDE5E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDFE0"/>
+        <bgColor rgb="00FDDFE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEDED"/>
+        <bgColor rgb="00FEEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFDFB"/>
+        <bgColor rgb="00FAFDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFEFE"/>
+        <bgColor rgb="00FEFEFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE1E1"/>
+        <bgColor rgb="00FDE1E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE5E6"/>
+        <bgColor rgb="00FDE5E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEAEB"/>
+        <bgColor rgb="00FEEAEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDCDC"/>
+        <bgColor rgb="00FDDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDD7D7"/>
+        <bgColor rgb="00FDD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF6F6"/>
+        <bgColor rgb="00FEF6F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7F5EB"/>
+        <bgColor rgb="00E7F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBF0E0"/>
+        <bgColor rgb="00DBF0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5F4E9"/>
+        <bgColor rgb="00E5F4E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF7F7"/>
+        <bgColor rgb="00FEF7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF8F8"/>
+        <bgColor rgb="00FEF8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEFEF"/>
+        <bgColor rgb="00FEEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFAFB"/>
+        <bgColor rgb="00FEFAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF4F4"/>
+        <bgColor rgb="00FEF4F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FCF8"/>
+        <bgColor rgb="00F7FCF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F9F3"/>
+        <bgColor rgb="00F1F9F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFAFA"/>
+        <bgColor rgb="00FEFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE9EA"/>
+        <bgColor rgb="00FEE9EA"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -52,12 +358,165 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,7 +1041,7 @@
       <c r="O2" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="P2" s="2" t="n">
         <v>23336.3</v>
       </c>
       <c r="Q2" s="1" t="n">
@@ -637,7 +1096,7 @@
       <c r="O3" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="P3" s="3" t="n">
         <v>23232.65</v>
       </c>
       <c r="Q3" s="1" t="n">
@@ -692,7 +1151,7 @@
       <c r="O4" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="P4" s="4" t="n">
         <v>23263.9</v>
       </c>
       <c r="Q4" s="1" t="n">
@@ -747,7 +1206,7 @@
       <c r="O5" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="P5" s="5" t="n">
         <v>23199.45</v>
       </c>
       <c r="Q5" s="1" t="n">
@@ -802,7 +1261,7 @@
       <c r="O6" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="P6" s="6" t="n">
         <v>23347.05</v>
       </c>
       <c r="Q6" s="1" t="n">
@@ -857,7 +1316,7 @@
       <c r="O7" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="P7" s="6" t="n">
         <v>23348.4</v>
       </c>
       <c r="Q7" s="1" t="n">
@@ -912,7 +1371,7 @@
       <c r="O8" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="P8" s="7" t="n">
         <v>23081.15</v>
       </c>
       <c r="Q8" s="1" t="n">
@@ -967,7 +1426,7 @@
       <c r="O9" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="P9" s="8" t="n">
         <v>22908.05</v>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1022,7 +1481,7 @@
       <c r="O10" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P10" s="1" t="n">
+      <c r="P10" s="9" t="n">
         <v>23368.85</v>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1077,7 +1536,7 @@
       <c r="O11" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P11" s="1" t="n">
+      <c r="P11" s="10" t="n">
         <v>23433.95</v>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1132,7 +1591,7 @@
       <c r="O12" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="P12" s="11" t="n">
         <v>23301.15</v>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1187,7 +1646,7 @@
       <c r="O13" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P13" s="1" t="n">
+      <c r="P13" s="4" t="n">
         <v>23264.8</v>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1242,7 +1701,7 @@
       <c r="O14" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P14" s="1" t="n">
+      <c r="P14" s="12" t="n">
         <v>23111.65</v>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1297,7 +1756,7 @@
       <c r="O15" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P15" s="1" t="n">
+      <c r="P15" s="13" t="n">
         <v>22995.65</v>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1352,7 +1811,7 @@
       <c r="O16" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P16" s="1" t="n">
+      <c r="P16" s="14" t="n">
         <v>23000</v>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1407,7 +1866,7 @@
       <c r="O17" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P17" s="1" t="inlineStr"/>
+      <c r="P17" s="15" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1458,7 +1917,7 @@
       <c r="O18" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P18" s="1" t="n">
+      <c r="P18" s="12" t="n">
         <v>23113.7</v>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1513,7 +1972,7 @@
       <c r="O19" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P19" s="1" t="n">
+      <c r="P19" s="16" t="n">
         <v>23126.3</v>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1568,7 +2027,7 @@
       <c r="O20" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P20" s="1" t="n">
+      <c r="P20" s="17" t="n">
         <v>23010.95</v>
       </c>
       <c r="Q20" s="1" t="n">
@@ -1623,7 +2082,7 @@
       <c r="O21" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P21" s="1" t="n">
+      <c r="P21" s="4" t="n">
         <v>23261.85</v>
       </c>
       <c r="Q21" s="1" t="n">
@@ -1678,7 +2137,7 @@
       <c r="O22" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P22" s="1" t="n">
+      <c r="P22" s="18" t="n">
         <v>23144.2</v>
       </c>
       <c r="Q22" s="1" t="n">
@@ -1733,7 +2192,7 @@
       <c r="O23" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P23" s="1" t="n">
+      <c r="P23" s="19" t="n">
         <v>23206.45</v>
       </c>
       <c r="Q23" s="1" t="n">
@@ -1788,7 +2247,7 @@
       <c r="O24" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P24" s="1" t="n">
+      <c r="P24" s="12" t="n">
         <v>23109.7</v>
       </c>
       <c r="Q24" s="1" t="n">
@@ -1843,7 +2302,7 @@
       <c r="O25" s="1" t="n">
         <v>83.33</v>
       </c>
-      <c r="P25" s="1" t="n">
+      <c r="P25" s="13" t="n">
         <v>22997.25</v>
       </c>
       <c r="Q25" s="1" t="n">
@@ -1898,7 +2357,7 @@
       <c r="O26" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P26" s="1" t="n">
+      <c r="P26" s="20" t="n">
         <v>22891.3</v>
       </c>
       <c r="Q26" s="1" t="n">
@@ -1953,7 +2412,7 @@
       <c r="O27" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P27" s="1" t="n">
+      <c r="P27" s="21" t="n">
         <v>22599.8</v>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2008,7 +2467,7 @@
       <c r="O28" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P28" s="1" t="n">
+      <c r="P28" s="22" t="n">
         <v>22114.45</v>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2063,7 +2522,7 @@
       <c r="O29" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P29" s="1" t="n">
+      <c r="P29" s="23" t="n">
         <v>22233.85</v>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2118,7 +2577,7 @@
       <c r="O30" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P30" s="1" t="n">
+      <c r="P30" s="24" t="n">
         <v>22370.15</v>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2173,7 +2632,7 @@
       <c r="O31" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P31" s="1" t="n">
+      <c r="P31" s="25" t="n">
         <v>22173.7</v>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2228,7 +2687,7 @@
       <c r="O32" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P32" s="1" t="n">
+      <c r="P32" s="26" t="n">
         <v>22465.35</v>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2283,7 +2742,7 @@
       <c r="O33" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P33" s="1" t="n">
+      <c r="P33" s="27" t="n">
         <v>22497.7</v>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2338,7 +2797,7 @@
       <c r="O34" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P34" s="1" t="n">
+      <c r="P34" s="28" t="n">
         <v>22451.85</v>
       </c>
       <c r="Q34" s="1" t="n">
@@ -2393,7 +2852,7 @@
       <c r="O35" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P35" s="1" t="n">
+      <c r="P35" s="29" t="n">
         <v>22521.1</v>
       </c>
       <c r="Q35" s="1" t="n">
@@ -2448,7 +2907,7 @@
       <c r="O36" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P36" s="1" t="n">
+      <c r="P36" s="30" t="n">
         <v>22437.95</v>
       </c>
       <c r="Q36" s="1" t="n">
@@ -2503,7 +2962,7 @@
       <c r="O37" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P37" s="1" t="n">
+      <c r="P37" s="31" t="n">
         <v>22657</v>
       </c>
       <c r="Q37" s="1" t="n">
@@ -2558,7 +3017,7 @@
       <c r="O38" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P38" s="1" t="inlineStr"/>
+      <c r="P38" s="15" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2609,7 +3068,7 @@
       <c r="O39" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P39" s="1" t="n">
+      <c r="P39" s="32" t="n">
         <v>22967.4</v>
       </c>
       <c r="Q39" s="1" t="n">
@@ -2664,7 +3123,7 @@
       <c r="O40" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P40" s="1" t="n">
+      <c r="P40" s="20" t="n">
         <v>22897.2</v>
       </c>
       <c r="Q40" s="1" t="n">
@@ -2719,7 +3178,7 @@
       <c r="O41" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P41" s="1" t="n">
+      <c r="P41" s="33" t="n">
         <v>22929.45</v>
       </c>
       <c r="Q41" s="1" t="n">
@@ -2774,7 +3233,7 @@
       <c r="O42" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P42" s="1" t="n">
+      <c r="P42" s="31" t="n">
         <v>22651.3</v>
       </c>
       <c r="Q42" s="1" t="n">
@@ -2829,7 +3288,7 @@
       <c r="O43" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P43" s="1" t="n">
+      <c r="P43" s="21" t="n">
         <v>22602.85</v>
       </c>
       <c r="Q43" s="1" t="n">
@@ -2884,7 +3343,7 @@
       <c r="O44" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P44" s="1" t="n">
+      <c r="P44" s="34" t="n">
         <v>22578.15</v>
       </c>
       <c r="Q44" s="1" t="n">
@@ -2939,7 +3398,7 @@
       <c r="O45" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P45" s="1" t="n">
+      <c r="P45" s="29" t="n">
         <v>22521.75</v>
       </c>
       <c r="Q45" s="1" t="n">
@@ -2994,7 +3453,7 @@
       <c r="O46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P46" s="1" t="n">
+      <c r="P46" s="35" t="n">
         <v>22461.05</v>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3049,7 +3508,7 @@
       <c r="O47" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P47" s="1" t="n">
+      <c r="P47" s="36" t="n">
         <v>22531.15</v>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3104,7 +3563,7 @@
       <c r="O48" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P48" s="1" t="n">
+      <c r="P48" s="37" t="n">
         <v>22613.1</v>
       </c>
       <c r="Q48" s="1" t="n">
@@ -3159,7 +3618,7 @@
       <c r="O49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P49" s="1" t="n">
+      <c r="P49" s="38" t="n">
         <v>22377.35</v>
       </c>
       <c r="Q49" s="1" t="n">
@@ -3214,7 +3673,7 @@
       <c r="O50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P50" s="1" t="n">
+      <c r="P50" s="39" t="n">
         <v>22299.9</v>
       </c>
       <c r="Q50" s="1" t="n">
@@ -3269,7 +3728,7 @@
       <c r="O51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P51" s="1" t="n">
+      <c r="P51" s="40" t="n">
         <v>22795.75</v>
       </c>
       <c r="Q51" s="1" t="n">
@@ -3324,7 +3783,7 @@
       <c r="O52" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P52" s="1" t="n">
+      <c r="P52" s="41" t="n">
         <v>23115.65</v>
       </c>
       <c r="Q52" s="1" t="n">
@@ -3379,7 +3838,7 @@
       <c r="O53" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P53" s="1" t="n">
+      <c r="P53" s="42" t="n">
         <v>23214</v>
       </c>
       <c r="Q53" s="1" t="n">
@@ -3434,7 +3893,7 @@
       <c r="O54" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="P54" s="1" t="n">
+      <c r="P54" s="43" t="n">
         <v>23133.4</v>
       </c>
       <c r="Q54" s="1" t="n">
@@ -3489,7 +3948,7 @@
       <c r="O55" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P55" s="1" t="n">
+      <c r="P55" s="44" t="n">
         <v>22808.25</v>
       </c>
       <c r="Q55" s="1" t="n">
@@ -3544,7 +4003,7 @@
       <c r="O56" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P56" s="1" t="n">
+      <c r="P56" s="45" t="n">
         <v>22830.75</v>
       </c>
       <c r="Q56" s="1" t="n">
@@ -3599,7 +4058,7 @@
       <c r="O57" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P57" s="1" t="inlineStr"/>
+      <c r="P57" s="15" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
     </row>
     <row r="58">
@@ -3648,7 +4107,7 @@
       <c r="O58" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P58" s="1" t="n">
+      <c r="P58" s="46" t="n">
         <v>22683.55</v>
       </c>
       <c r="Q58" s="1" t="n">
@@ -3701,7 +4160,7 @@
       <c r="O59" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P59" s="1" t="n">
+      <c r="P59" s="47" t="n">
         <v>22871</v>
       </c>
       <c r="Q59" s="1" t="n">
@@ -3754,7 +4213,7 @@
       <c r="O60" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P60" s="1" t="n">
+      <c r="P60" s="48" t="n">
         <v>22765.6</v>
       </c>
       <c r="Q60" s="1" t="n">
@@ -3807,7 +4266,7 @@
       <c r="O61" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P61" s="1" t="n">
+      <c r="P61" s="44" t="n">
         <v>22821.4</v>
       </c>
       <c r="Q61" s="1" t="n">
@@ -3860,7 +4319,7 @@
       <c r="O62" s="1" t="n">
         <v>16.67</v>
       </c>
-      <c r="P62" s="1" t="n">
+      <c r="P62" s="34" t="n">
         <v>22570.05</v>
       </c>
       <c r="Q62" s="1" t="n">
@@ -3911,7 +4370,7 @@
       <c r="O63" s="1" t="n">
         <v>33.33</v>
       </c>
-      <c r="P63" s="1" t="n">
+      <c r="P63" s="44" t="n">
         <v>22810.85</v>
       </c>
       <c r="Q63" s="1" t="n">
@@ -3962,7 +4421,7 @@
       <c r="O64" s="1" t="n">
         <v>66.67</v>
       </c>
-      <c r="P64" s="1" t="n">
+      <c r="P64" s="49" t="n">
         <v>22991.5</v>
       </c>
       <c r="Q64" s="1" t="n">
@@ -4013,7 +4472,7 @@
       <c r="O65" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P65" s="1" t="n">
+      <c r="P65" s="50" t="n">
         <v>23042.35</v>
       </c>
       <c r="Q65" s="1" t="n">
@@ -4064,7 +4523,7 @@
       <c r="O66" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P66" s="1" t="n">
+      <c r="P66" s="51" t="n">
         <v>22865.8</v>
       </c>
       <c r="Q66" s="1" t="n">
@@ -4115,7 +4574,7 @@
       <c r="O67" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P67" s="1" t="n">
+      <c r="P67" s="51" t="n">
         <v>22869.4</v>
       </c>
       <c r="Q67" s="1" t="n">
@@ -4166,7 +4625,7 @@
       <c r="O68" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P68" s="1" t="n">
+      <c r="P68" s="31" t="n">
         <v>22656.3</v>
       </c>
       <c r="Q68" s="1" t="n">
@@ -4217,7 +4676,7 @@
       <c r="O69" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P69" s="1" t="n">
+      <c r="P69" s="52" t="n">
         <v>22595.55</v>
       </c>
       <c r="Q69" s="1" t="n">
@@ -4268,7 +4727,7 @@
       <c r="O70" s="1" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="P70" s="1" t="n">
+      <c r="P70" s="25" t="n">
         <v>22179.05</v>
       </c>
       <c r="Q70" s="1" t="n">
@@ -4313,7 +4772,7 @@
       <c r="O71" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="P71" s="53" t="n">
         <v>22346.75</v>
       </c>
       <c r="Q71" s="1" t="n">

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -1000,46 +1000,46 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>475</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" s="1" t="n">
-        <v>99.98999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>33.33</v>
+        <v>55.5</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>83.33</v>
+        <v>62.53</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>100</v>
+        <v>50.87</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>100</v>
+        <v>44.07</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>23336.3</v>
@@ -1055,46 +1055,46 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1</v>
+        <v>3.18</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1</v>
+        <v>1.65</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1</v>
+        <v>447</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>5</v>
+        <v>0.67</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>2.53</v>
+        <v>0.95</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>33.33</v>
+        <v>56.01</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>66.67</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>83.33</v>
+        <v>56.06</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>66.67</v>
+        <v>50.2</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>23232.65</v>
@@ -1110,46 +1110,46 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="F4" s="1" t="n">
+        <v>452</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" s="1" t="n">
-        <v>7.5</v>
+        <v>2.25</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>33.33</v>
+        <v>57.83</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>66.67</v>
+        <v>64.13</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>83.33</v>
+        <v>59.12</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>83.33</v>
+        <v>54.19</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>23263.9</v>
@@ -1165,46 +1165,46 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1</v>
+        <v>1.74</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="G5" s="1" t="n">
+        <v>580</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" s="1" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>33.33</v>
+        <v>56.63</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>66.67</v>
+        <v>61.33</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>66.67</v>
+        <v>53.79</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>50</v>
+        <v>47.27</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>23199.45</v>
@@ -1220,46 +1220,46 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>4</v>
+        <v>381</v>
       </c>
       <c r="G6" s="1" t="n">
+        <v>368</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" s="1" t="n">
-        <v>1.66</v>
+        <v>0.79</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>33.33</v>
+        <v>56.97</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>50</v>
+        <v>65.2</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>83.33</v>
+        <v>65.11</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>83.33</v>
+        <v>64.45</v>
       </c>
       <c r="P6" s="6" t="n">
         <v>23347.05</v>
@@ -1275,46 +1275,46 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>6</v>
+        <v>605</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>99.98999999999999</v>
+        <v>11.15</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>33.33</v>
+        <v>55.59</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>50</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>83.33</v>
+        <v>64.45</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>83.33</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="P7" s="6" t="n">
         <v>23348.4</v>
@@ -1330,46 +1330,46 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>4</v>
+        <v>624</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>2</v>
+        <v>4.91</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>5.95</v>
+        <v>7.66</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>33.33</v>
+        <v>52.67</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>50</v>
+        <v>56.09</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>33.33</v>
+        <v>51.4</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>16.67</v>
+        <v>45.41</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>23081.15</v>
@@ -1385,46 +1385,46 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G9" s="1" t="n">
+        <v>665</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" s="1" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>33.33</v>
+        <v>49.74</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>50</v>
+        <v>49.92</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>50</v>
+        <v>37.82</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>33.33</v>
+        <v>26.1</v>
       </c>
       <c r="P9" s="8" t="n">
         <v>22908.05</v>
@@ -1440,46 +1440,46 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>3</v>
+        <v>241</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>3</v>
+        <v>506</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>33.33</v>
+        <v>56.28</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>50</v>
+        <v>60.75</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>66.67</v>
+        <v>58.06</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>83.33</v>
+        <v>51.66</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>23368.85</v>
@@ -1495,46 +1495,46 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>3</v>
+        <v>363</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>3</v>
+        <v>387</v>
       </c>
       <c r="H11" s="1" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="J11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" s="1" t="n">
-        <v>4.92</v>
+        <v>0.52</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>33.33</v>
+        <v>57.07</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>50</v>
+        <v>63.61</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>66.67</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>66.67</v>
+        <v>63.52</v>
       </c>
       <c r="P11" s="10" t="n">
         <v>23433.95</v>
@@ -1550,46 +1550,46 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>5</v>
+        <v>353</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>1</v>
+        <v>396</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>5</v>
+        <v>0.89</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>5.97</v>
+        <v>1.44</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>33.33</v>
+        <v>56.9</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>50</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>50</v>
+        <v>66.84</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>83.33</v>
+        <v>66.05</v>
       </c>
       <c r="P12" s="11" t="n">
         <v>23301.15</v>
@@ -1605,46 +1605,46 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>537</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" s="1" t="n">
-        <v>1.06</v>
+        <v>2.03</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>33.33</v>
+        <v>56.55</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>50</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>50</v>
+        <v>69.73</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>50</v>
+        <v>68.67</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>23264.8</v>
@@ -1660,46 +1660,46 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>3</v>
+        <v>416</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>3</v>
+        <v>334</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.58</v>
+        <v>3.41</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>33.33</v>
+        <v>52.93</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>50</v>
+        <v>60.15</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>50</v>
+        <v>61.47</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>50</v>
+        <v>57.07</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>23111.65</v>
@@ -1715,46 +1715,46 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>6</v>
+        <v>304</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>33.33</v>
+        <v>51.9</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>50</v>
+        <v>58.05</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>50</v>
+        <v>57.87</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>33.33</v>
+        <v>50.13</v>
       </c>
       <c r="P15" s="13" t="n">
         <v>22995.65</v>
@@ -1770,46 +1770,46 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>3</v>
+        <v>472</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>1</v>
+        <v>0.59</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>33.33</v>
+        <v>50.34</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>50</v>
+        <v>55.79</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>50</v>
+        <v>50.13</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>50</v>
+        <v>41.33</v>
       </c>
       <c r="P16" s="14" t="n">
         <v>23000</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>0</v>
@@ -1855,16 +1855,16 @@
         <v>0</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>33.33</v>
+        <v>52.59</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>50</v>
+        <v>59.85</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>66.67</v>
+        <v>60.27</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>66.67</v>
+        <v>50.8</v>
       </c>
       <c r="P17" s="15" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
@@ -1876,46 +1876,46 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0</v>
+        <v>6.88</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="G18" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="J18" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" s="1" t="n">
-        <v>4.49</v>
+        <v>0.55</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>33.33</v>
+        <v>52.41</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>66.67</v>
+        <v>60.27</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>66.67</v>
+        <v>50.8</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>23113.7</v>
@@ -1931,46 +1931,46 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>6</v>
+        <v>389</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>6</v>
+        <v>1.08</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>99.98999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>33.33</v>
+        <v>52.93</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>50</v>
+        <v>62.41</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>50</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>66.67</v>
+        <v>63.73</v>
       </c>
       <c r="P19" s="16" t="n">
         <v>23126.3</v>
@@ -1986,46 +1986,46 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>6</v>
+        <v>569</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>16.67</v>
+        <v>53.28</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>50</v>
+        <v>61.8</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>50</v>
+        <v>69.33</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>50</v>
+        <v>64.13</v>
       </c>
       <c r="P20" s="17" t="n">
         <v>23010.95</v>
@@ -2041,46 +2041,46 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>6</v>
+        <v>496</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>99.98999999999999</v>
+        <v>2.09</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>33.33</v>
+        <v>55.52</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>50</v>
+        <v>68.42</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>66.67</v>
+        <v>79.2</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>66.67</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>23261.85</v>
@@ -2096,46 +2096,46 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0</v>
+        <v>8.57</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>1</v>
+        <v>395</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>5</v>
+        <v>353</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.2</v>
+        <v>1.12</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>33.33</v>
+        <v>53.97</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>50</v>
+        <v>65.41</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>66.67</v>
+        <v>75.2</v>
       </c>
       <c r="P22" s="18" t="n">
         <v>23144.2</v>
@@ -2151,46 +2151,46 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0</v>
+        <v>16.57</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>3</v>
+        <v>448</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>3</v>
+        <v>302</v>
       </c>
       <c r="H23" s="1" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="J23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" s="1" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>16.67</v>
+        <v>53.28</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>50</v>
+        <v>65.86</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>66.67</v>
+        <v>76.8</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>83.33</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="P23" s="19" t="n">
         <v>23206.45</v>
@@ -2206,46 +2206,46 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0</v>
+        <v>10.35</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>6</v>
+        <v>452</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>6</v>
+        <v>1.53</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>99.98999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>16.67</v>
+        <v>51.9</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>50</v>
+        <v>63.61</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>83.33</v>
+        <v>74.67</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>100</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>23109.7</v>
@@ -2261,46 +2261,46 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>5</v>
+        <v>436</v>
       </c>
       <c r="G25" s="1" t="n">
+        <v>313</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="J25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" s="1" t="n">
-        <v>7.52</v>
+        <v>1.26</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>16.67</v>
+        <v>50.34</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>50</v>
+        <v>61.8</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>66.67</v>
+        <v>73.47</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>83.33</v>
+        <v>79.33</v>
       </c>
       <c r="P25" s="13" t="n">
         <v>22997.25</v>
@@ -2316,46 +2316,46 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>5</v>
+        <v>575</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>5.09</v>
+        <v>5.84</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>16.67</v>
+        <v>49.74</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>50</v>
+        <v>59.85</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>50</v>
+        <v>70.27</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>66.67</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P26" s="20" t="n">
         <v>22891.3</v>
@@ -2371,46 +2371,46 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>6</v>
+        <v>691</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>6</v>
+        <v>11.91</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>99.98999999999999</v>
+        <v>33.39</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>16.67</v>
+        <v>46.63</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>33.33</v>
+        <v>49.92</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>50</v>
+        <v>53.07</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>66.67</v>
+        <v>61.2</v>
       </c>
       <c r="P27" s="21" t="n">
         <v>22599.8</v>
@@ -2426,46 +2426,46 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>4</v>
+        <v>576</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>16.67</v>
+        <v>39.03</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>16.67</v>
+        <v>38.35</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>33.33</v>
+        <v>27.73</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>33.33</v>
+        <v>21.87</v>
       </c>
       <c r="P28" s="22" t="n">
         <v>22114.45</v>
@@ -2481,46 +2481,46 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>2</v>
+        <v>590</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>2</v>
+        <v>0.27</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>3.09</v>
+        <v>0.18</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>16.67</v>
+        <v>43.18</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>16.67</v>
+        <v>44.21</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>33.33</v>
+        <v>36.27</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>33.33</v>
+        <v>30.67</v>
       </c>
       <c r="P29" s="23" t="n">
         <v>22233.85</v>
@@ -2536,46 +2536,46 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>3</v>
+        <v>596</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>16.67</v>
+        <v>44.91</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0</v>
+        <v>50.98</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>33.33</v>
+        <v>43.87</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>33.33</v>
+        <v>43.2</v>
       </c>
       <c r="P30" s="24" t="n">
         <v>22370.15</v>
@@ -2591,46 +2591,46 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>5</v>
+        <v>648</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>16.67</v>
+        <v>41.45</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0</v>
+        <v>44.81</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>16.67</v>
+        <v>30.4</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>16.67</v>
+        <v>24.27</v>
       </c>
       <c r="P31" s="25" t="n">
         <v>22173.7</v>
@@ -2646,46 +2646,46 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>5</v>
+        <v>390</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.14</v>
+        <v>2.32</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>16.67</v>
+        <v>44.91</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0</v>
+        <v>55.04</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>50</v>
+        <v>44.93</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>50</v>
+        <v>45.33</v>
       </c>
       <c r="P32" s="26" t="n">
         <v>22465.35</v>
@@ -2701,46 +2701,46 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>3</v>
+        <v>400</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>3</v>
+        <v>350</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>16.67</v>
+        <v>44.81</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>0</v>
+        <v>56.99</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>33.33</v>
+        <v>45.6</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>33.33</v>
+        <v>43.33</v>
       </c>
       <c r="P33" s="27" t="n">
         <v>22497.7</v>
@@ -2756,46 +2756,46 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>2</v>
+        <v>1.06</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>3</v>
+        <v>308</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>3</v>
+        <v>441</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>16.67</v>
+        <v>43.77</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>16.67</v>
+        <v>57.29</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>16.67</v>
+        <v>43.33</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>33.33</v>
+        <v>37.73</v>
       </c>
       <c r="P34" s="28" t="n">
         <v>22451.85</v>
@@ -2811,46 +2811,46 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>4</v>
+        <v>469</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>2</v>
+        <v>279</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>33.33</v>
+        <v>60</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>33.33</v>
+        <v>43.87</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="P35" s="29" t="n">
         <v>22521.1</v>
@@ -2866,46 +2866,46 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1</v>
+        <v>1.93</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>2</v>
+        <v>221</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>4</v>
+        <v>529</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0</v>
+        <v>42.73</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0</v>
+        <v>58.95</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>16.67</v>
+        <v>38.13</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>33.33</v>
+        <v>31.87</v>
       </c>
       <c r="P36" s="30" t="n">
         <v>22437.95</v>
@@ -2921,46 +2921,46 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1</v>
+        <v>1.85</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>5</v>
+        <v>540</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>0</v>
+        <v>43.94</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>0</v>
+        <v>47.6</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>0</v>
+        <v>42.13</v>
       </c>
       <c r="P37" s="31" t="n">
         <v>22657</v>
@@ -2982,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1</v>
+        <v>2.11</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>0</v>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>0</v>
@@ -3006,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>16.67</v>
+        <v>47.58</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0</v>
+        <v>72.48</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>16.67</v>
+        <v>61.33</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>33.33</v>
+        <v>60.67</v>
       </c>
       <c r="P38" s="15" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
@@ -3027,46 +3027,46 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>1</v>
+        <v>2.15</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>1</v>
+        <v>389</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>5</v>
+        <v>359</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.02</v>
+        <v>4.35</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>16.67</v>
+        <v>47.66</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0</v>
+        <v>73.23</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>16.67</v>
+        <v>61.33</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>33.33</v>
+        <v>60.67</v>
       </c>
       <c r="P39" s="32" t="n">
         <v>22967.4</v>
@@ -3082,46 +3082,46 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="E40" s="1" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>362</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>386</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="J40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" s="1" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>16.67</v>
+        <v>46.88</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>16.67</v>
+        <v>73.83</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>33.33</v>
+        <v>62.13</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>66.67</v>
+        <v>63.47</v>
       </c>
       <c r="P40" s="20" t="n">
         <v>22897.2</v>
@@ -3137,46 +3137,46 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D41" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>566</v>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="J41" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K41" s="1" t="n">
-        <v>10.4</v>
+        <v>8.33</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>16.67</v>
+        <v>46.18</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>33.33</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>33.33</v>
+        <v>61.2</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>100</v>
+        <v>63.6</v>
       </c>
       <c r="P41" s="33" t="n">
         <v>22929.45</v>
@@ -3192,46 +3192,46 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>3</v>
+        <v>372</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>3</v>
+        <v>374</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>0</v>
+        <v>44.1</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0</v>
+        <v>68.12</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>16.67</v>
+        <v>48.8</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>50</v>
+        <v>46.93</v>
       </c>
       <c r="P42" s="31" t="n">
         <v>22651.3</v>
@@ -3247,46 +3247,46 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>1</v>
+        <v>445</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>4</v>
+        <v>302</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.25</v>
+        <v>1.47</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.22</v>
+        <v>2.81</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>0</v>
+        <v>42.01</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>16.67</v>
+        <v>48.13</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>16.67</v>
+        <v>45.73</v>
       </c>
       <c r="P43" s="21" t="n">
         <v>22602.85</v>
@@ -3302,46 +3302,46 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1</v>
+        <v>1.34</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>3</v>
+        <v>367</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>3</v>
+        <v>381</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.51</v>
+        <v>2.65</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>0</v>
+        <v>41.15</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0</v>
+        <v>66.77</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>16.67</v>
+        <v>42</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>16.67</v>
+        <v>38.13</v>
       </c>
       <c r="P44" s="34" t="n">
         <v>22578.15</v>
@@ -3357,46 +3357,46 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>3</v>
+        <v>493</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1</v>
+        <v>1.93</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.59</v>
+        <v>2.38</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>0</v>
+        <v>41.32</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>16.67</v>
+        <v>40.93</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>16.67</v>
+        <v>34.4</v>
       </c>
       <c r="P45" s="29" t="n">
         <v>22521.75</v>
@@ -3412,46 +3412,46 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>4</v>
+        <v>164</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>2</v>
+        <v>585</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>2</v>
+        <v>0.28</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>2.02</v>
+        <v>0.29</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>0</v>
+        <v>39.76</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>0</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>0</v>
+        <v>32.53</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>0</v>
+        <v>23.33</v>
       </c>
       <c r="P46" s="35" t="n">
         <v>22461.05</v>
@@ -3467,46 +3467,46 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>3</v>
+        <v>494</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>1</v>
+        <v>0.52</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>16.67</v>
+        <v>44.27</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0</v>
+        <v>71.13</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>0</v>
+        <v>42.27</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>0</v>
+        <v>31.87</v>
       </c>
       <c r="P47" s="36" t="n">
         <v>22531.15</v>
@@ -3522,46 +3522,46 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>4</v>
+        <v>424</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>2</v>
+        <v>326</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>4.49</v>
+        <v>3.4</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>16.67</v>
+        <v>44.79</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0</v>
+        <v>72.33</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>0</v>
+        <v>46.4</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>0</v>
+        <v>35.47</v>
       </c>
       <c r="P48" s="37" t="n">
         <v>22613.1</v>
@@ -3577,46 +3577,46 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0</v>
+        <v>449</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>6</v>
+        <v>298</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>0</v>
+        <v>43.23</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0</v>
+        <v>71.28</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>0</v>
+        <v>43.73</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>0</v>
+        <v>29.87</v>
       </c>
       <c r="P49" s="38" t="n">
         <v>22377.35</v>
@@ -3632,46 +3632,46 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>5</v>
+        <v>696</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>16.67</v>
+        <v>42.19</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>0</v>
+        <v>70.23</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>0</v>
+        <v>37.73</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>0</v>
+        <v>22.93</v>
       </c>
       <c r="P50" s="39" t="n">
         <v>22299.9</v>
@@ -3687,46 +3687,46 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>5</v>
+        <v>561</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J51" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>0.17</v>
+        <v>0.88</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>16.67</v>
+        <v>49.91</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>16.67</v>
+        <v>82.41</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>0</v>
+        <v>50.53</v>
       </c>
       <c r="P51" s="40" t="n">
         <v>22795.75</v>
@@ -3742,46 +3742,46 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C52" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>324</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>425</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="J52" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>33.33</v>
+        <v>54.78</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>16.67</v>
+        <v>87.22</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>16.67</v>
+        <v>82.27</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>16.67</v>
+        <v>73.47</v>
       </c>
       <c r="P52" s="41" t="n">
         <v>23115.65</v>
@@ -3797,46 +3797,46 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>33.33</v>
+        <v>56.52</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>16.67</v>
+        <v>87.97</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>50</v>
+        <v>87.87</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>50</v>
+        <v>82.67</v>
       </c>
       <c r="P53" s="42" t="n">
         <v>23214</v>
@@ -3852,46 +3852,46 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>4</v>
+        <v>605</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>2</v>
+        <v>4.17</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>3.16</v>
+        <v>6.12</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>33.33</v>
+        <v>52.52</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>33.33</v>
+        <v>86.92</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>50</v>
+        <v>86.8</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>50</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="P54" s="43" t="n">
         <v>23133.4</v>
@@ -3907,46 +3907,46 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>2</v>
+        <v>343</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>4</v>
+        <v>405</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.4</v>
+        <v>1.86</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>33.33</v>
+        <v>47.65</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>16.67</v>
+        <v>79.7</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>16.67</v>
+        <v>73.87</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>16.67</v>
+        <v>62.53</v>
       </c>
       <c r="P55" s="44" t="n">
         <v>22808.25</v>
@@ -3962,46 +3962,46 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>3</v>
+        <v>531</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>3</v>
+        <v>218</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>1</v>
+        <v>2.44</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>3.07</v>
+        <v>2.58</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>33.33</v>
+        <v>46.86</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>16.67</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>16.67</v>
+        <v>77.2</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>16.67</v>
+        <v>66.8</v>
       </c>
       <c r="P56" s="45" t="n">
         <v>22830.75</v>
@@ -4023,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>0</v>
@@ -4047,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>16.67</v>
+        <v>43.55</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>16.67</v>
+        <v>77.44</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>16.67</v>
+        <v>64.8</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>16.67</v>
+        <v>49.73</v>
       </c>
       <c r="P57" s="15" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
@@ -4068,44 +4068,44 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>2</v>
+        <v>196</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>4</v>
+        <v>552</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>16.67</v>
+        <v>41.77</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>16.67</v>
+        <v>77.47</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>16.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>16.67</v>
+        <v>55.07</v>
       </c>
       <c r="P58" s="46" t="n">
         <v>22683.55</v>
@@ -4121,44 +4121,44 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>3</v>
+        <v>370</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>3</v>
+        <v>378</v>
       </c>
       <c r="H59" s="1" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="J59" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K59" s="1" t="n">
-        <v>0.87</v>
+        <v>2.06</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>16.67</v>
+        <v>43.74</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>16.67</v>
+        <v>79.2</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>33.33</v>
+        <v>80.67</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>16.67</v>
+        <v>70.13</v>
       </c>
       <c r="P59" s="47" t="n">
         <v>22871</v>
@@ -4174,44 +4174,44 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>1</v>
+        <v>285</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>5</v>
+        <v>463</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.2</v>
+        <v>0.62</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>0.51</v>
+        <v>1.94</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>16.67</v>
+        <v>44.06</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>16.67</v>
+        <v>77.87</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>33.33</v>
+        <v>81.2</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>33.33</v>
+        <v>70.8</v>
       </c>
       <c r="P60" s="48" t="n">
         <v>22765.6</v>
@@ -4227,44 +4227,44 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>5</v>
+        <v>648</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>5</v>
+        <v>6.35</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>5.19</v>
+        <v>8.17</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>16.67</v>
+        <v>44.22</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>16.67</v>
+        <v>80.13</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>33.33</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>33.33</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="P61" s="44" t="n">
         <v>22821.4</v>
@@ -4280,44 +4280,44 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>4</v>
+        <v>590</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>0.57</v>
+        <v>0.37</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>16.67</v>
+        <v>40.1</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>33.33</v>
+        <v>78</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>16.67</v>
+        <v>62.13</v>
       </c>
       <c r="P62" s="34" t="n">
         <v>22570.05</v>
@@ -4333,42 +4333,42 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>6</v>
+        <v>511</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>16.67</v>
+        <v>42.63</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>16.67</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>33.33</v>
+        <v>87.33</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>33.33</v>
+        <v>82.13</v>
       </c>
       <c r="P63" s="44" t="n">
         <v>22810.85</v>
@@ -4384,42 +4384,42 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
+        <v>497</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="J64" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="K64" s="1" t="n">
-        <v>0.13</v>
+        <v>2.88</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>16.67</v>
+        <v>43.4</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>16.67</v>
+        <v>82.13</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>66.67</v>
+        <v>91.87</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>66.67</v>
+        <v>90</v>
       </c>
       <c r="P64" s="49" t="n">
         <v>22991.5</v>
@@ -4435,42 +4435,42 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>5</v>
+        <v>509</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>1</v>
+        <v>239</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>5</v>
+        <v>2.13</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>3.74</v>
+        <v>2.82</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>33.33</v>
+        <v>41.08</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>50</v>
+        <v>81.73</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>83.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>100</v>
+        <v>92.67</v>
       </c>
       <c r="P65" s="50" t="n">
         <v>23042.35</v>
@@ -4486,42 +4486,42 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>4</v>
+        <v>474</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>0.7</v>
+        <v>0.53</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>83.33</v>
+        <v>93.33</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>100</v>
+        <v>92.13</v>
       </c>
       <c r="P66" s="51" t="n">
         <v>22865.8</v>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -884,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -996,920 +996,924 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>28</v>
-      </c>
       <c r="D2" s="1" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>271</v>
+        <v>438</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>475</v>
+        <v>311</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.72</v>
+        <v>1.49</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>55.5</v>
+        <v>56.6</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>62.53</v>
+        <v>63.6</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>50.87</v>
+        <v>55.66</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>44.07</v>
+        <v>50.47</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23336.3</v>
+        <v>23338.05</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>3.18</v>
+        <v>1.51</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.95</v>
+        <v>0.72</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>56.01</v>
+        <v>55.5</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>56.06</v>
+        <v>50.87</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>23232.65</v>
+        <v>44.07</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>23336.3</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>4.9</v>
+        <v>3.18</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>299</v>
+        <v>447</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.51</v>
+        <v>0.67</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>2.25</v>
+        <v>0.95</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>57.83</v>
+        <v>56.01</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>64.13</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>59.12</v>
+        <v>56.06</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>54.19</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>23263.9</v>
+        <v>50.2</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>23232.65</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="D5" s="1" t="n">
-        <v>1.74</v>
+        <v>4.9</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>580</v>
+        <v>299</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.29</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.38</v>
+        <v>2.25</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>56.63</v>
+        <v>57.83</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>61.33</v>
+        <v>64.13</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>53.79</v>
+        <v>59.12</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>23199.45</v>
+        <v>54.19</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>23263.9</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>368</v>
+        <v>580</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>56.97</v>
+        <v>56.63</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>65.2</v>
+        <v>61.33</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>65.11</v>
+        <v>53.79</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>23347.05</v>
+        <v>47.27</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>23199.45</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>144</v>
+        <v>368</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>11.15</v>
+        <v>0.79</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>55.59</v>
+        <v>56.97</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N7" s="1" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>64.45</v>
       </c>
-      <c r="O7" s="1" t="n">
-        <v>64.18000000000001</v>
-      </c>
       <c r="P7" s="6" t="n">
-        <v>23348.4</v>
+        <v>23347.05</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>4.91</v>
+        <v>4.2</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>7.66</v>
+        <v>11.15</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>52.67</v>
+        <v>55.59</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>56.09</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>51.4</v>
+        <v>64.45</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>45.41</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>23081.15</v>
+        <v>64.18000000000001</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>23348.4</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>86</v>
+        <v>624</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>665</v>
+        <v>127</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.13</v>
+        <v>4.91</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>49.74</v>
+        <v>52.67</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>49.92</v>
+        <v>56.09</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>37.82</v>
+        <v>51.4</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="P9" s="8" t="n">
-        <v>22908.05</v>
+        <v>45.41</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>23081.15</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1.87</v>
+        <v>1.24</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>506</v>
+        <v>665</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>56.28</v>
+        <v>49.74</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>60.75</v>
+        <v>49.92</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>58.06</v>
+        <v>37.82</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>51.66</v>
-      </c>
-      <c r="P10" s="9" t="n">
-        <v>23368.85</v>
+        <v>26.1</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>22908.05</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>387</v>
+        <v>506</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>57.07</v>
+        <v>56.28</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>63.61</v>
+        <v>60.75</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>65.65000000000001</v>
+        <v>58.06</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>63.52</v>
-      </c>
-      <c r="P11" s="10" t="n">
-        <v>23433.95</v>
+        <v>51.66</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>23368.85</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>56.9</v>
+        <v>57.07</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>63.61</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>66.05</v>
-      </c>
-      <c r="P12" s="11" t="n">
-        <v>23301.15</v>
+        <v>63.52</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>23433.95</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>537</v>
+        <v>353</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>56.55</v>
+        <v>56.9</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>64.51000000000001</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>69.73</v>
+        <v>66.84</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>23264.8</v>
+        <v>66.05</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>416</v>
+        <v>537</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>52.93</v>
+        <v>56.55</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>60.15</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>61.47</v>
+        <v>69.73</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="P14" s="12" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>51.9</v>
+        <v>52.93</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>58.05</v>
+        <v>60.15</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>57.87</v>
+        <v>61.47</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>22995.65</v>
+        <v>57.07</v>
+      </c>
+      <c r="P15" s="12" t="n">
+        <v>23111.65</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>277</v>
+        <v>445</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>472</v>
+        <v>304</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>50.34</v>
+        <v>51.9</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>55.79</v>
+        <v>58.05</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O16" s="1" t="n">
         <v>50.13</v>
       </c>
-      <c r="O16" s="1" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="P16" s="14" t="n">
-        <v>23000</v>
+      <c r="P16" s="13" t="n">
+        <v>22995.65</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>4.73</v>
+        <v>2.71</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>52.59</v>
+        <v>50.34</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>59.85</v>
+        <v>55.79</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>60.27</v>
+        <v>50.13</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P17" s="15" t="inlineStr"/>
-      <c r="Q17" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>6.88</v>
+        <v>4.73</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>52.41</v>
+        <v>52.59</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>60</v>
+        <v>59.85</v>
       </c>
       <c r="N18" s="1" t="n">
         <v>60.27</v>
@@ -1917,1150 +1921,1150 @@
       <c r="O18" s="1" t="n">
         <v>50.8</v>
       </c>
-      <c r="P18" s="12" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q18" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="P18" s="15" t="inlineStr"/>
+      <c r="Q18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>6.56</v>
+        <v>6.88</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>389</v>
+        <v>249</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>52.93</v>
+        <v>52.41</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>62.41</v>
+        <v>60</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.27</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P19" s="16" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P19" s="12" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>4.94</v>
+        <v>6.56</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>569</v>
+        <v>361</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>53.28</v>
+        <v>52.93</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>61.8</v>
+        <v>62.41</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>69.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="P20" s="17" t="n">
-        <v>23010.95</v>
+        <v>63.73</v>
+      </c>
+      <c r="P20" s="16" t="n">
+        <v>23126.3</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>6.04</v>
+        <v>4.94</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.95</v>
+        <v>0.32</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>55.52</v>
+        <v>53.28</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>68.42</v>
+        <v>61.8</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>79.2</v>
+        <v>69.33</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>8.57</v>
+        <v>6.9</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>3.21</v>
+        <v>6.04</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>395</v>
+        <v>496</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>53.97</v>
+        <v>55.52</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>65.41</v>
+        <v>68.42</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>74</v>
+        <v>79.2</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="P22" s="18" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>16.57</v>
+        <v>8.57</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>53.28</v>
+        <v>53.97</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>65.86</v>
+        <v>65.41</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>76.8</v>
+        <v>74</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="P23" s="19" t="n">
-        <v>23206.45</v>
+        <v>75.2</v>
+      </c>
+      <c r="P23" s="18" t="n">
+        <v>23144.2</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>10.35</v>
+        <v>16.57</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>51.9</v>
+        <v>53.28</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>63.61</v>
+        <v>65.86</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>74.67</v>
+        <v>76.8</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="P24" s="12" t="n">
-        <v>23109.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="P24" s="19" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>4.7</v>
+        <v>10.35</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>50.34</v>
+        <v>51.9</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>61.8</v>
+        <v>63.61</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>73.47</v>
+        <v>74.67</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>79.33</v>
-      </c>
-      <c r="P25" s="13" t="n">
-        <v>22997.25</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="P25" s="12" t="n">
+        <v>23109.7</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>5.63</v>
+        <v>4.7</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>575</v>
+        <v>436</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>3.3</v>
+        <v>1.39</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>49.74</v>
+        <v>50.34</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>59.85</v>
+        <v>61.8</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>70.27</v>
+        <v>73.47</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P26" s="20" t="n">
-        <v>22891.3</v>
+        <v>79.33</v>
+      </c>
+      <c r="P26" s="13" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>2</v>
+        <v>5.63</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>691</v>
+        <v>575</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>11.91</v>
+        <v>3.3</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>33.39</v>
+        <v>5.84</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>46.63</v>
+        <v>49.74</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>49.92</v>
+        <v>59.85</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>53.07</v>
+        <v>70.27</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="P27" s="21" t="n">
-        <v>22599.8</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="P27" s="20" t="n">
+        <v>22891.3</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>173</v>
+        <v>691</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>576</v>
+        <v>58</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>39.03</v>
+        <v>46.63</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>38.35</v>
+        <v>49.92</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>27.73</v>
+        <v>53.07</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>21.87</v>
-      </c>
-      <c r="P28" s="22" t="n">
-        <v>22114.45</v>
+        <v>61.2</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>22599.8</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>43.18</v>
+        <v>39.03</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>44.21</v>
+        <v>38.35</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>36.27</v>
+        <v>27.73</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>30.67</v>
-      </c>
-      <c r="P29" s="23" t="n">
-        <v>22233.85</v>
+        <v>21.87</v>
+      </c>
+      <c r="P29" s="22" t="n">
+        <v>22114.45</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>596</v>
+        <v>160</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>153</v>
+        <v>590</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>3.9</v>
+        <v>0.27</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>44.91</v>
+        <v>43.18</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>50.98</v>
+        <v>44.21</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>43.87</v>
+        <v>36.27</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="P30" s="24" t="n">
-        <v>22370.15</v>
+        <v>30.67</v>
+      </c>
+      <c r="P30" s="23" t="n">
+        <v>22233.85</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>102</v>
+        <v>596</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>648</v>
+        <v>153</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.16</v>
+        <v>3.9</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>41.45</v>
+        <v>44.91</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>44.81</v>
+        <v>50.98</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>30.4</v>
+        <v>43.87</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>24.27</v>
-      </c>
-      <c r="P31" s="25" t="n">
-        <v>22173.7</v>
+        <v>43.2</v>
+      </c>
+      <c r="P31" s="24" t="n">
+        <v>22370.15</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>44.91</v>
+        <v>41.45</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>55.04</v>
+        <v>44.81</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>44.93</v>
+        <v>30.4</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="P32" s="26" t="n">
-        <v>22465.35</v>
+        <v>24.27</v>
+      </c>
+      <c r="P32" s="25" t="n">
+        <v>22173.7</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>1.9</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>44.81</v>
+        <v>44.91</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>56.99</v>
+        <v>55.04</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>45.6</v>
+        <v>44.93</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="P33" s="27" t="n">
-        <v>22497.7</v>
+        <v>45.33</v>
+      </c>
+      <c r="P33" s="26" t="n">
+        <v>22465.35</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>43.77</v>
+        <v>44.81</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>57.29</v>
+        <v>56.99</v>
       </c>
       <c r="N34" s="1" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>43.33</v>
       </c>
-      <c r="O34" s="1" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="P34" s="28" t="n">
-        <v>22451.85</v>
+      <c r="P34" s="27" t="n">
+        <v>22497.7</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>469</v>
+        <v>308</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>43.6</v>
+        <v>43.77</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>60</v>
+        <v>57.29</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>43.87</v>
+        <v>43.33</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="P35" s="29" t="n">
-        <v>22521.1</v>
+        <v>37.73</v>
+      </c>
+      <c r="P35" s="28" t="n">
+        <v>22451.85</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>221</v>
+        <v>469</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>42.73</v>
+        <v>43.6</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>38.13</v>
+        <v>43.87</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="P36" s="30" t="n">
-        <v>22437.95</v>
+        <v>40</v>
+      </c>
+      <c r="P36" s="29" t="n">
+        <v>22521.1</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J37" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>43.94</v>
+        <v>42.73</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>66.31999999999999</v>
+        <v>58.95</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>47.6</v>
+        <v>38.13</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>42.13</v>
-      </c>
-      <c r="P37" s="31" t="n">
-        <v>22657</v>
+        <v>31.87</v>
+      </c>
+      <c r="P37" s="30" t="n">
+        <v>22437.95</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>47.58</v>
+        <v>43.94</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>72.48</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>61.33</v>
+        <v>47.6</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P38" s="15" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P38" s="31" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q38" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>47.66</v>
+        <v>47.58</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>73.23</v>
+        <v>72.48</v>
       </c>
       <c r="N39" s="1" t="n">
         <v>61.33</v>
@@ -3068,94 +3072,90 @@
       <c r="O39" s="1" t="n">
         <v>60.67</v>
       </c>
-      <c r="P39" s="32" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q39" s="1" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="P39" s="15" t="inlineStr"/>
+      <c r="Q39" s="1" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>46.88</v>
+        <v>47.66</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>73.83</v>
+        <v>73.23</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>62.13</v>
+        <v>61.33</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P40" s="20" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P40" s="32" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>3.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>27</v>
@@ -3164,1427 +3164,1427 @@
         <v>1</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>8.33</v>
+        <v>1.98</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>46.18</v>
+        <v>46.88</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>74.73999999999999</v>
+        <v>73.83</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>61.2</v>
+        <v>62.13</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P41" s="33" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P41" s="20" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>372</v>
+        <v>566</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>374</v>
+        <v>183</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.99</v>
+        <v>3.09</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>2.48</v>
+        <v>8.33</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>44.1</v>
+        <v>46.18</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>68.12</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>48.8</v>
+        <v>61.2</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P42" s="31" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P42" s="33" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>1.47</v>
+        <v>0.99</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J43" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>42.01</v>
+        <v>44.1</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>68.56999999999999</v>
+        <v>68.12</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>48.13</v>
+        <v>48.8</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P43" s="21" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P43" s="31" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>367</v>
+        <v>445</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>381</v>
+        <v>302</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>41.15</v>
+        <v>42.01</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>66.77</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>42</v>
+        <v>48.13</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P44" s="34" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P44" s="21" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>493</v>
+        <v>367</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>41.32</v>
+        <v>41.15</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>67.06999999999999</v>
+        <v>66.77</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>40.93</v>
+        <v>42</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P45" s="29" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P45" s="34" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>39.76</v>
+        <v>41.32</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>32.53</v>
+        <v>40.93</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P46" s="35" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P46" s="29" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>44.27</v>
+        <v>39.76</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>71.13</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>42.27</v>
+        <v>32.53</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="P47" s="36" t="n">
-        <v>22531.15</v>
+        <v>23.33</v>
+      </c>
+      <c r="P47" s="35" t="n">
+        <v>22461.05</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>44.79</v>
+        <v>44.27</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>72.33</v>
+        <v>71.13</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>46.4</v>
+        <v>42.27</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>35.47</v>
-      </c>
-      <c r="P48" s="37" t="n">
-        <v>22613.1</v>
+        <v>31.87</v>
+      </c>
+      <c r="P48" s="36" t="n">
+        <v>22531.15</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E49" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L49" s="1" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="M49" s="1" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="N49" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O49" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P49" s="37" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q49" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F49" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K49" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L49" s="1" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="M49" s="1" t="n">
-        <v>71.28</v>
-      </c>
-      <c r="N49" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O49" s="1" t="n">
-        <v>29.87</v>
-      </c>
-      <c r="P49" s="38" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q49" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>696</v>
+        <v>298</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>42.19</v>
+        <v>43.23</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>70.23</v>
+        <v>71.28</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>37.73</v>
+        <v>43.73</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="P50" s="39" t="n">
-        <v>22299.9</v>
+        <v>29.87</v>
+      </c>
+      <c r="P50" s="38" t="n">
+        <v>22377.35</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>2.27</v>
+        <v>0.74</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>2.29</v>
+        <v>1.01</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>49.91</v>
+        <v>42.19</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>82.41</v>
+        <v>70.23</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.73</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>50.53</v>
-      </c>
-      <c r="P51" s="40" t="n">
-        <v>22795.75</v>
+        <v>22.93</v>
+      </c>
+      <c r="P51" s="39" t="n">
+        <v>22299.9</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>4.89</v>
+        <v>2.27</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>4.33</v>
+        <v>2.29</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>54.78</v>
+        <v>49.91</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>87.22</v>
+        <v>82.41</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>82.27</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>73.47</v>
-      </c>
-      <c r="P52" s="41" t="n">
-        <v>23115.65</v>
+        <v>50.53</v>
+      </c>
+      <c r="P52" s="40" t="n">
+        <v>22795.75</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>5.93</v>
+        <v>4.89</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J53" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>56.52</v>
+        <v>54.78</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>87.97</v>
+        <v>87.22</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>87.87</v>
+        <v>82.27</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="P53" s="42" t="n">
-        <v>23214</v>
+        <v>73.47</v>
+      </c>
+      <c r="P53" s="41" t="n">
+        <v>23115.65</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>52.52</v>
+        <v>56.52</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>86.92</v>
+        <v>87.97</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>86.8</v>
+        <v>87.87</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>80.93000000000001</v>
-      </c>
-      <c r="P54" s="43" t="n">
-        <v>23133.4</v>
+        <v>82.67</v>
+      </c>
+      <c r="P54" s="42" t="n">
+        <v>23214</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>343</v>
+        <v>605</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>405</v>
+        <v>145</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>47.65</v>
+        <v>52.52</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>79.7</v>
+        <v>86.92</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>73.87</v>
+        <v>86.8</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P55" s="44" t="n">
-        <v>22808.25</v>
+        <v>80.93000000000001</v>
+      </c>
+      <c r="P55" s="43" t="n">
+        <v>23133.4</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>531</v>
+        <v>343</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>46.86</v>
+        <v>47.65</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>80.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>77.2</v>
+        <v>73.87</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="P56" s="45" t="n">
-        <v>22830.75</v>
+        <v>62.53</v>
+      </c>
+      <c r="P56" s="44" t="n">
+        <v>22808.25</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>3.64</v>
+        <v>2.33</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>2.68</v>
+        <v>3.02</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>43.55</v>
+        <v>46.86</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>77.44</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>64.8</v>
+        <v>77.2</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="P57" s="15" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="P57" s="45" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q57" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>41.77</v>
+        <v>43.55</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>77.47</v>
+        <v>77.44</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="P58" s="46" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q58" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.73</v>
+      </c>
+      <c r="P58" s="15" t="inlineStr"/>
+      <c r="Q58" s="1" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>378</v>
+        <v>552</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>43.74</v>
+        <v>41.77</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>79.2</v>
+        <v>77.47</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>80.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>70.13</v>
-      </c>
-      <c r="P59" s="47" t="n">
-        <v>22871</v>
+        <v>55.07</v>
+      </c>
+      <c r="P59" s="46" t="n">
+        <v>22683.55</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>3.02</v>
+        <v>2.38</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>285</v>
+        <v>370</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>44.06</v>
+        <v>43.74</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>77.87</v>
+        <v>79.2</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>81.2</v>
+        <v>80.67</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="P60" s="48" t="n">
-        <v>22765.6</v>
+        <v>70.13</v>
+      </c>
+      <c r="P60" s="47" t="n">
+        <v>22871</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>648</v>
+        <v>285</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>6.35</v>
+        <v>0.62</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>44.22</v>
+        <v>44.06</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>80.13</v>
+        <v>77.87</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P61" s="44" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P61" s="48" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2.12</v>
+        <v>3.62</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>40.1</v>
+        <v>44.22</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>72</v>
+        <v>80.13</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>78</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P62" s="34" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P62" s="44" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>42.63</v>
+        <v>40.1</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>78.93000000000001</v>
+        <v>72</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>87.33</v>
+        <v>78</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P63" s="44" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P63" s="34" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>497</v>
+        <v>236</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>249</v>
+        <v>511</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>2</v>
+        <v>0.46</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J64" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>43.4</v>
+        <v>42.63</v>
       </c>
       <c r="M64" s="1" t="n">
+        <v>78.93000000000001</v>
+      </c>
+      <c r="N64" s="1" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="O64" s="1" t="n">
         <v>82.13</v>
       </c>
-      <c r="N64" s="1" t="n">
-        <v>91.87</v>
-      </c>
-      <c r="O64" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="P64" s="49" t="n">
-        <v>22991.5</v>
+      <c r="P64" s="44" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>41.08</v>
+        <v>43.4</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>81.73</v>
+        <v>82.13</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>91.87</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>92.67</v>
-      </c>
-      <c r="P65" s="50" t="n">
-        <v>23042.35</v>
+        <v>90</v>
+      </c>
+      <c r="P65" s="49" t="n">
+        <v>22991.5</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>93.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>92.13</v>
-      </c>
-      <c r="P66" s="51" t="n">
-        <v>22865.8</v>
+        <v>92.67</v>
+      </c>
+      <c r="P66" s="50" t="n">
+        <v>23042.35</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>5</v>
+        <v>0.58</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>7.36</v>
+        <v>0.53</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>100</v>
+        <v>92.13</v>
       </c>
       <c r="P67" s="51" t="n">
-        <v>22869.4</v>
+        <v>22865.8</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -4596,13 +4596,13 @@
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I68" s="1" t="n">
         <v>0</v>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>0.16</v>
+        <v>7.36</v>
       </c>
       <c r="L68" s="1" t="n">
         <v>16.67</v>
@@ -4620,22 +4620,22 @@
         <v>16.67</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O68" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P68" s="31" t="n">
-        <v>22656.3</v>
+      <c r="P68" s="51" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -4647,13 +4647,13 @@
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I69" s="1" t="n">
         <v>0</v>
@@ -4662,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>3.72</v>
+        <v>0.16</v>
       </c>
       <c r="L69" s="1" t="n">
         <v>16.67</v>
@@ -4671,116 +4671,167 @@
         <v>16.67</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O69" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P69" s="52" t="n">
-        <v>22595.55</v>
+      <c r="P69" s="31" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>0.49</v>
+        <v>5</v>
       </c>
       <c r="I70" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J70" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>0.75</v>
+        <v>3.72</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>31.26</v>
+        <v>16.67</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>52.93</v>
+        <v>16.67</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>84.27</v>
+        <v>83.33</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P70" s="25" t="n">
-        <v>22179.05</v>
+        <v>100</v>
+      </c>
+      <c r="P70" s="52" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G71" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J71" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L71" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M71" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N71" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O71" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P71" s="25" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q71" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1" t="inlineStr"/>
+      <c r="E72" s="1" t="inlineStr"/>
+      <c r="F72" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G71" s="1" t="n">
+      <c r="G72" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H71" s="1" t="n">
+      <c r="H72" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr"/>
-      <c r="L71" s="1" t="n">
+      <c r="I72" s="1" t="inlineStr"/>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
+      <c r="L72" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M71" s="1" t="n">
+      <c r="M72" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N71" s="1" t="n">
+      <c r="N72" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O71" s="1" t="n">
+      <c r="O72" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P71" s="53" t="n">
+      <c r="P72" s="53" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q71" s="1" t="n">
+      <c r="Q72" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B71">
+  <conditionalFormatting sqref="B2:B72">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4790,7 +4841,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C71">
+  <conditionalFormatting sqref="C2:C72">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4800,7 +4851,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E71">
+  <conditionalFormatting sqref="D2:E72">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4812,7 +4863,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F71">
+  <conditionalFormatting sqref="F2:F72">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4822,7 +4873,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G71">
+  <conditionalFormatting sqref="G2:G72">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4832,7 +4883,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H71">
+  <conditionalFormatting sqref="H2:H72">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4844,7 +4895,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I71">
+  <conditionalFormatting sqref="I2:I72">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4854,7 +4905,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J71">
+  <conditionalFormatting sqref="J2:J72">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4864,7 +4915,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K71">
+  <conditionalFormatting sqref="K2:K72">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4876,7 +4927,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O71">
+  <conditionalFormatting sqref="L2:O72">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4888,7 +4939,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q71">
+  <conditionalFormatting sqref="Q2:Q72">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="54">
+  <fills count="55">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D1"/>
+        <bgColor rgb="00C9E8D1"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -358,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -517,6 +523,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -884,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -996,2221 +1005,2221 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>438</v>
+        <v>396</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>56.6</v>
+        <v>57.04</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>63.6</v>
+        <v>63.02</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>55.66</v>
+        <v>56.67</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>50.47</v>
+        <v>53.33</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23338.05</v>
+        <v>23352.15</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>28</v>
-      </c>
       <c r="D3" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>1.51</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>1.53</v>
-      </c>
       <c r="F3" s="1" t="n">
-        <v>271</v>
+        <v>438</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>475</v>
+        <v>310</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.72</v>
+        <v>1.49</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>55.5</v>
+        <v>56.53</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>62.53</v>
+        <v>63.55</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>50.87</v>
+        <v>55.73</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>23336.3</v>
+        <v>50.53</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>23338.05</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>3.18</v>
+        <v>1.51</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.95</v>
+        <v>0.72</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>56.01</v>
+        <v>55.42</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>62.48</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>56.06</v>
+        <v>50.93</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>50.2</v>
+        <v>44.13</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>23232.65</v>
+        <v>23336.3</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>4.9</v>
+        <v>3.18</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>299</v>
+        <v>446</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.51</v>
+        <v>0.67</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>2.25</v>
+        <v>0.95</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>57.83</v>
+        <v>55.94</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>64.13</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>59.12</v>
+        <v>56.13</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>54.19</v>
+        <v>50.27</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="D6" s="1" t="n">
-        <v>1.74</v>
+        <v>4.9</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>170</v>
+        <v>451</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>580</v>
+        <v>299</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.29</v>
+        <v>1.51</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.38</v>
+        <v>2.25</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>56.63</v>
+        <v>57.76</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>61.33</v>
+        <v>64.09</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>53.79</v>
+        <v>59.2</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>47.27</v>
+        <v>54.27</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>368</v>
+        <v>579</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>56.97</v>
+        <v>56.55</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>65.2</v>
+        <v>61.28</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>65.11</v>
+        <v>53.87</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>64.45</v>
+        <v>47.33</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>144</v>
+        <v>367</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>11.15</v>
+        <v>0.79</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>55.59</v>
+        <v>56.9</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>64.45</v>
+        <v>65.2</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v>23348.4</v>
+        <v>64.53</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>4.91</v>
+        <v>4.19</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>7.66</v>
+        <v>11.14</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>52.67</v>
+        <v>55.52</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>56.09</v>
+        <v>64.89</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>51.4</v>
+        <v>64.53</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>45.41</v>
+        <v>64.27</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>86</v>
+        <v>623</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>665</v>
+        <v>127</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.13</v>
+        <v>4.91</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.6</v>
+        <v>7.65</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>49.74</v>
+        <v>52.59</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>49.92</v>
+        <v>56.02</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>37.82</v>
+        <v>51.47</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>26.1</v>
+        <v>45.47</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>506</v>
+        <v>664</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>56.28</v>
+        <v>49.66</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>60.75</v>
+        <v>49.85</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>58.06</v>
+        <v>37.87</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>51.66</v>
+        <v>26.13</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>23368.85</v>
+        <v>22908.05</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>387</v>
+        <v>505</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>57.07</v>
+        <v>56.21</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>63.61</v>
+        <v>60.69</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>65.65000000000001</v>
+        <v>58.13</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>63.52</v>
+        <v>51.73</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>23433.95</v>
+        <v>23368.85</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>56.9</v>
+        <v>56.99</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>66.84</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>66.05</v>
+        <v>63.6</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>23301.15</v>
+        <v>23433.95</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>537</v>
+        <v>353</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>212</v>
+        <v>395</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>2.03</v>
+        <v>1.45</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>56.55</v>
+        <v>56.82</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>64.51000000000001</v>
+        <v>64.91</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>69.73</v>
+        <v>66.8</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="P14" s="4" t="n">
-        <v>23264.8</v>
+        <v>66</v>
+      </c>
+      <c r="P14" s="12" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>416</v>
+        <v>536</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>52.93</v>
+        <v>56.48</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>60.15</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>61.47</v>
+        <v>69.69</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <v>23111.65</v>
+        <v>68.62</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>51.9</v>
+        <v>52.85</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>58.05</v>
+        <v>60.09</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>57.87</v>
+        <v>61.42</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>50.13</v>
+        <v>57.01</v>
       </c>
       <c r="P16" s="13" t="n">
-        <v>22995.65</v>
+        <v>23111.65</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>277</v>
+        <v>444</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>472</v>
+        <v>304</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>50.34</v>
+        <v>51.81</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>55.79</v>
+        <v>57.98</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>50.13</v>
+        <v>57.81</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>41.33</v>
+        <v>50.07</v>
       </c>
       <c r="P17" s="14" t="n">
-        <v>23000</v>
+        <v>22995.65</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>4.73</v>
+        <v>2.68</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>52.59</v>
+        <v>50.26</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>59.85</v>
+        <v>55.72</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>60.27</v>
+        <v>50.07</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P18" s="15" t="inlineStr"/>
-      <c r="Q18" s="1" t="inlineStr"/>
+        <v>41.26</v>
+      </c>
+      <c r="P18" s="15" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>6.88</v>
+        <v>4.69</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>52.41</v>
+        <v>52.5</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>60</v>
+        <v>59.79</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>60.27</v>
+        <v>60.21</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P19" s="12" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q19" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+        <v>50.73</v>
+      </c>
+      <c r="P19" s="16" t="inlineStr"/>
+      <c r="Q19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>3.69</v>
+        <v>2.66</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>6.56</v>
+        <v>6.84</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>389</v>
+        <v>248</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>52.93</v>
+        <v>52.33</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>62.41</v>
+        <v>59.94</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.21</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P20" s="16" t="n">
-        <v>23126.3</v>
+        <v>50.73</v>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>5.4</v>
+        <v>3.64</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>4.94</v>
+        <v>6.52</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>569</v>
+        <v>360</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>53.28</v>
+        <v>52.85</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>61.8</v>
+        <v>62.35</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>69.33</v>
+        <v>68.36</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>64.13</v>
+        <v>63.68</v>
       </c>
       <c r="P21" s="17" t="n">
-        <v>23010.95</v>
+        <v>23126.3</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>6.9</v>
+        <v>5.31</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>6.04</v>
+        <v>4.91</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>254</v>
+        <v>568</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.95</v>
+        <v>0.32</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>55.52</v>
+        <v>53.2</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>68.42</v>
+        <v>61.75</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>79.2</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>23261.85</v>
+        <v>64.09</v>
+      </c>
+      <c r="P22" s="18" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>8.57</v>
+        <v>6.8</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>3.21</v>
+        <v>6</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>395</v>
+        <v>495</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>53.97</v>
+        <v>55.44</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>65.41</v>
+        <v>68.37</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>74</v>
+        <v>79.17</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="P23" s="18" t="n">
-        <v>23144.2</v>
+        <v>81.04000000000001</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>16.57</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>3.01</v>
+        <v>3.18</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>53.28</v>
+        <v>53.89</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>65.86</v>
+        <v>65.36</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>76.8</v>
+        <v>73.97</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>79.59999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="P24" s="19" t="n">
-        <v>23206.45</v>
+        <v>23144.2</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>10.35</v>
+        <v>16.48</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>4.15</v>
+        <v>1.84</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>51.9</v>
+        <v>53.2</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>63.61</v>
+        <v>65.81</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>74.67</v>
+        <v>76.77</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="P25" s="12" t="n">
-        <v>23109.7</v>
+        <v>79.56999999999999</v>
+      </c>
+      <c r="P25" s="20" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>4.7</v>
+        <v>10.32</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>2.76</v>
+        <v>3.08</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>50.34</v>
+        <v>51.81</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>61.8</v>
+        <v>63.55</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>73.47</v>
+        <v>74.63</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>79.33</v>
+        <v>78.37</v>
       </c>
       <c r="P26" s="13" t="n">
-        <v>22997.25</v>
+        <v>23109.7</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>5.63</v>
+        <v>4.7</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>575</v>
+        <v>436</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>174</v>
+        <v>312</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>49.74</v>
+        <v>50.26</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>59.85</v>
+        <v>61.75</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>70.27</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P27" s="20" t="n">
-        <v>22891.3</v>
+        <v>79.44</v>
+      </c>
+      <c r="P27" s="14" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>2</v>
+        <v>5.62</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>691</v>
+        <v>575</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>58</v>
+        <v>173</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>11.91</v>
+        <v>3.32</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>33.39</v>
+        <v>5.85</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>46.63</v>
+        <v>49.65</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>49.92</v>
+        <v>59.79</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>53.07</v>
+        <v>70.23</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>61.2</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="P28" s="21" t="n">
-        <v>22599.8</v>
+        <v>22891.3</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.85</v>
+        <v>1.99</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1.09</v>
+        <v>1.89</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>173</v>
+        <v>690</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>576</v>
+        <v>58</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.3</v>
+        <v>11.9</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.74</v>
+        <v>33.38</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>39.03</v>
+        <v>46.54</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>38.35</v>
+        <v>49.85</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>27.73</v>
+        <v>53</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>21.87</v>
+        <v>61.15</v>
       </c>
       <c r="P29" s="22" t="n">
-        <v>22114.45</v>
+        <v>22599.8</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>1.23</v>
+        <v>0.84</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>43.18</v>
+        <v>39.1</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>44.21</v>
+        <v>38.25</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>36.27</v>
+        <v>27.77</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>30.67</v>
+        <v>21.9</v>
       </c>
       <c r="P30" s="23" t="n">
-        <v>22233.85</v>
+        <v>22114.45</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>596</v>
+        <v>160</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>153</v>
+        <v>589</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>3.9</v>
+        <v>0.27</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>44.91</v>
+        <v>43.08</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>50.98</v>
+        <v>44.13</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>43.87</v>
+        <v>36.18</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>43.2</v>
+        <v>30.57</v>
       </c>
       <c r="P31" s="24" t="n">
-        <v>22370.15</v>
+        <v>22233.85</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D32" s="1" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>1.22</v>
-      </c>
       <c r="F32" s="1" t="n">
-        <v>102</v>
+        <v>595</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>648</v>
+        <v>153</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.16</v>
+        <v>3.89</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>41.45</v>
+        <v>44.81</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>44.81</v>
+        <v>50.9</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>30.4</v>
+        <v>43.79</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>24.27</v>
+        <v>43.12</v>
       </c>
       <c r="P32" s="25" t="n">
-        <v>22173.7</v>
+        <v>22370.15</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.9</v>
+        <v>1.21</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>390</v>
+        <v>647</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>44.91</v>
+        <v>41.52</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>55.04</v>
+        <v>44.73</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>44.93</v>
+        <v>30.44</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>45.33</v>
+        <v>24.3</v>
       </c>
       <c r="P33" s="26" t="n">
-        <v>22465.35</v>
+        <v>22173.7</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>350</v>
+        <v>389</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>1.14</v>
+        <v>0.93</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L34" s="1" t="n">
         <v>44.81</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>56.99</v>
+        <v>54.97</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>45.6</v>
+        <v>44.86</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>43.33</v>
+        <v>45.26</v>
       </c>
       <c r="P34" s="27" t="n">
-        <v>22497.7</v>
+        <v>22465.35</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>43.77</v>
+        <v>44.71</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>57.29</v>
+        <v>56.93</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>43.33</v>
+        <v>45.53</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>37.73</v>
+        <v>43.26</v>
       </c>
       <c r="P35" s="28" t="n">
-        <v>22451.85</v>
+        <v>22497.7</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>469</v>
+        <v>307</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>43.6</v>
+        <v>43.67</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>60</v>
+        <v>57.23</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>43.87</v>
+        <v>43.26</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>40</v>
+        <v>37.65</v>
       </c>
       <c r="P36" s="29" t="n">
-        <v>22521.1</v>
+        <v>22451.85</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>221</v>
+        <v>468</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>42.73</v>
+        <v>43.5</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>58.95</v>
+        <v>59.94</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>38.13</v>
+        <v>43.79</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>31.87</v>
+        <v>39.92</v>
       </c>
       <c r="P37" s="30" t="n">
-        <v>22437.95</v>
+        <v>22521.1</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J38" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>43.94</v>
+        <v>42.81</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>66.31999999999999</v>
+        <v>58.89</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>47.6</v>
+        <v>38.05</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>42.13</v>
+        <v>31.78</v>
       </c>
       <c r="P38" s="31" t="n">
-        <v>22657</v>
+        <v>22437.95</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>47.58</v>
+        <v>44.02</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>72.48</v>
+        <v>66.27</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>61.33</v>
+        <v>47.66</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P39" s="15" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr"/>
+        <v>42.19</v>
+      </c>
+      <c r="P39" s="32" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q39" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1" t="n">
         <v>47.66</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>73.23</v>
+        <v>72.44</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>61.33</v>
+        <v>61.42</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P40" s="32" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q40" s="1" t="n">
-        <v>0.31</v>
-      </c>
+        <v>60.75</v>
+      </c>
+      <c r="P40" s="16" t="inlineStr"/>
+      <c r="Q40" s="1" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>46.88</v>
+        <v>47.74</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>73.83</v>
+        <v>73.19</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>62.13</v>
+        <v>61.42</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P41" s="20" t="n">
-        <v>22897.2</v>
+        <v>60.75</v>
+      </c>
+      <c r="P41" s="33" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>566</v>
+        <v>361</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>3.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>27</v>
@@ -3219,1423 +3228,1423 @@
         <v>1</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>8.33</v>
+        <v>1.98</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>46.18</v>
+        <v>46.96</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>74.73999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>61.2</v>
+        <v>62.22</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P42" s="33" t="n">
-        <v>22929.45</v>
+        <v>63.55</v>
+      </c>
+      <c r="P42" s="21" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>372</v>
+        <v>565</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>374</v>
+        <v>183</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.99</v>
+        <v>3.09</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>2.48</v>
+        <v>8.33</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>44.1</v>
+        <v>46.26</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>68.12</v>
+        <v>74.7</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>48.8</v>
+        <v>61.28</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P43" s="31" t="n">
-        <v>22651.3</v>
+        <v>63.68</v>
+      </c>
+      <c r="P43" s="34" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>302</v>
+        <v>373</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>1.47</v>
+        <v>1</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J44" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>42.01</v>
+        <v>44.17</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>68.56999999999999</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>48.13</v>
+        <v>48.87</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P44" s="21" t="n">
-        <v>22602.85</v>
+        <v>47</v>
+      </c>
+      <c r="P44" s="32" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>367</v>
+        <v>445</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>381</v>
+        <v>301</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.96</v>
+        <v>1.48</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>41.15</v>
+        <v>42.09</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>66.77</v>
+        <v>68.52</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>42</v>
+        <v>48.2</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P45" s="34" t="n">
-        <v>22578.15</v>
+        <v>45.79</v>
+      </c>
+      <c r="P45" s="22" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>493</v>
+        <v>366</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>41.32</v>
+        <v>41.22</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>67.06999999999999</v>
+        <v>66.72</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>40.93</v>
+        <v>42.06</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P46" s="29" t="n">
-        <v>22521.75</v>
+        <v>38.18</v>
+      </c>
+      <c r="P46" s="35" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>164</v>
+        <v>492</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.28</v>
+        <v>1.92</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>39.76</v>
+        <v>41.39</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>67.02</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>32.53</v>
+        <v>40.99</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P47" s="35" t="n">
-        <v>22461.05</v>
+        <v>34.45</v>
+      </c>
+      <c r="P47" s="30" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>494</v>
+        <v>584</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>44.27</v>
+        <v>39.83</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>71.13</v>
+        <v>64.91</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>42.27</v>
+        <v>32.58</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>31.87</v>
+        <v>23.36</v>
       </c>
       <c r="P48" s="36" t="n">
-        <v>22531.15</v>
+        <v>22461.05</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>326</v>
+        <v>493</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>44.79</v>
+        <v>44.35</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>72.33</v>
+        <v>71.08</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>46.4</v>
+        <v>42.32</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>35.47</v>
+        <v>31.91</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>22613.1</v>
+        <v>22531.15</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="E50" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>325</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L50" s="1" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="M50" s="1" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="N50" s="1" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="O50" s="1" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="P50" s="38" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q50" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F50" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I50" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J50" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K50" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L50" s="1" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="M50" s="1" t="n">
-        <v>71.28</v>
-      </c>
-      <c r="N50" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O50" s="1" t="n">
-        <v>29.87</v>
-      </c>
-      <c r="P50" s="38" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q50" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>54</v>
+        <v>448</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>696</v>
+        <v>298</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.08</v>
+        <v>1.5</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>42.19</v>
+        <v>43.3</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>70.23</v>
+        <v>71.23</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>37.73</v>
+        <v>43.66</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>22.93</v>
+        <v>29.91</v>
       </c>
       <c r="P51" s="39" t="n">
-        <v>22299.9</v>
+        <v>22377.35</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>65</v>
+        <v>211</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>2.27</v>
+        <v>0.74</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>2.29</v>
+        <v>1.01</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>561</v>
+        <v>695</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>49.91</v>
+        <v>42.26</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>82.41</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.65</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>50.53</v>
+        <v>22.96</v>
       </c>
       <c r="P52" s="40" t="n">
-        <v>22795.75</v>
+        <v>22299.9</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>4.89</v>
+        <v>2.26</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>4.33</v>
+        <v>2.29</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>324</v>
+        <v>187</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0.76</v>
+        <v>0.33</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>54.78</v>
+        <v>49.83</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>87.22</v>
+        <v>82.38</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>82.27</v>
+        <v>67.56</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>73.47</v>
+        <v>50.47</v>
       </c>
       <c r="P53" s="41" t="n">
-        <v>23115.65</v>
+        <v>22795.75</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>5.93</v>
+        <v>4.87</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>499</v>
+        <v>323</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J54" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>56.52</v>
+        <v>54.7</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>87.97</v>
+        <v>87.2</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>87.87</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>82.67</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="P54" s="42" t="n">
-        <v>23214</v>
+        <v>23115.65</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>145</v>
+        <v>249</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>52.52</v>
+        <v>56.62</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>86.92</v>
+        <v>87.95</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>86.8</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>80.93000000000001</v>
+        <v>82.64</v>
       </c>
       <c r="P55" s="43" t="n">
-        <v>23133.4</v>
+        <v>23214</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>343</v>
+        <v>604</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>405</v>
+        <v>145</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>47.65</v>
+        <v>52.61</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>79.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>73.87</v>
+        <v>86.78</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>62.53</v>
+        <v>80.91</v>
       </c>
       <c r="P56" s="44" t="n">
-        <v>22808.25</v>
+        <v>23133.4</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>531</v>
+        <v>343</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>218</v>
+        <v>404</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>46.86</v>
+        <v>47.74</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>80.59999999999999</v>
+        <v>79.67</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>77.2</v>
+        <v>73.83</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>66.8</v>
+        <v>62.48</v>
       </c>
       <c r="P57" s="45" t="n">
-        <v>22830.75</v>
+        <v>22808.25</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>3.64</v>
+        <v>2.33</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>43.55</v>
+        <v>46.95</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>77.44</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>64.8</v>
+        <v>77.17</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="P58" s="15" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr"/>
+        <v>66.76000000000001</v>
+      </c>
+      <c r="P58" s="46" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q58" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>41.77</v>
+        <v>43.63</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>77.47</v>
+        <v>77.41</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.75</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="P59" s="46" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q59" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.67</v>
+      </c>
+      <c r="P59" s="16" t="inlineStr"/>
+      <c r="Q59" s="1" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>378</v>
+        <v>551</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>43.74</v>
+        <v>41.84</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>79.2</v>
+        <v>77.44</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>80.67</v>
+        <v>73.03</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>70.13</v>
+        <v>55.01</v>
       </c>
       <c r="P60" s="47" t="n">
-        <v>22871</v>
+        <v>22683.55</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>3.02</v>
+        <v>2.38</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>285</v>
+        <v>370</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>463</v>
+        <v>377</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>44.06</v>
+        <v>43.81</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>77.87</v>
+        <v>79.17</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>81.2</v>
+        <v>80.64</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>70.8</v>
+        <v>70.09</v>
       </c>
       <c r="P61" s="48" t="n">
-        <v>22765.6</v>
+        <v>22871</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>648</v>
+        <v>284</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>6.35</v>
+        <v>0.61</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>44.22</v>
+        <v>43.97</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>80.13</v>
+        <v>77.84</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.17</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P62" s="44" t="n">
-        <v>22821.4</v>
+        <v>70.76000000000001</v>
+      </c>
+      <c r="P62" s="49" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>156</v>
+        <v>647</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0.26</v>
+        <v>6.34</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0.37</v>
+        <v>8.16</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>40.1</v>
+        <v>44.29</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>72</v>
+        <v>80.11</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>78</v>
+        <v>86.92</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P63" s="34" t="n">
-        <v>22570.05</v>
+        <v>81.58</v>
+      </c>
+      <c r="P63" s="45" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>511</v>
+        <v>589</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>42.63</v>
+        <v>40.16</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>78.93000000000001</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>87.33</v>
+        <v>77.97</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P64" s="44" t="n">
-        <v>22810.85</v>
+        <v>62.08</v>
+      </c>
+      <c r="P64" s="35" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>497</v>
+        <v>235</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>249</v>
+        <v>511</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>2</v>
+        <v>0.46</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J65" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>43.4</v>
+        <v>42.7</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>82.13</v>
+        <v>78.91</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>91.87</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="P65" s="49" t="n">
-        <v>22991.5</v>
+        <v>82.11</v>
+      </c>
+      <c r="P65" s="45" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>41.08</v>
+        <v>43.47</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>81.73</v>
+        <v>82.11</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>92.67</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="P66" s="50" t="n">
-        <v>23042.35</v>
+        <v>22991.5</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>93.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>92.13</v>
+        <v>92.67</v>
       </c>
       <c r="P67" s="51" t="n">
-        <v>22865.8</v>
+        <v>23042.35</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>5</v>
+        <v>0.58</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J68" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>7.36</v>
+        <v>0.53</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="P68" s="51" t="n">
-        <v>22869.4</v>
+        <v>92.13</v>
+      </c>
+      <c r="P68" s="52" t="n">
+        <v>22865.8</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
@@ -4647,13 +4656,13 @@
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I69" s="1" t="n">
         <v>0</v>
@@ -4662,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>0.16</v>
+        <v>7.36</v>
       </c>
       <c r="L69" s="1" t="n">
         <v>16.67</v>
@@ -4671,22 +4680,22 @@
         <v>16.67</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O69" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P69" s="31" t="n">
-        <v>22656.3</v>
+      <c r="P69" s="52" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -4698,13 +4707,13 @@
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I70" s="1" t="n">
         <v>0</v>
@@ -4713,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>3.72</v>
+        <v>0.16</v>
       </c>
       <c r="L70" s="1" t="n">
         <v>16.67</v>
@@ -4722,116 +4731,167 @@
         <v>16.67</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O70" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P70" s="52" t="n">
-        <v>22595.55</v>
+      <c r="P70" s="32" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>0.49</v>
+        <v>5</v>
       </c>
       <c r="I71" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J71" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>0.75</v>
+        <v>3.72</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>31.26</v>
+        <v>16.67</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>52.93</v>
+        <v>16.67</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>84.27</v>
+        <v>83.33</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P71" s="25" t="n">
-        <v>22179.05</v>
+        <v>100</v>
+      </c>
+      <c r="P71" s="53" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G72" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L72" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M72" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N72" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O72" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P72" s="26" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q72" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" s="1" t="inlineStr"/>
+      <c r="E73" s="1" t="inlineStr"/>
+      <c r="F73" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G72" s="1" t="n">
+      <c r="G73" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H72" s="1" t="n">
+      <c r="H73" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr"/>
-      <c r="L72" s="1" t="n">
+      <c r="I73" s="1" t="inlineStr"/>
+      <c r="J73" s="1" t="inlineStr"/>
+      <c r="K73" s="1" t="inlineStr"/>
+      <c r="L73" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="M73" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N72" s="1" t="n">
+      <c r="N73" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O72" s="1" t="n">
+      <c r="O73" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P72" s="53" t="n">
+      <c r="P73" s="54" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q72" s="1" t="n">
+      <c r="Q73" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B72">
+  <conditionalFormatting sqref="B2:B73">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4841,7 +4901,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C72">
+  <conditionalFormatting sqref="C2:C73">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4851,7 +4911,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E72">
+  <conditionalFormatting sqref="D2:E73">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4863,7 +4923,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F72">
+  <conditionalFormatting sqref="F2:F73">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4873,7 +4933,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G72">
+  <conditionalFormatting sqref="G2:G73">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4883,7 +4943,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H72">
+  <conditionalFormatting sqref="H2:H73">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4895,7 +4955,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I72">
+  <conditionalFormatting sqref="I2:I73">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4905,7 +4965,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J72">
+  <conditionalFormatting sqref="J2:J73">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4915,7 +4975,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K72">
+  <conditionalFormatting sqref="K2:K73">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4927,7 +4987,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O72">
+  <conditionalFormatting sqref="L2:O73">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4939,7 +4999,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q72">
+  <conditionalFormatting sqref="Q2:Q73">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -35,6 +35,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E4F3E8"/>
+        <bgColor rgb="00E4F3E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C9E8D1"/>
         <bgColor rgb="00C9E8D1"/>
       </patternFill>
@@ -133,12 +139,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5FAF6"/>
         <bgColor rgb="00F5FAF6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4F3E8"/>
-        <bgColor rgb="00E4F3E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1005,2276 +1005,2276 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.74</v>
+        <v>1.06</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>396</v>
+        <v>148</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>348</v>
+        <v>600</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1.14</v>
+        <v>0.25</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>2.2</v>
+        <v>0.54</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>57.04</v>
+        <v>54.55</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>63.02</v>
+        <v>58.27</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>56.67</v>
+        <v>43.68</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>53.33</v>
+        <v>35.42</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23352.15</v>
+        <v>23145.05</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>438</v>
+        <v>397</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1.49</v>
+        <v>2.21</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>56.53</v>
+        <v>57.12</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>63.55</v>
+        <v>63.07</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>55.73</v>
+        <v>56.59</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>50.53</v>
+        <v>53.26</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>23338.05</v>
+        <v>23352.15</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>28</v>
-      </c>
       <c r="D4" s="1" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>271</v>
+        <v>438</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>474</v>
+        <v>311</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.72</v>
+        <v>1.49</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>55.42</v>
+        <v>56.6</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>62.48</v>
+        <v>63.6</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>50.93</v>
+        <v>55.66</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>23336.3</v>
+        <v>50.47</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>23338.05</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>3.18</v>
+        <v>1.51</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.95</v>
+        <v>0.72</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>55.94</v>
+        <v>55.5</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>64.34999999999999</v>
+        <v>62.53</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>56.13</v>
+        <v>50.87</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>50.27</v>
+        <v>44.07</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>23232.65</v>
+        <v>23336.3</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>4.9</v>
+        <v>3.18</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>451</v>
+        <v>300</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>299</v>
+        <v>447</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.51</v>
+        <v>0.67</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>2.25</v>
+        <v>0.95</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>57.76</v>
+        <v>56.01</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>64.09</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>59.2</v>
+        <v>56.06</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>54.27</v>
+        <v>50.2</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>18</v>
-      </c>
       <c r="D7" s="1" t="n">
-        <v>1.74</v>
+        <v>4.9</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>579</v>
+        <v>299</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.29</v>
+        <v>1.51</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.38</v>
+        <v>2.25</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>56.55</v>
+        <v>57.83</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>61.28</v>
+        <v>64.13</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>53.87</v>
+        <v>59.12</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>47.33</v>
+        <v>54.19</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>367</v>
+        <v>580</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>56.9</v>
+        <v>56.63</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>65.15000000000001</v>
+        <v>61.33</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>65.2</v>
+        <v>53.79</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>64.53</v>
+        <v>47.27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>604</v>
+        <v>381</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>144</v>
+        <v>368</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>4.19</v>
+        <v>1.04</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>11.14</v>
+        <v>0.79</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>55.52</v>
+        <v>56.97</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>64.89</v>
+        <v>65.2</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>64.53</v>
+        <v>65.11</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P9" s="7" t="n">
-        <v>23348.4</v>
+        <v>64.45</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1.06</v>
+        <v>1.54</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>4.91</v>
+        <v>4.2</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>7.65</v>
+        <v>11.15</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>52.59</v>
+        <v>55.59</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>56.02</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>51.47</v>
+        <v>64.45</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>45.47</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>86</v>
+        <v>624</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>664</v>
+        <v>127</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.13</v>
+        <v>4.91</v>
       </c>
       <c r="I11" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>49.66</v>
+        <v>52.67</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>49.85</v>
+        <v>56.09</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>37.87</v>
+        <v>51.4</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>26.13</v>
+        <v>45.41</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>505</v>
+        <v>665</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>56.21</v>
+        <v>49.74</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>60.69</v>
+        <v>49.92</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>58.13</v>
+        <v>37.82</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>51.73</v>
+        <v>26.1</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>23368.85</v>
+        <v>22908.05</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>386</v>
+        <v>506</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>56.99</v>
+        <v>56.28</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>63.55</v>
+        <v>60.75</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>65.59999999999999</v>
+        <v>58.06</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>63.6</v>
+        <v>51.66</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>23433.95</v>
+        <v>23368.85</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>1.45</v>
+        <v>0.52</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>56.82</v>
+        <v>57.07</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>64.91</v>
+        <v>63.61</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>66.8</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>66</v>
+        <v>63.52</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>23301.15</v>
+        <v>23433.95</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>2.77</v>
+        <v>2.35</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>536</v>
+        <v>353</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>56.48</v>
+        <v>56.9</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>64.45999999999999</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>69.69</v>
+        <v>66.84</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>68.62</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>23264.8</v>
+        <v>66.05</v>
+      </c>
+      <c r="P15" s="13" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>415</v>
+        <v>537</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>1.24</v>
+        <v>2.53</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>52.85</v>
+        <v>56.55</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>60.09</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>61.42</v>
+        <v>69.73</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>57.01</v>
-      </c>
-      <c r="P16" s="13" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>51.81</v>
+        <v>52.93</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>57.98</v>
+        <v>60.15</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>57.81</v>
+        <v>61.47</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>50.07</v>
+        <v>57.07</v>
       </c>
       <c r="P17" s="14" t="n">
-        <v>22995.65</v>
+        <v>23111.65</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>277</v>
+        <v>445</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>471</v>
+        <v>304</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>50.26</v>
+        <v>51.9</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>55.72</v>
+        <v>58.05</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>50.07</v>
+        <v>57.87</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>41.26</v>
+        <v>50.13</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>23000</v>
+        <v>22995.65</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>4.69</v>
+        <v>2.71</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>52.5</v>
+        <v>50.34</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>59.79</v>
+        <v>55.79</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>60.21</v>
+        <v>50.13</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>50.73</v>
-      </c>
-      <c r="P19" s="16" t="inlineStr"/>
-      <c r="Q19" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>6.84</v>
+        <v>4.73</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>52.33</v>
+        <v>52.59</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>59.94</v>
+        <v>59.85</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>60.21</v>
+        <v>60.27</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>50.73</v>
-      </c>
-      <c r="P20" s="13" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q20" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+        <v>50.8</v>
+      </c>
+      <c r="P20" s="17" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>6.52</v>
+        <v>6.88</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>389</v>
+        <v>249</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="I21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>52.85</v>
+        <v>52.41</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>62.35</v>
+        <v>60</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>68.36</v>
+        <v>60.27</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>63.68</v>
-      </c>
-      <c r="P21" s="17" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P21" s="14" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>5.31</v>
+        <v>3.69</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>4.91</v>
+        <v>6.56</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>568</v>
+        <v>361</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>53.2</v>
+        <v>52.93</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>61.75</v>
+        <v>62.41</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>69.29000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>64.09</v>
+        <v>63.73</v>
       </c>
       <c r="P22" s="18" t="n">
-        <v>23010.95</v>
+        <v>23126.3</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>6</v>
+        <v>4.94</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>495</v>
+        <v>181</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.95</v>
+        <v>0.32</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>55.44</v>
+        <v>53.28</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>68.37</v>
+        <v>61.8</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>79.17</v>
+        <v>69.33</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>81.04000000000001</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P23" s="19" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>8.470000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>3.18</v>
+        <v>6.04</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>53.89</v>
+        <v>55.52</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>65.36</v>
+        <v>68.42</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>73.97</v>
+        <v>79.2</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>75.17</v>
-      </c>
-      <c r="P24" s="19" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>16.48</v>
+        <v>8.57</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1.84</v>
+        <v>1.05</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>53.2</v>
+        <v>53.97</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>65.81</v>
+        <v>65.41</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>76.77</v>
+        <v>74</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>79.56999999999999</v>
-      </c>
-      <c r="P25" s="20" t="n">
-        <v>23206.45</v>
+        <v>75.2</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>23144.2</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>10.32</v>
+        <v>16.57</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>51.81</v>
+        <v>53.28</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>63.55</v>
+        <v>65.86</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>74.63</v>
+        <v>76.8</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>78.37</v>
-      </c>
-      <c r="P26" s="13" t="n">
-        <v>23109.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="P26" s="20" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>4.7</v>
+        <v>10.35</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>50.26</v>
+        <v>51.9</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>61.75</v>
+        <v>63.61</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>73.43000000000001</v>
+        <v>74.67</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>79.44</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="P27" s="14" t="n">
-        <v>22997.25</v>
+        <v>23109.7</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>5.62</v>
+        <v>4.7</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>575</v>
+        <v>436</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>173</v>
+        <v>313</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>3.32</v>
+        <v>1.39</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>5.85</v>
+        <v>1.26</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>49.65</v>
+        <v>50.34</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>59.79</v>
+        <v>61.8</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>70.23</v>
+        <v>73.47</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>79.04000000000001</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>22891.3</v>
+        <v>79.33</v>
+      </c>
+      <c r="P28" s="15" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>1.99</v>
+        <v>5.63</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>1.89</v>
+        <v>2.83</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>690</v>
+        <v>575</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>11.9</v>
+        <v>3.3</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>33.38</v>
+        <v>5.84</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>46.54</v>
+        <v>49.74</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>49.85</v>
+        <v>59.85</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>53</v>
+        <v>70.27</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>61.15</v>
-      </c>
-      <c r="P29" s="22" t="n">
-        <v>22599.8</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="P29" s="21" t="n">
+        <v>22891.3</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.84</v>
+        <v>2</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>173</v>
+        <v>691</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>575</v>
+        <v>58</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>39.1</v>
+        <v>46.63</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>38.25</v>
+        <v>49.92</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>27.77</v>
+        <v>53.07</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="P30" s="23" t="n">
-        <v>22114.45</v>
+        <v>61.2</v>
+      </c>
+      <c r="P30" s="22" t="n">
+        <v>22599.8</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>1.22</v>
+        <v>0.85</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>43.08</v>
+        <v>39.03</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>44.13</v>
+        <v>38.35</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>36.18</v>
+        <v>27.73</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="P31" s="24" t="n">
-        <v>22233.85</v>
+        <v>21.87</v>
+      </c>
+      <c r="P31" s="23" t="n">
+        <v>22114.45</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>595</v>
+        <v>160</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>153</v>
+        <v>590</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>3.89</v>
+        <v>0.27</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>44.81</v>
+        <v>43.18</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>50.9</v>
+        <v>44.21</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>43.79</v>
+        <v>36.27</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>43.12</v>
-      </c>
-      <c r="P32" s="25" t="n">
-        <v>22370.15</v>
+        <v>30.67</v>
+      </c>
+      <c r="P32" s="24" t="n">
+        <v>22233.85</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>102</v>
+        <v>596</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>647</v>
+        <v>153</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.16</v>
+        <v>3.9</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>41.52</v>
+        <v>44.91</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>44.73</v>
+        <v>50.98</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>30.44</v>
+        <v>43.87</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="P33" s="26" t="n">
-        <v>22173.7</v>
+        <v>43.2</v>
+      </c>
+      <c r="P33" s="25" t="n">
+        <v>22370.15</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>389</v>
+        <v>648</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.93</v>
+        <v>0.16</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L34" s="1" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>44.81</v>
       </c>
-      <c r="M34" s="1" t="n">
-        <v>54.97</v>
-      </c>
       <c r="N34" s="1" t="n">
-        <v>44.86</v>
+        <v>30.4</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>45.26</v>
-      </c>
-      <c r="P34" s="27" t="n">
-        <v>22465.35</v>
+        <v>24.27</v>
+      </c>
+      <c r="P34" s="26" t="n">
+        <v>22173.7</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>44.71</v>
+        <v>44.91</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>56.93</v>
+        <v>55.04</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>45.53</v>
+        <v>44.93</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>43.26</v>
-      </c>
-      <c r="P35" s="28" t="n">
-        <v>22497.7</v>
+        <v>45.33</v>
+      </c>
+      <c r="P35" s="27" t="n">
+        <v>22465.35</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>307</v>
+        <v>400</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>43.67</v>
+        <v>44.81</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>57.23</v>
+        <v>56.99</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>43.26</v>
+        <v>45.6</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>37.65</v>
-      </c>
-      <c r="P36" s="29" t="n">
-        <v>22451.85</v>
+        <v>43.33</v>
+      </c>
+      <c r="P36" s="28" t="n">
+        <v>22497.7</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>468</v>
+        <v>308</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>43.5</v>
+        <v>43.77</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>59.94</v>
+        <v>57.29</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>43.79</v>
+        <v>43.33</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="P37" s="30" t="n">
-        <v>22521.1</v>
+        <v>37.73</v>
+      </c>
+      <c r="P37" s="29" t="n">
+        <v>22451.85</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>220</v>
+        <v>469</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>42.81</v>
+        <v>43.6</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>58.89</v>
+        <v>60</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>38.05</v>
+        <v>43.87</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="P38" s="31" t="n">
-        <v>22437.95</v>
+        <v>40</v>
+      </c>
+      <c r="P38" s="30" t="n">
+        <v>22521.1</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J39" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>44.02</v>
+        <v>42.73</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>66.27</v>
+        <v>58.95</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>47.66</v>
+        <v>38.13</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>42.19</v>
-      </c>
-      <c r="P39" s="32" t="n">
-        <v>22657</v>
+        <v>31.87</v>
+      </c>
+      <c r="P39" s="31" t="n">
+        <v>22437.95</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>47.66</v>
+        <v>43.94</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>72.44</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>61.42</v>
+        <v>47.6</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="P40" s="16" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P40" s="32" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q40" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>47.74</v>
+        <v>47.58</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>73.19</v>
+        <v>72.48</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>61.42</v>
+        <v>61.33</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="P41" s="33" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q41" s="1" t="n">
-        <v>0.31</v>
-      </c>
+        <v>60.67</v>
+      </c>
+      <c r="P41" s="17" t="inlineStr"/>
+      <c r="Q41" s="1" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>46.96</v>
+        <v>47.66</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>73.8</v>
+        <v>73.23</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>62.22</v>
+        <v>61.33</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>63.55</v>
-      </c>
-      <c r="P42" s="21" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P42" s="33" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>565</v>
+        <v>362</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>3.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I43" s="1" t="n">
         <v>27</v>
@@ -3283,1419 +3283,1419 @@
         <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>8.33</v>
+        <v>1.98</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46.26</v>
+        <v>46.88</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>74.7</v>
+        <v>73.83</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>61.28</v>
+        <v>62.13</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>63.68</v>
-      </c>
-      <c r="P43" s="34" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P43" s="21" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>372</v>
+        <v>566</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>373</v>
+        <v>183</v>
       </c>
       <c r="H44" s="1" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="J44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="J44" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="K44" s="1" t="n">
-        <v>2.48</v>
+        <v>8.33</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>44.17</v>
+        <v>46.18</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>68.06999999999999</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>48.87</v>
+        <v>61.2</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="P44" s="32" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P44" s="34" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>301</v>
+        <v>374</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1.48</v>
+        <v>0.99</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J45" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>42.09</v>
+        <v>44.1</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>68.52</v>
+        <v>68.12</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="P45" s="22" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P45" s="32" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>366</v>
+        <v>445</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>381</v>
+        <v>302</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>41.22</v>
+        <v>42.01</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>66.72</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>42.06</v>
+        <v>48.13</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="P46" s="35" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P46" s="22" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>492</v>
+        <v>367</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>1.92</v>
+        <v>0.96</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>41.39</v>
+        <v>41.15</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>67.02</v>
+        <v>66.77</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>40.99</v>
+        <v>42</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="P47" s="30" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P47" s="35" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>584</v>
+        <v>256</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>39.83</v>
+        <v>41.32</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>64.91</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>32.58</v>
+        <v>40.93</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>23.36</v>
-      </c>
-      <c r="P48" s="36" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P48" s="30" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>493</v>
+        <v>585</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>44.35</v>
+        <v>39.76</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>71.08</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>42.32</v>
+        <v>32.53</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="P49" s="37" t="n">
-        <v>22531.15</v>
+        <v>23.33</v>
+      </c>
+      <c r="P49" s="36" t="n">
+        <v>22461.05</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>325</v>
+        <v>494</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>44.87</v>
+        <v>44.27</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>72.29000000000001</v>
+        <v>71.13</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>46.33</v>
+        <v>42.27</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>35.51</v>
-      </c>
-      <c r="P50" s="38" t="n">
-        <v>22613.1</v>
+        <v>31.87</v>
+      </c>
+      <c r="P50" s="37" t="n">
+        <v>22531.15</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E51" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L51" s="1" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="N51" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O51" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P51" s="38" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q51" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F51" s="1" t="n">
-        <v>448</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H51" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I51" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J51" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K51" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L51" s="1" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="M51" s="1" t="n">
-        <v>71.23</v>
-      </c>
-      <c r="N51" s="1" t="n">
-        <v>43.66</v>
-      </c>
-      <c r="O51" s="1" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="P51" s="39" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q51" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>695</v>
+        <v>298</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>42.26</v>
+        <v>43.23</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>70.18000000000001</v>
+        <v>71.28</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>37.65</v>
+        <v>43.73</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>22.96</v>
-      </c>
-      <c r="P52" s="40" t="n">
-        <v>22299.9</v>
+        <v>29.87</v>
+      </c>
+      <c r="P52" s="39" t="n">
+        <v>22377.35</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>2.26</v>
+        <v>0.74</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>2.29</v>
+        <v>1.01</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0.33</v>
+        <v>0.08</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>49.83</v>
+        <v>42.19</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>82.38</v>
+        <v>70.23</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>67.56</v>
+        <v>37.73</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>50.47</v>
-      </c>
-      <c r="P53" s="41" t="n">
-        <v>22795.75</v>
+        <v>22.93</v>
+      </c>
+      <c r="P53" s="40" t="n">
+        <v>22299.9</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>4.87</v>
+        <v>2.27</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>4.32</v>
+        <v>2.29</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>323</v>
+        <v>188</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>54.7</v>
+        <v>49.91</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>87.2</v>
+        <v>82.41</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>82.23999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>73.43000000000001</v>
-      </c>
-      <c r="P54" s="42" t="n">
-        <v>23115.65</v>
+        <v>50.53</v>
+      </c>
+      <c r="P54" s="41" t="n">
+        <v>22795.75</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>5.93</v>
+        <v>4.89</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>249</v>
+        <v>425</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J55" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>56.62</v>
+        <v>54.78</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>87.95</v>
+        <v>87.22</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>87.84999999999999</v>
+        <v>82.27</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>82.64</v>
-      </c>
-      <c r="P55" s="43" t="n">
-        <v>23214</v>
+        <v>73.47</v>
+      </c>
+      <c r="P55" s="42" t="n">
+        <v>23115.65</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>604</v>
+        <v>499</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>52.61</v>
+        <v>56.52</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>86.90000000000001</v>
+        <v>87.97</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>86.78</v>
+        <v>87.87</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>80.91</v>
-      </c>
-      <c r="P56" s="44" t="n">
-        <v>23133.4</v>
+        <v>82.67</v>
+      </c>
+      <c r="P56" s="43" t="n">
+        <v>23214</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>343</v>
+        <v>605</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>404</v>
+        <v>145</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>47.74</v>
+        <v>52.52</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>79.67</v>
+        <v>86.92</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>73.83</v>
+        <v>86.8</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="P57" s="45" t="n">
-        <v>22808.25</v>
+        <v>80.93000000000001</v>
+      </c>
+      <c r="P57" s="44" t="n">
+        <v>23133.4</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>530</v>
+        <v>343</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>2.43</v>
+        <v>0.85</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>46.95</v>
+        <v>47.65</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>80.56999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>77.17</v>
+        <v>73.87</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>66.76000000000001</v>
-      </c>
-      <c r="P58" s="46" t="n">
-        <v>22830.75</v>
+        <v>62.53</v>
+      </c>
+      <c r="P58" s="45" t="n">
+        <v>22808.25</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>3.64</v>
+        <v>2.33</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>43.63</v>
+        <v>46.86</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>77.41</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>64.75</v>
+        <v>77.2</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="P59" s="16" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="P59" s="46" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q59" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>41.84</v>
+        <v>43.55</v>
       </c>
       <c r="M60" s="1" t="n">
         <v>77.44</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>73.03</v>
+        <v>64.8</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="P60" s="47" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q60" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.73</v>
+      </c>
+      <c r="P60" s="17" t="inlineStr"/>
+      <c r="Q60" s="1" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>377</v>
+        <v>552</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>43.81</v>
+        <v>41.77</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>79.17</v>
+        <v>77.47</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>80.64</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>70.09</v>
-      </c>
-      <c r="P61" s="48" t="n">
-        <v>22871</v>
+        <v>55.07</v>
+      </c>
+      <c r="P61" s="47" t="n">
+        <v>22683.55</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>3.02</v>
+        <v>2.38</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>284</v>
+        <v>370</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>43.97</v>
+        <v>43.74</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>77.84</v>
+        <v>79.2</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>81.17</v>
+        <v>80.67</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>70.76000000000001</v>
-      </c>
-      <c r="P62" s="49" t="n">
-        <v>22765.6</v>
+        <v>70.13</v>
+      </c>
+      <c r="P62" s="48" t="n">
+        <v>22871</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>647</v>
+        <v>285</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>6.34</v>
+        <v>0.62</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>8.16</v>
+        <v>1.94</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>44.29</v>
+        <v>44.06</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>80.11</v>
+        <v>77.87</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>86.92</v>
+        <v>81.2</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>81.58</v>
-      </c>
-      <c r="P63" s="45" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P63" s="49" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>589</v>
+        <v>102</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>40.16</v>
+        <v>44.22</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>71.95999999999999</v>
+        <v>80.13</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>77.97</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>62.08</v>
-      </c>
-      <c r="P64" s="35" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P64" s="45" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>42.7</v>
+        <v>40.1</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>78.91</v>
+        <v>72</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>87.31999999999999</v>
+        <v>78</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="P65" s="45" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P65" s="35" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>249</v>
+        <v>511</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>43.47</v>
+        <v>42.63</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>82.11</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>91.86</v>
+        <v>87.33</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="P66" s="50" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P66" s="45" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>41.08</v>
+        <v>43.47</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>81.73</v>
+        <v>82.11</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>92.67</v>
-      </c>
-      <c r="P67" s="51" t="n">
-        <v>23042.35</v>
+        <v>89.98999999999999</v>
+      </c>
+      <c r="P67" s="50" t="n">
+        <v>22991.5</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J68" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>93.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>92.13</v>
-      </c>
-      <c r="P68" s="52" t="n">
-        <v>22865.8</v>
+        <v>92.67</v>
+      </c>
+      <c r="P68" s="51" t="n">
+        <v>23042.35</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>5</v>
+        <v>0.58</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J69" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>7.36</v>
+        <v>0.53</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>100</v>
+        <v>92.13</v>
       </c>
       <c r="P69" s="52" t="n">
-        <v>22869.4</v>
+        <v>22865.8</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -4707,13 +4707,13 @@
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I70" s="1" t="n">
         <v>0</v>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>0.16</v>
+        <v>7.36</v>
       </c>
       <c r="L70" s="1" t="n">
         <v>16.67</v>
@@ -4731,22 +4731,22 @@
         <v>16.67</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O70" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P70" s="32" t="n">
-        <v>22656.3</v>
+      <c r="P70" s="52" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -4758,13 +4758,13 @@
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I71" s="1" t="n">
         <v>0</v>
@@ -4773,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>3.72</v>
+        <v>0.16</v>
       </c>
       <c r="L71" s="1" t="n">
         <v>16.67</v>
@@ -4782,116 +4782,167 @@
         <v>16.67</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O71" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P71" s="53" t="n">
-        <v>22595.55</v>
+      <c r="P71" s="32" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>0.49</v>
+        <v>5</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J72" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>0.75</v>
+        <v>3.72</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>31.26</v>
+        <v>16.67</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>52.93</v>
+        <v>16.67</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>84.27</v>
+        <v>83.33</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P72" s="26" t="n">
-        <v>22179.05</v>
+        <v>100</v>
+      </c>
+      <c r="P72" s="53" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G73" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J73" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L73" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M73" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N73" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O73" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P73" s="26" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q73" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="1" t="inlineStr"/>
+      <c r="E74" s="1" t="inlineStr"/>
+      <c r="F74" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G73" s="1" t="n">
+      <c r="G74" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="H74" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr"/>
-      <c r="L73" s="1" t="n">
+      <c r="I74" s="1" t="inlineStr"/>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
+      <c r="L74" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="M74" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N73" s="1" t="n">
+      <c r="N74" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O73" s="1" t="n">
+      <c r="O74" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P73" s="54" t="n">
+      <c r="P74" s="54" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q73" s="1" t="n">
+      <c r="Q74" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B73">
+  <conditionalFormatting sqref="B2:B74">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4901,7 +4952,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C73">
+  <conditionalFormatting sqref="C2:C74">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4911,7 +4962,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E73">
+  <conditionalFormatting sqref="D2:E74">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4923,7 +4974,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F73">
+  <conditionalFormatting sqref="F2:F74">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4933,7 +4984,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G73">
+  <conditionalFormatting sqref="G2:G74">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4943,7 +4994,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H73">
+  <conditionalFormatting sqref="H2:H74">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4955,7 +5006,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I73">
+  <conditionalFormatting sqref="I2:I74">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4965,7 +5016,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J73">
+  <conditionalFormatting sqref="J2:J74">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4975,7 +5026,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K73">
+  <conditionalFormatting sqref="K2:K74">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4987,7 +5038,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O73">
+  <conditionalFormatting sqref="L2:O74">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4999,7 +5050,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q73">
+  <conditionalFormatting sqref="Q2:Q74">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="55">
+  <fills count="56">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FCF9"/>
+        <bgColor rgb="00F9FCF9"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -364,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -526,6 +532,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1005,1085 +1014,1089 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>2.24</v>
+        <v>1.65</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>54.55</v>
+        <v>51.79</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>58.27</v>
+        <v>51.73</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>43.68</v>
+        <v>32.27</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>35.42</v>
+        <v>24.93</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23145.05</v>
+        <v>22982.4</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.74</v>
+        <v>1.09</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.74</v>
+        <v>2.36</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>397</v>
+        <v>147</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>348</v>
+        <v>600</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1.14</v>
+        <v>0.24</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>2.21</v>
+        <v>0.54</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>57.12</v>
+        <v>54.62</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>63.07</v>
+        <v>58.27</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>56.59</v>
+        <v>43.73</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>53.26</v>
+        <v>35.47</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>23352.15</v>
+        <v>23145.05</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>438</v>
+        <v>396</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>56.6</v>
+        <v>57.19</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>63.6</v>
+        <v>63.07</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>55.66</v>
+        <v>56.67</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>50.47</v>
+        <v>53.33</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23338.05</v>
+        <v>23352.15</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>28</v>
-      </c>
       <c r="D5" s="1" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>271</v>
+        <v>437</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>475</v>
+        <v>311</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.72</v>
+        <v>1.48</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>55.5</v>
+        <v>56.68</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>62.53</v>
+        <v>63.6</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>50.87</v>
+        <v>55.73</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>23336.3</v>
+        <v>50.53</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>23338.05</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>3.18</v>
+        <v>1.61</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>56.01</v>
+        <v>55.57</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>56.06</v>
+        <v>50.93</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>50.2</v>
+        <v>44.13</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>23232.65</v>
+        <v>23336.3</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>4.9</v>
+        <v>3.52</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>299</v>
+        <v>446</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.51</v>
+        <v>0.67</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>2.25</v>
+        <v>0.95</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>57.83</v>
+        <v>56.09</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>64.13</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>59.12</v>
+        <v>56.13</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>54.19</v>
+        <v>50.27</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1.74</v>
+        <v>5.57</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>580</v>
+        <v>298</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.29</v>
+        <v>1.52</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.38</v>
+        <v>2.26</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>56.63</v>
+        <v>57.9</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>61.33</v>
+        <v>64.13</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>53.79</v>
+        <v>59.2</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>47.27</v>
+        <v>54.27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>368</v>
+        <v>579</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>56.97</v>
+        <v>56.7</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>65.2</v>
+        <v>61.33</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>65.11</v>
+        <v>53.87</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>64.45</v>
+        <v>47.33</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>144</v>
+        <v>367</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>11.15</v>
+        <v>0.79</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>55.59</v>
+        <v>57.04</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>64.45</v>
+        <v>65.2</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="P10" s="8" t="n">
-        <v>23348.4</v>
+        <v>64.53</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>4.91</v>
+        <v>4.23</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>7.66</v>
+        <v>11.15</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>52.67</v>
+        <v>55.67</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>56.09</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>51.4</v>
+        <v>64.53</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>45.41</v>
+        <v>64.27</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>86</v>
+        <v>624</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>665</v>
+        <v>126</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.13</v>
+        <v>4.95</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>49.74</v>
+        <v>52.75</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>49.92</v>
+        <v>56.16</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>37.82</v>
+        <v>51.47</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>26.1</v>
+        <v>45.47</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>2.27</v>
+        <v>0.96</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>506</v>
+        <v>664</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>56.28</v>
+        <v>49.83</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>60.75</v>
+        <v>50</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>58.06</v>
+        <v>37.87</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>51.66</v>
+        <v>26.13</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>23368.85</v>
+        <v>22908.05</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>387</v>
+        <v>505</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>57.07</v>
+        <v>56.36</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>63.61</v>
+        <v>60.81</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>65.65000000000001</v>
+        <v>58.13</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>63.52</v>
+        <v>51.73</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>23433.95</v>
+        <v>23368.85</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2.45</v>
+        <v>3.57</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>56.9</v>
+        <v>57.14</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>63.66</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>66.84</v>
+        <v>65.73</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>66.05</v>
+        <v>63.6</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>23301.15</v>
+        <v>23433.95</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>537</v>
+        <v>353</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>56.55</v>
+        <v>56.97</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>64.51000000000001</v>
+        <v>65.02</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>69.73</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>23264.8</v>
+        <v>66.13</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>416</v>
+        <v>537</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>52.93</v>
+        <v>56.63</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>60.15</v>
+        <v>64.56</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>61.47</v>
+        <v>69.73</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>51.9</v>
+        <v>53.01</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>58.05</v>
+        <v>60.21</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>57.87</v>
+        <v>61.47</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>50.13</v>
+        <v>57.07</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>22995.65</v>
+        <v>23111.65</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>277</v>
+        <v>445</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>472</v>
+        <v>304</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>50.34</v>
+        <v>51.98</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>55.79</v>
+        <v>58.11</v>
       </c>
       <c r="N19" s="1" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O19" s="1" t="n">
         <v>50.13</v>
       </c>
-      <c r="O19" s="1" t="n">
-        <v>41.33</v>
-      </c>
       <c r="P19" s="16" t="n">
-        <v>23000</v>
+        <v>22995.65</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>4.73</v>
+        <v>2.71</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>52.59</v>
+        <v>50.43</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>59.85</v>
+        <v>55.86</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>60.27</v>
+        <v>50.13</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P20" s="17" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>6.88</v>
+        <v>4.73</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>52.41</v>
+        <v>52.67</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>60</v>
+        <v>59.91</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>60.27</v>
@@ -2091,1150 +2104,1150 @@
       <c r="O21" s="1" t="n">
         <v>50.8</v>
       </c>
-      <c r="P21" s="14" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q21" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="P21" s="18" t="inlineStr"/>
+      <c r="Q21" s="1" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>6.56</v>
+        <v>6.88</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>389</v>
+        <v>249</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>52.93</v>
+        <v>52.5</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>62.41</v>
+        <v>60.06</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.27</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P22" s="18" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P22" s="15" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>4.94</v>
+        <v>6.56</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>569</v>
+        <v>361</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>53.28</v>
+        <v>53.01</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>61.8</v>
+        <v>62.46</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>69.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>64.13</v>
+        <v>63.73</v>
       </c>
       <c r="P23" s="19" t="n">
-        <v>23010.95</v>
+        <v>23126.3</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>6.04</v>
+        <v>4.94</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>1.95</v>
+        <v>0.32</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>55.52</v>
+        <v>53.18</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>68.42</v>
+        <v>61.86</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>79.2</v>
+        <v>69.33</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P24" s="20" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>8.57</v>
+        <v>6.9</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>3.21</v>
+        <v>6.04</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>395</v>
+        <v>496</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>53.97</v>
+        <v>55.42</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>65.41</v>
+        <v>68.47</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>74</v>
+        <v>79.2</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P25" s="7" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>16.57</v>
+        <v>8.57</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>53.28</v>
+        <v>53.87</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>65.86</v>
+        <v>65.47</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>76.8</v>
+        <v>74</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="P26" s="20" t="n">
-        <v>23206.45</v>
+        <v>75.2</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>23144.2</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>10.35</v>
+        <v>16.57</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>51.9</v>
+        <v>53.18</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>63.61</v>
+        <v>65.92</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>74.67</v>
+        <v>76.8</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="P27" s="14" t="n">
-        <v>23109.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>4.7</v>
+        <v>10.35</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>50.34</v>
+        <v>51.81</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>61.8</v>
+        <v>63.66</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>73.47</v>
+        <v>74.67</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>79.33</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>22997.25</v>
+        <v>23109.7</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>5.63</v>
+        <v>4.7</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>575</v>
+        <v>436</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>3.3</v>
+        <v>1.39</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>49.74</v>
+        <v>50.26</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>59.85</v>
+        <v>61.86</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>70.27</v>
+        <v>73.47</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P29" s="21" t="n">
-        <v>22891.3</v>
+        <v>79.33</v>
+      </c>
+      <c r="P29" s="16" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>2</v>
+        <v>5.63</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>691</v>
+        <v>575</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>11.91</v>
+        <v>3.3</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>33.39</v>
+        <v>5.84</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>46.63</v>
+        <v>49.66</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>49.92</v>
+        <v>59.91</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>53.07</v>
+        <v>70.27</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>61.2</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P30" s="22" t="n">
-        <v>22599.8</v>
+        <v>22891.3</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>173</v>
+        <v>691</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>576</v>
+        <v>58</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>39.03</v>
+        <v>46.55</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>38.35</v>
+        <v>50</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>27.73</v>
+        <v>53.07</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>21.87</v>
+        <v>61.2</v>
       </c>
       <c r="P31" s="23" t="n">
-        <v>22114.45</v>
+        <v>22599.8</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>43.18</v>
+        <v>38.97</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>44.21</v>
+        <v>38.44</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>36.27</v>
+        <v>27.73</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>30.67</v>
+        <v>21.87</v>
       </c>
       <c r="P32" s="24" t="n">
-        <v>22233.85</v>
+        <v>22114.45</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>596</v>
+        <v>160</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>153</v>
+        <v>590</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>3.9</v>
+        <v>0.27</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>44.91</v>
+        <v>43.1</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>50.98</v>
+        <v>44.29</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>43.87</v>
+        <v>36.27</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>43.2</v>
+        <v>30.67</v>
       </c>
       <c r="P33" s="25" t="n">
-        <v>22370.15</v>
+        <v>22233.85</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>102</v>
+        <v>596</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>648</v>
+        <v>153</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.16</v>
+        <v>3.9</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>41.45</v>
+        <v>44.83</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>44.81</v>
+        <v>51.05</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>30.4</v>
+        <v>43.87</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>24.27</v>
+        <v>43.2</v>
       </c>
       <c r="P34" s="26" t="n">
-        <v>22173.7</v>
+        <v>22370.15</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>44.91</v>
+        <v>41.38</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>55.04</v>
+        <v>44.89</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>44.93</v>
+        <v>30.4</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>45.33</v>
+        <v>24.27</v>
       </c>
       <c r="P35" s="27" t="n">
-        <v>22465.35</v>
+        <v>22173.7</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>1.9</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>44.81</v>
+        <v>44.83</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>56.99</v>
+        <v>55.11</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>45.6</v>
+        <v>44.93</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>43.33</v>
+        <v>45.33</v>
       </c>
       <c r="P36" s="28" t="n">
-        <v>22497.7</v>
+        <v>22465.35</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>43.77</v>
+        <v>44.73</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>57.29</v>
+        <v>57.06</v>
       </c>
       <c r="N37" s="1" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>43.33</v>
       </c>
-      <c r="O37" s="1" t="n">
-        <v>37.73</v>
-      </c>
       <c r="P37" s="29" t="n">
-        <v>22451.85</v>
+        <v>22497.7</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>469</v>
+        <v>308</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>60</v>
+        <v>57.36</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>43.87</v>
+        <v>43.33</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>40</v>
+        <v>37.73</v>
       </c>
       <c r="P38" s="30" t="n">
-        <v>22521.1</v>
+        <v>22451.85</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>221</v>
+        <v>469</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>42.73</v>
+        <v>43.52</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>58.95</v>
+        <v>60.06</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>38.13</v>
+        <v>43.87</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>31.87</v>
+        <v>40</v>
       </c>
       <c r="P39" s="31" t="n">
-        <v>22437.95</v>
+        <v>22521.1</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J40" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>43.94</v>
+        <v>42.66</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>66.31999999999999</v>
+        <v>59.01</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>47.6</v>
+        <v>38.13</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>42.13</v>
+        <v>31.87</v>
       </c>
       <c r="P40" s="32" t="n">
-        <v>22657</v>
+        <v>22437.95</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>47.58</v>
+        <v>43.87</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>72.48</v>
+        <v>66.37</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>61.33</v>
+        <v>47.6</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P41" s="17" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P41" s="33" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q41" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>47.66</v>
+        <v>47.5</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>73.23</v>
+        <v>72.52</v>
       </c>
       <c r="N42" s="1" t="n">
         <v>61.33</v>
@@ -3242,94 +3255,90 @@
       <c r="O42" s="1" t="n">
         <v>60.67</v>
       </c>
-      <c r="P42" s="33" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q42" s="1" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="P42" s="18" t="inlineStr"/>
+      <c r="Q42" s="1" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>46.88</v>
+        <v>47.58</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>73.83</v>
+        <v>73.27</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>62.13</v>
+        <v>61.33</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P43" s="21" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P43" s="34" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>3.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>27</v>
@@ -3338,1415 +3347,1415 @@
         <v>1</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>8.33</v>
+        <v>1.98</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>46.18</v>
+        <v>46.79</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>74.73999999999999</v>
+        <v>73.87</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>61.2</v>
+        <v>62.13</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P44" s="34" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P44" s="22" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>372</v>
+        <v>566</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>374</v>
+        <v>183</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.99</v>
+        <v>3.09</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>2.48</v>
+        <v>8.33</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>44.1</v>
+        <v>46.1</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>68.12</v>
+        <v>74.77</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>48.8</v>
+        <v>61.2</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P45" s="32" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P45" s="35" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>1.47</v>
+        <v>0.99</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>42.01</v>
+        <v>44.02</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>68.56999999999999</v>
+        <v>68.17</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>48.13</v>
+        <v>48.8</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P46" s="22" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P46" s="33" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>367</v>
+        <v>445</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>381</v>
+        <v>302</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>41.15</v>
+        <v>41.94</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>66.77</v>
+        <v>68.62</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>42</v>
+        <v>48.13</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P47" s="35" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P47" s="23" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>493</v>
+        <v>367</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>41.32</v>
+        <v>41.07</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>67.06999999999999</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>40.93</v>
+        <v>42</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P48" s="30" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P48" s="36" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>39.76</v>
+        <v>41.25</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>64.95999999999999</v>
+        <v>67.12</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>32.53</v>
+        <v>40.93</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P49" s="36" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P49" s="31" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>44.27</v>
+        <v>39.69</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>71.13</v>
+        <v>65.02</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>42.27</v>
+        <v>32.53</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>31.87</v>
+        <v>23.33</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>22531.15</v>
+        <v>22461.05</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>44.79</v>
+        <v>44.19</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>72.33</v>
+        <v>71.17</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>46.4</v>
+        <v>42.27</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>35.47</v>
+        <v>31.87</v>
       </c>
       <c r="P51" s="38" t="n">
-        <v>22613.1</v>
+        <v>22531.15</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E52" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L52" s="1" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="M52" s="1" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="N52" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O52" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P52" s="39" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q52" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F52" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J52" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K52" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L52" s="1" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="M52" s="1" t="n">
-        <v>71.28</v>
-      </c>
-      <c r="N52" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O52" s="1" t="n">
-        <v>29.87</v>
-      </c>
-      <c r="P52" s="39" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q52" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>696</v>
+        <v>298</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>42.19</v>
+        <v>43.15</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>70.23</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>37.73</v>
+        <v>43.73</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>22.93</v>
+        <v>29.87</v>
       </c>
       <c r="P53" s="40" t="n">
-        <v>22299.9</v>
+        <v>22377.35</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>2.27</v>
+        <v>0.74</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>2.29</v>
+        <v>1.01</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>49.91</v>
+        <v>42.11</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>82.41</v>
+        <v>70.12</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.73</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>50.53</v>
+        <v>22.93</v>
       </c>
       <c r="P54" s="41" t="n">
-        <v>22795.75</v>
+        <v>22299.9</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>4.89</v>
+        <v>2.27</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>4.33</v>
+        <v>2.29</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>54.78</v>
+        <v>49.83</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>87.22</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>82.27</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>73.47</v>
+        <v>50.53</v>
       </c>
       <c r="P55" s="42" t="n">
-        <v>23115.65</v>
+        <v>22795.75</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>5.93</v>
+        <v>4.89</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>56.52</v>
+        <v>54.69</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>87.97</v>
+        <v>87.09</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>87.87</v>
+        <v>82.27</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>82.67</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="P56" s="43" t="n">
-        <v>23214</v>
+        <v>23115.65</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>52.52</v>
+        <v>56.42</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>86.92</v>
+        <v>87.84</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>86.8</v>
+        <v>87.87</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>80.93000000000001</v>
+        <v>82.67</v>
       </c>
       <c r="P57" s="44" t="n">
-        <v>23133.4</v>
+        <v>23214</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>343</v>
+        <v>605</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>405</v>
+        <v>145</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>47.65</v>
+        <v>52.43</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>79.7</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>73.87</v>
+        <v>86.8</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>62.53</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="P58" s="45" t="n">
-        <v>22808.25</v>
+        <v>23133.4</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>531</v>
+        <v>343</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>46.86</v>
+        <v>47.57</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>80.59999999999999</v>
+        <v>79.58</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>77.2</v>
+        <v>73.87</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>66.8</v>
+        <v>62.53</v>
       </c>
       <c r="P59" s="46" t="n">
-        <v>22830.75</v>
+        <v>22808.25</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>3.64</v>
+        <v>2.33</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>43.55</v>
+        <v>46.78</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>77.44</v>
+        <v>80.48</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>64.8</v>
+        <v>77.2</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="P60" s="17" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="P60" s="47" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q60" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>41.77</v>
+        <v>43.48</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>77.47</v>
+        <v>77.33</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="P61" s="47" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q61" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.73</v>
+      </c>
+      <c r="P61" s="18" t="inlineStr"/>
+      <c r="Q61" s="1" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>378</v>
+        <v>552</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>43.74</v>
+        <v>41.71</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>79.2</v>
+        <v>77.47</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>80.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>70.13</v>
+        <v>55.07</v>
       </c>
       <c r="P62" s="48" t="n">
-        <v>22871</v>
+        <v>22683.55</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>285</v>
+        <v>370</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>44.06</v>
+        <v>43.67</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>77.87</v>
+        <v>79.2</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>81.2</v>
+        <v>80.67</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>70.8</v>
+        <v>70.13</v>
       </c>
       <c r="P63" s="49" t="n">
-        <v>22765.6</v>
+        <v>22871</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>648</v>
+        <v>285</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>6.35</v>
+        <v>0.62</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>44.22</v>
+        <v>43.99</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>80.13</v>
+        <v>77.87</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P64" s="45" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P64" s="50" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>40.1</v>
+        <v>44.15</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>72</v>
+        <v>80.13</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>78</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P65" s="35" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P65" s="46" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>42.63</v>
+        <v>40.03</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>78.93000000000001</v>
+        <v>72</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>87.33</v>
+        <v>78</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P66" s="45" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P66" s="36" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>249</v>
+        <v>511</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>43.47</v>
+        <v>42.63</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>82.11</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>91.86</v>
+        <v>87.33</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="P67" s="50" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P67" s="46" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>41.08</v>
+        <v>43.47</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>81.73</v>
+        <v>82.11</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>92.67</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="P68" s="51" t="n">
-        <v>23042.35</v>
+        <v>22991.5</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J69" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>93.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>92.13</v>
+        <v>92.67</v>
       </c>
       <c r="P69" s="52" t="n">
-        <v>22865.8</v>
+        <v>23042.35</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>5</v>
+        <v>0.58</v>
       </c>
       <c r="I70" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J70" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>7.36</v>
+        <v>0.53</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="P70" s="52" t="n">
-        <v>22869.4</v>
+        <v>92.13</v>
+      </c>
+      <c r="P70" s="53" t="n">
+        <v>22865.8</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -4758,13 +4767,13 @@
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I71" s="1" t="n">
         <v>0</v>
@@ -4773,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>0.16</v>
+        <v>7.36</v>
       </c>
       <c r="L71" s="1" t="n">
         <v>16.67</v>
@@ -4782,22 +4791,22 @@
         <v>16.67</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O71" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P71" s="32" t="n">
-        <v>22656.3</v>
+      <c r="P71" s="53" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -4809,13 +4818,13 @@
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I72" s="1" t="n">
         <v>0</v>
@@ -4824,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>3.72</v>
+        <v>0.16</v>
       </c>
       <c r="L72" s="1" t="n">
         <v>16.67</v>
@@ -4833,116 +4842,167 @@
         <v>16.67</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O72" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P72" s="53" t="n">
-        <v>22595.55</v>
+      <c r="P72" s="33" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>0.49</v>
+        <v>5</v>
       </c>
       <c r="I73" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J73" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>0.75</v>
+        <v>3.72</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>31.26</v>
+        <v>16.67</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>52.93</v>
+        <v>16.67</v>
       </c>
       <c r="N73" s="1" t="n">
-        <v>84.27</v>
+        <v>83.33</v>
       </c>
       <c r="O73" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P73" s="26" t="n">
-        <v>22179.05</v>
+        <v>100</v>
+      </c>
+      <c r="P73" s="54" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D74" s="1" t="inlineStr"/>
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G74" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J74" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L74" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M74" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N74" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O74" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P74" s="27" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q74" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="1" t="inlineStr"/>
+      <c r="E75" s="1" t="inlineStr"/>
+      <c r="F75" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G74" s="1" t="n">
+      <c r="G75" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H74" s="1" t="n">
+      <c r="H75" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr"/>
-      <c r="L74" s="1" t="n">
+      <c r="I75" s="1" t="inlineStr"/>
+      <c r="J75" s="1" t="inlineStr"/>
+      <c r="K75" s="1" t="inlineStr"/>
+      <c r="L75" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="M75" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N74" s="1" t="n">
+      <c r="N75" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O74" s="1" t="n">
+      <c r="O75" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P74" s="54" t="n">
+      <c r="P75" s="55" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q74" s="1" t="n">
+      <c r="Q75" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B74">
+  <conditionalFormatting sqref="B2:B75">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4952,7 +5012,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C74">
+  <conditionalFormatting sqref="C2:C75">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4962,7 +5022,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E74">
+  <conditionalFormatting sqref="D2:E75">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -4974,7 +5034,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F74">
+  <conditionalFormatting sqref="F2:F75">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4984,7 +5044,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G74">
+  <conditionalFormatting sqref="G2:G75">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4994,7 +5054,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H74">
+  <conditionalFormatting sqref="H2:H75">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5006,7 +5066,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I74">
+  <conditionalFormatting sqref="I2:I75">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5016,7 +5076,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J74">
+  <conditionalFormatting sqref="J2:J75">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5026,7 +5086,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K74">
+  <conditionalFormatting sqref="K2:K75">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5038,7 +5098,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O74">
+  <conditionalFormatting sqref="L2:O75">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5050,7 +5110,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q74">
+  <conditionalFormatting sqref="Q2:Q75">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -35,6 +35,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEFDFD"/>
+        <bgColor rgb="00FEFDFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F9FCF9"/>
         <bgColor rgb="00F9FCF9"/>
       </patternFill>
@@ -85,12 +91,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00ECF7EF"/>
         <bgColor rgb="00ECF7EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFDFD"/>
-        <bgColor rgb="00FEFDFD"/>
       </patternFill>
     </fill>
     <fill>
@@ -902,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1014,1140 +1014,1144 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>170</v>
+        <v>369</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>577</v>
+        <v>380</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.29</v>
+        <v>0.97</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="n">
         <v>7</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>51.79</v>
+        <v>51.97</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>51.73</v>
+        <v>52.27</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>32.27</v>
+        <v>32.67</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>24.93</v>
+        <v>26.67</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>22982.4</v>
+        <v>22913.3</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>54.62</v>
+        <v>51.79</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>58.27</v>
+        <v>51.73</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>43.73</v>
+        <v>32.27</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>35.47</v>
+        <v>24.93</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>23145.05</v>
+        <v>22982.4</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>348</v>
+        <v>600</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1.14</v>
+        <v>0.24</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>2.2</v>
+        <v>0.54</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>57.19</v>
+        <v>54.62</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>63.07</v>
+        <v>58.27</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>56.67</v>
+        <v>43.73</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>53.33</v>
+        <v>35.47</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23352.15</v>
+        <v>23145.05</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>56.68</v>
+        <v>57.19</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>63.6</v>
+        <v>63.07</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>55.73</v>
+        <v>56.67</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>50.53</v>
+        <v>53.33</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>23338.05</v>
+        <v>23352.15</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>27</v>
-      </c>
       <c r="D6" s="1" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>271</v>
+        <v>437</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>474</v>
+        <v>311</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>55.57</v>
+        <v>56.68</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>62.53</v>
+        <v>63.6</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>50.93</v>
+        <v>55.73</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>23336.3</v>
+        <v>50.53</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>23338.05</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>3.52</v>
+        <v>1.61</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>56.09</v>
+        <v>55.57</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>56.13</v>
+        <v>50.93</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>50.27</v>
+        <v>44.13</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>23232.65</v>
+        <v>23336.3</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>5.57</v>
+        <v>3.52</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>298</v>
+        <v>446</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.52</v>
+        <v>0.67</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>2.26</v>
+        <v>0.95</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>57.9</v>
+        <v>56.09</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>64.13</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>59.2</v>
+        <v>56.13</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>54.27</v>
+        <v>50.27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1.83</v>
+        <v>5.57</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>579</v>
+        <v>298</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.29</v>
+        <v>1.52</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.38</v>
+        <v>2.26</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>56.7</v>
+        <v>57.9</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>61.33</v>
+        <v>64.13</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>53.87</v>
+        <v>59.2</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>47.33</v>
+        <v>54.27</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>367</v>
+        <v>579</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>57.04</v>
+        <v>56.7</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>65.2</v>
+        <v>61.33</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>65.2</v>
+        <v>53.87</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>64.53</v>
+        <v>47.33</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>4.23</v>
+        <v>1.04</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>11.15</v>
+        <v>0.79</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>55.67</v>
+        <v>57.04</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N11" s="1" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="O11" s="1" t="n">
         <v>64.53</v>
       </c>
-      <c r="O11" s="1" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P11" s="9" t="n">
-        <v>23348.4</v>
+      <c r="P11" s="10" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>4.95</v>
+        <v>4.23</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>7.66</v>
+        <v>11.15</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>52.75</v>
+        <v>55.67</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>56.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>51.47</v>
+        <v>64.53</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>45.47</v>
+        <v>64.27</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>86</v>
+        <v>624</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>664</v>
+        <v>126</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.13</v>
+        <v>4.95</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>49.83</v>
+        <v>52.75</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>50</v>
+        <v>56.16</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>37.87</v>
+        <v>51.47</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>26.13</v>
+        <v>45.47</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2.33</v>
+        <v>0.96</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>505</v>
+        <v>664</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>56.36</v>
+        <v>49.83</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>60.81</v>
+        <v>50</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>58.13</v>
+        <v>37.87</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="P14" s="12" t="n">
-        <v>23368.85</v>
+        <v>26.13</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>22908.05</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>3.57</v>
+        <v>2.33</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>386</v>
+        <v>505</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>57.14</v>
+        <v>56.36</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>63.66</v>
+        <v>60.81</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>65.73</v>
+        <v>58.13</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>23433.95</v>
+        <v>51.73</v>
+      </c>
+      <c r="P15" s="12" t="n">
+        <v>23368.85</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2.45</v>
+        <v>3.57</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>56.97</v>
+        <v>57.14</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>65.02</v>
+        <v>63.66</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>66.93000000000001</v>
+        <v>65.73</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>66.13</v>
-      </c>
-      <c r="P16" s="14" t="n">
-        <v>23301.15</v>
+        <v>63.6</v>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>23433.95</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>537</v>
+        <v>353</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>56.63</v>
+        <v>56.97</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>64.56</v>
+        <v>65.02</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>69.73</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <v>23264.8</v>
+        <v>66.13</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>416</v>
+        <v>537</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>53.01</v>
+        <v>56.63</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>60.21</v>
+        <v>64.56</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>61.47</v>
+        <v>69.73</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="P18" s="15" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>51.98</v>
+        <v>53.01</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>58.11</v>
+        <v>60.21</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>57.87</v>
+        <v>61.47</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="P19" s="16" t="n">
-        <v>22995.65</v>
+        <v>57.07</v>
+      </c>
+      <c r="P19" s="15" t="n">
+        <v>23111.65</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>277</v>
+        <v>445</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>472</v>
+        <v>304</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>50.43</v>
+        <v>51.98</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>55.86</v>
+        <v>58.11</v>
       </c>
       <c r="N20" s="1" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>50.13</v>
       </c>
-      <c r="O20" s="1" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="P20" s="17" t="n">
-        <v>23000</v>
+      <c r="P20" s="16" t="n">
+        <v>22995.65</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>4.73</v>
+        <v>2.71</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>52.67</v>
+        <v>50.43</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>59.91</v>
+        <v>55.86</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>60.27</v>
+        <v>50.13</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P21" s="18" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>6.88</v>
+        <v>4.73</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>52.5</v>
+        <v>52.67</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>60.06</v>
+        <v>59.91</v>
       </c>
       <c r="N22" s="1" t="n">
         <v>60.27</v>
@@ -2155,1150 +2159,1150 @@
       <c r="O22" s="1" t="n">
         <v>50.8</v>
       </c>
-      <c r="P22" s="15" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="P22" s="18" t="inlineStr"/>
+      <c r="Q22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>6.56</v>
+        <v>6.88</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>389</v>
+        <v>249</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>53.01</v>
+        <v>52.5</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>62.46</v>
+        <v>60.06</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.27</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P23" s="19" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P23" s="15" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>4.94</v>
+        <v>6.56</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>569</v>
+        <v>361</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>53.18</v>
+        <v>53.01</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>61.86</v>
+        <v>62.46</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>69.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="P24" s="20" t="n">
-        <v>23010.95</v>
+        <v>63.73</v>
+      </c>
+      <c r="P24" s="19" t="n">
+        <v>23126.3</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>6.04</v>
+        <v>4.94</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.95</v>
+        <v>0.32</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>55.42</v>
+        <v>53.18</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>68.47</v>
+        <v>61.86</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>79.2</v>
+        <v>69.33</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P25" s="7" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P25" s="20" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>8.57</v>
+        <v>6.9</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>3.21</v>
+        <v>6.04</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>395</v>
+        <v>496</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>53.87</v>
+        <v>55.42</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>65.47</v>
+        <v>68.47</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>74</v>
+        <v>79.2</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>16.57</v>
+        <v>8.57</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>53.18</v>
+        <v>53.87</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>65.92</v>
+        <v>65.47</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>76.8</v>
+        <v>74</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="P27" s="21" t="n">
-        <v>23206.45</v>
+        <v>75.2</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>23144.2</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>10.35</v>
+        <v>16.57</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>51.81</v>
+        <v>53.18</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>63.66</v>
+        <v>65.92</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>74.67</v>
+        <v>76.8</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="P28" s="15" t="n">
-        <v>23109.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>4.7</v>
+        <v>10.35</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>50.26</v>
+        <v>51.81</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>61.86</v>
+        <v>63.66</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>73.47</v>
+        <v>74.67</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>79.33</v>
-      </c>
-      <c r="P29" s="16" t="n">
-        <v>22997.25</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="P29" s="15" t="n">
+        <v>23109.7</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>5.63</v>
+        <v>4.7</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>575</v>
+        <v>436</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>3.3</v>
+        <v>1.39</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>49.66</v>
+        <v>50.26</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>59.91</v>
+        <v>61.86</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>70.27</v>
+        <v>73.47</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P30" s="22" t="n">
-        <v>22891.3</v>
+        <v>79.33</v>
+      </c>
+      <c r="P30" s="16" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>2</v>
+        <v>5.63</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>691</v>
+        <v>575</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>11.91</v>
+        <v>3.3</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>33.39</v>
+        <v>5.84</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>46.55</v>
+        <v>49.66</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>50</v>
+        <v>59.91</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>53.07</v>
+        <v>70.27</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="P31" s="23" t="n">
-        <v>22599.8</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="P31" s="22" t="n">
+        <v>22891.3</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>173</v>
+        <v>691</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>576</v>
+        <v>58</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>38.97</v>
+        <v>46.55</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>38.44</v>
+        <v>50</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>27.73</v>
+        <v>53.07</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>21.87</v>
-      </c>
-      <c r="P32" s="24" t="n">
-        <v>22114.45</v>
+        <v>61.2</v>
+      </c>
+      <c r="P32" s="23" t="n">
+        <v>22599.8</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>43.1</v>
+        <v>38.97</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>44.29</v>
+        <v>38.44</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>36.27</v>
+        <v>27.73</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>30.67</v>
-      </c>
-      <c r="P33" s="25" t="n">
-        <v>22233.85</v>
+        <v>21.87</v>
+      </c>
+      <c r="P33" s="24" t="n">
+        <v>22114.45</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>596</v>
+        <v>160</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>153</v>
+        <v>590</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>3.9</v>
+        <v>0.27</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>44.83</v>
+        <v>43.1</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>51.05</v>
+        <v>44.29</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>43.87</v>
+        <v>36.27</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="P34" s="26" t="n">
-        <v>22370.15</v>
+        <v>30.67</v>
+      </c>
+      <c r="P34" s="25" t="n">
+        <v>22233.85</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>102</v>
+        <v>596</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>648</v>
+        <v>153</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.16</v>
+        <v>3.9</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>41.38</v>
+        <v>44.83</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>44.89</v>
+        <v>51.05</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>30.4</v>
+        <v>43.87</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>24.27</v>
-      </c>
-      <c r="P35" s="27" t="n">
-        <v>22173.7</v>
+        <v>43.2</v>
+      </c>
+      <c r="P35" s="26" t="n">
+        <v>22370.15</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>44.83</v>
+        <v>41.38</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>55.11</v>
+        <v>44.89</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>44.93</v>
+        <v>30.4</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="P36" s="28" t="n">
-        <v>22465.35</v>
+        <v>24.27</v>
+      </c>
+      <c r="P36" s="27" t="n">
+        <v>22173.7</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>1.9</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>44.73</v>
+        <v>44.83</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>57.06</v>
+        <v>55.11</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>45.6</v>
+        <v>44.93</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="P37" s="29" t="n">
-        <v>22497.7</v>
+        <v>45.33</v>
+      </c>
+      <c r="P37" s="28" t="n">
+        <v>22465.35</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>43.7</v>
+        <v>44.73</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>57.36</v>
+        <v>57.06</v>
       </c>
       <c r="N38" s="1" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>43.33</v>
       </c>
-      <c r="O38" s="1" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="P38" s="30" t="n">
-        <v>22451.85</v>
+      <c r="P38" s="29" t="n">
+        <v>22497.7</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>469</v>
+        <v>308</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>43.52</v>
+        <v>43.7</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>60.06</v>
+        <v>57.36</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>43.87</v>
+        <v>43.33</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="P39" s="31" t="n">
-        <v>22521.1</v>
+        <v>37.73</v>
+      </c>
+      <c r="P39" s="30" t="n">
+        <v>22451.85</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>221</v>
+        <v>469</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>42.66</v>
+        <v>43.52</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>59.01</v>
+        <v>60.06</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>38.13</v>
+        <v>43.87</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="P40" s="32" t="n">
-        <v>22437.95</v>
+        <v>40</v>
+      </c>
+      <c r="P40" s="31" t="n">
+        <v>22521.1</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J41" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>43.87</v>
+        <v>42.66</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>66.37</v>
+        <v>59.01</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>47.6</v>
+        <v>38.13</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>42.13</v>
-      </c>
-      <c r="P41" s="33" t="n">
-        <v>22657</v>
+        <v>31.87</v>
+      </c>
+      <c r="P41" s="32" t="n">
+        <v>22437.95</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>47.5</v>
+        <v>43.87</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>72.52</v>
+        <v>66.37</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>61.33</v>
+        <v>47.6</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P42" s="18" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P42" s="33" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q42" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>47.58</v>
+        <v>47.5</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>73.27</v>
+        <v>72.52</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>61.33</v>
@@ -3306,94 +3310,90 @@
       <c r="O43" s="1" t="n">
         <v>60.67</v>
       </c>
-      <c r="P43" s="34" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q43" s="1" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="P43" s="18" t="inlineStr"/>
+      <c r="Q43" s="1" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>46.79</v>
+        <v>47.58</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>73.87</v>
+        <v>73.27</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>62.13</v>
+        <v>61.33</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P44" s="22" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P44" s="34" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>3.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I45" s="1" t="n">
         <v>27</v>
@@ -3402,1411 +3402,1411 @@
         <v>1</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>8.33</v>
+        <v>1.98</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46.1</v>
+        <v>46.79</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>74.77</v>
+        <v>73.87</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>61.2</v>
+        <v>62.13</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P45" s="35" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P45" s="22" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>372</v>
+        <v>566</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>374</v>
+        <v>183</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.99</v>
+        <v>3.09</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>2.48</v>
+        <v>8.32</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>44.02</v>
+        <v>46.1</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>68.17</v>
+        <v>74.77</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>48.8</v>
+        <v>61.2</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P46" s="33" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P46" s="35" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>1.47</v>
+        <v>0.99</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J47" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>41.94</v>
+        <v>44.02</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>68.62</v>
+        <v>68.17</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>48.13</v>
+        <v>48.8</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P47" s="23" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P47" s="33" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>367</v>
+        <v>445</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>381</v>
+        <v>302</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>41.07</v>
+        <v>41.94</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>66.81999999999999</v>
+        <v>68.62</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>42</v>
+        <v>48.13</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P48" s="36" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P48" s="23" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>493</v>
+        <v>367</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>41.25</v>
+        <v>41.07</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>67.12</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>40.93</v>
+        <v>42</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P49" s="31" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P49" s="36" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>39.69</v>
+        <v>41.25</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>65.02</v>
+        <v>67.12</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>32.53</v>
+        <v>40.93</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P50" s="37" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P50" s="31" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>44.19</v>
+        <v>39.69</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>71.17</v>
+        <v>65.02</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>42.27</v>
+        <v>32.53</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="P51" s="38" t="n">
-        <v>22531.15</v>
+        <v>23.33</v>
+      </c>
+      <c r="P51" s="37" t="n">
+        <v>22461.05</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>44.71</v>
+        <v>44.19</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>72.37</v>
+        <v>71.17</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>46.4</v>
+        <v>42.27</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>35.47</v>
-      </c>
-      <c r="P52" s="39" t="n">
-        <v>22613.1</v>
+        <v>31.87</v>
+      </c>
+      <c r="P52" s="38" t="n">
+        <v>22531.15</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E53" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L53" s="1" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="M53" s="1" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="N53" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P53" s="39" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q53" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F53" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K53" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L53" s="1" t="n">
-        <v>43.15</v>
-      </c>
-      <c r="M53" s="1" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="N53" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O53" s="1" t="n">
-        <v>29.87</v>
-      </c>
-      <c r="P53" s="40" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q53" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>696</v>
+        <v>298</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>42.11</v>
+        <v>43.15</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>70.12</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>37.73</v>
+        <v>43.73</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="P54" s="41" t="n">
-        <v>22299.9</v>
+        <v>29.87</v>
+      </c>
+      <c r="P54" s="40" t="n">
+        <v>22377.35</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>2.27</v>
+        <v>0.74</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>2.29</v>
+        <v>1.01</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>49.83</v>
+        <v>42.11</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>82.43000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.73</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>50.53</v>
-      </c>
-      <c r="P55" s="42" t="n">
-        <v>22795.75</v>
+        <v>22.93</v>
+      </c>
+      <c r="P55" s="41" t="n">
+        <v>22299.9</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>4.89</v>
+        <v>2.27</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>4.33</v>
+        <v>2.29</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>54.69</v>
+        <v>49.83</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>87.09</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>82.27</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="P56" s="43" t="n">
-        <v>23115.65</v>
+        <v>50.53</v>
+      </c>
+      <c r="P56" s="42" t="n">
+        <v>22795.75</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>5.93</v>
+        <v>4.89</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>56.42</v>
+        <v>54.69</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>87.84</v>
+        <v>87.09</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>87.87</v>
+        <v>82.27</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="P57" s="44" t="n">
-        <v>23214</v>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="P57" s="43" t="n">
+        <v>23115.65</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>52.43</v>
+        <v>56.42</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>86.79000000000001</v>
+        <v>87.84</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>86.8</v>
+        <v>87.87</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P58" s="45" t="n">
-        <v>23133.4</v>
+        <v>82.67</v>
+      </c>
+      <c r="P58" s="44" t="n">
+        <v>23214</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>343</v>
+        <v>605</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>405</v>
+        <v>145</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>47.57</v>
+        <v>52.43</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>79.58</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>73.87</v>
+        <v>86.8</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P59" s="46" t="n">
-        <v>22808.25</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P59" s="45" t="n">
+        <v>23133.4</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>531</v>
+        <v>343</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>46.78</v>
+        <v>47.57</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>80.48</v>
+        <v>79.58</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>77.2</v>
+        <v>73.87</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="P60" s="47" t="n">
-        <v>22830.75</v>
+        <v>62.53</v>
+      </c>
+      <c r="P60" s="46" t="n">
+        <v>22808.25</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>3.64</v>
+        <v>2.33</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>43.48</v>
+        <v>46.78</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>77.33</v>
+        <v>80.48</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>64.8</v>
+        <v>77.2</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="P61" s="18" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="P61" s="47" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q61" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2.08</v>
+        <v>3.64</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>41.71</v>
+        <v>43.48</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>77.47</v>
+        <v>77.33</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="P62" s="48" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q62" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.73</v>
+      </c>
+      <c r="P62" s="18" t="inlineStr"/>
+      <c r="Q62" s="1" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>378</v>
+        <v>552</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>43.67</v>
+        <v>41.71</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>79.2</v>
+        <v>77.47</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>80.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>70.13</v>
-      </c>
-      <c r="P63" s="49" t="n">
-        <v>22871</v>
+        <v>55.07</v>
+      </c>
+      <c r="P63" s="48" t="n">
+        <v>22683.55</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>285</v>
+        <v>370</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>43.99</v>
+        <v>43.67</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>77.87</v>
+        <v>79.2</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>81.2</v>
+        <v>80.67</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="P64" s="50" t="n">
-        <v>22765.6</v>
+        <v>70.13</v>
+      </c>
+      <c r="P64" s="49" t="n">
+        <v>22871</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>648</v>
+        <v>285</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>6.35</v>
+        <v>0.62</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>44.15</v>
+        <v>43.99</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>80.13</v>
+        <v>77.87</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P65" s="46" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P65" s="50" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>40.03</v>
+        <v>44.15</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>72</v>
+        <v>80.13</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>78</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P66" s="36" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P66" s="46" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>42.63</v>
+        <v>40.03</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>78.93000000000001</v>
+        <v>72</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>87.33</v>
+        <v>78</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P67" s="46" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P67" s="36" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>249</v>
+        <v>511</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J68" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>43.47</v>
+        <v>42.63</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>82.11</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>91.86</v>
+        <v>87.33</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="P68" s="51" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P68" s="46" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>41.08</v>
+        <v>43.47</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>81.73</v>
+        <v>82.11</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>92.67</v>
-      </c>
-      <c r="P69" s="52" t="n">
-        <v>23042.35</v>
+        <v>89.98999999999999</v>
+      </c>
+      <c r="P69" s="51" t="n">
+        <v>22991.5</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I70" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J70" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>93.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>92.13</v>
-      </c>
-      <c r="P70" s="53" t="n">
-        <v>22865.8</v>
+        <v>92.67</v>
+      </c>
+      <c r="P70" s="52" t="n">
+        <v>23042.35</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>5</v>
+        <v>0.58</v>
       </c>
       <c r="I71" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J71" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>7.36</v>
+        <v>0.53</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>100</v>
+        <v>92.13</v>
       </c>
       <c r="P71" s="53" t="n">
-        <v>22869.4</v>
+        <v>22865.8</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -4818,13 +4818,13 @@
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I72" s="1" t="n">
         <v>0</v>
@@ -4833,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>0.16</v>
+        <v>7.36</v>
       </c>
       <c r="L72" s="1" t="n">
         <v>16.67</v>
@@ -4842,22 +4842,22 @@
         <v>16.67</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O72" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P72" s="33" t="n">
-        <v>22656.3</v>
+      <c r="P72" s="53" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -4869,13 +4869,13 @@
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I73" s="1" t="n">
         <v>0</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>3.72</v>
+        <v>0.16</v>
       </c>
       <c r="L73" s="1" t="n">
         <v>16.67</v>
@@ -4893,116 +4893,167 @@
         <v>16.67</v>
       </c>
       <c r="N73" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O73" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P73" s="54" t="n">
-        <v>22595.55</v>
+      <c r="P73" s="33" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D74" s="1" t="inlineStr"/>
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>0.49</v>
+        <v>5</v>
       </c>
       <c r="I74" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J74" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>0.75</v>
+        <v>3.72</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>31.26</v>
+        <v>16.67</v>
       </c>
       <c r="M74" s="1" t="n">
-        <v>52.93</v>
+        <v>16.67</v>
       </c>
       <c r="N74" s="1" t="n">
-        <v>84.27</v>
+        <v>83.33</v>
       </c>
       <c r="O74" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P74" s="27" t="n">
-        <v>22179.05</v>
+        <v>100</v>
+      </c>
+      <c r="P74" s="54" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D75" s="1" t="inlineStr"/>
       <c r="E75" s="1" t="inlineStr"/>
       <c r="F75" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L75" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M75" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N75" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O75" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P75" s="27" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q75" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="1" t="inlineStr"/>
+      <c r="E76" s="1" t="inlineStr"/>
+      <c r="F76" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G75" s="1" t="n">
+      <c r="G76" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H75" s="1" t="n">
+      <c r="H76" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr"/>
-      <c r="L75" s="1" t="n">
+      <c r="I76" s="1" t="inlineStr"/>
+      <c r="J76" s="1" t="inlineStr"/>
+      <c r="K76" s="1" t="inlineStr"/>
+      <c r="L76" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="M76" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N75" s="1" t="n">
+      <c r="N76" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O75" s="1" t="n">
+      <c r="O76" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P75" s="55" t="n">
+      <c r="P76" s="55" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q75" s="1" t="n">
+      <c r="Q76" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B75">
+  <conditionalFormatting sqref="B2:B76">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5012,7 +5063,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C75">
+  <conditionalFormatting sqref="C2:C76">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5022,7 +5073,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E75">
+  <conditionalFormatting sqref="D2:E76">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5034,7 +5085,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F75">
+  <conditionalFormatting sqref="F2:F76">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5044,7 +5095,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G75">
+  <conditionalFormatting sqref="G2:G76">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5054,7 +5105,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H75">
+  <conditionalFormatting sqref="H2:H76">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5066,7 +5117,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I75">
+  <conditionalFormatting sqref="I2:I76">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5076,7 +5127,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J75">
+  <conditionalFormatting sqref="J2:J76">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5086,7 +5137,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K75">
+  <conditionalFormatting sqref="K2:K76">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5098,7 +5149,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O75">
+  <conditionalFormatting sqref="L2:O76">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5110,7 +5161,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q75">
+  <conditionalFormatting sqref="Q2:Q76">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -26,12 +26,78 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="56">
+  <fills count="57">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F3E7"/>
+        <bgColor rgb="00E2F3E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FCF9"/>
+        <bgColor rgb="00F9FCF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F3E8"/>
+        <bgColor rgb="00E4F3E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D1"/>
+        <bgColor rgb="00C9E8D1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBE9D3"/>
+        <bgColor rgb="00CBE9D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EFDE"/>
+        <bgColor rgb="00D8EFDE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDB"/>
+        <bgColor rgb="00D4EDDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E2"/>
+        <bgColor rgb="00DCF0E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D2"/>
+        <bgColor rgb="00C9E8D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF7EF"/>
+        <bgColor rgb="00ECF7EF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -41,60 +107,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F9FCF9"/>
-        <bgColor rgb="00F9FCF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4F3E8"/>
-        <bgColor rgb="00E4F3E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9E8D1"/>
-        <bgColor rgb="00C9E8D1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CBE9D3"/>
-        <bgColor rgb="00CBE9D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8EFDE"/>
-        <bgColor rgb="00D8EFDE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDB"/>
-        <bgColor rgb="00D4EDDB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCF0E2"/>
-        <bgColor rgb="00DCF0E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9E8D2"/>
-        <bgColor rgb="00C9E8D2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECF7EF"/>
-        <bgColor rgb="00ECF7EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C7E7CF"/>
         <bgColor rgb="00C7E7CF"/>
       </patternFill>
@@ -127,12 +139,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F6FBF8"/>
         <bgColor rgb="00F6FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -370,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -535,6 +541,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="55" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -902,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1014,1195 +1023,1195 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>369</v>
+        <v>574</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>380</v>
+        <v>174</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.97</v>
+        <v>3.3</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>51.97</v>
+        <v>53.33</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>52.27</v>
+        <v>58.13</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>32.67</v>
+        <v>49.07</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>26.67</v>
+        <v>46.4</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>22913.3</v>
+        <v>23153.1</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>-0.3</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>170</v>
+        <v>369</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>577</v>
+        <v>380</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.29</v>
+        <v>0.97</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>51.79</v>
+        <v>51.97</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>51.73</v>
+        <v>52.27</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>32.27</v>
+        <v>32.67</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>24.93</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>22982.4</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>-0.7</v>
-      </c>
+        <v>26.67</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>54.62</v>
+        <v>51.79</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>58.27</v>
+        <v>51.73</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>43.73</v>
+        <v>32.27</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>35.47</v>
+        <v>24.93</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23145.05</v>
+        <v>22982.4</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>348</v>
+        <v>600</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1.14</v>
+        <v>0.24</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>2.2</v>
+        <v>0.54</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>57.19</v>
+        <v>54.62</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>63.07</v>
+        <v>58.27</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>56.67</v>
+        <v>43.73</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>53.33</v>
+        <v>35.47</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>23352.15</v>
+        <v>23145.05</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>56.68</v>
+        <v>57.19</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>63.6</v>
+        <v>63.07</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>55.73</v>
+        <v>56.67</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>50.53</v>
+        <v>53.33</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>23338.05</v>
+        <v>23352.15</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>27</v>
-      </c>
       <c r="D7" s="1" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>271</v>
+        <v>437</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>474</v>
+        <v>311</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>55.57</v>
+        <v>56.68</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>62.53</v>
+        <v>63.6</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>50.93</v>
+        <v>55.73</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>23336.3</v>
+        <v>50.53</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>23338.05</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>3.52</v>
+        <v>1.61</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>56.09</v>
+        <v>55.57</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>56.13</v>
+        <v>50.93</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>50.27</v>
+        <v>44.13</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>23232.65</v>
+        <v>23336.3</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>5.57</v>
+        <v>3.52</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>298</v>
+        <v>446</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>1.52</v>
+        <v>0.67</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>2.26</v>
+        <v>0.95</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>57.9</v>
+        <v>56.09</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>64.13</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>59.2</v>
+        <v>56.13</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>54.27</v>
+        <v>50.27</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1.83</v>
+        <v>5.57</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>579</v>
+        <v>298</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.29</v>
+        <v>1.52</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.38</v>
+        <v>2.26</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>56.7</v>
+        <v>57.9</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>61.33</v>
+        <v>64.13</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>53.87</v>
+        <v>59.2</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>47.33</v>
+        <v>54.27</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>367</v>
+        <v>579</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>57.04</v>
+        <v>56.7</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>65.2</v>
+        <v>61.33</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>65.2</v>
+        <v>53.87</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>64.53</v>
+        <v>47.33</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>4.23</v>
+        <v>1.04</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>11.15</v>
+        <v>0.79</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>55.67</v>
+        <v>57.04</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N12" s="1" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>64.53</v>
       </c>
-      <c r="O12" s="1" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P12" s="10" t="n">
-        <v>23348.4</v>
+      <c r="P12" s="11" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>4.95</v>
+        <v>4.23</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>7.66</v>
+        <v>11.15</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>52.75</v>
+        <v>55.67</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>56.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>51.47</v>
+        <v>64.53</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>45.47</v>
+        <v>64.27</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>86</v>
+        <v>624</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>664</v>
+        <v>126</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.13</v>
+        <v>4.95</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>49.83</v>
+        <v>52.75</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>50</v>
+        <v>56.16</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>37.87</v>
+        <v>51.47</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>26.13</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>22908.05</v>
+        <v>45.47</v>
+      </c>
+      <c r="P14" s="12" t="n">
+        <v>23081.15</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2.33</v>
+        <v>0.96</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>505</v>
+        <v>664</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>56.36</v>
+        <v>49.83</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>60.81</v>
+        <v>50</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>58.13</v>
+        <v>37.87</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <v>23368.85</v>
+        <v>26.13</v>
+      </c>
+      <c r="P15" s="13" t="n">
+        <v>22908.05</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>3.57</v>
+        <v>2.33</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>386</v>
+        <v>505</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>57.14</v>
+        <v>56.36</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>63.66</v>
+        <v>60.81</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>65.73</v>
+        <v>58.13</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P16" s="13" t="n">
-        <v>23433.95</v>
+        <v>51.73</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>23368.85</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.45</v>
+        <v>3.57</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>56.97</v>
+        <v>57.14</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>65.02</v>
+        <v>63.66</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>66.93000000000001</v>
+        <v>65.73</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>66.13</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <v>23301.15</v>
+        <v>63.6</v>
+      </c>
+      <c r="P17" s="15" t="n">
+        <v>23433.95</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>537</v>
+        <v>353</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>56.63</v>
+        <v>56.97</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>64.56</v>
+        <v>65.02</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>69.73</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>23264.8</v>
+        <v>66.13</v>
+      </c>
+      <c r="P18" s="16" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>416</v>
+        <v>537</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>53.01</v>
+        <v>56.63</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>60.21</v>
+        <v>64.56</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>61.47</v>
+        <v>69.73</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="P19" s="15" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>51.98</v>
+        <v>53.01</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>58.11</v>
+        <v>60.21</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>57.87</v>
+        <v>61.47</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="P20" s="16" t="n">
-        <v>22995.65</v>
+        <v>57.07</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>23111.65</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>277</v>
+        <v>445</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>472</v>
+        <v>304</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>50.43</v>
+        <v>51.98</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>55.86</v>
+        <v>58.11</v>
       </c>
       <c r="N21" s="1" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>50.13</v>
       </c>
-      <c r="O21" s="1" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="P21" s="17" t="n">
-        <v>23000</v>
+      <c r="P21" s="18" t="n">
+        <v>22995.65</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>4.73</v>
+        <v>2.71</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>52.67</v>
+        <v>50.43</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>59.91</v>
+        <v>55.86</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>60.27</v>
+        <v>50.13</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P22" s="18" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P22" s="19" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>6.88</v>
+        <v>4.73</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>52.5</v>
+        <v>52.67</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>60.06</v>
+        <v>59.91</v>
       </c>
       <c r="N23" s="1" t="n">
         <v>60.27</v>
@@ -2210,1150 +2219,1150 @@
       <c r="O23" s="1" t="n">
         <v>50.8</v>
       </c>
-      <c r="P23" s="15" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="1" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>6.56</v>
+        <v>6.88</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>389</v>
+        <v>249</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>53.01</v>
+        <v>52.5</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>62.46</v>
+        <v>60.06</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.27</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P24" s="19" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>4.94</v>
+        <v>6.56</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>569</v>
+        <v>361</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>53.18</v>
+        <v>53.01</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>61.86</v>
+        <v>62.46</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>69.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>64.13</v>
+        <v>63.73</v>
       </c>
       <c r="P25" s="20" t="n">
-        <v>23010.95</v>
+        <v>23126.3</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>6.04</v>
+        <v>4.94</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1.95</v>
+        <v>0.32</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>55.42</v>
+        <v>53.18</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>68.47</v>
+        <v>61.86</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>79.2</v>
+        <v>69.33</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P26" s="21" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>8.57</v>
+        <v>6.9</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>3.21</v>
+        <v>6.04</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>395</v>
+        <v>496</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>53.87</v>
+        <v>55.42</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>65.47</v>
+        <v>68.47</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>74</v>
+        <v>79.2</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>16.57</v>
+        <v>8.57</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>53.18</v>
+        <v>53.87</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>65.92</v>
+        <v>65.47</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>76.8</v>
+        <v>74</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="P28" s="21" t="n">
-        <v>23206.45</v>
+        <v>75.2</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>23144.2</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>10.35</v>
+        <v>16.57</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>51.81</v>
+        <v>53.18</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>63.66</v>
+        <v>65.92</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>74.67</v>
+        <v>76.8</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="P29" s="15" t="n">
-        <v>23109.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="P29" s="22" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>4.7</v>
+        <v>10.35</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>50.26</v>
+        <v>51.81</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>61.86</v>
+        <v>63.66</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>73.47</v>
+        <v>74.67</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>79.33</v>
-      </c>
-      <c r="P30" s="16" t="n">
-        <v>22997.25</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>23109.7</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>5.63</v>
+        <v>4.7</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>575</v>
+        <v>436</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>3.3</v>
+        <v>1.39</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>49.66</v>
+        <v>50.26</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>59.91</v>
+        <v>61.86</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>70.27</v>
+        <v>73.47</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P31" s="22" t="n">
-        <v>22891.3</v>
+        <v>79.33</v>
+      </c>
+      <c r="P31" s="18" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>2</v>
+        <v>5.63</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>691</v>
+        <v>575</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>11.91</v>
+        <v>3.3</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>33.39</v>
+        <v>5.84</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>46.55</v>
+        <v>49.66</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>50</v>
+        <v>59.91</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>53.07</v>
+        <v>70.27</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>61.2</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P32" s="23" t="n">
-        <v>22599.8</v>
+        <v>22891.3</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>173</v>
+        <v>691</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>576</v>
+        <v>58</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>38.97</v>
+        <v>46.55</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>38.44</v>
+        <v>50</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>27.73</v>
+        <v>53.07</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>21.87</v>
+        <v>61.2</v>
       </c>
       <c r="P33" s="24" t="n">
-        <v>22114.45</v>
+        <v>22599.8</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>43.1</v>
+        <v>38.97</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>44.29</v>
+        <v>38.44</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>36.27</v>
+        <v>27.73</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>30.67</v>
+        <v>21.87</v>
       </c>
       <c r="P34" s="25" t="n">
-        <v>22233.85</v>
+        <v>22114.45</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>596</v>
+        <v>160</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>153</v>
+        <v>590</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>3.9</v>
+        <v>0.27</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>44.83</v>
+        <v>43.1</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>51.05</v>
+        <v>44.29</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>43.87</v>
+        <v>36.27</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>43.2</v>
+        <v>30.67</v>
       </c>
       <c r="P35" s="26" t="n">
-        <v>22370.15</v>
+        <v>22233.85</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>102</v>
+        <v>596</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>648</v>
+        <v>153</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.16</v>
+        <v>3.9</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>41.38</v>
+        <v>44.83</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>44.89</v>
+        <v>51.05</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>30.4</v>
+        <v>43.87</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>24.27</v>
+        <v>43.2</v>
       </c>
       <c r="P36" s="27" t="n">
-        <v>22173.7</v>
+        <v>22370.15</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>44.83</v>
+        <v>41.38</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>55.11</v>
+        <v>44.89</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>44.93</v>
+        <v>30.4</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>45.33</v>
+        <v>24.27</v>
       </c>
       <c r="P37" s="28" t="n">
-        <v>22465.35</v>
+        <v>22173.7</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>1.9</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>44.73</v>
+        <v>44.83</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>57.06</v>
+        <v>55.11</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>45.6</v>
+        <v>44.93</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>43.33</v>
+        <v>45.33</v>
       </c>
       <c r="P38" s="29" t="n">
-        <v>22497.7</v>
+        <v>22465.35</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>43.7</v>
+        <v>44.73</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>57.36</v>
+        <v>57.06</v>
       </c>
       <c r="N39" s="1" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="O39" s="1" t="n">
         <v>43.33</v>
       </c>
-      <c r="O39" s="1" t="n">
-        <v>37.73</v>
-      </c>
       <c r="P39" s="30" t="n">
-        <v>22451.85</v>
+        <v>22497.7</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>469</v>
+        <v>308</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>43.52</v>
+        <v>43.7</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>60.06</v>
+        <v>57.36</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>43.87</v>
+        <v>43.33</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>40</v>
+        <v>37.73</v>
       </c>
       <c r="P40" s="31" t="n">
-        <v>22521.1</v>
+        <v>22451.85</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>221</v>
+        <v>469</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>42.66</v>
+        <v>43.52</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>59.01</v>
+        <v>60.06</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>38.13</v>
+        <v>43.87</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>31.87</v>
+        <v>40</v>
       </c>
       <c r="P41" s="32" t="n">
-        <v>22437.95</v>
+        <v>22521.1</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J42" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>43.87</v>
+        <v>42.66</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>66.37</v>
+        <v>59.01</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>47.6</v>
+        <v>38.13</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>42.13</v>
+        <v>31.87</v>
       </c>
       <c r="P42" s="33" t="n">
-        <v>22657</v>
+        <v>22437.95</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>47.5</v>
+        <v>43.87</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>72.52</v>
+        <v>66.37</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>61.33</v>
+        <v>47.6</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P43" s="18" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P43" s="34" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q43" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>47.58</v>
+        <v>47.5</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>73.27</v>
+        <v>72.52</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>61.33</v>
@@ -3361,94 +3370,90 @@
       <c r="O44" s="1" t="n">
         <v>60.67</v>
       </c>
-      <c r="P44" s="34" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q44" s="1" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="1" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>46.79</v>
+        <v>47.58</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>73.87</v>
+        <v>73.27</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>62.13</v>
+        <v>61.33</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P45" s="22" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P45" s="35" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>3.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I46" s="1" t="n">
         <v>27</v>
@@ -3457,1407 +3462,1407 @@
         <v>1</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>8.32</v>
+        <v>1.98</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>46.1</v>
+        <v>46.79</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>74.77</v>
+        <v>73.87</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>61.2</v>
+        <v>62.13</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P46" s="35" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P46" s="23" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>372</v>
+        <v>566</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>374</v>
+        <v>183</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.99</v>
+        <v>3.09</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>2.48</v>
+        <v>8.32</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>44.02</v>
+        <v>46.1</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>68.17</v>
+        <v>74.77</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>48.8</v>
+        <v>61.2</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P47" s="33" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P47" s="36" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>1.47</v>
+        <v>0.99</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J48" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>41.94</v>
+        <v>44.02</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>68.62</v>
+        <v>68.17</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>48.13</v>
+        <v>48.8</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P48" s="23" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P48" s="34" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>367</v>
+        <v>445</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>381</v>
+        <v>302</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>41.07</v>
+        <v>41.94</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>66.81999999999999</v>
+        <v>68.62</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>42</v>
+        <v>48.13</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P49" s="36" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P49" s="24" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>493</v>
+        <v>367</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>41.25</v>
+        <v>41.07</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>67.12</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>40.93</v>
+        <v>42</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P50" s="31" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P50" s="37" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>39.69</v>
+        <v>41.25</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>65.02</v>
+        <v>67.12</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>32.53</v>
+        <v>40.93</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P51" s="37" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P51" s="32" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>44.19</v>
+        <v>39.69</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>71.17</v>
+        <v>65.02</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>42.27</v>
+        <v>32.53</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>31.87</v>
+        <v>23.33</v>
       </c>
       <c r="P52" s="38" t="n">
-        <v>22531.15</v>
+        <v>22461.05</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>44.71</v>
+        <v>44.19</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>72.37</v>
+        <v>71.17</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>46.4</v>
+        <v>42.27</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>35.47</v>
+        <v>31.87</v>
       </c>
       <c r="P53" s="39" t="n">
-        <v>22613.1</v>
+        <v>22531.15</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E54" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L54" s="1" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="M54" s="1" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="N54" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O54" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P54" s="40" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q54" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F54" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>43.15</v>
-      </c>
-      <c r="M54" s="1" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="N54" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O54" s="1" t="n">
-        <v>29.87</v>
-      </c>
-      <c r="P54" s="40" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q54" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>696</v>
+        <v>298</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>42.11</v>
+        <v>43.15</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>70.12</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>37.73</v>
+        <v>43.73</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>22.93</v>
+        <v>29.87</v>
       </c>
       <c r="P55" s="41" t="n">
-        <v>22299.9</v>
+        <v>22377.35</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>2.27</v>
+        <v>0.74</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>2.29</v>
+        <v>1.01</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>49.83</v>
+        <v>42.11</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>82.43000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.73</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>50.53</v>
+        <v>22.93</v>
       </c>
       <c r="P56" s="42" t="n">
-        <v>22795.75</v>
+        <v>22299.9</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>4.89</v>
+        <v>2.27</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>4.33</v>
+        <v>2.29</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>54.69</v>
+        <v>49.83</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>87.09</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>82.27</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>73.59999999999999</v>
+        <v>50.53</v>
       </c>
       <c r="P57" s="43" t="n">
-        <v>23115.65</v>
+        <v>22795.75</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>5.93</v>
+        <v>4.89</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J58" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>56.42</v>
+        <v>54.69</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>87.84</v>
+        <v>87.09</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>87.87</v>
+        <v>82.27</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>82.67</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="P58" s="44" t="n">
-        <v>23214</v>
+        <v>23115.65</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>52.43</v>
+        <v>56.42</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>86.79000000000001</v>
+        <v>87.84</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>86.8</v>
+        <v>87.87</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>81.06999999999999</v>
+        <v>82.67</v>
       </c>
       <c r="P59" s="45" t="n">
-        <v>23133.4</v>
+        <v>23214</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>343</v>
+        <v>605</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>405</v>
+        <v>145</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>47.57</v>
+        <v>52.43</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>79.58</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>73.87</v>
+        <v>86.8</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>62.53</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="P60" s="46" t="n">
-        <v>22808.25</v>
+        <v>23133.4</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>531</v>
+        <v>343</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J61" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>46.78</v>
+        <v>47.57</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>80.48</v>
+        <v>79.58</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>77.2</v>
+        <v>73.87</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>66.8</v>
+        <v>62.53</v>
       </c>
       <c r="P61" s="47" t="n">
-        <v>22830.75</v>
+        <v>22808.25</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>3.64</v>
+        <v>2.33</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>43.48</v>
+        <v>46.78</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>77.33</v>
+        <v>80.48</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>64.8</v>
+        <v>77.2</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="P62" s="18" t="inlineStr"/>
-      <c r="Q62" s="1" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="P62" s="48" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q62" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>41.71</v>
+        <v>43.48</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>77.47</v>
+        <v>77.33</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="P63" s="48" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q63" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.73</v>
+      </c>
+      <c r="P63" s="3" t="inlineStr"/>
+      <c r="Q63" s="1" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>378</v>
+        <v>552</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>43.67</v>
+        <v>41.71</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>79.2</v>
+        <v>77.47</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>80.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>70.13</v>
+        <v>55.07</v>
       </c>
       <c r="P64" s="49" t="n">
-        <v>22871</v>
+        <v>22683.55</v>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>285</v>
+        <v>370</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>43.99</v>
+        <v>43.67</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>77.87</v>
+        <v>79.2</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>81.2</v>
+        <v>80.67</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>70.8</v>
+        <v>70.13</v>
       </c>
       <c r="P65" s="50" t="n">
-        <v>22765.6</v>
+        <v>22871</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>648</v>
+        <v>285</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>6.35</v>
+        <v>0.62</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>44.15</v>
+        <v>43.99</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>80.13</v>
+        <v>77.87</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P66" s="46" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P66" s="51" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>40.03</v>
+        <v>44.15</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>72</v>
+        <v>80.13</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>78</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P67" s="36" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P67" s="47" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>42.63</v>
+        <v>40.03</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>78.93000000000001</v>
+        <v>72</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>87.33</v>
+        <v>78</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P68" s="46" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P68" s="37" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>249</v>
+        <v>511</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J69" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>43.47</v>
+        <v>42.63</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>82.11</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>91.86</v>
+        <v>87.33</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="P69" s="51" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P69" s="47" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="I70" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J70" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>41.08</v>
+        <v>43.47</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>81.73</v>
+        <v>82.11</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>92.67</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="P70" s="52" t="n">
-        <v>23042.35</v>
+        <v>22991.5</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I71" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J71" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>93.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>92.13</v>
+        <v>92.67</v>
       </c>
       <c r="P71" s="53" t="n">
-        <v>22865.8</v>
+        <v>23042.35</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>5</v>
+        <v>0.58</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J72" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>7.36</v>
+        <v>0.53</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="P72" s="53" t="n">
-        <v>22869.4</v>
+        <v>92.13</v>
+      </c>
+      <c r="P72" s="54" t="n">
+        <v>22865.8</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -4869,13 +4874,13 @@
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I73" s="1" t="n">
         <v>0</v>
@@ -4884,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>0.16</v>
+        <v>7.36</v>
       </c>
       <c r="L73" s="1" t="n">
         <v>16.67</v>
@@ -4893,22 +4898,22 @@
         <v>16.67</v>
       </c>
       <c r="N73" s="1" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O73" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P73" s="33" t="n">
-        <v>22656.3</v>
+      <c r="P73" s="54" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -4920,13 +4925,13 @@
       <c r="D74" s="1" t="inlineStr"/>
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I74" s="1" t="n">
         <v>0</v>
@@ -4935,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>3.72</v>
+        <v>0.16</v>
       </c>
       <c r="L74" s="1" t="n">
         <v>16.67</v>
@@ -4944,116 +4949,167 @@
         <v>16.67</v>
       </c>
       <c r="N74" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O74" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P74" s="54" t="n">
-        <v>22595.55</v>
+      <c r="P74" s="34" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D75" s="1" t="inlineStr"/>
       <c r="E75" s="1" t="inlineStr"/>
       <c r="F75" s="1" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>0.49</v>
+        <v>5</v>
       </c>
       <c r="I75" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J75" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>0.75</v>
+        <v>3.72</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>31.26</v>
+        <v>16.67</v>
       </c>
       <c r="M75" s="1" t="n">
-        <v>52.93</v>
+        <v>16.67</v>
       </c>
       <c r="N75" s="1" t="n">
-        <v>84.27</v>
+        <v>83.33</v>
       </c>
       <c r="O75" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P75" s="27" t="n">
-        <v>22179.05</v>
+        <v>100</v>
+      </c>
+      <c r="P75" s="55" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D76" s="1" t="inlineStr"/>
       <c r="E76" s="1" t="inlineStr"/>
       <c r="F76" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G76" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J76" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L76" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M76" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N76" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O76" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P76" s="28" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q76" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" s="1" t="inlineStr"/>
+      <c r="E77" s="1" t="inlineStr"/>
+      <c r="F77" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G76" s="1" t="n">
+      <c r="G77" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H76" s="1" t="n">
+      <c r="H77" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr"/>
-      <c r="L76" s="1" t="n">
+      <c r="I77" s="1" t="inlineStr"/>
+      <c r="J77" s="1" t="inlineStr"/>
+      <c r="K77" s="1" t="inlineStr"/>
+      <c r="L77" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="M77" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N76" s="1" t="n">
+      <c r="N77" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O76" s="1" t="n">
+      <c r="O77" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P76" s="55" t="n">
+      <c r="P77" s="56" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q76" s="1" t="n">
+      <c r="Q77" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B76">
+  <conditionalFormatting sqref="B2:B77">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5063,7 +5119,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C76">
+  <conditionalFormatting sqref="C2:C77">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5073,7 +5129,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E76">
+  <conditionalFormatting sqref="D2:E77">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5085,7 +5141,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F76">
+  <conditionalFormatting sqref="F2:F77">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5095,7 +5151,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G76">
+  <conditionalFormatting sqref="G2:G77">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5105,7 +5161,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H76">
+  <conditionalFormatting sqref="H2:H77">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5117,7 +5173,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I76">
+  <conditionalFormatting sqref="I2:I77">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5127,7 +5183,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J76">
+  <conditionalFormatting sqref="J2:J77">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5137,7 +5193,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K76">
+  <conditionalFormatting sqref="K2:K77">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5149,7 +5205,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O76">
+  <conditionalFormatting sqref="L2:O77">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5161,7 +5217,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q76">
+  <conditionalFormatting sqref="Q2:Q77">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -35,114 +35,120 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E7F5EB"/>
+        <bgColor rgb="00E7F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2F3E7"/>
         <bgColor rgb="00E2F3E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEFDFD"/>
+        <bgColor rgb="00FEFDFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FCF9"/>
+        <bgColor rgb="00F9FCF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F3E8"/>
+        <bgColor rgb="00E4F3E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D1"/>
+        <bgColor rgb="00C9E8D1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBE9D3"/>
+        <bgColor rgb="00CBE9D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EFDE"/>
+        <bgColor rgb="00D8EFDE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDB"/>
+        <bgColor rgb="00D4EDDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E2"/>
+        <bgColor rgb="00DCF0E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D2"/>
+        <bgColor rgb="00C9E8D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF7EF"/>
+        <bgColor rgb="00ECF7EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C7E7CF"/>
+        <bgColor rgb="00C7E7CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BEE4C8"/>
+        <bgColor rgb="00BEE4C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFEBD7"/>
+        <bgColor rgb="00CFEBD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5EB"/>
+        <bgColor rgb="00E8F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FBF8"/>
+        <bgColor rgb="00F7FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6FBF8"/>
+        <bgColor rgb="00F6FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F9FCF9"/>
-        <bgColor rgb="00F9FCF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4F3E8"/>
-        <bgColor rgb="00E4F3E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9E8D1"/>
-        <bgColor rgb="00C9E8D1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CBE9D3"/>
-        <bgColor rgb="00CBE9D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8EFDE"/>
-        <bgColor rgb="00D8EFDE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDB"/>
-        <bgColor rgb="00D4EDDB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCF0E2"/>
-        <bgColor rgb="00DCF0E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9E8D2"/>
-        <bgColor rgb="00C9E8D2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECF7EF"/>
-        <bgColor rgb="00ECF7EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFDFD"/>
-        <bgColor rgb="00FEFDFD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C7E7CF"/>
-        <bgColor rgb="00C7E7CF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BEE4C8"/>
-        <bgColor rgb="00BEE4C8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CFEBD7"/>
-        <bgColor rgb="00CFEBD7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5EB"/>
-        <bgColor rgb="00E8F5EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7FBF8"/>
-        <bgColor rgb="00F7FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6FBF8"/>
-        <bgColor rgb="00F6FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E6F4EA"/>
         <bgColor rgb="00E6F4EA"/>
       </patternFill>
@@ -283,12 +289,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FEF6F6"/>
         <bgColor rgb="00FEF6F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7F5EB"/>
-        <bgColor rgb="00E7F5EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1023,1246 +1023,1254 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>574</v>
+        <v>242</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>174</v>
+        <v>507</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>3.3</v>
+        <v>0.48</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>2.48</v>
+        <v>0.48</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>53.33</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>58.13</v>
+        <v>54.27</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>49.07</v>
+        <v>41.87</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>46.4</v>
+        <v>39.73</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23153.1</v>
+        <v>23114.9</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>0.74</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>369</v>
+        <v>574</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>380</v>
+        <v>174</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.97</v>
+        <v>3.3</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>51.97</v>
+        <v>53.33</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>52.27</v>
+        <v>58.13</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>32.67</v>
+        <v>49.07</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="1" t="inlineStr"/>
+        <v>46.4</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>23153.1</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>1.05</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>170</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>577</v>
+        <v>380</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.29</v>
+        <v>0.97</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>7</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>51.79</v>
+        <v>51.97</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>51.73</v>
+        <v>52.27</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>32.27</v>
+        <v>32.67</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>24.93</v>
+        <v>26.67</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>22982.4</v>
+        <v>22913.3</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>54.62</v>
+        <v>51.79</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>58.27</v>
+        <v>51.73</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>43.73</v>
+        <v>32.27</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>35.47</v>
+        <v>24.93</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>23145.05</v>
+        <v>22982.4</v>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>348</v>
+        <v>600</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1.14</v>
+        <v>0.24</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>2.2</v>
+        <v>0.54</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>57.19</v>
+        <v>54.62</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>63.07</v>
+        <v>58.27</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>56.67</v>
+        <v>43.73</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>53.33</v>
+        <v>35.47</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>23352.15</v>
+        <v>23145.05</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>56.68</v>
+        <v>57.19</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>63.6</v>
+        <v>63.07</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>55.73</v>
+        <v>56.67</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>50.53</v>
+        <v>53.33</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>23338.05</v>
+        <v>23352.15</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>27</v>
-      </c>
       <c r="D8" s="1" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>271</v>
+        <v>437</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>474</v>
+        <v>311</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>55.57</v>
+        <v>56.68</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>62.53</v>
+        <v>63.6</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>50.93</v>
+        <v>55.73</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>23336.3</v>
+        <v>50.53</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>23338.05</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>3.52</v>
+        <v>1.61</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>56.09</v>
+        <v>55.57</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>56.13</v>
+        <v>50.93</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>50.27</v>
+        <v>44.13</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>23232.65</v>
+        <v>23336.3</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>5.57</v>
+        <v>3.52</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>298</v>
+        <v>446</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>1.52</v>
+        <v>0.67</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>2.26</v>
+        <v>0.95</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>57.9</v>
+        <v>56.09</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>64.13</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>59.2</v>
+        <v>56.13</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>54.27</v>
+        <v>50.27</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>1.83</v>
+        <v>5.57</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>579</v>
+        <v>298</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.29</v>
+        <v>1.52</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.38</v>
+        <v>2.26</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>56.7</v>
+        <v>57.9</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>61.33</v>
+        <v>64.13</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>53.87</v>
+        <v>59.2</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>47.33</v>
+        <v>54.27</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>367</v>
+        <v>579</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>57.04</v>
+        <v>56.7</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>65.2</v>
+        <v>61.33</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>65.2</v>
+        <v>53.87</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>64.53</v>
+        <v>47.33</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>4.23</v>
+        <v>1.04</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>11.15</v>
+        <v>0.79</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>55.67</v>
+        <v>57.04</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N13" s="1" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>64.53</v>
       </c>
-      <c r="O13" s="1" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P13" s="11" t="n">
-        <v>23348.4</v>
+      <c r="P13" s="12" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>4.95</v>
+        <v>4.23</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>7.66</v>
+        <v>11.15</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>52.75</v>
+        <v>55.67</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>56.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>51.47</v>
+        <v>64.53</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>45.47</v>
+        <v>64.27</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>86</v>
+        <v>624</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>664</v>
+        <v>126</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.13</v>
+        <v>4.95</v>
       </c>
       <c r="I15" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>49.83</v>
+        <v>52.75</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>50</v>
+        <v>56.16</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>37.87</v>
+        <v>51.47</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>26.13</v>
+        <v>45.47</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2.33</v>
+        <v>0.96</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>505</v>
+        <v>664</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>56.36</v>
+        <v>49.83</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>60.81</v>
+        <v>50</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>58.13</v>
+        <v>37.87</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="P16" s="14" t="n">
-        <v>23368.85</v>
+        <v>26.13</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>22908.05</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>3.57</v>
+        <v>2.33</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>386</v>
+        <v>505</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>57.14</v>
+        <v>56.36</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>63.66</v>
+        <v>60.81</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>65.73</v>
+        <v>58.13</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P17" s="15" t="n">
-        <v>23433.95</v>
+        <v>51.73</v>
+      </c>
+      <c r="P17" s="14" t="n">
+        <v>23368.85</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2.45</v>
+        <v>3.57</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I18" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>56.97</v>
+        <v>57.14</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>65.02</v>
+        <v>63.66</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>66.93000000000001</v>
+        <v>65.73</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>66.13</v>
-      </c>
-      <c r="P18" s="16" t="n">
-        <v>23301.15</v>
+        <v>63.6</v>
+      </c>
+      <c r="P18" s="15" t="n">
+        <v>23433.95</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>537</v>
+        <v>353</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>56.63</v>
+        <v>56.97</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>64.56</v>
+        <v>65.02</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>69.73</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="P19" s="9" t="n">
-        <v>23264.8</v>
+        <v>66.13</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>416</v>
+        <v>537</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>53.01</v>
+        <v>56.63</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>60.21</v>
+        <v>64.56</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>61.47</v>
+        <v>69.73</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="P20" s="17" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>51.98</v>
+        <v>53.01</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>58.11</v>
+        <v>60.21</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>57.87</v>
+        <v>61.47</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="P21" s="18" t="n">
-        <v>22995.65</v>
+        <v>57.07</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>23111.65</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>277</v>
+        <v>445</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>472</v>
+        <v>304</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>50.43</v>
+        <v>51.98</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>55.86</v>
+        <v>58.11</v>
       </c>
       <c r="N22" s="1" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>50.13</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="P22" s="19" t="n">
-        <v>23000</v>
+      <c r="P22" s="18" t="n">
+        <v>22995.65</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>4.73</v>
+        <v>2.71</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>52.67</v>
+        <v>50.43</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>59.91</v>
+        <v>55.86</v>
       </c>
       <c r="N23" s="1" t="n">
-        <v>60.27</v>
+        <v>50.13</v>
       </c>
       <c r="O23" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P23" s="19" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>6.88</v>
+        <v>4.73</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>52.5</v>
+        <v>52.67</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>60.06</v>
+        <v>59.91</v>
       </c>
       <c r="N24" s="1" t="n">
         <v>60.27</v>
@@ -2270,1150 +2278,1150 @@
       <c r="O24" s="1" t="n">
         <v>50.8</v>
       </c>
-      <c r="P24" s="17" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="P24" s="20" t="inlineStr"/>
+      <c r="Q24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>6.56</v>
+        <v>6.88</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>389</v>
+        <v>249</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>53.01</v>
+        <v>52.5</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>62.46</v>
+        <v>60.06</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.27</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P25" s="20" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>4.94</v>
+        <v>6.56</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>569</v>
+        <v>361</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>53.18</v>
+        <v>53.01</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>61.86</v>
+        <v>62.46</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>69.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>64.13</v>
+        <v>63.73</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>23010.95</v>
+        <v>23126.3</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>6.04</v>
+        <v>4.94</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1.95</v>
+        <v>0.32</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>55.42</v>
+        <v>53.18</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>68.47</v>
+        <v>61.86</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>79.2</v>
+        <v>69.33</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P27" s="9" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P27" s="22" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>8.57</v>
+        <v>6.9</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>3.21</v>
+        <v>6.04</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>395</v>
+        <v>496</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>53.87</v>
+        <v>55.42</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>65.47</v>
+        <v>68.47</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>74</v>
+        <v>79.2</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P28" s="10" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>16.57</v>
+        <v>8.57</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>53.18</v>
+        <v>53.87</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>65.92</v>
+        <v>65.47</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>76.8</v>
+        <v>74</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="P29" s="22" t="n">
-        <v>23206.45</v>
+        <v>75.2</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>23144.2</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>10.35</v>
+        <v>16.57</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>51.81</v>
+        <v>53.18</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>63.66</v>
+        <v>65.92</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>74.67</v>
+        <v>76.8</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="P30" s="17" t="n">
-        <v>23109.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="P30" s="23" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>4.7</v>
+        <v>10.35</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>50.26</v>
+        <v>51.81</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>61.86</v>
+        <v>63.66</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>73.47</v>
+        <v>74.67</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>79.33</v>
-      </c>
-      <c r="P31" s="18" t="n">
-        <v>22997.25</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="P31" s="17" t="n">
+        <v>23109.7</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>5.63</v>
+        <v>4.7</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>575</v>
+        <v>436</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>3.3</v>
+        <v>1.39</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>49.66</v>
+        <v>50.26</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>59.91</v>
+        <v>61.86</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>70.27</v>
+        <v>73.47</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P32" s="23" t="n">
-        <v>22891.3</v>
+        <v>79.33</v>
+      </c>
+      <c r="P32" s="18" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>2</v>
+        <v>5.63</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>691</v>
+        <v>575</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>11.91</v>
+        <v>3.3</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>33.39</v>
+        <v>5.84</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>46.55</v>
+        <v>49.66</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>50</v>
+        <v>59.91</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>53.07</v>
+        <v>70.27</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>61.2</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="P33" s="24" t="n">
-        <v>22599.8</v>
+        <v>22891.3</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>173</v>
+        <v>691</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>576</v>
+        <v>58</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>38.97</v>
+        <v>46.55</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>38.44</v>
+        <v>50</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>27.73</v>
+        <v>53.07</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>21.87</v>
+        <v>61.2</v>
       </c>
       <c r="P34" s="25" t="n">
-        <v>22114.45</v>
+        <v>22599.8</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>43.1</v>
+        <v>38.97</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>44.29</v>
+        <v>38.44</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>36.27</v>
+        <v>27.73</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>30.67</v>
+        <v>21.87</v>
       </c>
       <c r="P35" s="26" t="n">
-        <v>22233.85</v>
+        <v>22114.45</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>596</v>
+        <v>160</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>153</v>
+        <v>590</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>3.9</v>
+        <v>0.27</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>44.83</v>
+        <v>43.1</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>51.05</v>
+        <v>44.29</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>43.87</v>
+        <v>36.27</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>43.2</v>
+        <v>30.67</v>
       </c>
       <c r="P36" s="27" t="n">
-        <v>22370.15</v>
+        <v>22233.85</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>102</v>
+        <v>596</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>648</v>
+        <v>153</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.16</v>
+        <v>3.9</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>41.38</v>
+        <v>44.83</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>44.89</v>
+        <v>51.05</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>30.4</v>
+        <v>43.87</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>24.27</v>
+        <v>43.2</v>
       </c>
       <c r="P37" s="28" t="n">
-        <v>22173.7</v>
+        <v>22370.15</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>44.83</v>
+        <v>41.38</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>55.11</v>
+        <v>44.89</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>44.93</v>
+        <v>30.4</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>45.33</v>
+        <v>24.27</v>
       </c>
       <c r="P38" s="29" t="n">
-        <v>22465.35</v>
+        <v>22173.7</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>1.9</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>44.73</v>
+        <v>44.83</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>57.06</v>
+        <v>55.11</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>45.6</v>
+        <v>44.93</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>43.33</v>
+        <v>45.33</v>
       </c>
       <c r="P39" s="30" t="n">
-        <v>22497.7</v>
+        <v>22465.35</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>43.7</v>
+        <v>44.73</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>57.36</v>
+        <v>57.06</v>
       </c>
       <c r="N40" s="1" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="O40" s="1" t="n">
         <v>43.33</v>
       </c>
-      <c r="O40" s="1" t="n">
-        <v>37.73</v>
-      </c>
       <c r="P40" s="31" t="n">
-        <v>22451.85</v>
+        <v>22497.7</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>469</v>
+        <v>308</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>43.52</v>
+        <v>43.7</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>60.06</v>
+        <v>57.36</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>43.87</v>
+        <v>43.33</v>
       </c>
       <c r="O41" s="1" t="n">
-        <v>40</v>
+        <v>37.73</v>
       </c>
       <c r="P41" s="32" t="n">
-        <v>22521.1</v>
+        <v>22451.85</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>221</v>
+        <v>469</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>42.66</v>
+        <v>43.52</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>59.01</v>
+        <v>60.06</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>38.13</v>
+        <v>43.87</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>31.87</v>
+        <v>40</v>
       </c>
       <c r="P42" s="33" t="n">
-        <v>22437.95</v>
+        <v>22521.1</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J43" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>43.87</v>
+        <v>42.66</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>66.37</v>
+        <v>59.01</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>47.6</v>
+        <v>38.13</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>42.13</v>
+        <v>31.87</v>
       </c>
       <c r="P43" s="34" t="n">
-        <v>22657</v>
+        <v>22437.95</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>47.5</v>
+        <v>43.87</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>72.52</v>
+        <v>66.37</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>61.33</v>
+        <v>47.6</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P44" s="35" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q44" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>47.58</v>
+        <v>47.5</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>73.27</v>
+        <v>72.52</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>61.33</v>
@@ -3421,94 +3429,90 @@
       <c r="O45" s="1" t="n">
         <v>60.67</v>
       </c>
-      <c r="P45" s="35" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q45" s="1" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="P45" s="20" t="inlineStr"/>
+      <c r="Q45" s="1" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>46.79</v>
+        <v>47.58</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>73.87</v>
+        <v>73.27</v>
       </c>
       <c r="N46" s="1" t="n">
-        <v>62.13</v>
+        <v>61.33</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P46" s="23" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P46" s="36" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>3.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I47" s="1" t="n">
         <v>27</v>
@@ -3517,1403 +3521,1403 @@
         <v>1</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>8.32</v>
+        <v>1.98</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>46.1</v>
+        <v>46.79</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>74.77</v>
+        <v>73.87</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>61.2</v>
+        <v>62.13</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P47" s="36" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P47" s="24" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>372</v>
+        <v>566</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>374</v>
+        <v>183</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.99</v>
+        <v>3.09</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>2.48</v>
+        <v>8.32</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>44.02</v>
+        <v>46.1</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>68.17</v>
+        <v>74.77</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>48.8</v>
+        <v>61.2</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P48" s="34" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P48" s="37" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>1.47</v>
+        <v>0.99</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J49" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>41.94</v>
+        <v>44.02</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>68.62</v>
+        <v>68.17</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>48.13</v>
+        <v>48.8</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P49" s="24" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P49" s="35" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>367</v>
+        <v>445</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>381</v>
+        <v>302</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>41.07</v>
+        <v>41.94</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>66.81999999999999</v>
+        <v>68.62</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>42</v>
+        <v>48.13</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P50" s="37" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P50" s="25" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>493</v>
+        <v>367</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>41.25</v>
+        <v>41.07</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>67.12</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>40.93</v>
+        <v>42</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P51" s="32" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P51" s="38" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>39.69</v>
+        <v>41.25</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>65.02</v>
+        <v>67.12</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>32.53</v>
+        <v>40.93</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P52" s="38" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P52" s="33" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>44.19</v>
+        <v>39.69</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>71.17</v>
+        <v>65.02</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>42.27</v>
+        <v>32.53</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>31.87</v>
+        <v>23.33</v>
       </c>
       <c r="P53" s="39" t="n">
-        <v>22531.15</v>
+        <v>22461.05</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>44.71</v>
+        <v>44.19</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>72.37</v>
+        <v>71.17</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>46.4</v>
+        <v>42.27</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>35.47</v>
+        <v>31.87</v>
       </c>
       <c r="P54" s="40" t="n">
-        <v>22613.1</v>
+        <v>22531.15</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E55" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L55" s="1" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="M55" s="1" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="N55" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O55" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P55" s="41" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q55" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F55" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H55" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I55" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J55" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L55" s="1" t="n">
-        <v>43.15</v>
-      </c>
-      <c r="M55" s="1" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="N55" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O55" s="1" t="n">
-        <v>29.87</v>
-      </c>
-      <c r="P55" s="41" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q55" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>696</v>
+        <v>298</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>42.11</v>
+        <v>43.15</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>70.12</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="N56" s="1" t="n">
-        <v>37.73</v>
+        <v>43.73</v>
       </c>
       <c r="O56" s="1" t="n">
-        <v>22.93</v>
+        <v>29.87</v>
       </c>
       <c r="P56" s="42" t="n">
-        <v>22299.9</v>
+        <v>22377.35</v>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>2.27</v>
+        <v>0.74</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>2.29</v>
+        <v>1.01</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>49.83</v>
+        <v>42.11</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>82.43000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.73</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>50.53</v>
+        <v>22.93</v>
       </c>
       <c r="P57" s="43" t="n">
-        <v>22795.75</v>
+        <v>22299.9</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>4.89</v>
+        <v>2.27</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>54.69</v>
+        <v>49.83</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>87.09</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>82.27</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>73.59999999999999</v>
+        <v>50.53</v>
       </c>
       <c r="P58" s="44" t="n">
-        <v>23115.65</v>
+        <v>22795.75</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>5.93</v>
+        <v>4.89</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J59" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>56.42</v>
+        <v>54.69</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>87.84</v>
+        <v>87.09</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>87.87</v>
+        <v>82.27</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="P59" s="45" t="n">
-        <v>23214</v>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>23115.65</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>52.43</v>
+        <v>56.42</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>86.79000000000001</v>
+        <v>87.84</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>86.8</v>
+        <v>87.87</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P60" s="46" t="n">
-        <v>23133.4</v>
+        <v>82.67</v>
+      </c>
+      <c r="P60" s="45" t="n">
+        <v>23214</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>343</v>
+        <v>605</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>405</v>
+        <v>145</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>47.57</v>
+        <v>52.43</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>79.58</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>73.87</v>
+        <v>86.8</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P61" s="47" t="n">
-        <v>22808.25</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P61" s="46" t="n">
+        <v>23133.4</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>531</v>
+        <v>343</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>46.78</v>
+        <v>47.57</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>80.48</v>
+        <v>79.58</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>77.2</v>
+        <v>73.87</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="P62" s="48" t="n">
-        <v>22830.75</v>
+        <v>62.53</v>
+      </c>
+      <c r="P62" s="47" t="n">
+        <v>22808.25</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>43.48</v>
+        <v>46.78</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>77.33</v>
+        <v>80.48</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>64.8</v>
+        <v>77.2</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="P63" s="3" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="P63" s="48" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q63" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>41.71</v>
+        <v>43.48</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>77.47</v>
+        <v>77.33</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="P64" s="49" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q64" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.73</v>
+      </c>
+      <c r="P64" s="20" t="inlineStr"/>
+      <c r="Q64" s="1" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>378</v>
+        <v>552</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>43.67</v>
+        <v>41.71</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>79.2</v>
+        <v>77.47</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>80.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>70.13</v>
-      </c>
-      <c r="P65" s="50" t="n">
-        <v>22871</v>
+        <v>55.07</v>
+      </c>
+      <c r="P65" s="49" t="n">
+        <v>22683.55</v>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>285</v>
+        <v>370</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>43.99</v>
+        <v>43.67</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>77.87</v>
+        <v>79.2</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>81.2</v>
+        <v>80.67</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="P66" s="51" t="n">
-        <v>22765.6</v>
+        <v>70.13</v>
+      </c>
+      <c r="P66" s="50" t="n">
+        <v>22871</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>648</v>
+        <v>285</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>6.35</v>
+        <v>0.62</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>44.15</v>
+        <v>43.99</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>80.13</v>
+        <v>77.87</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P67" s="47" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P67" s="51" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>40.03</v>
+        <v>44.15</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>72</v>
+        <v>80.13</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>78</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P68" s="37" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P68" s="47" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>42.63</v>
+        <v>40.03</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>78.93000000000001</v>
+        <v>72</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>87.33</v>
+        <v>78</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P69" s="47" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P69" s="38" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>249</v>
+        <v>511</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="I70" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J70" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>43.47</v>
+        <v>42.63</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>82.11</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>91.86</v>
+        <v>87.33</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="P70" s="52" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P70" s="47" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="n">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="I71" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J71" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>41.08</v>
+        <v>43.47</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>81.73</v>
+        <v>82.11</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>92.67</v>
-      </c>
-      <c r="P71" s="53" t="n">
-        <v>23042.35</v>
+        <v>89.98999999999999</v>
+      </c>
+      <c r="P71" s="52" t="n">
+        <v>22991.5</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J72" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>93.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>92.13</v>
-      </c>
-      <c r="P72" s="54" t="n">
-        <v>22865.8</v>
+        <v>92.67</v>
+      </c>
+      <c r="P72" s="53" t="n">
+        <v>23042.35</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>5</v>
+        <v>0.58</v>
       </c>
       <c r="I73" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J73" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>7.36</v>
+        <v>0.53</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N73" s="1" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="O73" s="1" t="n">
-        <v>100</v>
+        <v>92.13</v>
       </c>
       <c r="P73" s="54" t="n">
-        <v>22869.4</v>
+        <v>22865.8</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
@@ -4925,13 +4929,13 @@
       <c r="D74" s="1" t="inlineStr"/>
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I74" s="1" t="n">
         <v>0</v>
@@ -4940,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>0.16</v>
+        <v>7.36</v>
       </c>
       <c r="L74" s="1" t="n">
         <v>16.67</v>
@@ -4949,22 +4953,22 @@
         <v>16.67</v>
       </c>
       <c r="N74" s="1" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O74" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P74" s="34" t="n">
-        <v>22656.3</v>
+      <c r="P74" s="54" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -4976,13 +4980,13 @@
       <c r="D75" s="1" t="inlineStr"/>
       <c r="E75" s="1" t="inlineStr"/>
       <c r="F75" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I75" s="1" t="n">
         <v>0</v>
@@ -4991,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>3.72</v>
+        <v>0.16</v>
       </c>
       <c r="L75" s="1" t="n">
         <v>16.67</v>
@@ -5000,116 +5004,167 @@
         <v>16.67</v>
       </c>
       <c r="N75" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O75" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P75" s="55" t="n">
-        <v>22595.55</v>
+      <c r="P75" s="35" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D76" s="1" t="inlineStr"/>
       <c r="E76" s="1" t="inlineStr"/>
       <c r="F76" s="1" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>0.49</v>
+        <v>5</v>
       </c>
       <c r="I76" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J76" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>0.75</v>
+        <v>3.72</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>31.26</v>
+        <v>16.67</v>
       </c>
       <c r="M76" s="1" t="n">
-        <v>52.93</v>
+        <v>16.67</v>
       </c>
       <c r="N76" s="1" t="n">
-        <v>84.27</v>
+        <v>83.33</v>
       </c>
       <c r="O76" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P76" s="28" t="n">
-        <v>22179.05</v>
+        <v>100</v>
+      </c>
+      <c r="P76" s="55" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D77" s="1" t="inlineStr"/>
       <c r="E77" s="1" t="inlineStr"/>
       <c r="F77" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G77" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J77" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L77" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M77" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N77" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O77" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P77" s="29" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q77" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="1" t="inlineStr"/>
+      <c r="E78" s="1" t="inlineStr"/>
+      <c r="F78" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G77" s="1" t="n">
+      <c r="G78" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H77" s="1" t="n">
+      <c r="H78" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr"/>
-      <c r="L77" s="1" t="n">
+      <c r="I78" s="1" t="inlineStr"/>
+      <c r="J78" s="1" t="inlineStr"/>
+      <c r="K78" s="1" t="inlineStr"/>
+      <c r="L78" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="M78" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N77" s="1" t="n">
+      <c r="N78" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O77" s="1" t="n">
+      <c r="O78" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P77" s="56" t="n">
+      <c r="P78" s="56" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q77" s="1" t="n">
+      <c r="Q78" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B77">
+  <conditionalFormatting sqref="B2:B78">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5119,7 +5174,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C77">
+  <conditionalFormatting sqref="C2:C78">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5129,7 +5184,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E77">
+  <conditionalFormatting sqref="D2:E78">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5141,7 +5196,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F77">
+  <conditionalFormatting sqref="F2:F78">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5151,7 +5206,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G77">
+  <conditionalFormatting sqref="G2:G78">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5161,7 +5216,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H77">
+  <conditionalFormatting sqref="H2:H78">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5173,7 +5228,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I77">
+  <conditionalFormatting sqref="I2:I78">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5183,7 +5238,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J77">
+  <conditionalFormatting sqref="J2:J78">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5193,7 +5248,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K77">
+  <conditionalFormatting sqref="K2:K78">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5205,7 +5260,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O77">
+  <conditionalFormatting sqref="L2:O78">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5217,7 +5272,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q77">
+  <conditionalFormatting sqref="Q2:Q78">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -35,260 +35,260 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D1"/>
+        <bgColor rgb="00C9E8D1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F3E7"/>
+        <bgColor rgb="00E2F3E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FCF9"/>
+        <bgColor rgb="00F9FCF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F3E8"/>
+        <bgColor rgb="00E4F3E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBE9D3"/>
+        <bgColor rgb="00CBE9D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EFDE"/>
+        <bgColor rgb="00D8EFDE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDB"/>
+        <bgColor rgb="00D4EDDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E2"/>
+        <bgColor rgb="00DCF0E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D2"/>
+        <bgColor rgb="00C9E8D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF7EF"/>
+        <bgColor rgb="00ECF7EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFDFD"/>
+        <bgColor rgb="00FEFDFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C7E7CF"/>
+        <bgColor rgb="00C7E7CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BEE4C8"/>
+        <bgColor rgb="00BEE4C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFEBD7"/>
+        <bgColor rgb="00CFEBD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5EB"/>
+        <bgColor rgb="00E8F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FBF8"/>
+        <bgColor rgb="00F7FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6FBF8"/>
+        <bgColor rgb="00F6FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5FAF6"/>
+        <bgColor rgb="00F5FAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E1"/>
+        <bgColor rgb="00DCF0E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFCFC"/>
+        <bgColor rgb="00FEFCFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEAEA"/>
+        <bgColor rgb="00FEEAEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCCBCC"/>
+        <bgColor rgb="00FCCBCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCD3D3"/>
+        <bgColor rgb="00FCD3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDBDC"/>
+        <bgColor rgb="00FDDBDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCCFD0"/>
+        <bgColor rgb="00FCCFD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE1E2"/>
+        <bgColor rgb="00FDE1E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE3E4"/>
+        <bgColor rgb="00FDE3E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE0E1"/>
+        <bgColor rgb="00FDE0E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE5E5"/>
+        <bgColor rgb="00FDE5E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDFE0"/>
+        <bgColor rgb="00FDDFE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEDED"/>
+        <bgColor rgb="00FEEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFDFB"/>
+        <bgColor rgb="00FAFDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFEFE"/>
+        <bgColor rgb="00FEFEFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE1E1"/>
+        <bgColor rgb="00FDE1E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE5E6"/>
+        <bgColor rgb="00FDE5E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEEAEB"/>
+        <bgColor rgb="00FEEAEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDDCDC"/>
+        <bgColor rgb="00FDDCDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDD7D7"/>
+        <bgColor rgb="00FDD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF6F6"/>
+        <bgColor rgb="00FEF6F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E7F5EB"/>
         <bgColor rgb="00E7F5EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F3E7"/>
-        <bgColor rgb="00E2F3E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFDFD"/>
-        <bgColor rgb="00FEFDFD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9FCF9"/>
-        <bgColor rgb="00F9FCF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4F3E8"/>
-        <bgColor rgb="00E4F3E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9E8D1"/>
-        <bgColor rgb="00C9E8D1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CBE9D3"/>
-        <bgColor rgb="00CBE9D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8EFDE"/>
-        <bgColor rgb="00D8EFDE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDB"/>
-        <bgColor rgb="00D4EDDB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCF0E2"/>
-        <bgColor rgb="00DCF0E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9E8D2"/>
-        <bgColor rgb="00C9E8D2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECF7EF"/>
-        <bgColor rgb="00ECF7EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C7E7CF"/>
-        <bgColor rgb="00C7E7CF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BEE4C8"/>
-        <bgColor rgb="00BEE4C8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CFEBD7"/>
-        <bgColor rgb="00CFEBD7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5EB"/>
-        <bgColor rgb="00E8F5EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7FBF8"/>
-        <bgColor rgb="00F7FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6FBF8"/>
-        <bgColor rgb="00F6FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5FAF6"/>
-        <bgColor rgb="00F5FAF6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCF0E1"/>
-        <bgColor rgb="00DCF0E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFCFC"/>
-        <bgColor rgb="00FEFCFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEEAEA"/>
-        <bgColor rgb="00FEEAEA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCCBCC"/>
-        <bgColor rgb="00FCCBCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCD3D3"/>
-        <bgColor rgb="00FCD3D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDDBDC"/>
-        <bgColor rgb="00FDDBDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCCFD0"/>
-        <bgColor rgb="00FCCFD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE1E2"/>
-        <bgColor rgb="00FDE1E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE3E4"/>
-        <bgColor rgb="00FDE3E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE0E1"/>
-        <bgColor rgb="00FDE0E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE5E5"/>
-        <bgColor rgb="00FDE5E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDDFE0"/>
-        <bgColor rgb="00FDDFE0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEEDED"/>
-        <bgColor rgb="00FEEDED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAFDFB"/>
-        <bgColor rgb="00FAFDFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFEFE"/>
-        <bgColor rgb="00FEFEFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE8E8"/>
-        <bgColor rgb="00FDE8E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE1E1"/>
-        <bgColor rgb="00FDE1E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE5E6"/>
-        <bgColor rgb="00FDE5E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEEAEB"/>
-        <bgColor rgb="00FEEAEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDDCDC"/>
-        <bgColor rgb="00FDDCDC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDD7D7"/>
-        <bgColor rgb="00FDD7D7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF6F6"/>
-        <bgColor rgb="00FEF6F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1023,1305 +1023,1301 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>543</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>507</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K2" s="1" t="n">
-        <v>0.48</v>
+        <v>2.61</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>53.33</v>
+        <v>57.09</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>54.27</v>
+        <v>58.8</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>41.87</v>
+        <v>52</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>39.73</v>
+        <v>55.6</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23114.9</v>
+        <v>23352.6</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>-0.16</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>574</v>
+        <v>242</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>174</v>
+        <v>507</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>3.3</v>
+        <v>0.48</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>2.48</v>
+        <v>0.48</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>53.33</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>58.13</v>
+        <v>54.27</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>49.07</v>
+        <v>41.87</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>23153.1</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>1.05</v>
-      </c>
+        <v>39.73</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>369</v>
+        <v>574</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>380</v>
+        <v>174</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.97</v>
+        <v>3.3</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>51.97</v>
+        <v>53.33</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>52.27</v>
+        <v>58.13</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>32.67</v>
+        <v>49.07</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>26.67</v>
+        <v>46.4</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>22913.3</v>
+        <v>23153.1</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>-0.3</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>170</v>
+        <v>369</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>577</v>
+        <v>380</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.29</v>
+        <v>0.97</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>7</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>51.79</v>
+        <v>51.97</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>51.73</v>
+        <v>52.27</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>32.27</v>
+        <v>32.67</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>24.93</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>22982.4</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>-0.7</v>
-      </c>
+        <v>26.67</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>54.62</v>
+        <v>51.79</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>58.27</v>
+        <v>51.73</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>43.73</v>
+        <v>32.27</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>35.47</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>23145.05</v>
+        <v>24.93</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>22982.4</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>348</v>
+        <v>600</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.14</v>
+        <v>0.24</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>2.2</v>
+        <v>0.54</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>57.19</v>
+        <v>54.62</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>63.07</v>
+        <v>58.27</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>56.67</v>
+        <v>43.73</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="P7" s="7" t="n">
-        <v>23352.15</v>
+        <v>35.47</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>23145.05</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>56.68</v>
+        <v>57.19</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>63.6</v>
+        <v>63.07</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>55.73</v>
+        <v>56.67</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>50.53</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>23338.05</v>
+        <v>53.33</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>23352.15</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>27</v>
-      </c>
       <c r="D9" s="1" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>271</v>
+        <v>437</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>474</v>
+        <v>311</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>55.57</v>
+        <v>56.68</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>62.53</v>
+        <v>63.6</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>50.93</v>
+        <v>55.73</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="P9" s="8" t="n">
-        <v>23336.3</v>
+        <v>50.53</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>23338.05</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>3.52</v>
+        <v>1.61</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>56.09</v>
+        <v>55.57</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>56.13</v>
+        <v>50.93</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>50.27</v>
-      </c>
-      <c r="P10" s="9" t="n">
-        <v>23232.65</v>
+        <v>44.13</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>23336.3</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>5.57</v>
+        <v>3.52</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>298</v>
+        <v>446</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>1.52</v>
+        <v>0.67</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>2.26</v>
+        <v>0.95</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>57.9</v>
+        <v>56.09</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>64.13</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>59.2</v>
+        <v>56.13</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="P11" s="10" t="n">
-        <v>23263.9</v>
+        <v>50.27</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>23232.65</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>1.83</v>
+        <v>5.57</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>579</v>
+        <v>298</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.29</v>
+        <v>1.52</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.38</v>
+        <v>2.26</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>56.7</v>
+        <v>57.9</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>61.33</v>
+        <v>64.13</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>53.87</v>
+        <v>59.2</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="P12" s="11" t="n">
-        <v>23199.45</v>
+        <v>54.27</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>23263.9</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>367</v>
+        <v>579</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>57.04</v>
+        <v>56.7</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>65.2</v>
+        <v>61.33</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>65.2</v>
+        <v>53.87</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>64.53</v>
-      </c>
-      <c r="P13" s="12" t="n">
-        <v>23347.05</v>
+        <v>47.33</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>23199.45</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>4.23</v>
+        <v>1.04</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>11.15</v>
+        <v>0.79</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>55.67</v>
+        <v>57.04</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N14" s="1" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>64.53</v>
       </c>
-      <c r="O14" s="1" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P14" s="12" t="n">
-        <v>23348.4</v>
+      <c r="P14" s="11" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>4.95</v>
+        <v>4.23</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>7.66</v>
+        <v>11.15</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>52.75</v>
+        <v>55.67</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>56.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N15" s="1" t="n">
-        <v>51.47</v>
+        <v>64.53</v>
       </c>
       <c r="O15" s="1" t="n">
-        <v>45.47</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>23081.15</v>
+        <v>64.27</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>23348.4</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>86</v>
+        <v>624</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>664</v>
+        <v>126</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.13</v>
+        <v>4.95</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>49.83</v>
+        <v>52.75</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>50</v>
+        <v>56.16</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>37.87</v>
+        <v>51.47</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>26.13</v>
-      </c>
-      <c r="P16" s="4" t="n">
-        <v>22908.05</v>
+        <v>45.47</v>
+      </c>
+      <c r="P16" s="12" t="n">
+        <v>23081.15</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2.33</v>
+        <v>0.96</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>505</v>
+        <v>664</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.48</v>
+        <v>0.13</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>56.36</v>
+        <v>49.83</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>60.81</v>
+        <v>50</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>58.13</v>
+        <v>37.87</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>51.73</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <v>23368.85</v>
+        <v>26.13</v>
+      </c>
+      <c r="P17" s="13" t="n">
+        <v>22908.05</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>-0.28</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>3.57</v>
+        <v>2.33</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>386</v>
+        <v>505</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>57.14</v>
+        <v>56.36</v>
       </c>
       <c r="M18" s="1" t="n">
-        <v>63.66</v>
+        <v>60.81</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>65.73</v>
+        <v>58.13</v>
       </c>
       <c r="O18" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P18" s="15" t="n">
-        <v>23433.95</v>
+        <v>51.73</v>
+      </c>
+      <c r="P18" s="14" t="n">
+        <v>23368.85</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>2.45</v>
+        <v>3.57</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>56.97</v>
+        <v>57.14</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>65.02</v>
+        <v>63.66</v>
       </c>
       <c r="N19" s="1" t="n">
-        <v>66.93000000000001</v>
+        <v>65.73</v>
       </c>
       <c r="O19" s="1" t="n">
-        <v>66.13</v>
-      </c>
-      <c r="P19" s="16" t="n">
-        <v>23301.15</v>
+        <v>63.6</v>
+      </c>
+      <c r="P19" s="15" t="n">
+        <v>23433.95</v>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>537</v>
+        <v>353</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>2.53</v>
+        <v>0.89</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>56.63</v>
+        <v>56.97</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>64.56</v>
+        <v>65.02</v>
       </c>
       <c r="N20" s="1" t="n">
-        <v>69.73</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="O20" s="1" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="P20" s="10" t="n">
-        <v>23264.8</v>
+        <v>66.13</v>
+      </c>
+      <c r="P20" s="16" t="n">
+        <v>23301.15</v>
       </c>
       <c r="Q20" s="1" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>1.77</v>
+        <v>2.87</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>416</v>
+        <v>537</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>1.25</v>
+        <v>2.53</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>3.41</v>
+        <v>2.03</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>53.01</v>
+        <v>56.63</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>60.21</v>
+        <v>64.56</v>
       </c>
       <c r="N21" s="1" t="n">
-        <v>61.47</v>
+        <v>69.73</v>
       </c>
       <c r="O21" s="1" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="P21" s="17" t="n">
-        <v>23111.65</v>
+        <v>68.67</v>
+      </c>
+      <c r="P21" s="9" t="n">
+        <v>23264.8</v>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>51.98</v>
+        <v>53.01</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>58.11</v>
+        <v>60.21</v>
       </c>
       <c r="N22" s="1" t="n">
-        <v>57.87</v>
+        <v>61.47</v>
       </c>
       <c r="O22" s="1" t="n">
-        <v>50.13</v>
-      </c>
-      <c r="P22" s="18" t="n">
-        <v>22995.65</v>
+        <v>57.07</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>23111.65</v>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>277</v>
+        <v>445</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>472</v>
+        <v>304</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.59</v>
+        <v>1.46</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>50.43</v>
+        <v>51.98</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>55.86</v>
+        <v>58.11</v>
       </c>
       <c r="N23" s="1" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="O23" s="1" t="n">
         <v>50.13</v>
       </c>
-      <c r="O23" s="1" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="P23" s="19" t="n">
-        <v>23000</v>
+      <c r="P23" s="18" t="n">
+        <v>22995.65</v>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>4.73</v>
+        <v>2.71</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>52.67</v>
+        <v>50.43</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>59.91</v>
+        <v>55.86</v>
       </c>
       <c r="N24" s="1" t="n">
-        <v>60.27</v>
+        <v>50.13</v>
       </c>
       <c r="O24" s="1" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="P24" s="20" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr"/>
+        <v>41.33</v>
+      </c>
+      <c r="P24" s="19" t="n">
+        <v>23000</v>
+      </c>
+      <c r="Q24" s="1" t="n">
+        <v>-0.49</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>6.88</v>
+        <v>4.73</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>52.5</v>
+        <v>52.67</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>60.06</v>
+        <v>59.91</v>
       </c>
       <c r="N25" s="1" t="n">
         <v>60.27</v>
@@ -2329,1150 +2325,1150 @@
       <c r="O25" s="1" t="n">
         <v>50.8</v>
       </c>
-      <c r="P25" s="17" t="n">
-        <v>23113.7</v>
-      </c>
-      <c r="Q25" s="1" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="1" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>3.69</v>
+        <v>2.68</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>6.56</v>
+        <v>6.88</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>389</v>
+        <v>249</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>361</v>
+        <v>500</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>53.01</v>
+        <v>52.5</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>62.46</v>
+        <v>60.06</v>
       </c>
       <c r="N26" s="1" t="n">
-        <v>68.40000000000001</v>
+        <v>60.27</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>63.73</v>
-      </c>
-      <c r="P26" s="21" t="n">
-        <v>23126.3</v>
+        <v>50.8</v>
+      </c>
+      <c r="P26" s="17" t="n">
+        <v>23113.7</v>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>5.4</v>
+        <v>3.69</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>4.94</v>
+        <v>6.56</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>181</v>
+        <v>389</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>569</v>
+        <v>361</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>53.18</v>
+        <v>53.01</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>61.86</v>
+        <v>62.46</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>69.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="P27" s="22" t="n">
-        <v>23010.95</v>
+        <v>63.73</v>
+      </c>
+      <c r="P27" s="20" t="n">
+        <v>23126.3</v>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>-1.08</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>6.04</v>
+        <v>4.94</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>496</v>
+        <v>181</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>1.95</v>
+        <v>0.32</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>2.09</v>
+        <v>0.27</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>55.42</v>
+        <v>53.18</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>68.47</v>
+        <v>61.86</v>
       </c>
       <c r="N28" s="1" t="n">
-        <v>79.2</v>
+        <v>69.33</v>
       </c>
       <c r="O28" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P28" s="10" t="n">
-        <v>23261.85</v>
+        <v>64.13</v>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>23010.95</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>0.51</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>8.57</v>
+        <v>6.9</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>3.21</v>
+        <v>6.04</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>395</v>
+        <v>496</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>1.05</v>
+        <v>2.09</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>53.87</v>
+        <v>55.42</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>65.47</v>
+        <v>68.47</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>74</v>
+        <v>79.2</v>
       </c>
       <c r="O29" s="1" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>23144.2</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>23261.85</v>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>-0.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>16.57</v>
+        <v>8.57</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>3.01</v>
+        <v>3.21</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>448</v>
+        <v>395</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>53.18</v>
+        <v>53.87</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>65.92</v>
+        <v>65.47</v>
       </c>
       <c r="N30" s="1" t="n">
-        <v>76.8</v>
+        <v>74</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="P30" s="23" t="n">
-        <v>23206.45</v>
+        <v>75.2</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>23144.2</v>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>10.35</v>
+        <v>16.57</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>51.81</v>
+        <v>53.18</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>63.66</v>
+        <v>65.92</v>
       </c>
       <c r="N31" s="1" t="n">
-        <v>74.67</v>
+        <v>76.8</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="P31" s="17" t="n">
-        <v>23109.7</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="P31" s="22" t="n">
+        <v>23206.45</v>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>4.7</v>
+        <v>10.35</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>1.26</v>
+        <v>4.15</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>50.26</v>
+        <v>51.81</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>61.86</v>
+        <v>63.66</v>
       </c>
       <c r="N32" s="1" t="n">
-        <v>73.47</v>
+        <v>74.67</v>
       </c>
       <c r="O32" s="1" t="n">
-        <v>79.33</v>
-      </c>
-      <c r="P32" s="18" t="n">
-        <v>22997.25</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="P32" s="17" t="n">
+        <v>23109.7</v>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>5.63</v>
+        <v>4.7</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>575</v>
+        <v>436</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>3.3</v>
+        <v>1.39</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>5.84</v>
+        <v>1.26</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>49.66</v>
+        <v>50.26</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>59.91</v>
+        <v>61.86</v>
       </c>
       <c r="N33" s="1" t="n">
-        <v>70.27</v>
+        <v>73.47</v>
       </c>
       <c r="O33" s="1" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="P33" s="24" t="n">
-        <v>22891.3</v>
+        <v>79.33</v>
+      </c>
+      <c r="P33" s="18" t="n">
+        <v>22997.25</v>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>1.29</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>2</v>
+        <v>5.63</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>1.9</v>
+        <v>2.83</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>691</v>
+        <v>575</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>11.91</v>
+        <v>3.3</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>33.39</v>
+        <v>5.84</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>46.55</v>
+        <v>49.66</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>50</v>
+        <v>59.91</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>53.07</v>
+        <v>70.27</v>
       </c>
       <c r="O34" s="1" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="P34" s="25" t="n">
-        <v>22599.8</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="P34" s="23" t="n">
+        <v>22891.3</v>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>173</v>
+        <v>691</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>576</v>
+        <v>58</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.3</v>
+        <v>11.91</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>0.74</v>
+        <v>33.39</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>38.97</v>
+        <v>46.55</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>38.44</v>
+        <v>50</v>
       </c>
       <c r="N35" s="1" t="n">
-        <v>27.73</v>
+        <v>53.07</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>21.87</v>
-      </c>
-      <c r="P35" s="26" t="n">
-        <v>22114.45</v>
+        <v>61.2</v>
+      </c>
+      <c r="P35" s="24" t="n">
+        <v>22599.8</v>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>-0.54</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.18</v>
+        <v>0.74</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>43.1</v>
+        <v>38.97</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>44.29</v>
+        <v>38.44</v>
       </c>
       <c r="N36" s="1" t="n">
-        <v>36.27</v>
+        <v>27.73</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>30.67</v>
-      </c>
-      <c r="P36" s="27" t="n">
-        <v>22233.85</v>
+        <v>21.87</v>
+      </c>
+      <c r="P36" s="25" t="n">
+        <v>22114.45</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>-0.61</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>596</v>
+        <v>160</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>153</v>
+        <v>590</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>3.9</v>
+        <v>0.27</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>1.9</v>
+        <v>0.18</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>44.83</v>
+        <v>43.1</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>51.05</v>
+        <v>44.29</v>
       </c>
       <c r="N37" s="1" t="n">
-        <v>43.87</v>
+        <v>36.27</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="P37" s="28" t="n">
-        <v>22370.15</v>
+        <v>30.67</v>
+      </c>
+      <c r="P37" s="26" t="n">
+        <v>22233.85</v>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>0.89</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>102</v>
+        <v>596</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>648</v>
+        <v>153</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.16</v>
+        <v>3.9</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.14</v>
+        <v>1.9</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>41.38</v>
+        <v>44.83</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>44.89</v>
+        <v>51.05</v>
       </c>
       <c r="N38" s="1" t="n">
-        <v>30.4</v>
+        <v>43.87</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>24.27</v>
-      </c>
-      <c r="P38" s="29" t="n">
-        <v>22173.7</v>
+        <v>43.2</v>
+      </c>
+      <c r="P38" s="27" t="n">
+        <v>22370.15</v>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>-1.3</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>390</v>
+        <v>648</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.92</v>
+        <v>0.16</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>44.83</v>
+        <v>41.38</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>55.11</v>
+        <v>44.89</v>
       </c>
       <c r="N39" s="1" t="n">
-        <v>44.93</v>
+        <v>30.4</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="P39" s="30" t="n">
-        <v>22465.35</v>
+        <v>24.27</v>
+      </c>
+      <c r="P39" s="28" t="n">
+        <v>22173.7</v>
       </c>
       <c r="Q39" s="1" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>1.9</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>44.73</v>
+        <v>44.83</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>57.06</v>
+        <v>55.11</v>
       </c>
       <c r="N40" s="1" t="n">
-        <v>45.6</v>
+        <v>44.93</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="P40" s="31" t="n">
-        <v>22497.7</v>
+        <v>45.33</v>
+      </c>
+      <c r="P40" s="29" t="n">
+        <v>22465.35</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>441</v>
+        <v>350</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>43.7</v>
+        <v>44.73</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>57.36</v>
+        <v>57.06</v>
       </c>
       <c r="N41" s="1" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="O41" s="1" t="n">
         <v>43.33</v>
       </c>
-      <c r="O41" s="1" t="n">
-        <v>37.73</v>
-      </c>
-      <c r="P41" s="32" t="n">
-        <v>22451.85</v>
+      <c r="P41" s="30" t="n">
+        <v>22497.7</v>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>469</v>
+        <v>308</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>1.68</v>
+        <v>0.7</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>43.52</v>
+        <v>43.7</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>60.06</v>
+        <v>57.36</v>
       </c>
       <c r="N42" s="1" t="n">
-        <v>43.87</v>
+        <v>43.33</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="P42" s="33" t="n">
-        <v>22521.1</v>
+        <v>37.73</v>
+      </c>
+      <c r="P42" s="31" t="n">
+        <v>22451.85</v>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>0.37</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>221</v>
+        <v>469</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.31</v>
+        <v>2.72</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>42.66</v>
+        <v>43.52</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>59.01</v>
+        <v>60.06</v>
       </c>
       <c r="N43" s="1" t="n">
-        <v>38.13</v>
+        <v>43.87</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="P43" s="34" t="n">
-        <v>22437.95</v>
+        <v>40</v>
+      </c>
+      <c r="P43" s="32" t="n">
+        <v>22521.1</v>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>-0.97</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J44" s="1" t="n">
         <v>10</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>43.87</v>
+        <v>42.66</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>66.37</v>
+        <v>59.01</v>
       </c>
       <c r="N44" s="1" t="n">
-        <v>47.6</v>
+        <v>38.13</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>42.13</v>
-      </c>
-      <c r="P44" s="35" t="n">
-        <v>22657</v>
+        <v>31.87</v>
+      </c>
+      <c r="P44" s="33" t="n">
+        <v>22437.95</v>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>-1.35</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>3.73</v>
+        <v>2.02</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>47.5</v>
+        <v>43.87</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>72.52</v>
+        <v>66.37</v>
       </c>
       <c r="N45" s="1" t="n">
-        <v>61.33</v>
+        <v>47.6</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="P45" s="20" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr"/>
+        <v>42.13</v>
+      </c>
+      <c r="P45" s="34" t="n">
+        <v>22657</v>
+      </c>
+      <c r="Q45" s="1" t="n">
+        <v>-1.35</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>3.98</v>
+        <v>3.73</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>47.58</v>
+        <v>47.5</v>
       </c>
       <c r="M46" s="1" t="n">
-        <v>73.27</v>
+        <v>72.52</v>
       </c>
       <c r="N46" s="1" t="n">
         <v>61.33</v>
@@ -3480,94 +3476,90 @@
       <c r="O46" s="1" t="n">
         <v>60.67</v>
       </c>
-      <c r="P46" s="36" t="n">
-        <v>22967.4</v>
-      </c>
-      <c r="Q46" s="1" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="1" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>1.98</v>
+        <v>4.35</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>46.79</v>
+        <v>47.58</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>73.87</v>
+        <v>73.27</v>
       </c>
       <c r="N47" s="1" t="n">
-        <v>62.13</v>
+        <v>61.33</v>
       </c>
       <c r="O47" s="1" t="n">
-        <v>63.47</v>
-      </c>
-      <c r="P47" s="24" t="n">
-        <v>22897.2</v>
+        <v>60.67</v>
+      </c>
+      <c r="P47" s="35" t="n">
+        <v>22967.4</v>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>-0.14</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>4.64</v>
+        <v>4.3</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.9</v>
+        <v>2.12</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>566</v>
+        <v>362</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>183</v>
+        <v>386</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>3.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I48" s="1" t="n">
         <v>27</v>
@@ -3576,1399 +3568,1399 @@
         <v>1</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>8.32</v>
+        <v>1.98</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>46.1</v>
+        <v>46.79</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>74.77</v>
+        <v>73.87</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>61.2</v>
+        <v>62.13</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="P48" s="37" t="n">
-        <v>22929.45</v>
+        <v>63.47</v>
+      </c>
+      <c r="P48" s="23" t="n">
+        <v>22897.2</v>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>1.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>372</v>
+        <v>566</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>374</v>
+        <v>183</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.99</v>
+        <v>3.09</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>2.48</v>
+        <v>8.32</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>44.02</v>
+        <v>46.1</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>68.17</v>
+        <v>74.77</v>
       </c>
       <c r="N49" s="1" t="n">
-        <v>48.8</v>
+        <v>61.2</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="P49" s="35" t="n">
-        <v>22651.3</v>
+        <v>63.6</v>
+      </c>
+      <c r="P49" s="36" t="n">
+        <v>22929.45</v>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>0.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>1.47</v>
+        <v>0.99</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J50" s="1" t="n">
         <v>2</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>41.94</v>
+        <v>44.02</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>68.62</v>
+        <v>68.17</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>48.13</v>
+        <v>48.8</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>45.73</v>
-      </c>
-      <c r="P50" s="25" t="n">
-        <v>22602.85</v>
+        <v>46.93</v>
+      </c>
+      <c r="P50" s="34" t="n">
+        <v>22651.3</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>367</v>
+        <v>445</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>381</v>
+        <v>302</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.96</v>
+        <v>1.47</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>41.07</v>
+        <v>41.94</v>
       </c>
       <c r="M51" s="1" t="n">
-        <v>66.81999999999999</v>
+        <v>68.62</v>
       </c>
       <c r="N51" s="1" t="n">
-        <v>42</v>
+        <v>48.13</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="P51" s="38" t="n">
-        <v>22578.15</v>
+        <v>45.73</v>
+      </c>
+      <c r="P51" s="24" t="n">
+        <v>22602.85</v>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>493</v>
+        <v>367</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K52" s="1" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>41.25</v>
+        <v>41.07</v>
       </c>
       <c r="M52" s="1" t="n">
-        <v>67.12</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="N52" s="1" t="n">
-        <v>40.93</v>
+        <v>42</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P52" s="33" t="n">
-        <v>22521.75</v>
+        <v>38.13</v>
+      </c>
+      <c r="P52" s="37" t="n">
+        <v>22578.15</v>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>164</v>
+        <v>493</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>585</v>
+        <v>256</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>0.28</v>
+        <v>1.93</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>39.69</v>
+        <v>41.25</v>
       </c>
       <c r="M53" s="1" t="n">
-        <v>65.02</v>
+        <v>67.12</v>
       </c>
       <c r="N53" s="1" t="n">
-        <v>32.53</v>
+        <v>40.93</v>
       </c>
       <c r="O53" s="1" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="P53" s="39" t="n">
-        <v>22461.05</v>
+        <v>34.4</v>
+      </c>
+      <c r="P53" s="32" t="n">
+        <v>22521.75</v>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>494</v>
+        <v>585</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>44.19</v>
+        <v>39.69</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>71.17</v>
+        <v>65.02</v>
       </c>
       <c r="N54" s="1" t="n">
-        <v>42.27</v>
+        <v>32.53</v>
       </c>
       <c r="O54" s="1" t="n">
-        <v>31.87</v>
-      </c>
-      <c r="P54" s="40" t="n">
-        <v>22531.15</v>
+        <v>23.33</v>
+      </c>
+      <c r="P54" s="38" t="n">
+        <v>22461.05</v>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>424</v>
+        <v>256</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>326</v>
+        <v>494</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>1.3</v>
+        <v>0.52</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>3.4</v>
+        <v>0.92</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>44.71</v>
+        <v>44.19</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>72.37</v>
+        <v>71.17</v>
       </c>
       <c r="N55" s="1" t="n">
-        <v>46.4</v>
+        <v>42.27</v>
       </c>
       <c r="O55" s="1" t="n">
-        <v>35.47</v>
-      </c>
-      <c r="P55" s="41" t="n">
-        <v>22613.1</v>
+        <v>31.87</v>
+      </c>
+      <c r="P55" s="39" t="n">
+        <v>22531.15</v>
       </c>
       <c r="Q55" s="1" t="n">
-        <v>1.05</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
         <v>41</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E56" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="G56" s="1" t="n">
+        <v>326</v>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L56" s="1" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="M56" s="1" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="N56" s="1" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O56" s="1" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="P56" s="40" t="n">
+        <v>22613.1</v>
+      </c>
+      <c r="Q56" s="1" t="n">
         <v>1.05</v>
-      </c>
-      <c r="F56" s="1" t="n">
-        <v>449</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>298</v>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J56" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="K56" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L56" s="1" t="n">
-        <v>43.15</v>
-      </c>
-      <c r="M56" s="1" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="N56" s="1" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="O56" s="1" t="n">
-        <v>29.87</v>
-      </c>
-      <c r="P56" s="42" t="n">
-        <v>22377.35</v>
-      </c>
-      <c r="Q56" s="1" t="n">
-        <v>0.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>696</v>
+        <v>298</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0.08</v>
+        <v>1.51</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J57" s="1" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K57" s="1" t="n">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>42.11</v>
+        <v>43.15</v>
       </c>
       <c r="M57" s="1" t="n">
-        <v>70.12</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="N57" s="1" t="n">
-        <v>37.73</v>
+        <v>43.73</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>22.93</v>
-      </c>
-      <c r="P57" s="43" t="n">
-        <v>22299.9</v>
+        <v>29.87</v>
+      </c>
+      <c r="P57" s="41" t="n">
+        <v>22377.35</v>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>-2.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>2.27</v>
+        <v>0.74</v>
       </c>
       <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>561</v>
+        <v>696</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>49.83</v>
+        <v>42.11</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>82.43000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="N58" s="1" t="n">
-        <v>67.59999999999999</v>
+        <v>37.73</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>50.53</v>
-      </c>
-      <c r="P58" s="44" t="n">
-        <v>22795.75</v>
+        <v>22.93</v>
+      </c>
+      <c r="P58" s="42" t="n">
+        <v>22299.9</v>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>-1.38</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>4.89</v>
+        <v>2.27</v>
       </c>
       <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="n">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.76</v>
+        <v>0.34</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>1.53</v>
+        <v>0.88</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>54.69</v>
+        <v>49.83</v>
       </c>
       <c r="M59" s="1" t="n">
-        <v>87.09</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="N59" s="1" t="n">
-        <v>82.27</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>23115.65</v>
+        <v>50.53</v>
+      </c>
+      <c r="P59" s="43" t="n">
+        <v>22795.75</v>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>5.93</v>
+        <v>4.89</v>
       </c>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="n">
-        <v>499</v>
+        <v>324</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>2</v>
+        <v>0.76</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J60" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>56.42</v>
+        <v>54.69</v>
       </c>
       <c r="M60" s="1" t="n">
-        <v>87.84</v>
+        <v>87.09</v>
       </c>
       <c r="N60" s="1" t="n">
-        <v>87.87</v>
+        <v>82.27</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="P60" s="45" t="n">
-        <v>23214</v>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="P60" s="44" t="n">
+        <v>23115.65</v>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>0.35</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="n">
-        <v>605</v>
+        <v>499</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>4.17</v>
+        <v>2</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>6.12</v>
+        <v>1.69</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>52.43</v>
+        <v>56.42</v>
       </c>
       <c r="M61" s="1" t="n">
-        <v>86.79000000000001</v>
+        <v>87.84</v>
       </c>
       <c r="N61" s="1" t="n">
-        <v>86.8</v>
+        <v>87.87</v>
       </c>
       <c r="O61" s="1" t="n">
-        <v>81.06999999999999</v>
-      </c>
-      <c r="P61" s="46" t="n">
-        <v>23133.4</v>
+        <v>82.67</v>
+      </c>
+      <c r="P61" s="45" t="n">
+        <v>23214</v>
       </c>
       <c r="Q61" s="1" t="n">
-        <v>1.43</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="n">
-        <v>343</v>
+        <v>605</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>405</v>
+        <v>145</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>0.85</v>
+        <v>4.17</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J62" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>1.86</v>
+        <v>6.12</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>47.57</v>
+        <v>52.43</v>
       </c>
       <c r="M62" s="1" t="n">
-        <v>79.58</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="N62" s="1" t="n">
-        <v>73.87</v>
+        <v>86.8</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="P62" s="47" t="n">
-        <v>22808.25</v>
+        <v>81.06999999999999</v>
+      </c>
+      <c r="P62" s="46" t="n">
+        <v>23133.4</v>
       </c>
       <c r="Q62" s="1" t="n">
-        <v>-0.1</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
       <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="n">
-        <v>531</v>
+        <v>343</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>218</v>
+        <v>405</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>46.78</v>
+        <v>47.57</v>
       </c>
       <c r="M63" s="1" t="n">
-        <v>80.48</v>
+        <v>79.58</v>
       </c>
       <c r="N63" s="1" t="n">
-        <v>77.2</v>
+        <v>73.87</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="P63" s="48" t="n">
-        <v>22830.75</v>
+        <v>62.53</v>
+      </c>
+      <c r="P63" s="47" t="n">
+        <v>22808.25</v>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>0.65</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>43.48</v>
+        <v>46.78</v>
       </c>
       <c r="M64" s="1" t="n">
-        <v>77.33</v>
+        <v>80.48</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>64.8</v>
+        <v>77.2</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>49.73</v>
-      </c>
-      <c r="P64" s="20" t="inlineStr"/>
-      <c r="Q64" s="1" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="P64" s="48" t="n">
+        <v>22830.75</v>
+      </c>
+      <c r="Q64" s="1" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
       <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>41.71</v>
+        <v>43.48</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>77.47</v>
+        <v>77.33</v>
       </c>
       <c r="N65" s="1" t="n">
-        <v>73.06999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="P65" s="49" t="n">
-        <v>22683.55</v>
-      </c>
-      <c r="Q65" s="1" t="n">
-        <v>-0.82</v>
-      </c>
+        <v>49.73</v>
+      </c>
+      <c r="P65" s="3" t="inlineStr"/>
+      <c r="Q65" s="1" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="n">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>378</v>
+        <v>552</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>0.98</v>
+        <v>0.36</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K66" s="1" t="n">
-        <v>2.06</v>
+        <v>0.54</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>43.67</v>
+        <v>41.71</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>79.2</v>
+        <v>77.47</v>
       </c>
       <c r="N66" s="1" t="n">
-        <v>80.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>70.13</v>
-      </c>
-      <c r="P66" s="50" t="n">
-        <v>22871</v>
+        <v>55.07</v>
+      </c>
+      <c r="P66" s="49" t="n">
+        <v>22683.55</v>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>0.46</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="n">
-        <v>285</v>
+        <v>370</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J67" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" s="1" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>43.99</v>
+        <v>43.67</v>
       </c>
       <c r="M67" s="1" t="n">
-        <v>77.87</v>
+        <v>79.2</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>81.2</v>
+        <v>80.67</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="P67" s="51" t="n">
-        <v>22765.6</v>
+        <v>70.13</v>
+      </c>
+      <c r="P67" s="50" t="n">
+        <v>22871</v>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>-0.24</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D68" s="1" t="inlineStr"/>
       <c r="E68" s="1" t="inlineStr"/>
       <c r="F68" s="1" t="n">
-        <v>648</v>
+        <v>285</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>102</v>
+        <v>463</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>6.35</v>
+        <v>0.62</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>8.17</v>
+        <v>1.94</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>44.15</v>
+        <v>43.99</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>80.13</v>
+        <v>77.87</v>
       </c>
       <c r="N68" s="1" t="n">
-        <v>86.93000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="P68" s="47" t="n">
-        <v>22821.4</v>
+        <v>70.8</v>
+      </c>
+      <c r="P68" s="51" t="n">
+        <v>22765.6</v>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>1.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="n">
-        <v>156</v>
+        <v>648</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>590</v>
+        <v>102</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>0.26</v>
+        <v>6.35</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>0.37</v>
+        <v>8.17</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>40.03</v>
+        <v>44.15</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>72</v>
+        <v>80.13</v>
       </c>
       <c r="N69" s="1" t="n">
-        <v>78</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="P69" s="38" t="n">
-        <v>22570.05</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="P69" s="47" t="n">
+        <v>22821.4</v>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>-1.06</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>0.46</v>
+        <v>0.26</v>
       </c>
       <c r="I70" s="1" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J70" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K70" s="1" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>42.63</v>
+        <v>40.03</v>
       </c>
       <c r="M70" s="1" t="n">
-        <v>78.93000000000001</v>
+        <v>72</v>
       </c>
       <c r="N70" s="1" t="n">
-        <v>87.33</v>
+        <v>78</v>
       </c>
       <c r="O70" s="1" t="n">
-        <v>82.13</v>
-      </c>
-      <c r="P70" s="47" t="n">
-        <v>22810.85</v>
+        <v>62.13</v>
+      </c>
+      <c r="P70" s="37" t="n">
+        <v>22570.05</v>
       </c>
       <c r="Q70" s="1" t="n">
-        <v>-0.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="n">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>249</v>
+        <v>511</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="I71" s="1" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J71" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>2.88</v>
+        <v>0.66</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>43.47</v>
+        <v>42.63</v>
       </c>
       <c r="M71" s="1" t="n">
-        <v>82.11</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="N71" s="1" t="n">
-        <v>91.86</v>
+        <v>87.33</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="P71" s="52" t="n">
-        <v>22991.5</v>
+        <v>82.13</v>
+      </c>
+      <c r="P71" s="47" t="n">
+        <v>22810.85</v>
       </c>
       <c r="Q71" s="1" t="n">
-        <v>-0.22</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="n">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J72" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>41.08</v>
+        <v>43.47</v>
       </c>
       <c r="M72" s="1" t="n">
-        <v>81.73</v>
+        <v>82.11</v>
       </c>
       <c r="N72" s="1" t="n">
-        <v>93.59999999999999</v>
+        <v>91.86</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>92.67</v>
-      </c>
-      <c r="P72" s="53" t="n">
-        <v>23042.35</v>
+        <v>89.98999999999999</v>
+      </c>
+      <c r="P72" s="52" t="n">
+        <v>22991.5</v>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="n">
-        <v>276</v>
+        <v>509</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="H73" s="1" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="I73" s="1" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J73" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>0.53</v>
+        <v>2.82</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>38.69</v>
+        <v>41.08</v>
       </c>
       <c r="M73" s="1" t="n">
-        <v>76.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="N73" s="1" t="n">
-        <v>93.33</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O73" s="1" t="n">
-        <v>92.13</v>
-      </c>
-      <c r="P73" s="54" t="n">
-        <v>22865.8</v>
+        <v>92.67</v>
+      </c>
+      <c r="P73" s="53" t="n">
+        <v>23042.35</v>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D74" s="1" t="inlineStr"/>
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="H74" s="1" t="n">
-        <v>5</v>
+        <v>0.58</v>
       </c>
       <c r="I74" s="1" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J74" s="1" t="n">
         <v>0</v>
       </c>
       <c r="K74" s="1" t="n">
-        <v>7.36</v>
+        <v>0.53</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>16.67</v>
+        <v>38.69</v>
       </c>
       <c r="M74" s="1" t="n">
-        <v>16.67</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="N74" s="1" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="O74" s="1" t="n">
-        <v>100</v>
+        <v>92.13</v>
       </c>
       <c r="P74" s="54" t="n">
-        <v>22869.4</v>
+        <v>22865.8</v>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
@@ -4980,13 +4972,13 @@
       <c r="D75" s="1" t="inlineStr"/>
       <c r="E75" s="1" t="inlineStr"/>
       <c r="F75" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="I75" s="1" t="n">
         <v>0</v>
@@ -4995,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="1" t="n">
-        <v>0.16</v>
+        <v>7.36</v>
       </c>
       <c r="L75" s="1" t="n">
         <v>16.67</v>
@@ -5004,22 +4996,22 @@
         <v>16.67</v>
       </c>
       <c r="N75" s="1" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O75" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P75" s="35" t="n">
-        <v>22656.3</v>
+      <c r="P75" s="54" t="n">
+        <v>22869.4</v>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
@@ -5031,13 +5023,13 @@
       <c r="D76" s="1" t="inlineStr"/>
       <c r="E76" s="1" t="inlineStr"/>
       <c r="F76" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="I76" s="1" t="n">
         <v>0</v>
@@ -5046,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="1" t="n">
-        <v>3.72</v>
+        <v>0.16</v>
       </c>
       <c r="L76" s="1" t="n">
         <v>16.67</v>
@@ -5055,116 +5047,167 @@
         <v>16.67</v>
       </c>
       <c r="N76" s="1" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="O76" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="P76" s="55" t="n">
-        <v>22595.55</v>
+      <c r="P76" s="34" t="n">
+        <v>22656.3</v>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>1.88</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D77" s="1" t="inlineStr"/>
       <c r="E77" s="1" t="inlineStr"/>
       <c r="F77" s="1" t="n">
-        <v>244</v>
+        <v>5</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>501</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>0.49</v>
+        <v>5</v>
       </c>
       <c r="I77" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J77" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K77" s="1" t="n">
-        <v>0.75</v>
+        <v>3.72</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>31.26</v>
+        <v>16.67</v>
       </c>
       <c r="M77" s="1" t="n">
-        <v>52.93</v>
+        <v>16.67</v>
       </c>
       <c r="N77" s="1" t="n">
-        <v>84.27</v>
+        <v>83.33</v>
       </c>
       <c r="O77" s="1" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P77" s="29" t="n">
-        <v>22179.05</v>
+        <v>100</v>
+      </c>
+      <c r="P77" s="55" t="n">
+        <v>22595.55</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>-0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D78" s="1" t="inlineStr"/>
       <c r="E78" s="1" t="inlineStr"/>
       <c r="F78" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="J78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L78" s="1" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="M78" s="1" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="N78" s="1" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="O78" s="1" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="P78" s="28" t="n">
+        <v>22179.05</v>
+      </c>
+      <c r="Q78" s="1" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="1" t="inlineStr"/>
+      <c r="E79" s="1" t="inlineStr"/>
+      <c r="F79" s="1" t="n">
         <v>653</v>
       </c>
-      <c r="G78" s="1" t="n">
+      <c r="G79" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="H79" s="1" t="n">
         <v>7.02</v>
       </c>
-      <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr"/>
-      <c r="L78" s="1" t="n">
+      <c r="I79" s="1" t="inlineStr"/>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
+      <c r="L79" s="1" t="n">
         <v>31.42</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="M79" s="1" t="n">
         <v>56.67</v>
       </c>
-      <c r="N78" s="1" t="n">
+      <c r="N79" s="1" t="n">
         <v>89.33</v>
       </c>
-      <c r="O78" s="1" t="n">
+      <c r="O79" s="1" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="P78" s="56" t="n">
+      <c r="P79" s="56" t="n">
         <v>22346.75</v>
       </c>
-      <c r="Q78" s="1" t="n">
+      <c r="Q79" s="1" t="n">
         <v>1.4</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B78">
+  <conditionalFormatting sqref="B2:B79">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5174,7 +5217,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C78">
+  <conditionalFormatting sqref="C2:C79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5184,7 +5227,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:E78">
+  <conditionalFormatting sqref="D2:E79">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5196,7 +5239,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F78">
+  <conditionalFormatting sqref="F2:F79">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5206,7 +5249,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G78">
+  <conditionalFormatting sqref="G2:G79">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5216,7 +5259,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H78">
+  <conditionalFormatting sqref="H2:H79">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5228,7 +5271,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I78">
+  <conditionalFormatting sqref="I2:I79">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5238,7 +5281,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J78">
+  <conditionalFormatting sqref="J2:J79">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5248,7 +5291,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K78">
+  <conditionalFormatting sqref="K2:K79">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.5"/>
@@ -5260,7 +5303,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:O78">
+  <conditionalFormatting sqref="L2:O79">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5272,7 +5315,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q78">
+  <conditionalFormatting sqref="Q2:Q79">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-2"/>

--- a/NSE_Market_Monitor.xlsx
+++ b/NSE_Market_Monitor.xlsx
@@ -41,108 +41,114 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E7F5EB"/>
+        <bgColor rgb="00E7F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F3E7"/>
+        <bgColor rgb="00E2F3E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFDFD"/>
+        <bgColor rgb="00FEFDFD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FCF9"/>
+        <bgColor rgb="00F9FCF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F3E8"/>
+        <bgColor rgb="00E4F3E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CBE9D3"/>
+        <bgColor rgb="00CBE9D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EFDE"/>
+        <bgColor rgb="00D8EFDE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDB"/>
+        <bgColor rgb="00D4EDDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCF0E2"/>
+        <bgColor rgb="00DCF0E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9E8D2"/>
+        <bgColor rgb="00C9E8D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF7EF"/>
+        <bgColor rgb="00ECF7EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C7E7CF"/>
+        <bgColor rgb="00C7E7CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BEE4C8"/>
+        <bgColor rgb="00BEE4C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFEBD7"/>
+        <bgColor rgb="00CFEBD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5EB"/>
+        <bgColor rgb="00E8F5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FBF8"/>
+        <bgColor rgb="00F7FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6FBF8"/>
+        <bgColor rgb="00F6FBF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F3E7"/>
-        <bgColor rgb="00E2F3E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9FCF9"/>
-        <bgColor rgb="00F9FCF9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4F3E8"/>
-        <bgColor rgb="00E4F3E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CBE9D3"/>
-        <bgColor rgb="00CBE9D3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8EFDE"/>
-        <bgColor rgb="00D8EFDE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDB"/>
-        <bgColor rgb="00D4EDDB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCF0E2"/>
-        <bgColor rgb="00DCF0E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C9E8D2"/>
-        <bgColor rgb="00C9E8D2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECF7EF"/>
-        <bgColor rgb="00ECF7EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEFDFD"/>
-        <bgColor rgb="00FEFDFD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C7E7CF"/>
-        <bgColor rgb="00C7E7CF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BEE4C8"/>
-        <bgColor rgb="00BEE4C8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CFEBD7"/>
-        <bgColor rgb="00CFEBD7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5EB"/>
-        <bgColor rgb="00E8F5EB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7FBF8"/>
-        <bgColor rgb="00F7FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6FBF8"/>
-        <bgColor rgb="00F6FBF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E6F4EA"/>
         <bgColor rgb="00E6F4EA"/>
       </patternFill>
@@ -283,12 +289,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FEF6F6"/>
         <bgColor rgb="00FEF6F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7F5EB"/>
-        <bgColor rgb="00E7F5EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1023,1352 +1023,1364 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>543</v>
+        <v>221</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>205</v>
+        <v>526</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>2.65</v>
+        <v>0.42</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>2.61</v>
+        <v>0.82</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>57.09</v>
+        <v>56.48</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>58.8</v>
+        <v>54.53</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>52</v>
+        <v>46.4</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>55.6</v>
+        <v>45.2</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>23352.6</v>
+        <v>23353.55</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>543</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>507</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="K3" s="1" t="n">
-        <v>0.48</v>
+        <v>2.61</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>53.33</v>
+        <v>57.09</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>54.27</v>
+        <v>58.8</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>41.87</v>
+        <v>52</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="1" t="inlineStr"/>
+        <v>55.6</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>23352.6</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>1.03</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>574</v>
+        <v>242</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>174</v>
+        <v>507</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>3.3</v>
+        <v>0.48</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>2.48</v>
+        <v>0.48</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>53.33</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>58.13</v>
+        <v>54.27</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>49.07</v>
+        <v>41.87</v>
       </c>
       <c r="O4" s="1" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>23153.1</v>
+        <v>39.73</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>23114.9</v>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>0.74</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>369</v>
+        <v>574</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>380</v>
+        <v>174</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.97</v>
+        <v>3.3</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>51.97</v>
+        <v>53.33</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>52.27</v>
+        <v>58.13</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>32.67</v>
+        <v>49.07</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="1" t="inlineStr"/>
+        <v>46.4</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>23153.1</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1.05</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>170</v>
+        <v>369</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>577</v>
+        <v>380</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.29</v>
+        <v>0.97</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>51.79</v>
+        <v>51.97</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>51.73</v>
+        <v>52.27</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>32.27</v>
+        <v>32.67</v>
       </c>
       <c r="O6" s="1" t="n">
-        <v>24.93</v>
+        <v>26.67</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>22982.4</v>
+        <v>22913.3</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>1.09</v>
+        <v>0.84</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>54.62</v>
+        <v>51.79</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>58.27</v>
+        <v>51.73</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>43.73</v>
+        <v>32.27</v>
       </c>
       <c r="O7" s="1" t="n">
-        <v>35.47</v>
+        <v>24.93</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>23145.05</v>
+        <v>22982.4</v>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1.82</v>
+        <v>1.09</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>348</v>
+        <v>600</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>1.14</v>
+        <v>0.24</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>2.2</v>
+        <v>0.54</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>57.19</v>
+        <v>54.62</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>63.07</v>
+        <v>58.27</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>56.67</v>
+        <v>43.73</v>
       </c>
       <c r="O8" s="1" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>23352.15</v>
+        <v>35.47</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>23145.05</v>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>56.68</v>
+        <v>57.19</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>63.6</v>
+        <v>63.07</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>55.73</v>
+        <v>56.67</v>
       </c>
       <c r="O9" s="1" t="n">
-        <v>50.53</v>
-      </c>
-      <c r="P9" s="7" t="n">
-        <v>23338.05</v>
+        <v>53.33</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>23352.15</v>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>27</v>
-      </c>
       <c r="D10" s="1" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>271</v>
+        <v>437</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>474</v>
+        <v>311</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>0.57</v>
+        <v>1.41</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>55.57</v>
+        <v>56.68</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>62.53</v>
+        <v>63.6</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>50.93</v>
+        <v>55.73</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="P10" s="7" t="n">
-        <v>23336.3</v>
+        <v>50.53</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>23338.05</v>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>3.52</v>
+        <v>1.61</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>56.09</v>
+        <v>55.57</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>64.40000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>56.13</v>
+        <v>50.93</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>50.27</v>
+        <v>44.13</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>23232.65</v>
+        <v>23336.3</v>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>-0.13</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>5.57</v>
+        <v>3.52</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>452</v>
+        <v>300</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>298</v>
+        <v>446</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>1.52</v>
+        <v>0.67</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>2.26</v>
+        <v>0.95</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>57.9</v>
+        <v>56.09</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>64.13</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N12" s="1" t="n">
-        <v>59.2</v>
+        <v>56.13</v>
       </c>
       <c r="O12" s="1" t="n">
-        <v>54.27</v>
+        <v>50.27</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>23263.9</v>
+        <v>23232.65</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.83</v>
+        <v>5.57</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>579</v>
+        <v>298</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.29</v>
+        <v>1.52</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>5</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.38</v>
+        <v>2.26</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>56.7</v>
+        <v>57.9</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>61.33</v>
+        <v>64.13</v>
       </c>
       <c r="N13" s="1" t="n">
-        <v>53.87</v>
+        <v>59.2</v>
       </c>
       <c r="O13" s="1" t="n">
-        <v>47.33</v>
+        <v>54.27</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>23199.45</v>
+        <v>23263.9</v>
       </c>
       <c r="Q13" s="1" t="n">
-        <v>-0.63</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>381</v>
+        <v>170</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>367</v>
+        <v>579</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>57.04</v>
+        <v>56.7</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>65.2</v>
+        <v>61.33</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>65.2</v>
+        <v>53.87</v>
       </c>
       <c r="O14" s="1" t="n">
-        <v>64.53</v>
+        <v>47.33</v>
       </c>
       <c r="P14" s="11" t="n">
-        <v>23347.05</v>
+        <v>23199.45</v>
       </c>
       <c r="Q14" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>605</v>
+        <v>381</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>4.23</v>
+        <v>1.04</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>11.15</v>
+        <v>0.79</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>55.67</v>
+        <v>57.04</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>64.93000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>64.53</v>
       </c>
-      <c r="O15" s="1" t="n">
-        <v>64.27</v>
-      </c>
-      <c r="P15" s="11" t="n">
-        <v>23348.4</v>
+      <c r="P15" s="12" t="n">
+        <v>23347.05</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>1.16</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>4.95</v>
+        <v>4.23</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>7.66</v>
+        <v>11.15</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>52.75</v>
+        <v>55.67</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>56.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N16" s="1" t="n">
-        <v>51.47</v>
+        <v>64.53</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>45.47</v>
+        <v>64.27</v>
       </c>
       <c r="P16" s="12" t="n">
-        <v>23081.15</v>
+        <v>23348.4</v>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>0.76</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>86</v>
+        <v>624</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>664</v>
+        <v>126</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.13</v>
+        <v>4.95</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.6</v>
+        <v>7.66</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>49.83</v>
+        <v>52.75</v>
       </c>
       <c r="M17" s="1" t="n">
-        <v>50</v>
+        <v>56.16</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>37.87</v>
+        <v>51.47</v>
       </c>
       <c r="O17" s="1" t="n">
-        <v>26.13</v>
+        <v>45.47</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>22908.05</v>
+        <v>23081.15</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>-1.97</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
 